--- a/data.xlsx
+++ b/data.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$1047</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$1373</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67405,6 +67405,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N1373"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$1373</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9618" uniqueCount="2182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9989" uniqueCount="2238">
   <si>
     <t>Date</t>
   </si>
@@ -6364,147 +6364,12 @@
     <t>Saif_HQ_(client)</t>
   </si>
   <si>
-    <t>1.2042 EUR</t>
-  </si>
-  <si>
-    <t>2.7647 EUR</t>
-  </si>
-  <si>
-    <t>3.9689 EUR</t>
-  </si>
-  <si>
-    <t>14.201 EUR</t>
-  </si>
-  <si>
-    <t>8.569 EUR</t>
-  </si>
-  <si>
-    <t>22.77 EUR</t>
-  </si>
-  <si>
-    <t>11.948 EUR</t>
-  </si>
-  <si>
-    <t>28.383 EUR</t>
-  </si>
-  <si>
-    <t>40.331 EUR</t>
-  </si>
-  <si>
-    <t>0.2457 EUR</t>
-  </si>
-  <si>
-    <t>2.9423 EUR</t>
-  </si>
-  <si>
-    <t>3.188 EUR</t>
-  </si>
-  <si>
-    <t>7.1123 EUR</t>
-  </si>
-  <si>
-    <t>16.8369 EUR</t>
-  </si>
-  <si>
-    <t>23.9492 EUR</t>
-  </si>
-  <si>
-    <t>0.938 EUR</t>
-  </si>
-  <si>
-    <t>8.246 EUR</t>
-  </si>
-  <si>
-    <t>9.184 EUR</t>
-  </si>
-  <si>
-    <t>0.896 EUR</t>
-  </si>
-  <si>
-    <t>0.976 EUR</t>
-  </si>
-  <si>
-    <t>1.872 EUR</t>
-  </si>
-  <si>
-    <t>0.1549 EUR</t>
-  </si>
-  <si>
-    <t>0.2093 EUR</t>
-  </si>
-  <si>
-    <t>0.3642 EUR</t>
-  </si>
-  <si>
-    <t>0.4263 EUR</t>
-  </si>
-  <si>
-    <t>0.3473 EUR</t>
-  </si>
-  <si>
-    <t>0.7736 EUR</t>
-  </si>
-  <si>
-    <t>0.1877 EUR</t>
-  </si>
-  <si>
-    <t>0.4732 EUR</t>
-  </si>
-  <si>
-    <t>0.6609 EUR</t>
-  </si>
-  <si>
-    <t>0.56 EUR</t>
-  </si>
-  <si>
-    <t>2.8 EUR</t>
-  </si>
-  <si>
-    <t>0.1622 EUR</t>
-  </si>
-  <si>
-    <t>0.663 EUR</t>
-  </si>
-  <si>
-    <t>0.8252 EUR</t>
-  </si>
-  <si>
-    <t>0.48688 EUR</t>
-  </si>
-  <si>
-    <t>0.12113 EUR</t>
-  </si>
-  <si>
-    <t>0.608 EUR</t>
-  </si>
-  <si>
-    <t>0.68844 EUR</t>
-  </si>
-  <si>
-    <t>0.15156 EUR</t>
-  </si>
-  <si>
-    <t>0.1272 EUR</t>
-  </si>
-  <si>
     <t>0.3022 EUR</t>
   </si>
   <si>
     <t>0.5134 EUR</t>
   </si>
   <si>
-    <t>0.2564 EUR</t>
-  </si>
-  <si>
-    <t>0.1316 EUR</t>
-  </si>
-  <si>
-    <t>0.388 EUR</t>
-  </si>
-  <si>
-    <t>0.0651 EUR</t>
-  </si>
-  <si>
     <t>0.07786 EUR</t>
   </si>
   <si>
@@ -6514,63 +6379,21 @@
     <t>0.53266 EUR</t>
   </si>
   <si>
-    <t>0.2124 EUR</t>
-  </si>
-  <si>
-    <t>0.0572 EUR</t>
-  </si>
-  <si>
-    <t>0.2696 EUR</t>
-  </si>
-  <si>
     <t>0.13421 EUR</t>
   </si>
   <si>
     <t>0.07379 EUR</t>
   </si>
   <si>
-    <t>0.0416 EUR</t>
-  </si>
-  <si>
-    <t>0.01375 EUR</t>
-  </si>
-  <si>
-    <t>0.1235 EUR</t>
-  </si>
-  <si>
-    <t>0.13725 EUR</t>
-  </si>
-  <si>
     <t>0.4 EUR</t>
   </si>
   <si>
     <t>0.1395 EUR</t>
   </si>
   <si>
-    <t>0.0656 EUR</t>
-  </si>
-  <si>
-    <t>0.318 EUR</t>
-  </si>
-  <si>
-    <t>0.402 EUR</t>
-  </si>
-  <si>
-    <t>0.0425 EUR</t>
-  </si>
-  <si>
     <t>0.0535 EUR</t>
   </si>
   <si>
-    <t>0.1015 EUR</t>
-  </si>
-  <si>
-    <t>0.0328 EUR</t>
-  </si>
-  <si>
-    <t>0.0482 EUR</t>
-  </si>
-  <si>
     <t>0.0594 EUR</t>
   </si>
   <si>
@@ -6580,13 +6403,358 @@
     <t>0.0063 EUR</t>
   </si>
   <si>
-    <t>0.0218 EUR</t>
-  </si>
-  <si>
     <t>0.00125 EUR</t>
   </si>
   <si>
     <t>0.0065 EUR</t>
+  </si>
+  <si>
+    <t>17.4145 EUR</t>
+  </si>
+  <si>
+    <t>10.4955 EUR</t>
+  </si>
+  <si>
+    <t>27.91 EUR</t>
+  </si>
+  <si>
+    <t>1.23945 EUR</t>
+  </si>
+  <si>
+    <t>2.83865 EUR</t>
+  </si>
+  <si>
+    <t>4.0781 EUR</t>
+  </si>
+  <si>
+    <t>12.0876 EUR</t>
+  </si>
+  <si>
+    <t>28.7394 EUR</t>
+  </si>
+  <si>
+    <t>40.827 EUR</t>
+  </si>
+  <si>
+    <t>0.2625 EUR</t>
+  </si>
+  <si>
+    <t>3.1495 EUR</t>
+  </si>
+  <si>
+    <t>3.412 EUR</t>
+  </si>
+  <si>
+    <t>8.5851 EUR</t>
+  </si>
+  <si>
+    <t>20.3229 EUR</t>
+  </si>
+  <si>
+    <t>28.908 EUR</t>
+  </si>
+  <si>
+    <t>0.941 EUR</t>
+  </si>
+  <si>
+    <t>8.306 EUR</t>
+  </si>
+  <si>
+    <t>9.247 EUR</t>
+  </si>
+  <si>
+    <t>0.9086 EUR</t>
+  </si>
+  <si>
+    <t>0.9904 EUR</t>
+  </si>
+  <si>
+    <t>1.899 EUR</t>
+  </si>
+  <si>
+    <t>0.1807 EUR</t>
+  </si>
+  <si>
+    <t>0.2828 EUR</t>
+  </si>
+  <si>
+    <t>0.4635 EUR</t>
+  </si>
+  <si>
+    <t>0.5157 EUR</t>
+  </si>
+  <si>
+    <t>0.4197 EUR</t>
+  </si>
+  <si>
+    <t>0.9354 EUR</t>
+  </si>
+  <si>
+    <t>1.01219 EUR</t>
+  </si>
+  <si>
+    <t>0.25181 EUR</t>
+  </si>
+  <si>
+    <t>1.264 EUR</t>
+  </si>
+  <si>
+    <t>0.1773 EUR</t>
+  </si>
+  <si>
+    <t>1.348 EUR</t>
+  </si>
+  <si>
+    <t>3.672 EUR</t>
+  </si>
+  <si>
+    <t>5.02 EUR</t>
+  </si>
+  <si>
+    <t>0.2091 EUR</t>
+  </si>
+  <si>
+    <t>0.5116 EUR</t>
+  </si>
+  <si>
+    <t>0.7207 EUR</t>
+  </si>
+  <si>
+    <t>0.1755 EUR</t>
+  </si>
+  <si>
+    <t>0.7395 EUR</t>
+  </si>
+  <si>
+    <t>0.915 EUR</t>
+  </si>
+  <si>
+    <t>0.03135 EUR</t>
+  </si>
+  <si>
+    <t>0.06355 EUR</t>
+  </si>
+  <si>
+    <t>0.0949 EUR</t>
+  </si>
+  <si>
+    <t>0.86184 EUR</t>
+  </si>
+  <si>
+    <t>0.20616 EUR</t>
+  </si>
+  <si>
+    <t>1.068 EUR</t>
+  </si>
+  <si>
+    <t>0.0338 EUR</t>
+  </si>
+  <si>
+    <t>0.2366 EUR</t>
+  </si>
+  <si>
+    <t>0.507 EUR</t>
+  </si>
+  <si>
+    <t>1.325 EUR</t>
+  </si>
+  <si>
+    <t>1.675 EUR</t>
+  </si>
+  <si>
+    <t>0.0234 EUR</t>
+  </si>
+  <si>
+    <t>0.0789 EUR</t>
+  </si>
+  <si>
+    <t>0.21855 EUR</t>
+  </si>
+  <si>
+    <t>0.05765 EUR</t>
+  </si>
+  <si>
+    <t>0.2762 EUR</t>
+  </si>
+  <si>
+    <t>0.594 EUR</t>
+  </si>
+  <si>
+    <t>0.01835 EUR</t>
+  </si>
+  <si>
+    <t>0.1475 EUR</t>
+  </si>
+  <si>
+    <t>0.16585 EUR</t>
+  </si>
+  <si>
+    <t>0.0445 EUR</t>
+  </si>
+  <si>
+    <t>1.05 EUR</t>
+  </si>
+  <si>
+    <t>0.1024 EUR</t>
+  </si>
+  <si>
+    <t>0.188 EUR</t>
+  </si>
+  <si>
+    <t>0.0686 EUR</t>
+  </si>
+  <si>
+    <t>0.1114 EUR</t>
+  </si>
+  <si>
+    <t>0.03781 EUR</t>
+  </si>
+  <si>
+    <t>0.11419 EUR</t>
+  </si>
+  <si>
+    <t>0.152 EUR</t>
+  </si>
+  <si>
+    <t>0.0668 EUR</t>
+  </si>
+  <si>
+    <t>0.0431 EUR</t>
+  </si>
+  <si>
+    <t>0.0182 EUR</t>
+  </si>
+  <si>
+    <t>TLight_HQ(Client)</t>
+  </si>
+  <si>
+    <t>13.827 EUR</t>
+  </si>
+  <si>
+    <t>8.263 EUR</t>
+  </si>
+  <si>
+    <t>22.09 EUR</t>
+  </si>
+  <si>
+    <t>6.12264 EUR</t>
+  </si>
+  <si>
+    <t>14.4918 EUR</t>
+  </si>
+  <si>
+    <t>20.61444 EUR</t>
+  </si>
+  <si>
+    <t>1.8456 EUR</t>
+  </si>
+  <si>
+    <t>0.4387 EUR</t>
+  </si>
+  <si>
+    <t>0.3567 EUR</t>
+  </si>
+  <si>
+    <t>0.7954 EUR</t>
+  </si>
+  <si>
+    <t>0.6402 EUR</t>
+  </si>
+  <si>
+    <t>1.6538 EUR</t>
+  </si>
+  <si>
+    <t>2.294 EUR</t>
+  </si>
+  <si>
+    <t>0.602 EUR</t>
+  </si>
+  <si>
+    <t>2.408 EUR</t>
+  </si>
+  <si>
+    <t>3.01 EUR</t>
+  </si>
+  <si>
+    <t>0.0463 EUR</t>
+  </si>
+  <si>
+    <t>0.0467 EUR</t>
+  </si>
+  <si>
+    <t>0.1188 EUR</t>
+  </si>
+  <si>
+    <t>0.1468 EUR</t>
+  </si>
+  <si>
+    <t>0.2742 EUR</t>
+  </si>
+  <si>
+    <t>0.421 EUR</t>
+  </si>
+  <si>
+    <t>0.03685 EUR</t>
+  </si>
+  <si>
+    <t>0.02615 EUR</t>
+  </si>
+  <si>
+    <t>0.22181 EUR</t>
+  </si>
+  <si>
+    <t>0.07219 EUR</t>
+  </si>
+  <si>
+    <t>0.294 EUR</t>
+  </si>
+  <si>
+    <t>0.0908 EUR</t>
+  </si>
+  <si>
+    <t>0.3305 EUR</t>
+  </si>
+  <si>
+    <t>0.351 EUR</t>
+  </si>
+  <si>
+    <t>0.424 EUR</t>
+  </si>
+  <si>
+    <t>0.536 EUR</t>
+  </si>
+  <si>
+    <t>0.176 EUR</t>
+  </si>
+  <si>
+    <t>0.714 EUR</t>
+  </si>
+  <si>
+    <t>0.0081 EUR</t>
+  </si>
+  <si>
+    <t>0.0477 EUR</t>
+  </si>
+  <si>
+    <t>0.264 EUR</t>
+  </si>
+  <si>
+    <t>0.0738 EUR</t>
+  </si>
+  <si>
+    <t>0.0406 EUR</t>
+  </si>
+  <si>
+    <t>0.0214 EUR</t>
+  </si>
+  <si>
+    <t>0.0029 EUR</t>
+  </si>
+  <si>
+    <t>0.0003 EUR</t>
+  </si>
+  <si>
+    <t>0.0133 EUR</t>
   </si>
 </sst>
 </file>
@@ -6974,7 +7142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1373"/>
+  <dimension ref="A1:N1426"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -64021,34 +64189,34 @@
         <v>46283</v>
       </c>
       <c r="B1297" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="C1297">
-        <v>2434</v>
+        <v>2791</v>
       </c>
       <c r="D1297">
-        <v>2195</v>
+        <v>2656</v>
       </c>
       <c r="E1297" s="3">
-        <v>0.90180769999999999</v>
+        <v>0.95163019999999998</v>
       </c>
       <c r="F1297" t="s">
-        <v>2107</v>
+        <v>2122</v>
       </c>
       <c r="G1297" t="s">
-        <v>2108</v>
+        <v>2123</v>
       </c>
       <c r="H1297" t="s">
-        <v>2109</v>
+        <v>2124</v>
       </c>
       <c r="I1297" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1297" t="s">
         <v>19</v>
       </c>
       <c r="K1297" t="s">
-        <v>2108</v>
+        <v>2123</v>
       </c>
       <c r="L1297">
         <v>0</v>
@@ -64065,34 +64233,34 @@
         <v>46283</v>
       </c>
       <c r="B1298" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C1298">
-        <v>2277</v>
+        <v>2494</v>
       </c>
       <c r="D1298">
-        <v>2170</v>
+        <v>2253</v>
       </c>
       <c r="E1298" s="3">
-        <v>0.95300830000000003</v>
+        <v>0.90336810000000001</v>
       </c>
       <c r="F1298" t="s">
-        <v>2110</v>
+        <v>2125</v>
       </c>
       <c r="G1298" t="s">
-        <v>2111</v>
+        <v>2126</v>
       </c>
       <c r="H1298" t="s">
-        <v>2112</v>
+        <v>2127</v>
       </c>
       <c r="I1298" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1298" t="s">
         <v>19</v>
       </c>
       <c r="K1298" t="s">
-        <v>2111</v>
+        <v>2126</v>
       </c>
       <c r="L1298">
         <v>0</v>
@@ -64112,22 +64280,22 @@
         <v>49</v>
       </c>
       <c r="C1299">
-        <v>1301</v>
+        <v>1317</v>
       </c>
       <c r="D1299">
-        <v>1118</v>
+        <v>1134</v>
       </c>
       <c r="E1299" s="3">
-        <v>0.85933899999999996</v>
+        <v>0.86104780000000003</v>
       </c>
       <c r="F1299" t="s">
-        <v>2113</v>
+        <v>2128</v>
       </c>
       <c r="G1299" t="s">
-        <v>2114</v>
+        <v>2129</v>
       </c>
       <c r="H1299" t="s">
-        <v>2115</v>
+        <v>2130</v>
       </c>
       <c r="I1299" t="s">
         <v>28</v>
@@ -64136,7 +64304,7 @@
         <v>19</v>
       </c>
       <c r="K1299" t="s">
-        <v>2114</v>
+        <v>2129</v>
       </c>
       <c r="L1299">
         <v>0</v>
@@ -64156,22 +64324,22 @@
         <v>45</v>
       </c>
       <c r="C1300">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="D1300">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="E1300" s="3">
-        <v>0.99750000000000005</v>
+        <v>0.99766359999999998</v>
       </c>
       <c r="F1300" t="s">
-        <v>2116</v>
+        <v>2131</v>
       </c>
       <c r="G1300" t="s">
-        <v>2117</v>
+        <v>2132</v>
       </c>
       <c r="H1300" t="s">
-        <v>2118</v>
+        <v>2133</v>
       </c>
       <c r="I1300" t="s">
         <v>23</v>
@@ -64180,7 +64348,7 @@
         <v>19</v>
       </c>
       <c r="K1300" t="s">
-        <v>2117</v>
+        <v>2132</v>
       </c>
       <c r="L1300">
         <v>0</v>
@@ -64200,22 +64368,22 @@
         <v>148</v>
       </c>
       <c r="C1301">
-        <v>341</v>
+        <v>411</v>
       </c>
       <c r="D1301">
-        <v>266</v>
+        <v>315</v>
       </c>
       <c r="E1301" s="3">
-        <v>0.78005869999999999</v>
+        <v>0.76642339999999998</v>
       </c>
       <c r="F1301" t="s">
-        <v>2119</v>
+        <v>2134</v>
       </c>
       <c r="G1301" t="s">
-        <v>2120</v>
+        <v>2135</v>
       </c>
       <c r="H1301" t="s">
-        <v>2121</v>
+        <v>2136</v>
       </c>
       <c r="I1301" t="s">
         <v>28</v>
@@ -64224,7 +64392,7 @@
         <v>19</v>
       </c>
       <c r="K1301" t="s">
-        <v>2120</v>
+        <v>2135</v>
       </c>
       <c r="L1301">
         <v>0</v>
@@ -64244,22 +64412,22 @@
         <v>1117</v>
       </c>
       <c r="C1302">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D1302">
         <v>161</v>
       </c>
       <c r="E1302" s="3">
-        <v>0.50949370000000005</v>
+        <v>0.50788639999999996</v>
       </c>
       <c r="F1302" t="s">
-        <v>2122</v>
+        <v>2137</v>
       </c>
       <c r="G1302" t="s">
-        <v>2123</v>
+        <v>2138</v>
       </c>
       <c r="H1302" t="s">
-        <v>2124</v>
+        <v>2139</v>
       </c>
       <c r="I1302" t="s">
         <v>23</v>
@@ -64268,7 +64436,7 @@
         <v>19</v>
       </c>
       <c r="K1302" t="s">
-        <v>2123</v>
+        <v>2138</v>
       </c>
       <c r="L1302">
         <v>0</v>
@@ -64288,22 +64456,22 @@
         <v>124</v>
       </c>
       <c r="C1303">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D1303">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E1303" s="3">
-        <v>0.95192310000000002</v>
+        <v>0.95260659999999997</v>
       </c>
       <c r="F1303" t="s">
-        <v>2125</v>
+        <v>2140</v>
       </c>
       <c r="G1303" t="s">
-        <v>2126</v>
+        <v>2141</v>
       </c>
       <c r="H1303" t="s">
-        <v>2127</v>
+        <v>2142</v>
       </c>
       <c r="I1303" t="s">
         <v>23</v>
@@ -64312,7 +64480,7 @@
         <v>19</v>
       </c>
       <c r="K1303" t="s">
-        <v>2126</v>
+        <v>2141</v>
       </c>
       <c r="L1303">
         <v>0</v>
@@ -64332,22 +64500,22 @@
         <v>168</v>
       </c>
       <c r="C1304">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="D1304">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="E1304" s="3">
-        <v>0.92783510000000002</v>
+        <v>0.94326239999999995</v>
       </c>
       <c r="F1304" t="s">
-        <v>2128</v>
+        <v>2143</v>
       </c>
       <c r="G1304" t="s">
-        <v>2129</v>
+        <v>2144</v>
       </c>
       <c r="H1304" t="s">
-        <v>2130</v>
+        <v>2145</v>
       </c>
       <c r="I1304" t="s">
         <v>18</v>
@@ -64356,7 +64524,7 @@
         <v>19</v>
       </c>
       <c r="K1304" t="s">
-        <v>2129</v>
+        <v>2144</v>
       </c>
       <c r="L1304">
         <v>0</v>
@@ -64376,22 +64544,22 @@
         <v>101</v>
       </c>
       <c r="C1305">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D1305">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E1305" s="3">
-        <v>0.87341769999999996</v>
+        <v>0.88541669999999995</v>
       </c>
       <c r="F1305" t="s">
-        <v>2131</v>
+        <v>2146</v>
       </c>
       <c r="G1305" t="s">
-        <v>2132</v>
+        <v>2147</v>
       </c>
       <c r="H1305" t="s">
-        <v>2133</v>
+        <v>2148</v>
       </c>
       <c r="I1305" t="s">
         <v>23</v>
@@ -64400,7 +64568,7 @@
         <v>19</v>
       </c>
       <c r="K1305" t="s">
-        <v>2132</v>
+        <v>2147</v>
       </c>
       <c r="L1305">
         <v>0</v>
@@ -64417,25 +64585,25 @@
         <v>46283</v>
       </c>
       <c r="B1306" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="C1306">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D1306">
-        <v>29</v>
-      </c>
-      <c r="E1306" s="3">
-        <v>0.65909090000000004</v>
+        <v>0</v>
+      </c>
+      <c r="E1306" s="4">
+        <v>0</v>
       </c>
       <c r="F1306" t="s">
-        <v>2134</v>
+        <v>2149</v>
       </c>
       <c r="G1306" t="s">
-        <v>2135</v>
+        <v>2150</v>
       </c>
       <c r="H1306" t="s">
-        <v>2136</v>
+        <v>2151</v>
       </c>
       <c r="I1306" t="s">
         <v>18</v>
@@ -64444,7 +64612,7 @@
         <v>19</v>
       </c>
       <c r="K1306" t="s">
-        <v>2135</v>
+        <v>2150</v>
       </c>
       <c r="L1306">
         <v>0</v>
@@ -64461,34 +64629,34 @@
         <v>46283</v>
       </c>
       <c r="B1307" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="C1307">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D1307">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E1307" s="3">
-        <v>0.92500000000000004</v>
+        <v>0.86956520000000004</v>
       </c>
       <c r="F1307" t="s">
-        <v>2137</v>
+        <v>1084</v>
       </c>
       <c r="G1307" t="s">
-        <v>629</v>
+        <v>2152</v>
       </c>
       <c r="H1307" t="s">
-        <v>2138</v>
+        <v>1419</v>
       </c>
       <c r="I1307" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1307" t="s">
         <v>19</v>
       </c>
       <c r="K1307" t="s">
-        <v>629</v>
+        <v>2152</v>
       </c>
       <c r="L1307">
         <v>0</v>
@@ -64505,34 +64673,34 @@
         <v>46283</v>
       </c>
       <c r="B1308" t="s">
-        <v>308</v>
+        <v>105</v>
       </c>
       <c r="C1308">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D1308">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="E1308" s="3">
-        <v>0.625</v>
+        <v>0.9393939</v>
       </c>
       <c r="F1308" t="s">
-        <v>2139</v>
+        <v>2153</v>
       </c>
       <c r="G1308" t="s">
-        <v>2140</v>
+        <v>2154</v>
       </c>
       <c r="H1308" t="s">
-        <v>2141</v>
+        <v>2155</v>
       </c>
       <c r="I1308" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1308" t="s">
         <v>19</v>
       </c>
       <c r="K1308" t="s">
-        <v>2140</v>
+        <v>2154</v>
       </c>
       <c r="L1308">
         <v>0</v>
@@ -64549,25 +64717,25 @@
         <v>46283</v>
       </c>
       <c r="B1309" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="C1309">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D1309">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E1309" s="4">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="F1309" t="s">
-        <v>2142</v>
+        <v>2156</v>
       </c>
       <c r="G1309" t="s">
-        <v>2143</v>
+        <v>2157</v>
       </c>
       <c r="H1309" t="s">
-        <v>2144</v>
+        <v>2158</v>
       </c>
       <c r="I1309" t="s">
         <v>18</v>
@@ -64576,7 +64744,7 @@
         <v>19</v>
       </c>
       <c r="K1309" t="s">
-        <v>2143</v>
+        <v>2157</v>
       </c>
       <c r="L1309">
         <v>0</v>
@@ -64593,34 +64761,34 @@
         <v>46283</v>
       </c>
       <c r="B1310" t="s">
-        <v>175</v>
+        <v>308</v>
       </c>
       <c r="C1310">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D1310">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E1310" s="3">
-        <v>0.91176469999999998</v>
+        <v>0.63636360000000003</v>
       </c>
       <c r="F1310" t="s">
-        <v>483</v>
+        <v>2159</v>
       </c>
       <c r="G1310" t="s">
-        <v>233</v>
+        <v>2160</v>
       </c>
       <c r="H1310" t="s">
-        <v>1187</v>
+        <v>2161</v>
       </c>
       <c r="I1310" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1310" t="s">
         <v>19</v>
       </c>
       <c r="K1310" t="s">
-        <v>233</v>
+        <v>2160</v>
       </c>
       <c r="L1310">
         <v>0</v>
@@ -64637,34 +64805,34 @@
         <v>46283</v>
       </c>
       <c r="B1311" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="C1311">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D1311">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E1311" s="3">
-        <v>3.0303E-2</v>
+        <v>0.90476190000000001</v>
       </c>
       <c r="F1311" t="s">
-        <v>2145</v>
+        <v>2162</v>
       </c>
       <c r="G1311" t="s">
-        <v>2146</v>
+        <v>2163</v>
       </c>
       <c r="H1311" t="s">
-        <v>1044</v>
+        <v>2164</v>
       </c>
       <c r="I1311" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1311" t="s">
         <v>19</v>
       </c>
       <c r="K1311" t="s">
-        <v>2146</v>
+        <v>2163</v>
       </c>
       <c r="L1311">
         <v>0</v>
@@ -64681,34 +64849,34 @@
         <v>46283</v>
       </c>
       <c r="B1312" t="s">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="C1312">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D1312">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E1312" s="3">
-        <v>0.62962960000000001</v>
+        <v>2.3809500000000001E-2</v>
       </c>
       <c r="F1312" t="s">
-        <v>1826</v>
+        <v>2165</v>
       </c>
       <c r="G1312" t="s">
-        <v>2147</v>
+        <v>2166</v>
       </c>
       <c r="H1312" t="s">
-        <v>1556</v>
+        <v>2167</v>
       </c>
       <c r="I1312" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1312" t="s">
         <v>19</v>
       </c>
       <c r="K1312" t="s">
-        <v>2147</v>
+        <v>2166</v>
       </c>
       <c r="L1312">
         <v>0</v>
@@ -64725,34 +64893,34 @@
         <v>46283</v>
       </c>
       <c r="B1313" t="s">
-        <v>183</v>
+        <v>325</v>
       </c>
       <c r="C1313">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D1313">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E1313" s="3">
-        <v>0.47619050000000002</v>
+        <v>0.9736842</v>
       </c>
       <c r="F1313" t="s">
-        <v>437</v>
+        <v>2168</v>
       </c>
       <c r="G1313" t="s">
-        <v>2148</v>
+        <v>1789</v>
       </c>
       <c r="H1313" t="s">
-        <v>2149</v>
+        <v>1334</v>
       </c>
       <c r="I1313" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1313" t="s">
         <v>19</v>
       </c>
       <c r="K1313" t="s">
-        <v>2148</v>
+        <v>1789</v>
       </c>
       <c r="L1313">
         <v>0</v>
@@ -64769,34 +64937,34 @@
         <v>46283</v>
       </c>
       <c r="B1314" t="s">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="C1314">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D1314">
-        <v>0</v>
-      </c>
-      <c r="E1314" s="4">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="E1314" s="3">
+        <v>0.91176469999999998</v>
       </c>
       <c r="F1314" t="s">
-        <v>2150</v>
+        <v>483</v>
       </c>
       <c r="G1314" t="s">
-        <v>2151</v>
+        <v>233</v>
       </c>
       <c r="H1314" t="s">
-        <v>2152</v>
+        <v>1187</v>
       </c>
       <c r="I1314" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1314" t="s">
         <v>19</v>
       </c>
       <c r="K1314" t="s">
-        <v>2151</v>
+        <v>233</v>
       </c>
       <c r="L1314">
         <v>0</v>
@@ -64813,34 +64981,34 @@
         <v>46283</v>
       </c>
       <c r="B1315" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C1315">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D1315">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E1315" s="4">
         <v>1</v>
       </c>
       <c r="F1315" t="s">
-        <v>680</v>
+        <v>1777</v>
       </c>
       <c r="G1315" t="s">
-        <v>2006</v>
+        <v>1778</v>
       </c>
       <c r="H1315" t="s">
-        <v>2153</v>
+        <v>1779</v>
       </c>
       <c r="I1315" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1315" t="s">
         <v>19</v>
       </c>
       <c r="K1315" t="s">
-        <v>2006</v>
+        <v>1778</v>
       </c>
       <c r="L1315">
         <v>0</v>
@@ -64857,25 +65025,25 @@
         <v>46283</v>
       </c>
       <c r="B1316" t="s">
-        <v>409</v>
+        <v>73</v>
       </c>
       <c r="C1316">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D1316">
-        <v>12</v>
-      </c>
-      <c r="E1316" s="3">
-        <v>0.70588240000000002</v>
+        <v>0</v>
+      </c>
+      <c r="E1316" s="4">
+        <v>0</v>
       </c>
       <c r="F1316" t="s">
-        <v>1000</v>
+        <v>1987</v>
       </c>
       <c r="G1316" t="s">
-        <v>616</v>
+        <v>2169</v>
       </c>
       <c r="H1316" t="s">
-        <v>122</v>
+        <v>2170</v>
       </c>
       <c r="I1316" t="s">
         <v>18</v>
@@ -64884,7 +65052,7 @@
         <v>19</v>
       </c>
       <c r="K1316" t="s">
-        <v>616</v>
+        <v>2169</v>
       </c>
       <c r="L1316">
         <v>0</v>
@@ -64901,25 +65069,25 @@
         <v>46283</v>
       </c>
       <c r="B1317" t="s">
-        <v>29</v>
+        <v>172</v>
       </c>
       <c r="C1317">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D1317">
-        <v>15</v>
-      </c>
-      <c r="E1317" s="3">
-        <v>0.8823529</v>
+        <v>25</v>
+      </c>
+      <c r="E1317" s="4">
+        <v>1</v>
       </c>
       <c r="F1317" t="s">
-        <v>2154</v>
+        <v>777</v>
       </c>
       <c r="G1317" t="s">
-        <v>2155</v>
+        <v>2171</v>
       </c>
       <c r="H1317" t="s">
-        <v>2156</v>
+        <v>2172</v>
       </c>
       <c r="I1317" t="s">
         <v>28</v>
@@ -64928,7 +65096,7 @@
         <v>19</v>
       </c>
       <c r="K1317" t="s">
-        <v>2155</v>
+        <v>2171</v>
       </c>
       <c r="L1317">
         <v>0</v>
@@ -64945,34 +65113,34 @@
         <v>46283</v>
       </c>
       <c r="B1318" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="C1318">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D1318">
-        <v>15</v>
-      </c>
-      <c r="E1318" s="3">
-        <v>0.9375</v>
+        <v>24</v>
+      </c>
+      <c r="E1318" s="4">
+        <v>1</v>
       </c>
       <c r="F1318" t="s">
-        <v>303</v>
+        <v>2173</v>
       </c>
       <c r="G1318" t="s">
-        <v>1228</v>
+        <v>681</v>
       </c>
       <c r="H1318" t="s">
-        <v>1985</v>
+        <v>2174</v>
       </c>
       <c r="I1318" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1318" t="s">
         <v>19</v>
       </c>
       <c r="K1318" t="s">
-        <v>1228</v>
+        <v>681</v>
       </c>
       <c r="L1318">
         <v>0</v>
@@ -64989,34 +65157,34 @@
         <v>46283</v>
       </c>
       <c r="B1319" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="C1319">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D1319">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1319" s="3">
-        <v>0.6875</v>
+        <v>0.57142859999999995</v>
       </c>
       <c r="F1319" t="s">
-        <v>2157</v>
+        <v>437</v>
       </c>
       <c r="G1319" t="s">
-        <v>2158</v>
+        <v>2107</v>
       </c>
       <c r="H1319" t="s">
-        <v>2159</v>
+        <v>2108</v>
       </c>
       <c r="I1319" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1319" t="s">
         <v>19</v>
       </c>
       <c r="K1319" t="s">
-        <v>2158</v>
+        <v>2107</v>
       </c>
       <c r="L1319">
         <v>0</v>
@@ -65033,25 +65201,25 @@
         <v>46283</v>
       </c>
       <c r="B1320" t="s">
-        <v>97</v>
+        <v>211</v>
       </c>
       <c r="C1320">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D1320">
-        <v>6</v>
-      </c>
-      <c r="E1320" s="4">
-        <v>0.5</v>
+        <v>14</v>
+      </c>
+      <c r="E1320" s="3">
+        <v>0.73684210000000006</v>
       </c>
       <c r="F1320" t="s">
-        <v>2160</v>
+        <v>2175</v>
       </c>
       <c r="G1320" t="s">
-        <v>2161</v>
+        <v>2176</v>
       </c>
       <c r="H1320" t="s">
-        <v>253</v>
+        <v>2177</v>
       </c>
       <c r="I1320" t="s">
         <v>18</v>
@@ -65060,7 +65228,7 @@
         <v>19</v>
       </c>
       <c r="K1320" t="s">
-        <v>2161</v>
+        <v>2176</v>
       </c>
       <c r="L1320">
         <v>0</v>
@@ -65077,25 +65245,25 @@
         <v>46283</v>
       </c>
       <c r="B1321" t="s">
-        <v>128</v>
+        <v>409</v>
       </c>
       <c r="C1321">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D1321">
-        <v>10</v>
-      </c>
-      <c r="E1321" s="4">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E1321" s="3">
+        <v>0.72222220000000004</v>
       </c>
       <c r="F1321" t="s">
-        <v>1199</v>
+        <v>495</v>
       </c>
       <c r="G1321" t="s">
-        <v>219</v>
+        <v>1705</v>
       </c>
       <c r="H1321" t="s">
-        <v>1705</v>
+        <v>893</v>
       </c>
       <c r="I1321" t="s">
         <v>18</v>
@@ -65104,7 +65272,7 @@
         <v>19</v>
       </c>
       <c r="K1321" t="s">
-        <v>219</v>
+        <v>1705</v>
       </c>
       <c r="L1321">
         <v>0</v>
@@ -65121,25 +65289,25 @@
         <v>46283</v>
       </c>
       <c r="B1322" t="s">
-        <v>325</v>
+        <v>29</v>
       </c>
       <c r="C1322">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D1322">
-        <v>10</v>
-      </c>
-      <c r="E1322" s="4">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="E1322" s="3">
+        <v>0.8823529</v>
       </c>
       <c r="F1322" t="s">
-        <v>1911</v>
+        <v>2109</v>
       </c>
       <c r="G1322" t="s">
-        <v>298</v>
+        <v>2110</v>
       </c>
       <c r="H1322" t="s">
-        <v>2162</v>
+        <v>2111</v>
       </c>
       <c r="I1322" t="s">
         <v>28</v>
@@ -65148,7 +65316,7 @@
         <v>19</v>
       </c>
       <c r="K1322" t="s">
-        <v>298</v>
+        <v>2110</v>
       </c>
       <c r="L1322">
         <v>0</v>
@@ -65165,34 +65333,34 @@
         <v>46283</v>
       </c>
       <c r="B1323" t="s">
-        <v>660</v>
+        <v>20</v>
       </c>
       <c r="C1323">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D1323">
-        <v>7</v>
-      </c>
-      <c r="E1323" s="4">
-        <v>0.7</v>
+        <v>15</v>
+      </c>
+      <c r="E1323" s="3">
+        <v>0.9375</v>
       </c>
       <c r="F1323" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G1323" t="s">
-        <v>321</v>
+        <v>1228</v>
       </c>
       <c r="H1323" t="s">
-        <v>227</v>
+        <v>1985</v>
       </c>
       <c r="I1323" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1323" t="s">
         <v>19</v>
       </c>
       <c r="K1323" t="s">
-        <v>321</v>
+        <v>1228</v>
       </c>
       <c r="L1323">
         <v>0</v>
@@ -65209,34 +65377,34 @@
         <v>46283</v>
       </c>
       <c r="B1324" t="s">
-        <v>237</v>
+        <v>128</v>
       </c>
       <c r="C1324">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D1324">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E1324" s="4">
         <v>1</v>
       </c>
       <c r="F1324" t="s">
-        <v>2163</v>
+        <v>194</v>
       </c>
       <c r="G1324" t="s">
-        <v>2164</v>
+        <v>893</v>
       </c>
       <c r="H1324" t="s">
-        <v>2165</v>
+        <v>2178</v>
       </c>
       <c r="I1324" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1324" t="s">
         <v>19</v>
       </c>
       <c r="K1324" t="s">
-        <v>2164</v>
+        <v>893</v>
       </c>
       <c r="L1324">
         <v>0</v>
@@ -65253,34 +65421,34 @@
         <v>46283</v>
       </c>
       <c r="B1325" t="s">
-        <v>140</v>
+        <v>237</v>
       </c>
       <c r="C1325">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D1325">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E1325" s="4">
         <v>1</v>
       </c>
       <c r="F1325" t="s">
-        <v>1205</v>
+        <v>2179</v>
       </c>
       <c r="G1325" t="s">
-        <v>1206</v>
+        <v>2180</v>
       </c>
       <c r="H1325" t="s">
-        <v>1207</v>
+        <v>2181</v>
       </c>
       <c r="I1325" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1325" t="s">
         <v>19</v>
       </c>
       <c r="K1325" t="s">
-        <v>1206</v>
+        <v>2180</v>
       </c>
       <c r="L1325">
         <v>0</v>
@@ -65297,34 +65465,34 @@
         <v>46283</v>
       </c>
       <c r="B1326" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C1326">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D1326">
-        <v>3</v>
-      </c>
-      <c r="E1326" s="3">
-        <v>0.3333333</v>
+        <v>6</v>
+      </c>
+      <c r="E1326" s="4">
+        <v>0.5</v>
       </c>
       <c r="F1326" t="s">
-        <v>1071</v>
+        <v>2112</v>
       </c>
       <c r="G1326" t="s">
-        <v>784</v>
+        <v>2113</v>
       </c>
       <c r="H1326" t="s">
-        <v>1524</v>
+        <v>253</v>
       </c>
       <c r="I1326" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1326" t="s">
         <v>19</v>
       </c>
       <c r="K1326" t="s">
-        <v>784</v>
+        <v>2113</v>
       </c>
       <c r="L1326">
         <v>0</v>
@@ -65341,34 +65509,34 @@
         <v>46283</v>
       </c>
       <c r="B1327" t="s">
-        <v>230</v>
+        <v>660</v>
       </c>
       <c r="C1327">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D1327">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E1327" s="4">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F1327" t="s">
-        <v>2166</v>
+        <v>300</v>
       </c>
       <c r="G1327" t="s">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="H1327" t="s">
-        <v>2166</v>
+        <v>227</v>
       </c>
       <c r="I1327" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1327" t="s">
         <v>19</v>
       </c>
       <c r="K1327" t="s">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="L1327">
         <v>0</v>
@@ -65385,34 +65553,34 @@
         <v>46283</v>
       </c>
       <c r="B1328" t="s">
-        <v>1360</v>
+        <v>271</v>
       </c>
       <c r="C1328">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D1328">
         <v>7</v>
       </c>
-      <c r="E1328" s="3">
-        <v>0.875</v>
+      <c r="E1328" s="4">
+        <v>0.7</v>
       </c>
       <c r="F1328" t="s">
-        <v>648</v>
+        <v>2182</v>
       </c>
       <c r="G1328" t="s">
-        <v>540</v>
+        <v>442</v>
       </c>
       <c r="H1328" t="s">
-        <v>2167</v>
+        <v>231</v>
       </c>
       <c r="I1328" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1328" t="s">
         <v>19</v>
       </c>
       <c r="K1328" t="s">
-        <v>540</v>
+        <v>442</v>
       </c>
       <c r="L1328">
         <v>0</v>
@@ -65429,25 +65597,25 @@
         <v>46283</v>
       </c>
       <c r="B1329" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C1329">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D1329">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E1329" s="4">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="F1329" t="s">
-        <v>1911</v>
+        <v>1938</v>
       </c>
       <c r="G1329" t="s">
-        <v>549</v>
+        <v>771</v>
       </c>
       <c r="H1329" t="s">
-        <v>1342</v>
+        <v>2183</v>
       </c>
       <c r="I1329" t="s">
         <v>28</v>
@@ -65456,7 +65624,7 @@
         <v>19</v>
       </c>
       <c r="K1329" t="s">
-        <v>549</v>
+        <v>771</v>
       </c>
       <c r="L1329">
         <v>0</v>
@@ -65473,34 +65641,34 @@
         <v>46283</v>
       </c>
       <c r="B1330" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C1330">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1330">
-        <v>5</v>
-      </c>
-      <c r="E1330" s="3">
-        <v>0.625</v>
+        <v>9</v>
+      </c>
+      <c r="E1330" s="4">
+        <v>1</v>
       </c>
       <c r="F1330" t="s">
-        <v>283</v>
+        <v>2184</v>
       </c>
       <c r="G1330" t="s">
-        <v>205</v>
+        <v>445</v>
       </c>
       <c r="H1330" t="s">
-        <v>2105</v>
+        <v>2185</v>
       </c>
       <c r="I1330" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1330" t="s">
         <v>19</v>
       </c>
       <c r="K1330" t="s">
-        <v>205</v>
+        <v>445</v>
       </c>
       <c r="L1330">
         <v>0</v>
@@ -65520,22 +65688,22 @@
         <v>461</v>
       </c>
       <c r="C1331">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D1331">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1331" s="4">
         <v>1</v>
       </c>
       <c r="F1331" t="s">
-        <v>227</v>
+        <v>2186</v>
       </c>
       <c r="G1331" t="s">
-        <v>490</v>
+        <v>2187</v>
       </c>
       <c r="H1331" t="s">
-        <v>209</v>
+        <v>662</v>
       </c>
       <c r="I1331" t="s">
         <v>23</v>
@@ -65544,7 +65712,7 @@
         <v>19</v>
       </c>
       <c r="K1331" t="s">
-        <v>490</v>
+        <v>2187</v>
       </c>
       <c r="L1331">
         <v>0</v>
@@ -65561,34 +65729,34 @@
         <v>46283</v>
       </c>
       <c r="B1332" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="C1332">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1332">
-        <v>5</v>
-      </c>
-      <c r="E1332" s="3">
-        <v>0.71428570000000002</v>
+        <v>0</v>
+      </c>
+      <c r="E1332" s="4">
+        <v>0</v>
       </c>
       <c r="F1332" t="s">
-        <v>1921</v>
+        <v>2114</v>
       </c>
       <c r="G1332" t="s">
-        <v>2168</v>
+        <v>19</v>
       </c>
       <c r="H1332" t="s">
-        <v>504</v>
+        <v>2114</v>
       </c>
       <c r="I1332" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1332" t="s">
         <v>19</v>
       </c>
       <c r="K1332" t="s">
-        <v>2168</v>
+        <v>19</v>
       </c>
       <c r="L1332">
         <v>0</v>
@@ -65605,34 +65773,34 @@
         <v>46283</v>
       </c>
       <c r="B1333" t="s">
-        <v>172</v>
+        <v>1360</v>
       </c>
       <c r="C1333">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1333">
-        <v>6</v>
-      </c>
-      <c r="E1333" s="4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="E1333" s="3">
+        <v>0.875</v>
       </c>
       <c r="F1333" t="s">
-        <v>508</v>
+        <v>648</v>
       </c>
       <c r="G1333" t="s">
-        <v>2169</v>
+        <v>540</v>
       </c>
       <c r="H1333" t="s">
-        <v>2170</v>
+        <v>2115</v>
       </c>
       <c r="I1333" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1333" t="s">
         <v>19</v>
       </c>
       <c r="K1333" t="s">
-        <v>2169</v>
+        <v>540</v>
       </c>
       <c r="L1333">
         <v>0</v>
@@ -65649,25 +65817,25 @@
         <v>46283</v>
       </c>
       <c r="B1334" t="s">
-        <v>271</v>
+        <v>89</v>
       </c>
       <c r="C1334">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1334">
-        <v>3</v>
-      </c>
-      <c r="E1334" s="4">
-        <v>0.5</v>
+        <v>5</v>
+      </c>
+      <c r="E1334" s="3">
+        <v>0.625</v>
       </c>
       <c r="F1334" t="s">
-        <v>2171</v>
+        <v>283</v>
       </c>
       <c r="G1334" t="s">
-        <v>2172</v>
+        <v>205</v>
       </c>
       <c r="H1334" t="s">
-        <v>1199</v>
+        <v>2105</v>
       </c>
       <c r="I1334" t="s">
         <v>23</v>
@@ -65676,7 +65844,7 @@
         <v>19</v>
       </c>
       <c r="K1334" t="s">
-        <v>2172</v>
+        <v>205</v>
       </c>
       <c r="L1334">
         <v>0</v>
@@ -65693,25 +65861,25 @@
         <v>46283</v>
       </c>
       <c r="B1335" t="s">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="C1335">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D1335">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E1335" s="4">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F1335" t="s">
-        <v>298</v>
+        <v>2188</v>
       </c>
       <c r="G1335" t="s">
-        <v>254</v>
+        <v>2189</v>
       </c>
       <c r="H1335" t="s">
-        <v>259</v>
+        <v>2190</v>
       </c>
       <c r="I1335" t="s">
         <v>18</v>
@@ -65720,7 +65888,7 @@
         <v>19</v>
       </c>
       <c r="K1335" t="s">
-        <v>254</v>
+        <v>2189</v>
       </c>
       <c r="L1335">
         <v>0</v>
@@ -65737,34 +65905,34 @@
         <v>46283</v>
       </c>
       <c r="B1336" t="s">
-        <v>93</v>
+        <v>204</v>
       </c>
       <c r="C1336">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D1336">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1336" s="4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F1336" t="s">
-        <v>826</v>
+        <v>2095</v>
       </c>
       <c r="G1336" t="s">
-        <v>991</v>
+        <v>2191</v>
       </c>
       <c r="H1336" t="s">
-        <v>662</v>
+        <v>205</v>
       </c>
       <c r="I1336" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1336" t="s">
         <v>19</v>
       </c>
       <c r="K1336" t="s">
-        <v>991</v>
+        <v>2191</v>
       </c>
       <c r="L1336">
         <v>0</v>
@@ -65784,22 +65952,22 @@
         <v>152</v>
       </c>
       <c r="C1337">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1337">
-        <v>1</v>
-      </c>
-      <c r="E1337" s="4">
-        <v>0.2</v>
+        <v>3</v>
+      </c>
+      <c r="E1337" s="3">
+        <v>0.42857139999999999</v>
       </c>
       <c r="F1337" t="s">
-        <v>931</v>
+        <v>2192</v>
       </c>
       <c r="G1337" t="s">
-        <v>1340</v>
+        <v>1333</v>
       </c>
       <c r="H1337" t="s">
-        <v>2173</v>
+        <v>2180</v>
       </c>
       <c r="I1337" t="s">
         <v>23</v>
@@ -65808,7 +65976,7 @@
         <v>19</v>
       </c>
       <c r="K1337" t="s">
-        <v>1340</v>
+        <v>1333</v>
       </c>
       <c r="L1337">
         <v>0</v>
@@ -65825,34 +65993,34 @@
         <v>46283</v>
       </c>
       <c r="B1338" t="s">
-        <v>156</v>
+        <v>275</v>
       </c>
       <c r="C1338">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1338">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E1338" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1338" t="s">
-        <v>208</v>
+        <v>453</v>
       </c>
       <c r="G1338" t="s">
-        <v>153</v>
+        <v>276</v>
       </c>
       <c r="H1338" t="s">
-        <v>449</v>
+        <v>495</v>
       </c>
       <c r="I1338" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1338" t="s">
         <v>19</v>
       </c>
       <c r="K1338" t="s">
-        <v>153</v>
+        <v>276</v>
       </c>
       <c r="L1338">
         <v>0</v>
@@ -65869,34 +66037,34 @@
         <v>46283</v>
       </c>
       <c r="B1339" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="C1339">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1339">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E1339" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1339" t="s">
-        <v>2174</v>
+        <v>196</v>
       </c>
       <c r="G1339" t="s">
-        <v>2175</v>
+        <v>694</v>
       </c>
       <c r="H1339" t="s">
-        <v>270</v>
+        <v>688</v>
       </c>
       <c r="I1339" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1339" t="s">
         <v>19</v>
       </c>
       <c r="K1339" t="s">
-        <v>2175</v>
+        <v>694</v>
       </c>
       <c r="L1339">
         <v>0</v>
@@ -65913,25 +66081,25 @@
         <v>46283</v>
       </c>
       <c r="B1340" t="s">
-        <v>1222</v>
+        <v>179</v>
       </c>
       <c r="C1340">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1340">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1340" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1340" t="s">
-        <v>284</v>
+        <v>1467</v>
       </c>
       <c r="G1340" t="s">
-        <v>648</v>
+        <v>249</v>
       </c>
       <c r="H1340" t="s">
-        <v>309</v>
+        <v>661</v>
       </c>
       <c r="I1340" t="s">
         <v>23</v>
@@ -65940,7 +66108,7 @@
         <v>19</v>
       </c>
       <c r="K1340" t="s">
-        <v>648</v>
+        <v>249</v>
       </c>
       <c r="L1340">
         <v>0</v>
@@ -65957,25 +66125,25 @@
         <v>46283</v>
       </c>
       <c r="B1341" t="s">
-        <v>708</v>
+        <v>261</v>
       </c>
       <c r="C1341">
         <v>4</v>
       </c>
       <c r="D1341">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E1341" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1341" t="s">
+        <v>1483</v>
+      </c>
+      <c r="G1341" t="s">
         <v>303</v>
       </c>
-      <c r="G1341" t="s">
-        <v>258</v>
-      </c>
       <c r="H1341" t="s">
-        <v>321</v>
+        <v>527</v>
       </c>
       <c r="I1341" t="s">
         <v>23</v>
@@ -65984,7 +66152,7 @@
         <v>19</v>
       </c>
       <c r="K1341" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="L1341">
         <v>0</v>
@@ -66001,34 +66169,34 @@
         <v>46283</v>
       </c>
       <c r="B1342" t="s">
-        <v>215</v>
+        <v>1222</v>
       </c>
       <c r="C1342">
         <v>4</v>
       </c>
       <c r="D1342">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E1342" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F1342" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G1342" t="s">
-        <v>281</v>
+        <v>648</v>
       </c>
       <c r="H1342" t="s">
-        <v>449</v>
+        <v>309</v>
       </c>
       <c r="I1342" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1342" t="s">
         <v>19</v>
       </c>
       <c r="K1342" t="s">
-        <v>281</v>
+        <v>648</v>
       </c>
       <c r="L1342">
         <v>0</v>
@@ -66045,7 +66213,7 @@
         <v>46283</v>
       </c>
       <c r="B1343" t="s">
-        <v>529</v>
+        <v>708</v>
       </c>
       <c r="C1343">
         <v>4</v>
@@ -66057,13 +66225,13 @@
         <v>0</v>
       </c>
       <c r="F1343" t="s">
-        <v>918</v>
+        <v>303</v>
       </c>
       <c r="G1343" t="s">
+        <v>258</v>
+      </c>
+      <c r="H1343" t="s">
         <v>321</v>
-      </c>
-      <c r="H1343" t="s">
-        <v>1467</v>
       </c>
       <c r="I1343" t="s">
         <v>23</v>
@@ -66072,7 +66240,7 @@
         <v>19</v>
       </c>
       <c r="K1343" t="s">
-        <v>321</v>
+        <v>258</v>
       </c>
       <c r="L1343">
         <v>0</v>
@@ -66089,25 +66257,25 @@
         <v>46283</v>
       </c>
       <c r="B1344" t="s">
-        <v>195</v>
+        <v>315</v>
       </c>
       <c r="C1344">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1344">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E1344" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1344" t="s">
-        <v>2176</v>
+        <v>2193</v>
       </c>
       <c r="G1344" t="s">
-        <v>473</v>
+        <v>1205</v>
       </c>
       <c r="H1344" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="I1344" t="s">
         <v>23</v>
@@ -66116,7 +66284,7 @@
         <v>19</v>
       </c>
       <c r="K1344" t="s">
-        <v>473</v>
+        <v>1205</v>
       </c>
       <c r="L1344">
         <v>0</v>
@@ -66133,10 +66301,10 @@
         <v>46283</v>
       </c>
       <c r="B1345" t="s">
-        <v>61</v>
+        <v>156</v>
       </c>
       <c r="C1345">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1345">
         <v>0</v>
@@ -66145,13 +66313,13 @@
         <v>0</v>
       </c>
       <c r="F1345" t="s">
-        <v>254</v>
+        <v>208</v>
       </c>
       <c r="G1345" t="s">
-        <v>803</v>
+        <v>153</v>
       </c>
       <c r="H1345" t="s">
-        <v>541</v>
+        <v>449</v>
       </c>
       <c r="I1345" t="s">
         <v>28</v>
@@ -66160,7 +66328,7 @@
         <v>19</v>
       </c>
       <c r="K1345" t="s">
-        <v>803</v>
+        <v>153</v>
       </c>
       <c r="L1345">
         <v>0</v>
@@ -66177,25 +66345,25 @@
         <v>46283</v>
       </c>
       <c r="B1346" t="s">
-        <v>289</v>
+        <v>529</v>
       </c>
       <c r="C1346">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1346">
-        <v>1</v>
-      </c>
-      <c r="E1346" s="3">
-        <v>0.3333333</v>
+        <v>0</v>
+      </c>
+      <c r="E1346" s="4">
+        <v>0</v>
       </c>
       <c r="F1346" t="s">
-        <v>276</v>
+        <v>918</v>
       </c>
       <c r="G1346" t="s">
-        <v>492</v>
+        <v>321</v>
       </c>
       <c r="H1346" t="s">
-        <v>499</v>
+        <v>1467</v>
       </c>
       <c r="I1346" t="s">
         <v>23</v>
@@ -66204,7 +66372,7 @@
         <v>19</v>
       </c>
       <c r="K1346" t="s">
-        <v>492</v>
+        <v>321</v>
       </c>
       <c r="L1346">
         <v>0</v>
@@ -66221,25 +66389,25 @@
         <v>46283</v>
       </c>
       <c r="B1347" t="s">
-        <v>198</v>
+        <v>61</v>
       </c>
       <c r="C1347">
         <v>3</v>
       </c>
       <c r="D1347">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1347" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1347" t="s">
-        <v>474</v>
+        <v>254</v>
       </c>
       <c r="G1347" t="s">
-        <v>196</v>
+        <v>803</v>
       </c>
       <c r="H1347" t="s">
-        <v>637</v>
+        <v>541</v>
       </c>
       <c r="I1347" t="s">
         <v>28</v>
@@ -66248,7 +66416,7 @@
         <v>19</v>
       </c>
       <c r="K1347" t="s">
-        <v>196</v>
+        <v>803</v>
       </c>
       <c r="L1347">
         <v>0</v>
@@ -66265,34 +66433,34 @@
         <v>46283</v>
       </c>
       <c r="B1348" t="s">
-        <v>512</v>
+        <v>195</v>
       </c>
       <c r="C1348">
         <v>3</v>
       </c>
       <c r="D1348">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1348" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1348" t="s">
-        <v>513</v>
+        <v>2117</v>
       </c>
       <c r="G1348" t="s">
-        <v>514</v>
+        <v>473</v>
       </c>
       <c r="H1348" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="I1348" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1348" t="s">
         <v>19</v>
       </c>
       <c r="K1348" t="s">
-        <v>514</v>
+        <v>473</v>
       </c>
       <c r="L1348">
         <v>0</v>
@@ -66309,25 +66477,25 @@
         <v>46283</v>
       </c>
       <c r="B1349" t="s">
-        <v>517</v>
+        <v>289</v>
       </c>
       <c r="C1349">
         <v>3</v>
       </c>
       <c r="D1349">
-        <v>0</v>
-      </c>
-      <c r="E1349" s="4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E1349" s="3">
+        <v>0.3333333</v>
       </c>
       <c r="F1349" t="s">
-        <v>507</v>
+        <v>276</v>
       </c>
       <c r="G1349" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="H1349" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="I1349" t="s">
         <v>23</v>
@@ -66336,7 +66504,7 @@
         <v>19</v>
       </c>
       <c r="K1349" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="L1349">
         <v>0</v>
@@ -66353,7 +66521,7 @@
         <v>46283</v>
       </c>
       <c r="B1350" t="s">
-        <v>315</v>
+        <v>512</v>
       </c>
       <c r="C1350">
         <v>3</v>
@@ -66365,22 +66533,22 @@
         <v>1</v>
       </c>
       <c r="F1350" t="s">
-        <v>799</v>
+        <v>513</v>
       </c>
       <c r="G1350" t="s">
-        <v>327</v>
+        <v>514</v>
       </c>
       <c r="H1350" t="s">
-        <v>698</v>
+        <v>284</v>
       </c>
       <c r="I1350" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1350" t="s">
         <v>19</v>
       </c>
       <c r="K1350" t="s">
-        <v>327</v>
+        <v>514</v>
       </c>
       <c r="L1350">
         <v>0</v>
@@ -66397,34 +66565,34 @@
         <v>46283</v>
       </c>
       <c r="B1351" t="s">
-        <v>695</v>
+        <v>517</v>
       </c>
       <c r="C1351">
         <v>3</v>
       </c>
       <c r="D1351">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1351" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1351" t="s">
-        <v>284</v>
+        <v>507</v>
       </c>
       <c r="G1351" t="s">
-        <v>205</v>
+        <v>518</v>
       </c>
       <c r="H1351" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="I1351" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1351" t="s">
         <v>19</v>
       </c>
       <c r="K1351" t="s">
-        <v>205</v>
+        <v>518</v>
       </c>
       <c r="L1351">
         <v>0</v>
@@ -66441,34 +66609,34 @@
         <v>46283</v>
       </c>
       <c r="B1352" t="s">
-        <v>531</v>
+        <v>695</v>
       </c>
       <c r="C1352">
         <v>3</v>
       </c>
       <c r="D1352">
-        <v>2</v>
-      </c>
-      <c r="E1352" s="3">
-        <v>0.66666669999999995</v>
+        <v>3</v>
+      </c>
+      <c r="E1352" s="4">
+        <v>1</v>
       </c>
       <c r="F1352" t="s">
-        <v>532</v>
+        <v>284</v>
       </c>
       <c r="G1352" t="s">
-        <v>514</v>
+        <v>205</v>
       </c>
       <c r="H1352" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="I1352" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1352" t="s">
         <v>19</v>
       </c>
       <c r="K1352" t="s">
-        <v>514</v>
+        <v>205</v>
       </c>
       <c r="L1352">
         <v>0</v>
@@ -66485,25 +66653,25 @@
         <v>46283</v>
       </c>
       <c r="B1353" t="s">
-        <v>53</v>
+        <v>531</v>
       </c>
       <c r="C1353">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1353">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1353" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1353" t="s">
-        <v>1818</v>
+        <v>532</v>
       </c>
       <c r="G1353" t="s">
-        <v>472</v>
+        <v>514</v>
       </c>
       <c r="H1353" t="s">
-        <v>248</v>
+        <v>533</v>
       </c>
       <c r="I1353" t="s">
         <v>18</v>
@@ -66512,7 +66680,7 @@
         <v>19</v>
       </c>
       <c r="K1353" t="s">
-        <v>472</v>
+        <v>514</v>
       </c>
       <c r="L1353">
         <v>0</v>
@@ -66529,25 +66697,25 @@
         <v>46283</v>
       </c>
       <c r="B1354" t="s">
-        <v>2177</v>
+        <v>2194</v>
       </c>
       <c r="C1354">
         <v>2</v>
       </c>
       <c r="D1354">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1354" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1354" t="s">
-        <v>293</v>
+        <v>545</v>
       </c>
       <c r="G1354" t="s">
-        <v>312</v>
+        <v>637</v>
       </c>
       <c r="H1354" t="s">
-        <v>474</v>
+        <v>528</v>
       </c>
       <c r="I1354" t="s">
         <v>23</v>
@@ -66556,7 +66724,7 @@
         <v>19</v>
       </c>
       <c r="K1354" t="s">
-        <v>312</v>
+        <v>637</v>
       </c>
       <c r="L1354">
         <v>0</v>
@@ -66573,34 +66741,34 @@
         <v>46283</v>
       </c>
       <c r="B1355" t="s">
-        <v>847</v>
+        <v>53</v>
       </c>
       <c r="C1355">
         <v>2</v>
       </c>
       <c r="D1355">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1355" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1355" t="s">
-        <v>202</v>
+        <v>1818</v>
       </c>
       <c r="G1355" t="s">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="H1355" t="s">
-        <v>504</v>
+        <v>248</v>
       </c>
       <c r="I1355" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1355" t="s">
         <v>19</v>
       </c>
       <c r="K1355" t="s">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="L1355">
         <v>0</v>
@@ -66617,25 +66785,25 @@
         <v>46283</v>
       </c>
       <c r="B1356" t="s">
-        <v>1115</v>
+        <v>1232</v>
       </c>
       <c r="C1356">
         <v>2</v>
       </c>
       <c r="D1356">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1356" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1356" t="s">
-        <v>248</v>
+        <v>303</v>
       </c>
       <c r="G1356" t="s">
-        <v>538</v>
+        <v>453</v>
       </c>
       <c r="H1356" t="s">
-        <v>1199</v>
+        <v>528</v>
       </c>
       <c r="I1356" t="s">
         <v>18</v>
@@ -66644,7 +66812,7 @@
         <v>19</v>
       </c>
       <c r="K1356" t="s">
-        <v>538</v>
+        <v>453</v>
       </c>
       <c r="L1356">
         <v>0</v>
@@ -66661,7 +66829,7 @@
         <v>46283</v>
       </c>
       <c r="B1357" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C1357">
         <v>2</v>
@@ -66673,13 +66841,13 @@
         <v>0</v>
       </c>
       <c r="F1357" t="s">
-        <v>838</v>
+        <v>1830</v>
       </c>
       <c r="G1357" t="s">
         <v>472</v>
       </c>
       <c r="H1357" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I1357" t="s">
         <v>23</v>
@@ -66705,7 +66873,7 @@
         <v>46283</v>
       </c>
       <c r="B1358" t="s">
-        <v>250</v>
+        <v>2118</v>
       </c>
       <c r="C1358">
         <v>2</v>
@@ -66717,13 +66885,13 @@
         <v>0</v>
       </c>
       <c r="F1358" t="s">
-        <v>1229</v>
+        <v>293</v>
       </c>
       <c r="G1358" t="s">
-        <v>1230</v>
+        <v>312</v>
       </c>
       <c r="H1358" t="s">
-        <v>231</v>
+        <v>474</v>
       </c>
       <c r="I1358" t="s">
         <v>23</v>
@@ -66732,7 +66900,7 @@
         <v>19</v>
       </c>
       <c r="K1358" t="s">
-        <v>1230</v>
+        <v>312</v>
       </c>
       <c r="L1358">
         <v>0</v>
@@ -66749,7 +66917,7 @@
         <v>46283</v>
       </c>
       <c r="B1359" t="s">
-        <v>246</v>
+        <v>847</v>
       </c>
       <c r="C1359">
         <v>2</v>
@@ -66761,22 +66929,22 @@
         <v>1</v>
       </c>
       <c r="F1359" t="s">
-        <v>1453</v>
+        <v>202</v>
       </c>
       <c r="G1359" t="s">
-        <v>701</v>
+        <v>496</v>
       </c>
       <c r="H1359" t="s">
-        <v>1467</v>
+        <v>504</v>
       </c>
       <c r="I1359" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1359" t="s">
         <v>19</v>
       </c>
       <c r="K1359" t="s">
-        <v>701</v>
+        <v>496</v>
       </c>
       <c r="L1359">
         <v>0</v>
@@ -66793,34 +66961,34 @@
         <v>46283</v>
       </c>
       <c r="B1360" t="s">
-        <v>1237</v>
+        <v>670</v>
       </c>
       <c r="C1360">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1360">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1360" s="4">
         <v>1</v>
       </c>
       <c r="F1360" t="s">
-        <v>323</v>
+        <v>545</v>
       </c>
       <c r="G1360" t="s">
-        <v>242</v>
+        <v>293</v>
       </c>
       <c r="H1360" t="s">
-        <v>2178</v>
+        <v>296</v>
       </c>
       <c r="I1360" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1360" t="s">
         <v>19</v>
       </c>
       <c r="K1360" t="s">
-        <v>242</v>
+        <v>293</v>
       </c>
       <c r="L1360">
         <v>0</v>
@@ -66837,10 +67005,10 @@
         <v>46283</v>
       </c>
       <c r="B1361" t="s">
-        <v>475</v>
+        <v>1115</v>
       </c>
       <c r="C1361">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1361">
         <v>0</v>
@@ -66849,13 +67017,13 @@
         <v>0</v>
       </c>
       <c r="F1361" t="s">
-        <v>545</v>
+        <v>248</v>
       </c>
       <c r="G1361" t="s">
-        <v>276</v>
+        <v>538</v>
       </c>
       <c r="H1361" t="s">
-        <v>208</v>
+        <v>1199</v>
       </c>
       <c r="I1361" t="s">
         <v>18</v>
@@ -66864,7 +67032,7 @@
         <v>19</v>
       </c>
       <c r="K1361" t="s">
-        <v>276</v>
+        <v>538</v>
       </c>
       <c r="L1361">
         <v>0</v>
@@ -66881,10 +67049,10 @@
         <v>46283</v>
       </c>
       <c r="B1362" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="C1362">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1362">
         <v>0</v>
@@ -66893,13 +67061,13 @@
         <v>0</v>
       </c>
       <c r="F1362" t="s">
-        <v>2179</v>
+        <v>838</v>
       </c>
       <c r="G1362" t="s">
-        <v>700</v>
+        <v>472</v>
       </c>
       <c r="H1362" t="s">
-        <v>244</v>
+        <v>539</v>
       </c>
       <c r="I1362" t="s">
         <v>23</v>
@@ -66908,7 +67076,7 @@
         <v>19</v>
       </c>
       <c r="K1362" t="s">
-        <v>700</v>
+        <v>472</v>
       </c>
       <c r="L1362">
         <v>0</v>
@@ -66925,34 +67093,34 @@
         <v>46283</v>
       </c>
       <c r="B1363" t="s">
-        <v>14</v>
+        <v>250</v>
       </c>
       <c r="C1363">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1363">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1363" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1363" t="s">
-        <v>2180</v>
+        <v>1229</v>
       </c>
       <c r="G1363" t="s">
-        <v>1350</v>
+        <v>1230</v>
       </c>
       <c r="H1363" t="s">
-        <v>303</v>
+        <v>231</v>
       </c>
       <c r="I1363" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1363" t="s">
         <v>19</v>
       </c>
       <c r="K1363" t="s">
-        <v>1350</v>
+        <v>1230</v>
       </c>
       <c r="L1363">
         <v>0</v>
@@ -66969,25 +67137,25 @@
         <v>46283</v>
       </c>
       <c r="B1364" t="s">
-        <v>1479</v>
+        <v>246</v>
       </c>
       <c r="C1364">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1364">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1364" s="4">
         <v>1</v>
       </c>
       <c r="F1364" t="s">
-        <v>286</v>
+        <v>1453</v>
       </c>
       <c r="G1364" t="s">
-        <v>254</v>
+        <v>701</v>
       </c>
       <c r="H1364" t="s">
-        <v>474</v>
+        <v>1467</v>
       </c>
       <c r="I1364" t="s">
         <v>23</v>
@@ -66996,7 +67164,7 @@
         <v>19</v>
       </c>
       <c r="K1364" t="s">
-        <v>254</v>
+        <v>701</v>
       </c>
       <c r="L1364">
         <v>0</v>
@@ -67013,7 +67181,7 @@
         <v>46283</v>
       </c>
       <c r="B1365" t="s">
-        <v>1585</v>
+        <v>1237</v>
       </c>
       <c r="C1365">
         <v>1</v>
@@ -67025,22 +67193,22 @@
         <v>1</v>
       </c>
       <c r="F1365" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="G1365" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="H1365" t="s">
-        <v>196</v>
+        <v>2119</v>
       </c>
       <c r="I1365" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1365" t="s">
         <v>19</v>
       </c>
       <c r="K1365" t="s">
-        <v>276</v>
+        <v>242</v>
       </c>
       <c r="L1365">
         <v>0</v>
@@ -67057,25 +67225,25 @@
         <v>46283</v>
       </c>
       <c r="B1366" t="s">
-        <v>670</v>
+        <v>475</v>
       </c>
       <c r="C1366">
         <v>1</v>
       </c>
       <c r="D1366">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1366" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1366" t="s">
-        <v>286</v>
+        <v>545</v>
       </c>
       <c r="G1366" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="H1366" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="I1366" t="s">
         <v>18</v>
@@ -67084,7 +67252,7 @@
         <v>19</v>
       </c>
       <c r="K1366" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="L1366">
         <v>0</v>
@@ -67101,7 +67269,7 @@
         <v>46283</v>
       </c>
       <c r="B1367" t="s">
-        <v>525</v>
+        <v>14</v>
       </c>
       <c r="C1367">
         <v>1</v>
@@ -67113,22 +67281,22 @@
         <v>1</v>
       </c>
       <c r="F1367" t="s">
-        <v>699</v>
+        <v>2120</v>
       </c>
       <c r="G1367" t="s">
-        <v>700</v>
+        <v>1350</v>
       </c>
       <c r="H1367" t="s">
-        <v>701</v>
+        <v>303</v>
       </c>
       <c r="I1367" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1367" t="s">
         <v>19</v>
       </c>
       <c r="K1367" t="s">
-        <v>700</v>
+        <v>1350</v>
       </c>
       <c r="L1367">
         <v>0</v>
@@ -67145,34 +67313,34 @@
         <v>46283</v>
       </c>
       <c r="B1368" t="s">
-        <v>1587</v>
+        <v>1479</v>
       </c>
       <c r="C1368">
         <v>1</v>
       </c>
       <c r="D1368">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1368" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1368" t="s">
         <v>286</v>
       </c>
       <c r="G1368" t="s">
-        <v>293</v>
+        <v>254</v>
       </c>
       <c r="H1368" t="s">
-        <v>303</v>
+        <v>474</v>
       </c>
       <c r="I1368" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1368" t="s">
         <v>19</v>
       </c>
       <c r="K1368" t="s">
-        <v>293</v>
+        <v>254</v>
       </c>
       <c r="L1368">
         <v>0</v>
@@ -67189,34 +67357,34 @@
         <v>46283</v>
       </c>
       <c r="B1369" t="s">
-        <v>226</v>
+        <v>1585</v>
       </c>
       <c r="C1369">
         <v>1</v>
       </c>
       <c r="D1369">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1369" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1369" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="G1369" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1369" t="s">
-        <v>232</v>
+        <v>196</v>
       </c>
       <c r="I1369" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1369" t="s">
         <v>19</v>
       </c>
       <c r="K1369" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L1369">
         <v>0</v>
@@ -67233,7 +67401,7 @@
         <v>46283</v>
       </c>
       <c r="B1370" t="s">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="C1370">
         <v>1</v>
@@ -67245,13 +67413,13 @@
         <v>1</v>
       </c>
       <c r="F1370" t="s">
-        <v>296</v>
+        <v>699</v>
       </c>
       <c r="G1370" t="s">
-        <v>244</v>
+        <v>700</v>
       </c>
       <c r="H1370" t="s">
-        <v>298</v>
+        <v>701</v>
       </c>
       <c r="I1370" t="s">
         <v>28</v>
@@ -67260,7 +67428,7 @@
         <v>19</v>
       </c>
       <c r="K1370" t="s">
-        <v>244</v>
+        <v>700</v>
       </c>
       <c r="L1370">
         <v>0</v>
@@ -67277,25 +67445,25 @@
         <v>46283</v>
       </c>
       <c r="B1371" t="s">
-        <v>33</v>
+        <v>1587</v>
       </c>
       <c r="C1371">
         <v>1</v>
       </c>
       <c r="D1371">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1371" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1371" t="s">
-        <v>684</v>
+        <v>286</v>
       </c>
       <c r="G1371" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="H1371" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="I1371" t="s">
         <v>18</v>
@@ -67304,7 +67472,7 @@
         <v>19</v>
       </c>
       <c r="K1371" t="s">
-        <v>324</v>
+        <v>293</v>
       </c>
       <c r="L1371">
         <v>0</v>
@@ -67321,7 +67489,7 @@
         <v>46283</v>
       </c>
       <c r="B1372" t="s">
-        <v>2106</v>
+        <v>226</v>
       </c>
       <c r="C1372">
         <v>1</v>
@@ -67333,13 +67501,13 @@
         <v>0</v>
       </c>
       <c r="F1372" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="G1372" t="s">
-        <v>698</v>
+        <v>277</v>
       </c>
       <c r="H1372" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="I1372" t="s">
         <v>23</v>
@@ -67348,7 +67516,7 @@
         <v>19</v>
       </c>
       <c r="K1372" t="s">
-        <v>698</v>
+        <v>277</v>
       </c>
       <c r="L1372">
         <v>0</v>
@@ -67365,42 +67533,2374 @@
         <v>46283</v>
       </c>
       <c r="B1373" t="s">
+        <v>544</v>
+      </c>
+      <c r="C1373">
+        <v>1</v>
+      </c>
+      <c r="D1373">
+        <v>1</v>
+      </c>
+      <c r="E1373" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1373" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1373" t="s">
+        <v>244</v>
+      </c>
+      <c r="H1373" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1373" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1373" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1373" t="s">
+        <v>244</v>
+      </c>
+      <c r="L1373">
+        <v>0</v>
+      </c>
+      <c r="M1373" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:14">
+      <c r="A1374" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1374">
+        <v>1</v>
+      </c>
+      <c r="D1374">
+        <v>1</v>
+      </c>
+      <c r="E1374" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1374" t="s">
+        <v>684</v>
+      </c>
+      <c r="G1374" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1374" t="s">
+        <v>258</v>
+      </c>
+      <c r="I1374" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1374" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1374" t="s">
+        <v>324</v>
+      </c>
+      <c r="L1374">
+        <v>0</v>
+      </c>
+      <c r="M1374" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:14">
+      <c r="A1375" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C1375">
+        <v>1</v>
+      </c>
+      <c r="D1375">
+        <v>0</v>
+      </c>
+      <c r="E1375" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1375" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1375" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1375" t="s">
+        <v>258</v>
+      </c>
+      <c r="I1375" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1375" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1375" t="s">
+        <v>698</v>
+      </c>
+      <c r="L1375">
+        <v>0</v>
+      </c>
+      <c r="M1375" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:14">
+      <c r="A1376" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B1376" t="s">
         <v>1941</v>
       </c>
-      <c r="C1373">
-        <v>1</v>
-      </c>
-      <c r="D1373">
-        <v>0</v>
-      </c>
-      <c r="E1373" s="4">
-        <v>0</v>
-      </c>
-      <c r="F1373" t="s">
+      <c r="C1376">
+        <v>1</v>
+      </c>
+      <c r="D1376">
+        <v>0</v>
+      </c>
+      <c r="E1376" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1376" t="s">
         <v>279</v>
       </c>
-      <c r="G1373" t="s">
-        <v>2181</v>
-      </c>
-      <c r="H1373" t="s">
+      <c r="G1376" t="s">
+        <v>2121</v>
+      </c>
+      <c r="H1376" t="s">
         <v>208</v>
       </c>
-      <c r="I1373" t="s">
+      <c r="I1376" t="s">
         <v>18</v>
       </c>
-      <c r="J1373" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1373" t="s">
-        <v>2181</v>
-      </c>
-      <c r="L1373">
-        <v>0</v>
-      </c>
-      <c r="M1373" s="4">
-        <v>0</v>
-      </c>
-      <c r="N1373">
+      <c r="J1376" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1376" t="s">
+        <v>2121</v>
+      </c>
+      <c r="L1376">
+        <v>0</v>
+      </c>
+      <c r="M1376" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:14">
+      <c r="A1377" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1377">
+        <v>2209</v>
+      </c>
+      <c r="D1377">
+        <v>2097</v>
+      </c>
+      <c r="E1377" s="3">
+        <v>0.94929830000000004</v>
+      </c>
+      <c r="F1377" t="s">
+        <v>2195</v>
+      </c>
+      <c r="G1377" t="s">
+        <v>2196</v>
+      </c>
+      <c r="H1377" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1377" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1377" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1377" t="s">
+        <v>2196</v>
+      </c>
+      <c r="L1377">
+        <v>0</v>
+      </c>
+      <c r="M1377" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:14">
+      <c r="A1378" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1378">
+        <v>291</v>
+      </c>
+      <c r="D1378">
+        <v>227</v>
+      </c>
+      <c r="E1378" s="3">
+        <v>0.78006869999999995</v>
+      </c>
+      <c r="F1378" t="s">
+        <v>2198</v>
+      </c>
+      <c r="G1378" t="s">
+        <v>2199</v>
+      </c>
+      <c r="H1378" t="s">
+        <v>2200</v>
+      </c>
+      <c r="I1378" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1378" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1378" t="s">
+        <v>2199</v>
+      </c>
+      <c r="L1378">
+        <v>0</v>
+      </c>
+      <c r="M1378" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:14">
+      <c r="A1379" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1379">
+        <v>252</v>
+      </c>
+      <c r="D1379">
+        <v>251</v>
+      </c>
+      <c r="E1379" s="3">
+        <v>0.99603169999999996</v>
+      </c>
+      <c r="F1379" t="s">
+        <v>416</v>
+      </c>
+      <c r="G1379" t="s">
+        <v>2201</v>
+      </c>
+      <c r="H1379" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I1379" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1379" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1379" t="s">
+        <v>2201</v>
+      </c>
+      <c r="L1379">
+        <v>0</v>
+      </c>
+      <c r="M1379" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:14">
+      <c r="A1380" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1380">
+        <v>82</v>
+      </c>
+      <c r="D1380">
+        <v>77</v>
+      </c>
+      <c r="E1380" s="3">
+        <v>0.93902439999999998</v>
+      </c>
+      <c r="F1380" t="s">
+        <v>2202</v>
+      </c>
+      <c r="G1380" t="s">
+        <v>2203</v>
+      </c>
+      <c r="H1380" t="s">
+        <v>2204</v>
+      </c>
+      <c r="I1380" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1380" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1380" t="s">
+        <v>2203</v>
+      </c>
+      <c r="L1380">
+        <v>0</v>
+      </c>
+      <c r="M1380" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:14">
+      <c r="A1381" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1381">
+        <v>74</v>
+      </c>
+      <c r="D1381">
+        <v>66</v>
+      </c>
+      <c r="E1381" s="3">
+        <v>0.89189189999999996</v>
+      </c>
+      <c r="F1381" t="s">
+        <v>2205</v>
+      </c>
+      <c r="G1381" t="s">
+        <v>2206</v>
+      </c>
+      <c r="H1381" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I1381" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1381" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1381" t="s">
+        <v>2206</v>
+      </c>
+      <c r="L1381">
+        <v>0</v>
+      </c>
+      <c r="M1381" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:14">
+      <c r="A1382" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1382">
+        <v>43</v>
+      </c>
+      <c r="D1382">
+        <v>43</v>
+      </c>
+      <c r="E1382" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1382" t="s">
+        <v>2208</v>
+      </c>
+      <c r="G1382" t="s">
+        <v>2209</v>
+      </c>
+      <c r="H1382" t="s">
+        <v>2210</v>
+      </c>
+      <c r="I1382" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1382" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1382" t="s">
+        <v>2209</v>
+      </c>
+      <c r="L1382">
+        <v>0</v>
+      </c>
+      <c r="M1382" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:14">
+      <c r="A1383" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1383">
+        <v>35</v>
+      </c>
+      <c r="D1383">
+        <v>28</v>
+      </c>
+      <c r="E1383" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="F1383" t="s">
+        <v>2211</v>
+      </c>
+      <c r="G1383" t="s">
+        <v>667</v>
+      </c>
+      <c r="H1383" t="s">
+        <v>535</v>
+      </c>
+      <c r="I1383" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1383" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1383" t="s">
+        <v>667</v>
+      </c>
+      <c r="L1383">
+        <v>0</v>
+      </c>
+      <c r="M1383" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:14">
+      <c r="A1384" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1384">
+        <v>31</v>
+      </c>
+      <c r="D1384">
+        <v>25</v>
+      </c>
+      <c r="E1384" s="3">
+        <v>0.80645160000000005</v>
+      </c>
+      <c r="F1384" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1384" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1384" t="s">
+        <v>253</v>
+      </c>
+      <c r="I1384" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1384" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1384" t="s">
+        <v>157</v>
+      </c>
+      <c r="L1384">
+        <v>0</v>
+      </c>
+      <c r="M1384" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:14">
+      <c r="A1385" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1385">
+        <v>30</v>
+      </c>
+      <c r="D1385">
+        <v>28</v>
+      </c>
+      <c r="E1385" s="3">
+        <v>0.93333330000000003</v>
+      </c>
+      <c r="F1385" t="s">
+        <v>458</v>
+      </c>
+      <c r="G1385" t="s">
+        <v>2212</v>
+      </c>
+      <c r="H1385" t="s">
+        <v>1648</v>
+      </c>
+      <c r="I1385" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1385" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1385" t="s">
+        <v>2212</v>
+      </c>
+      <c r="L1385">
+        <v>0</v>
+      </c>
+      <c r="M1385" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:14">
+      <c r="A1386" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1386">
+        <v>26</v>
+      </c>
+      <c r="D1386">
+        <v>23</v>
+      </c>
+      <c r="E1386" s="3">
+        <v>0.88461540000000005</v>
+      </c>
+      <c r="F1386" t="s">
+        <v>2213</v>
+      </c>
+      <c r="G1386" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H1386" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I1386" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1386" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1386" t="s">
+        <v>1554</v>
+      </c>
+      <c r="L1386">
+        <v>0</v>
+      </c>
+      <c r="M1386" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:14">
+      <c r="A1387" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1387">
+        <v>25</v>
+      </c>
+      <c r="D1387">
+        <v>22</v>
+      </c>
+      <c r="E1387" s="4">
+        <v>0.88</v>
+      </c>
+      <c r="F1387" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1387" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1387" t="s">
+        <v>143</v>
+      </c>
+      <c r="I1387" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1387" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1387" t="s">
+        <v>142</v>
+      </c>
+      <c r="L1387">
+        <v>0</v>
+      </c>
+      <c r="M1387" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:14">
+      <c r="A1388" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1388">
+        <v>23</v>
+      </c>
+      <c r="D1388">
+        <v>0</v>
+      </c>
+      <c r="E1388" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1388" t="s">
+        <v>2214</v>
+      </c>
+      <c r="G1388" t="s">
+        <v>2215</v>
+      </c>
+      <c r="H1388" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I1388" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1388" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1388" t="s">
+        <v>2215</v>
+      </c>
+      <c r="L1388">
+        <v>0</v>
+      </c>
+      <c r="M1388" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:14">
+      <c r="A1389" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1389">
+        <v>22</v>
+      </c>
+      <c r="D1389">
+        <v>0</v>
+      </c>
+      <c r="E1389" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1389" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G1389" t="s">
+        <v>483</v>
+      </c>
+      <c r="H1389" t="s">
+        <v>1635</v>
+      </c>
+      <c r="I1389" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1389" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1389" t="s">
+        <v>483</v>
+      </c>
+      <c r="L1389">
+        <v>0</v>
+      </c>
+      <c r="M1389" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:14">
+      <c r="A1390" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1390">
+        <v>21</v>
+      </c>
+      <c r="D1390">
+        <v>18</v>
+      </c>
+      <c r="E1390" s="3">
+        <v>0.85714290000000004</v>
+      </c>
+      <c r="F1390" t="s">
+        <v>2217</v>
+      </c>
+      <c r="G1390" t="s">
+        <v>2218</v>
+      </c>
+      <c r="H1390" t="s">
+        <v>255</v>
+      </c>
+      <c r="I1390" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1390" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1390" t="s">
+        <v>2218</v>
+      </c>
+      <c r="L1390">
+        <v>0</v>
+      </c>
+      <c r="M1390" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:14">
+      <c r="A1391" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1391">
+        <v>18</v>
+      </c>
+      <c r="D1391">
+        <v>0</v>
+      </c>
+      <c r="E1391" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1391" t="s">
+        <v>2219</v>
+      </c>
+      <c r="G1391" t="s">
+        <v>2220</v>
+      </c>
+      <c r="H1391" t="s">
+        <v>2221</v>
+      </c>
+      <c r="I1391" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1391" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1391" t="s">
+        <v>2220</v>
+      </c>
+      <c r="L1391">
+        <v>0</v>
+      </c>
+      <c r="M1391" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:14">
+      <c r="A1392" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1392">
+        <v>13</v>
+      </c>
+      <c r="D1392">
+        <v>10</v>
+      </c>
+      <c r="E1392" s="3">
+        <v>0.76923079999999999</v>
+      </c>
+      <c r="F1392" t="s">
+        <v>2222</v>
+      </c>
+      <c r="G1392" t="s">
+        <v>262</v>
+      </c>
+      <c r="H1392" t="s">
+        <v>1919</v>
+      </c>
+      <c r="I1392" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1392" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1392" t="s">
+        <v>262</v>
+      </c>
+      <c r="L1392">
+        <v>0</v>
+      </c>
+      <c r="M1392" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:14">
+      <c r="A1393" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1393">
+        <v>13</v>
+      </c>
+      <c r="D1393">
+        <v>13</v>
+      </c>
+      <c r="E1393" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1393" t="s">
+        <v>805</v>
+      </c>
+      <c r="G1393" t="s">
+        <v>2223</v>
+      </c>
+      <c r="H1393" t="s">
+        <v>2224</v>
+      </c>
+      <c r="I1393" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1393" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1393" t="s">
+        <v>2223</v>
+      </c>
+      <c r="L1393">
+        <v>0</v>
+      </c>
+      <c r="M1393" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:14">
+      <c r="A1394" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1394">
+        <v>12</v>
+      </c>
+      <c r="D1394">
+        <v>11</v>
+      </c>
+      <c r="E1394" s="3">
+        <v>0.91666669999999995</v>
+      </c>
+      <c r="F1394" t="s">
+        <v>1554</v>
+      </c>
+      <c r="G1394" t="s">
+        <v>797</v>
+      </c>
+      <c r="H1394" t="s">
+        <v>1555</v>
+      </c>
+      <c r="I1394" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1394" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1394" t="s">
+        <v>797</v>
+      </c>
+      <c r="L1394">
+        <v>0</v>
+      </c>
+      <c r="M1394" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:14">
+      <c r="A1395" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1395">
+        <v>8</v>
+      </c>
+      <c r="D1395">
+        <v>8</v>
+      </c>
+      <c r="E1395" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1395" t="s">
+        <v>239</v>
+      </c>
+      <c r="G1395" t="s">
+        <v>2225</v>
+      </c>
+      <c r="H1395" t="s">
+        <v>2226</v>
+      </c>
+      <c r="I1395" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1395" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1395" t="s">
+        <v>2225</v>
+      </c>
+      <c r="L1395">
+        <v>0</v>
+      </c>
+      <c r="M1395" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:14">
+      <c r="A1396" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1396">
+        <v>8</v>
+      </c>
+      <c r="D1396">
+        <v>4</v>
+      </c>
+      <c r="E1396" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1396" t="s">
+        <v>804</v>
+      </c>
+      <c r="G1396" t="s">
+        <v>1542</v>
+      </c>
+      <c r="H1396" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I1396" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1396" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1396" t="s">
+        <v>1542</v>
+      </c>
+      <c r="L1396">
+        <v>0</v>
+      </c>
+      <c r="M1396" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:14">
+      <c r="A1397" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1397">
+        <v>8</v>
+      </c>
+      <c r="D1397">
+        <v>8</v>
+      </c>
+      <c r="E1397" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1397" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1397" t="s">
+        <v>2227</v>
+      </c>
+      <c r="H1397" t="s">
+        <v>804</v>
+      </c>
+      <c r="I1397" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1397" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1397" t="s">
+        <v>2227</v>
+      </c>
+      <c r="L1397">
+        <v>0</v>
+      </c>
+      <c r="M1397" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:14">
+      <c r="A1398" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1398">
+        <v>7</v>
+      </c>
+      <c r="D1398">
+        <v>5</v>
+      </c>
+      <c r="E1398" s="3">
+        <v>0.71428570000000002</v>
+      </c>
+      <c r="F1398" t="s">
+        <v>284</v>
+      </c>
+      <c r="G1398" t="s">
+        <v>2116</v>
+      </c>
+      <c r="H1398" t="s">
+        <v>442</v>
+      </c>
+      <c r="I1398" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1398" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1398" t="s">
+        <v>2116</v>
+      </c>
+      <c r="L1398">
+        <v>0</v>
+      </c>
+      <c r="M1398" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:14">
+      <c r="A1399" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1399">
+        <v>7</v>
+      </c>
+      <c r="D1399">
+        <v>0</v>
+      </c>
+      <c r="E1399" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1399" t="s">
+        <v>212</v>
+      </c>
+      <c r="G1399" t="s">
+        <v>2228</v>
+      </c>
+      <c r="H1399" t="s">
+        <v>1044</v>
+      </c>
+      <c r="I1399" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1399" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1399" t="s">
+        <v>2228</v>
+      </c>
+      <c r="L1399">
+        <v>0</v>
+      </c>
+      <c r="M1399" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:14">
+      <c r="A1400" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1400">
+        <v>6</v>
+      </c>
+      <c r="D1400">
+        <v>3</v>
+      </c>
+      <c r="E1400" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1400" t="s">
+        <v>408</v>
+      </c>
+      <c r="G1400" t="s">
+        <v>256</v>
+      </c>
+      <c r="H1400" t="s">
+        <v>540</v>
+      </c>
+      <c r="I1400" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1400" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1400" t="s">
+        <v>256</v>
+      </c>
+      <c r="L1400">
+        <v>0</v>
+      </c>
+      <c r="M1400" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:14">
+      <c r="A1401" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1401">
+        <v>6</v>
+      </c>
+      <c r="D1401">
+        <v>5</v>
+      </c>
+      <c r="E1401" s="3">
+        <v>0.83333330000000005</v>
+      </c>
+      <c r="F1401" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G1401" t="s">
+        <v>1818</v>
+      </c>
+      <c r="H1401" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I1401" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1401" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1401" t="s">
+        <v>1818</v>
+      </c>
+      <c r="L1401">
+        <v>0</v>
+      </c>
+      <c r="M1401" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:14">
+      <c r="A1402" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1402">
+        <v>6</v>
+      </c>
+      <c r="D1402">
+        <v>6</v>
+      </c>
+      <c r="E1402" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1402" t="s">
+        <v>453</v>
+      </c>
+      <c r="G1402" t="s">
+        <v>2231</v>
+      </c>
+      <c r="H1402" t="s">
+        <v>219</v>
+      </c>
+      <c r="I1402" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1402" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1402" t="s">
+        <v>2231</v>
+      </c>
+      <c r="L1402">
+        <v>0</v>
+      </c>
+      <c r="M1402" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:14">
+      <c r="A1403" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>660</v>
+      </c>
+      <c r="C1403">
+        <v>5</v>
+      </c>
+      <c r="D1403">
+        <v>4</v>
+      </c>
+      <c r="E1403" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="F1403" t="s">
+        <v>294</v>
+      </c>
+      <c r="G1403" t="s">
+        <v>283</v>
+      </c>
+      <c r="H1403" t="s">
+        <v>671</v>
+      </c>
+      <c r="I1403" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1403" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1403" t="s">
+        <v>283</v>
+      </c>
+      <c r="L1403">
+        <v>0</v>
+      </c>
+      <c r="M1403" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:14">
+      <c r="A1404" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1404">
+        <v>4</v>
+      </c>
+      <c r="D1404">
+        <v>4</v>
+      </c>
+      <c r="E1404" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1404" t="s">
+        <v>507</v>
+      </c>
+      <c r="G1404" t="s">
+        <v>284</v>
+      </c>
+      <c r="H1404" t="s">
+        <v>518</v>
+      </c>
+      <c r="I1404" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1404" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1404" t="s">
+        <v>284</v>
+      </c>
+      <c r="L1404">
+        <v>0</v>
+      </c>
+      <c r="M1404" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:14">
+      <c r="A1405" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1405">
+        <v>4</v>
+      </c>
+      <c r="D1405">
+        <v>1</v>
+      </c>
+      <c r="E1405" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="F1405" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G1405" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1405" t="s">
+        <v>199</v>
+      </c>
+      <c r="I1405" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1405" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1405" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1405">
+        <v>0</v>
+      </c>
+      <c r="M1405" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:14">
+      <c r="A1406" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1406">
+        <v>4</v>
+      </c>
+      <c r="D1406">
+        <v>0</v>
+      </c>
+      <c r="E1406" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1406" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G1406" t="s">
+        <v>1342</v>
+      </c>
+      <c r="H1406" t="s">
+        <v>509</v>
+      </c>
+      <c r="I1406" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1406" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1406" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L1406">
+        <v>0</v>
+      </c>
+      <c r="M1406" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:14">
+      <c r="A1407" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1407">
+        <v>4</v>
+      </c>
+      <c r="D1407">
+        <v>3</v>
+      </c>
+      <c r="E1407" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F1407" t="s">
+        <v>1827</v>
+      </c>
+      <c r="G1407" t="s">
+        <v>680</v>
+      </c>
+      <c r="H1407" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1407" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1407" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1407" t="s">
+        <v>680</v>
+      </c>
+      <c r="L1407">
+        <v>0</v>
+      </c>
+      <c r="M1407" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:14">
+      <c r="A1408" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1408">
+        <v>3</v>
+      </c>
+      <c r="D1408">
+        <v>0</v>
+      </c>
+      <c r="E1408" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1408" t="s">
+        <v>2117</v>
+      </c>
+      <c r="G1408" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1408" t="s">
+        <v>260</v>
+      </c>
+      <c r="I1408" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1408" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1408" t="s">
+        <v>473</v>
+      </c>
+      <c r="L1408">
+        <v>0</v>
+      </c>
+      <c r="M1408" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:14">
+      <c r="A1409" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1409">
+        <v>3</v>
+      </c>
+      <c r="D1409">
+        <v>0</v>
+      </c>
+      <c r="E1409" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1409" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G1409" t="s">
+        <v>2234</v>
+      </c>
+      <c r="H1409" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1409" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1409" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1409" t="s">
+        <v>2234</v>
+      </c>
+      <c r="L1409">
+        <v>0</v>
+      </c>
+      <c r="M1409" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:14">
+      <c r="A1410" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1410">
+        <v>3</v>
+      </c>
+      <c r="D1410">
+        <v>3</v>
+      </c>
+      <c r="E1410" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1410" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1410" t="s">
+        <v>514</v>
+      </c>
+      <c r="H1410" t="s">
+        <v>284</v>
+      </c>
+      <c r="I1410" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1410" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1410" t="s">
+        <v>514</v>
+      </c>
+      <c r="L1410">
+        <v>0</v>
+      </c>
+      <c r="M1410" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:14">
+      <c r="A1411" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1411">
+        <v>2</v>
+      </c>
+      <c r="D1411">
+        <v>2</v>
+      </c>
+      <c r="E1411" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1411" t="s">
+        <v>284</v>
+      </c>
+      <c r="G1411" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1411" t="s">
+        <v>453</v>
+      </c>
+      <c r="I1411" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1411" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1411" t="s">
+        <v>298</v>
+      </c>
+      <c r="L1411">
+        <v>0</v>
+      </c>
+      <c r="M1411" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:14">
+      <c r="A1412" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1412">
+        <v>2</v>
+      </c>
+      <c r="D1412">
+        <v>2</v>
+      </c>
+      <c r="E1412" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1412" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1412" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1412" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1412" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1412" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1412" t="s">
+        <v>276</v>
+      </c>
+      <c r="L1412">
+        <v>0</v>
+      </c>
+      <c r="M1412" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:14">
+      <c r="A1413" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C1413">
+        <v>2</v>
+      </c>
+      <c r="D1413">
+        <v>2</v>
+      </c>
+      <c r="E1413" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1413" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1413" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1413" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1413" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1413" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1413" t="s">
+        <v>298</v>
+      </c>
+      <c r="L1413">
+        <v>0</v>
+      </c>
+      <c r="M1413" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:14">
+      <c r="A1414" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1414">
+        <v>2</v>
+      </c>
+      <c r="D1414">
+        <v>2</v>
+      </c>
+      <c r="E1414" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1414" t="s">
+        <v>2235</v>
+      </c>
+      <c r="G1414" t="s">
+        <v>2236</v>
+      </c>
+      <c r="H1414" t="s">
+        <v>700</v>
+      </c>
+      <c r="I1414" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1414" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1414" t="s">
+        <v>2236</v>
+      </c>
+      <c r="L1414">
+        <v>0</v>
+      </c>
+      <c r="M1414" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:14">
+      <c r="A1415" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1415">
+        <v>2</v>
+      </c>
+      <c r="D1415">
+        <v>0</v>
+      </c>
+      <c r="E1415" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1415" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1415" t="s">
+        <v>471</v>
+      </c>
+      <c r="H1415" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1415" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1415" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1415" t="s">
+        <v>471</v>
+      </c>
+      <c r="L1415">
+        <v>0</v>
+      </c>
+      <c r="M1415" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:14">
+      <c r="A1416" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1416">
+        <v>1</v>
+      </c>
+      <c r="D1416">
+        <v>0</v>
+      </c>
+      <c r="E1416" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1416" t="s">
+        <v>293</v>
+      </c>
+      <c r="G1416" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1416" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1416" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1416" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1416" t="s">
+        <v>254</v>
+      </c>
+      <c r="L1416">
+        <v>0</v>
+      </c>
+      <c r="M1416" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:14">
+      <c r="A1417" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>708</v>
+      </c>
+      <c r="C1417">
+        <v>1</v>
+      </c>
+      <c r="D1417">
+        <v>0</v>
+      </c>
+      <c r="E1417" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1417" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1417" t="s">
+        <v>284</v>
+      </c>
+      <c r="H1417" t="s">
+        <v>300</v>
+      </c>
+      <c r="I1417" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1417" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1417" t="s">
+        <v>284</v>
+      </c>
+      <c r="L1417">
+        <v>0</v>
+      </c>
+      <c r="M1417" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:14">
+      <c r="A1418" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1418">
+        <v>1</v>
+      </c>
+      <c r="D1418">
+        <v>1</v>
+      </c>
+      <c r="E1418" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1418" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G1418" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1418" t="s">
+        <v>1474</v>
+      </c>
+      <c r="I1418" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1418" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1418" t="s">
+        <v>266</v>
+      </c>
+      <c r="L1418">
+        <v>0</v>
+      </c>
+      <c r="M1418" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:14">
+      <c r="A1419" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>529</v>
+      </c>
+      <c r="C1419">
+        <v>1</v>
+      </c>
+      <c r="D1419">
+        <v>1</v>
+      </c>
+      <c r="E1419" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1419" t="s">
+        <v>293</v>
+      </c>
+      <c r="G1419" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1419" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1419" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1419" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1419" t="s">
+        <v>196</v>
+      </c>
+      <c r="L1419">
+        <v>0</v>
+      </c>
+      <c r="M1419" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:14">
+      <c r="A1420" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1420">
+        <v>1</v>
+      </c>
+      <c r="D1420">
+        <v>0</v>
+      </c>
+      <c r="E1420" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1420" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1420" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1420" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1420" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1420" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1420" t="s">
+        <v>254</v>
+      </c>
+      <c r="L1420">
+        <v>0</v>
+      </c>
+      <c r="M1420" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:14">
+      <c r="A1421" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>517</v>
+      </c>
+      <c r="C1421">
+        <v>1</v>
+      </c>
+      <c r="D1421">
+        <v>1</v>
+      </c>
+      <c r="E1421" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1421" t="s">
+        <v>2237</v>
+      </c>
+      <c r="G1421" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1421" t="s">
+        <v>524</v>
+      </c>
+      <c r="I1421" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1421" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1421" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1421">
+        <v>0</v>
+      </c>
+      <c r="M1421" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:14">
+      <c r="A1422" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1422">
+        <v>1</v>
+      </c>
+      <c r="D1422">
+        <v>1</v>
+      </c>
+      <c r="E1422" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1422" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1422" t="s">
+        <v>258</v>
+      </c>
+      <c r="H1422" t="s">
+        <v>321</v>
+      </c>
+      <c r="I1422" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1422" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1422" t="s">
+        <v>258</v>
+      </c>
+      <c r="L1422">
+        <v>0</v>
+      </c>
+      <c r="M1422" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:14">
+      <c r="A1423" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1423">
+        <v>1</v>
+      </c>
+      <c r="D1423">
+        <v>1</v>
+      </c>
+      <c r="E1423" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1423" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1423" t="s">
+        <v>300</v>
+      </c>
+      <c r="H1423" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1423" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1423" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1423" t="s">
+        <v>300</v>
+      </c>
+      <c r="L1423">
+        <v>0</v>
+      </c>
+      <c r="M1423" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:14">
+      <c r="A1424" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1424">
+        <v>1</v>
+      </c>
+      <c r="D1424">
+        <v>1</v>
+      </c>
+      <c r="E1424" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1424" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G1424" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1424" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1424" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1424" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1424" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1424">
+        <v>0</v>
+      </c>
+      <c r="M1424" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:14">
+      <c r="A1425" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1425">
+        <v>1</v>
+      </c>
+      <c r="D1425">
+        <v>1</v>
+      </c>
+      <c r="E1425" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1425" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1425" t="s">
+        <v>303</v>
+      </c>
+      <c r="H1425" t="s">
+        <v>304</v>
+      </c>
+      <c r="I1425" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1425" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1425" t="s">
+        <v>303</v>
+      </c>
+      <c r="L1425">
+        <v>0</v>
+      </c>
+      <c r="M1425" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:14">
+      <c r="A1426" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>525</v>
+      </c>
+      <c r="C1426">
+        <v>1</v>
+      </c>
+      <c r="D1426">
+        <v>1</v>
+      </c>
+      <c r="E1426" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1426" t="s">
+        <v>699</v>
+      </c>
+      <c r="G1426" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1426" t="s">
+        <v>701</v>
+      </c>
+      <c r="I1426" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1426" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1426" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1426">
+        <v>0</v>
+      </c>
+      <c r="M1426" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1426">
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\new clone\Salefile\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9C5B0F-A56F-4A57-8D2B-E3E8385ADF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$1373</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -29,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9989" uniqueCount="2238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10318" uniqueCount="2285">
   <si>
     <t>Date</t>
   </si>
@@ -6628,27 +6627,6 @@
     <t>TLight_HQ(Client)</t>
   </si>
   <si>
-    <t>13.827 EUR</t>
-  </si>
-  <si>
-    <t>8.263 EUR</t>
-  </si>
-  <si>
-    <t>22.09 EUR</t>
-  </si>
-  <si>
-    <t>6.12264 EUR</t>
-  </si>
-  <si>
-    <t>14.4918 EUR</t>
-  </si>
-  <si>
-    <t>20.61444 EUR</t>
-  </si>
-  <si>
-    <t>1.8456 EUR</t>
-  </si>
-  <si>
     <t>0.4387 EUR</t>
   </si>
   <si>
@@ -6658,96 +6636,18 @@
     <t>0.7954 EUR</t>
   </si>
   <si>
-    <t>0.6402 EUR</t>
-  </si>
-  <si>
-    <t>1.6538 EUR</t>
-  </si>
-  <si>
-    <t>2.294 EUR</t>
-  </si>
-  <si>
-    <t>0.602 EUR</t>
-  </si>
-  <si>
-    <t>2.408 EUR</t>
-  </si>
-  <si>
-    <t>3.01 EUR</t>
-  </si>
-  <si>
-    <t>0.0463 EUR</t>
-  </si>
-  <si>
-    <t>0.0467 EUR</t>
-  </si>
-  <si>
     <t>0.1188 EUR</t>
   </si>
   <si>
-    <t>0.1468 EUR</t>
-  </si>
-  <si>
-    <t>0.2742 EUR</t>
-  </si>
-  <si>
-    <t>0.421 EUR</t>
-  </si>
-  <si>
-    <t>0.03685 EUR</t>
-  </si>
-  <si>
-    <t>0.02615 EUR</t>
-  </si>
-  <si>
-    <t>0.22181 EUR</t>
-  </si>
-  <si>
-    <t>0.07219 EUR</t>
-  </si>
-  <si>
-    <t>0.294 EUR</t>
-  </si>
-  <si>
     <t>0.0908 EUR</t>
   </si>
   <si>
-    <t>0.3305 EUR</t>
-  </si>
-  <si>
-    <t>0.351 EUR</t>
-  </si>
-  <si>
-    <t>0.424 EUR</t>
-  </si>
-  <si>
-    <t>0.536 EUR</t>
-  </si>
-  <si>
-    <t>0.176 EUR</t>
-  </si>
-  <si>
     <t>0.714 EUR</t>
   </si>
   <si>
-    <t>0.0081 EUR</t>
-  </si>
-  <si>
-    <t>0.0477 EUR</t>
-  </si>
-  <si>
     <t>0.264 EUR</t>
   </si>
   <si>
-    <t>0.0738 EUR</t>
-  </si>
-  <si>
-    <t>0.0406 EUR</t>
-  </si>
-  <si>
-    <t>0.0214 EUR</t>
-  </si>
-  <si>
     <t>0.0029 EUR</t>
   </si>
   <si>
@@ -6755,12 +6655,252 @@
   </si>
   <si>
     <t>0.0133 EUR</t>
+  </si>
+  <si>
+    <t>3.30215 EUR</t>
+  </si>
+  <si>
+    <t>7.52635 EUR</t>
+  </si>
+  <si>
+    <t>10.8285 EUR</t>
+  </si>
+  <si>
+    <t>17.335 EUR</t>
+  </si>
+  <si>
+    <t>10.315 EUR</t>
+  </si>
+  <si>
+    <t>27.65 EUR</t>
+  </si>
+  <si>
+    <t>7.49024 EUR</t>
+  </si>
+  <si>
+    <t>17.7288 EUR</t>
+  </si>
+  <si>
+    <t>25.21904 EUR</t>
+  </si>
+  <si>
+    <t>0.1646 EUR</t>
+  </si>
+  <si>
+    <t>1.9714 EUR</t>
+  </si>
+  <si>
+    <t>2.136 EUR</t>
+  </si>
+  <si>
+    <t>0.9254 EUR</t>
+  </si>
+  <si>
+    <t>2.3916 EUR</t>
+  </si>
+  <si>
+    <t>3.317 EUR</t>
+  </si>
+  <si>
+    <t>0.0915 EUR</t>
+  </si>
+  <si>
+    <t>0.91 EUR</t>
+  </si>
+  <si>
+    <t>3.445 EUR</t>
+  </si>
+  <si>
+    <t>4.355 EUR</t>
+  </si>
+  <si>
+    <t>0.0678 EUR</t>
+  </si>
+  <si>
+    <t>0.0393 EUR</t>
+  </si>
+  <si>
+    <t>0.0633 EUR</t>
+  </si>
+  <si>
+    <t>0.1026 EUR</t>
+  </si>
+  <si>
+    <t>0.3092 EUR</t>
+  </si>
+  <si>
+    <t>0.3898 EUR</t>
+  </si>
+  <si>
+    <t>0.699 EUR</t>
+  </si>
+  <si>
+    <t>0.1398 EUR</t>
+  </si>
+  <si>
+    <t>0.764 EUR</t>
+  </si>
+  <si>
+    <t>0.426 EUR</t>
+  </si>
+  <si>
+    <t>0.582 EUR</t>
+  </si>
+  <si>
+    <t>0.24744 EUR</t>
+  </si>
+  <si>
+    <t>0.07856 EUR</t>
+  </si>
+  <si>
+    <t>0.326 EUR</t>
+  </si>
+  <si>
+    <t>1.04 EUR</t>
+  </si>
+  <si>
+    <t>1.365 EUR</t>
+  </si>
+  <si>
+    <t>0.1248 EUR</t>
+  </si>
+  <si>
+    <t>0.39 EUR</t>
+  </si>
+  <si>
+    <t>0.5148 EUR</t>
+  </si>
+  <si>
+    <t>0.191 EUR</t>
+  </si>
+  <si>
+    <t>0.0129 EUR</t>
+  </si>
+  <si>
+    <t>0.0693 EUR</t>
+  </si>
+  <si>
+    <t>0.3392 EUR</t>
+  </si>
+  <si>
+    <t>0.461 EUR</t>
+  </si>
+  <si>
+    <t>0.1386 EUR</t>
+  </si>
+  <si>
+    <t>0.0278 EUR</t>
+  </si>
+  <si>
+    <t>0.0692 EUR</t>
+  </si>
+  <si>
+    <t>0.082 EUR</t>
+  </si>
+  <si>
+    <t>1.71362 EUR</t>
+  </si>
+  <si>
+    <t>14.87804 EUR</t>
+  </si>
+  <si>
+    <t>16.59165 EUR</t>
+  </si>
+  <si>
+    <t>14.1015 EUR</t>
+  </si>
+  <si>
+    <t>8.5085 EUR</t>
+  </si>
+  <si>
+    <t>22.61 EUR</t>
+  </si>
+  <si>
+    <t>5.28104 EUR</t>
+  </si>
+  <si>
+    <t>12.4998 EUR</t>
+  </si>
+  <si>
+    <t>17.78084 EUR</t>
+  </si>
+  <si>
+    <t>1.4652 EUR</t>
+  </si>
+  <si>
+    <t>1.584 EUR</t>
+  </si>
+  <si>
+    <t>1.0172 EUR</t>
+  </si>
+  <si>
+    <t>3.4364 EUR</t>
+  </si>
+  <si>
+    <t>0.5445 EUR</t>
+  </si>
+  <si>
+    <t>0.4455 EUR</t>
+  </si>
+  <si>
+    <t>0.3136 EUR</t>
+  </si>
+  <si>
+    <t>0.48688 EUR</t>
+  </si>
+  <si>
+    <t>0.12113 EUR</t>
+  </si>
+  <si>
+    <t>0.608 EUR</t>
+  </si>
+  <si>
+    <t>2.12 EUR</t>
+  </si>
+  <si>
+    <t>2.57 EUR</t>
+  </si>
+  <si>
+    <t>0.2131 EUR</t>
+  </si>
+  <si>
+    <t>0.1736 EUR</t>
+  </si>
+  <si>
+    <t>0.3867 EUR</t>
+  </si>
+  <si>
+    <t>0.3082 EUR</t>
+  </si>
+  <si>
+    <t>0.3126 EUR</t>
+  </si>
+  <si>
+    <t>0.03581 EUR</t>
+  </si>
+  <si>
+    <t>0.16819 EUR</t>
+  </si>
+  <si>
+    <t>0.3168 EUR</t>
+  </si>
+  <si>
+    <t>0.1286 EUR</t>
+  </si>
+  <si>
+    <t>0.0694 EUR</t>
+  </si>
+  <si>
+    <t>0.02681 EUR</t>
+  </si>
+  <si>
+    <t>0.06319 EUR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -7141,8 +7281,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1426"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N1473"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -67709,34 +67849,34 @@
         <v>46284</v>
       </c>
       <c r="B1377" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C1377">
-        <v>2209</v>
+        <v>7136</v>
       </c>
       <c r="D1377">
-        <v>2097</v>
+        <v>6639</v>
       </c>
       <c r="E1377" s="3">
-        <v>0.94929830000000004</v>
+        <v>0.93035310000000004</v>
       </c>
       <c r="F1377" t="s">
-        <v>2195</v>
+        <v>2205</v>
       </c>
       <c r="G1377" t="s">
-        <v>2196</v>
+        <v>2206</v>
       </c>
       <c r="H1377" t="s">
-        <v>2197</v>
+        <v>2207</v>
       </c>
       <c r="I1377" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1377" t="s">
         <v>19</v>
       </c>
       <c r="K1377" t="s">
-        <v>2196</v>
+        <v>2206</v>
       </c>
       <c r="L1377">
         <v>0</v>
@@ -67753,25 +67893,25 @@
         <v>46284</v>
       </c>
       <c r="B1378" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="C1378">
-        <v>291</v>
+        <v>2765</v>
       </c>
       <c r="D1378">
-        <v>227</v>
+        <v>2625</v>
       </c>
       <c r="E1378" s="3">
-        <v>0.78006869999999995</v>
+        <v>0.94936710000000002</v>
       </c>
       <c r="F1378" t="s">
-        <v>2198</v>
+        <v>2208</v>
       </c>
       <c r="G1378" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
       <c r="H1378" t="s">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="I1378" t="s">
         <v>28</v>
@@ -67780,7 +67920,7 @@
         <v>19</v>
       </c>
       <c r="K1378" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
       <c r="L1378">
         <v>0</v>
@@ -67797,34 +67937,34 @@
         <v>46284</v>
       </c>
       <c r="B1379" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="C1379">
-        <v>252</v>
+        <v>356</v>
       </c>
       <c r="D1379">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="E1379" s="3">
-        <v>0.99603169999999996</v>
+        <v>0.77528090000000005</v>
       </c>
       <c r="F1379" t="s">
-        <v>416</v>
+        <v>2211</v>
       </c>
       <c r="G1379" t="s">
-        <v>2201</v>
+        <v>2212</v>
       </c>
       <c r="H1379" t="s">
-        <v>1062</v>
+        <v>2213</v>
       </c>
       <c r="I1379" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1379" t="s">
         <v>19</v>
       </c>
       <c r="K1379" t="s">
-        <v>2201</v>
+        <v>2212</v>
       </c>
       <c r="L1379">
         <v>0</v>
@@ -67841,25 +67981,25 @@
         <v>46284</v>
       </c>
       <c r="B1380" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="C1380">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="D1380">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="E1380" s="3">
-        <v>0.93902439999999998</v>
+        <v>0.99628249999999996</v>
       </c>
       <c r="F1380" t="s">
-        <v>2202</v>
+        <v>2214</v>
       </c>
       <c r="G1380" t="s">
-        <v>2203</v>
+        <v>2215</v>
       </c>
       <c r="H1380" t="s">
-        <v>2204</v>
+        <v>2216</v>
       </c>
       <c r="I1380" t="s">
         <v>23</v>
@@ -67868,7 +68008,7 @@
         <v>19</v>
       </c>
       <c r="K1380" t="s">
-        <v>2203</v>
+        <v>2215</v>
       </c>
       <c r="L1380">
         <v>0</v>
@@ -67888,22 +68028,22 @@
         <v>49</v>
       </c>
       <c r="C1381">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D1381">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="E1381" s="3">
-        <v>0.89189189999999996</v>
+        <v>0.86915889999999996</v>
       </c>
       <c r="F1381" t="s">
-        <v>2205</v>
+        <v>2217</v>
       </c>
       <c r="G1381" t="s">
-        <v>2206</v>
+        <v>2218</v>
       </c>
       <c r="H1381" t="s">
-        <v>2207</v>
+        <v>2219</v>
       </c>
       <c r="I1381" t="s">
         <v>28</v>
@@ -67912,7 +68052,7 @@
         <v>19</v>
       </c>
       <c r="K1381" t="s">
-        <v>2206</v>
+        <v>2218</v>
       </c>
       <c r="L1381">
         <v>0</v>
@@ -67929,34 +68069,34 @@
         <v>46284</v>
       </c>
       <c r="B1382" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C1382">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="D1382">
-        <v>43</v>
-      </c>
-      <c r="E1382" s="4">
-        <v>1</v>
+        <v>77</v>
+      </c>
+      <c r="E1382" s="3">
+        <v>0.93902439999999998</v>
       </c>
       <c r="F1382" t="s">
-        <v>2208</v>
+        <v>2195</v>
       </c>
       <c r="G1382" t="s">
-        <v>2209</v>
+        <v>2196</v>
       </c>
       <c r="H1382" t="s">
-        <v>2210</v>
+        <v>2197</v>
       </c>
       <c r="I1382" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1382" t="s">
         <v>19</v>
       </c>
       <c r="K1382" t="s">
-        <v>2209</v>
+        <v>2196</v>
       </c>
       <c r="L1382">
         <v>0</v>
@@ -67973,34 +68113,34 @@
         <v>46284</v>
       </c>
       <c r="B1383" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C1383">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D1383">
+        <v>66</v>
+      </c>
+      <c r="E1383" s="3">
+        <v>0.9428571</v>
+      </c>
+      <c r="F1383" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G1383" t="s">
+        <v>1691</v>
+      </c>
+      <c r="H1383" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I1383" t="s">
         <v>28</v>
       </c>
-      <c r="E1383" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="F1383" t="s">
-        <v>2211</v>
-      </c>
-      <c r="G1383" t="s">
-        <v>667</v>
-      </c>
-      <c r="H1383" t="s">
-        <v>535</v>
-      </c>
-      <c r="I1383" t="s">
-        <v>18</v>
-      </c>
       <c r="J1383" t="s">
         <v>19</v>
       </c>
       <c r="K1383" t="s">
-        <v>667</v>
+        <v>1691</v>
       </c>
       <c r="L1383">
         <v>0</v>
@@ -68017,34 +68157,34 @@
         <v>46284</v>
       </c>
       <c r="B1384" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="C1384">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D1384">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E1384" s="3">
-        <v>0.80645160000000005</v>
+        <v>0.95714290000000002</v>
       </c>
       <c r="F1384" t="s">
-        <v>205</v>
+        <v>2220</v>
       </c>
       <c r="G1384" t="s">
-        <v>157</v>
+        <v>1331</v>
       </c>
       <c r="H1384" t="s">
-        <v>253</v>
+        <v>1179</v>
       </c>
       <c r="I1384" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1384" t="s">
         <v>19</v>
       </c>
       <c r="K1384" t="s">
-        <v>157</v>
+        <v>1331</v>
       </c>
       <c r="L1384">
         <v>0</v>
@@ -68061,34 +68201,34 @@
         <v>46284</v>
       </c>
       <c r="B1385" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C1385">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D1385">
+        <v>65</v>
+      </c>
+      <c r="E1385" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1385" t="s">
+        <v>2221</v>
+      </c>
+      <c r="G1385" t="s">
+        <v>2222</v>
+      </c>
+      <c r="H1385" t="s">
+        <v>2223</v>
+      </c>
+      <c r="I1385" t="s">
         <v>28</v>
       </c>
-      <c r="E1385" s="3">
-        <v>0.93333330000000003</v>
-      </c>
-      <c r="F1385" t="s">
-        <v>458</v>
-      </c>
-      <c r="G1385" t="s">
-        <v>2212</v>
-      </c>
-      <c r="H1385" t="s">
-        <v>1648</v>
-      </c>
-      <c r="I1385" t="s">
-        <v>18</v>
-      </c>
       <c r="J1385" t="s">
         <v>19</v>
       </c>
       <c r="K1385" t="s">
-        <v>2212</v>
+        <v>2222</v>
       </c>
       <c r="L1385">
         <v>0</v>
@@ -68105,34 +68245,34 @@
         <v>46284</v>
       </c>
       <c r="B1386" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="C1386">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D1386">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="E1386" s="3">
-        <v>0.88461540000000005</v>
+        <v>0.89090910000000001</v>
       </c>
       <c r="F1386" t="s">
-        <v>2213</v>
+        <v>157</v>
       </c>
       <c r="G1386" t="s">
-        <v>1554</v>
+        <v>2224</v>
       </c>
       <c r="H1386" t="s">
-        <v>2002</v>
+        <v>82</v>
       </c>
       <c r="I1386" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1386" t="s">
         <v>19</v>
       </c>
       <c r="K1386" t="s">
-        <v>1554</v>
+        <v>2224</v>
       </c>
       <c r="L1386">
         <v>0</v>
@@ -68152,22 +68292,22 @@
         <v>140</v>
       </c>
       <c r="C1387">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D1387">
-        <v>22</v>
-      </c>
-      <c r="E1387" s="4">
-        <v>0.88</v>
+        <v>48</v>
+      </c>
+      <c r="E1387" s="3">
+        <v>0.88888889999999998</v>
       </c>
       <c r="F1387" t="s">
-        <v>141</v>
+        <v>2225</v>
       </c>
       <c r="G1387" t="s">
-        <v>142</v>
+        <v>2226</v>
       </c>
       <c r="H1387" t="s">
-        <v>143</v>
+        <v>2227</v>
       </c>
       <c r="I1387" t="s">
         <v>18</v>
@@ -68176,7 +68316,7 @@
         <v>19</v>
       </c>
       <c r="K1387" t="s">
-        <v>142</v>
+        <v>2226</v>
       </c>
       <c r="L1387">
         <v>0</v>
@@ -68196,7 +68336,7 @@
         <v>73</v>
       </c>
       <c r="C1388">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D1388">
         <v>0</v>
@@ -68205,13 +68345,13 @@
         <v>0</v>
       </c>
       <c r="F1388" t="s">
-        <v>2214</v>
+        <v>2228</v>
       </c>
       <c r="G1388" t="s">
-        <v>2215</v>
+        <v>2229</v>
       </c>
       <c r="H1388" t="s">
-        <v>2216</v>
+        <v>2230</v>
       </c>
       <c r="I1388" t="s">
         <v>18</v>
@@ -68220,7 +68360,7 @@
         <v>19</v>
       </c>
       <c r="K1388" t="s">
-        <v>2215</v>
+        <v>2229</v>
       </c>
       <c r="L1388">
         <v>0</v>
@@ -68237,25 +68377,25 @@
         <v>46284</v>
       </c>
       <c r="B1389" t="s">
-        <v>57</v>
+        <v>220</v>
       </c>
       <c r="C1389">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D1389">
-        <v>0</v>
-      </c>
-      <c r="E1389" s="4">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="E1389" s="3">
+        <v>0.80645160000000005</v>
       </c>
       <c r="F1389" t="s">
-        <v>1460</v>
+        <v>205</v>
       </c>
       <c r="G1389" t="s">
-        <v>483</v>
+        <v>157</v>
       </c>
       <c r="H1389" t="s">
-        <v>1635</v>
+        <v>253</v>
       </c>
       <c r="I1389" t="s">
         <v>23</v>
@@ -68264,7 +68404,7 @@
         <v>19</v>
       </c>
       <c r="K1389" t="s">
-        <v>483</v>
+        <v>157</v>
       </c>
       <c r="L1389">
         <v>0</v>
@@ -68281,34 +68421,34 @@
         <v>46284</v>
       </c>
       <c r="B1390" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C1390">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D1390">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E1390" s="3">
-        <v>0.85714290000000004</v>
+        <v>0.90322579999999997</v>
       </c>
       <c r="F1390" t="s">
-        <v>2217</v>
+        <v>2231</v>
       </c>
       <c r="G1390" t="s">
-        <v>2218</v>
+        <v>971</v>
       </c>
       <c r="H1390" t="s">
-        <v>255</v>
+        <v>464</v>
       </c>
       <c r="I1390" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1390" t="s">
         <v>19</v>
       </c>
       <c r="K1390" t="s">
-        <v>2218</v>
+        <v>971</v>
       </c>
       <c r="L1390">
         <v>0</v>
@@ -68325,25 +68465,25 @@
         <v>46284</v>
       </c>
       <c r="B1391" t="s">
-        <v>65</v>
+        <v>308</v>
       </c>
       <c r="C1391">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D1391">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E1391" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1391" t="s">
-        <v>2219</v>
+        <v>248</v>
       </c>
       <c r="G1391" t="s">
-        <v>2220</v>
+        <v>2232</v>
       </c>
       <c r="H1391" t="s">
-        <v>2221</v>
+        <v>1297</v>
       </c>
       <c r="I1391" t="s">
         <v>18</v>
@@ -68352,7 +68492,7 @@
         <v>19</v>
       </c>
       <c r="K1391" t="s">
-        <v>2220</v>
+        <v>2232</v>
       </c>
       <c r="L1391">
         <v>0</v>
@@ -68369,34 +68509,34 @@
         <v>46284</v>
       </c>
       <c r="B1392" t="s">
-        <v>211</v>
+        <v>57</v>
       </c>
       <c r="C1392">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D1392">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E1392" s="3">
-        <v>0.76923079999999999</v>
+        <v>4.3478299999999998E-2</v>
       </c>
       <c r="F1392" t="s">
-        <v>2222</v>
+        <v>2233</v>
       </c>
       <c r="G1392" t="s">
-        <v>262</v>
+        <v>1106</v>
       </c>
       <c r="H1392" t="s">
-        <v>1919</v>
+        <v>2234</v>
       </c>
       <c r="I1392" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1392" t="s">
         <v>19</v>
       </c>
       <c r="K1392" t="s">
-        <v>262</v>
+        <v>1106</v>
       </c>
       <c r="L1392">
         <v>0</v>
@@ -68413,25 +68553,25 @@
         <v>46284</v>
       </c>
       <c r="B1393" t="s">
-        <v>308</v>
+        <v>65</v>
       </c>
       <c r="C1393">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D1393">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E1393" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1393" t="s">
-        <v>805</v>
+        <v>2235</v>
       </c>
       <c r="G1393" t="s">
-        <v>2223</v>
+        <v>2236</v>
       </c>
       <c r="H1393" t="s">
-        <v>2224</v>
+        <v>2237</v>
       </c>
       <c r="I1393" t="s">
         <v>18</v>
@@ -68440,7 +68580,7 @@
         <v>19</v>
       </c>
       <c r="K1393" t="s">
-        <v>2223</v>
+        <v>2236</v>
       </c>
       <c r="L1393">
         <v>0</v>
@@ -68457,25 +68597,25 @@
         <v>46284</v>
       </c>
       <c r="B1394" t="s">
-        <v>128</v>
+        <v>211</v>
       </c>
       <c r="C1394">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1394">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1394" s="3">
-        <v>0.91666669999999995</v>
+        <v>0.76923079999999999</v>
       </c>
       <c r="F1394" t="s">
-        <v>1554</v>
+        <v>2199</v>
       </c>
       <c r="G1394" t="s">
-        <v>797</v>
+        <v>262</v>
       </c>
       <c r="H1394" t="s">
-        <v>1555</v>
+        <v>1919</v>
       </c>
       <c r="I1394" t="s">
         <v>18</v>
@@ -68484,7 +68624,7 @@
         <v>19</v>
       </c>
       <c r="K1394" t="s">
-        <v>797</v>
+        <v>262</v>
       </c>
       <c r="L1394">
         <v>0</v>
@@ -68501,25 +68641,25 @@
         <v>46284</v>
       </c>
       <c r="B1395" t="s">
-        <v>172</v>
+        <v>85</v>
       </c>
       <c r="C1395">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D1395">
-        <v>8</v>
-      </c>
-      <c r="E1395" s="4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E1395" s="3">
+        <v>0.3846154</v>
       </c>
       <c r="F1395" t="s">
-        <v>239</v>
+        <v>1076</v>
       </c>
       <c r="G1395" t="s">
-        <v>2225</v>
+        <v>2238</v>
       </c>
       <c r="H1395" t="s">
-        <v>2226</v>
+        <v>2239</v>
       </c>
       <c r="I1395" t="s">
         <v>28</v>
@@ -68528,7 +68668,7 @@
         <v>19</v>
       </c>
       <c r="K1395" t="s">
-        <v>2225</v>
+        <v>2238</v>
       </c>
       <c r="L1395">
         <v>0</v>
@@ -68545,34 +68685,34 @@
         <v>46284</v>
       </c>
       <c r="B1396" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="C1396">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D1396">
-        <v>4</v>
-      </c>
-      <c r="E1396" s="4">
-        <v>0.5</v>
+        <v>12</v>
+      </c>
+      <c r="E1396" s="3">
+        <v>0.92307689999999998</v>
       </c>
       <c r="F1396" t="s">
-        <v>804</v>
+        <v>2240</v>
       </c>
       <c r="G1396" t="s">
-        <v>1542</v>
+        <v>2241</v>
       </c>
       <c r="H1396" t="s">
-        <v>1044</v>
+        <v>2242</v>
       </c>
       <c r="I1396" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1396" t="s">
         <v>19</v>
       </c>
       <c r="K1396" t="s">
-        <v>1542</v>
+        <v>2241</v>
       </c>
       <c r="L1396">
         <v>0</v>
@@ -68589,34 +68729,34 @@
         <v>46284</v>
       </c>
       <c r="B1397" t="s">
-        <v>409</v>
+        <v>461</v>
       </c>
       <c r="C1397">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D1397">
-        <v>8</v>
-      </c>
-      <c r="E1397" s="4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="E1397" s="3">
+        <v>0.3333333</v>
       </c>
       <c r="F1397" t="s">
-        <v>258</v>
+        <v>842</v>
       </c>
       <c r="G1397" t="s">
-        <v>2227</v>
+        <v>2243</v>
       </c>
       <c r="H1397" t="s">
-        <v>804</v>
+        <v>2020</v>
       </c>
       <c r="I1397" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1397" t="s">
         <v>19</v>
       </c>
       <c r="K1397" t="s">
-        <v>2227</v>
+        <v>2243</v>
       </c>
       <c r="L1397">
         <v>0</v>
@@ -68633,25 +68773,25 @@
         <v>46284</v>
       </c>
       <c r="B1398" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="C1398">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D1398">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E1398" s="3">
-        <v>0.71428570000000002</v>
+        <v>0.90909090000000004</v>
       </c>
       <c r="F1398" t="s">
-        <v>284</v>
+        <v>2244</v>
       </c>
       <c r="G1398" t="s">
-        <v>2116</v>
+        <v>1922</v>
       </c>
       <c r="H1398" t="s">
-        <v>442</v>
+        <v>2245</v>
       </c>
       <c r="I1398" t="s">
         <v>18</v>
@@ -68660,7 +68800,7 @@
         <v>19</v>
       </c>
       <c r="K1398" t="s">
-        <v>2116</v>
+        <v>1922</v>
       </c>
       <c r="L1398">
         <v>0</v>
@@ -68677,34 +68817,34 @@
         <v>46284</v>
       </c>
       <c r="B1399" t="s">
-        <v>164</v>
+        <v>409</v>
       </c>
       <c r="C1399">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D1399">
-        <v>0</v>
-      </c>
-      <c r="E1399" s="4">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="E1399" s="3">
+        <v>0.81818179999999996</v>
       </c>
       <c r="F1399" t="s">
-        <v>212</v>
+        <v>1220</v>
       </c>
       <c r="G1399" t="s">
-        <v>2228</v>
+        <v>1553</v>
       </c>
       <c r="H1399" t="s">
-        <v>1044</v>
+        <v>755</v>
       </c>
       <c r="I1399" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1399" t="s">
         <v>19</v>
       </c>
       <c r="K1399" t="s">
-        <v>2228</v>
+        <v>1553</v>
       </c>
       <c r="L1399">
         <v>0</v>
@@ -68721,25 +68861,25 @@
         <v>46284</v>
       </c>
       <c r="B1400" t="s">
-        <v>461</v>
+        <v>183</v>
       </c>
       <c r="C1400">
+        <v>10</v>
+      </c>
+      <c r="D1400">
         <v>6</v>
       </c>
-      <c r="D1400">
-        <v>3</v>
-      </c>
       <c r="E1400" s="4">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F1400" t="s">
-        <v>408</v>
+        <v>802</v>
       </c>
       <c r="G1400" t="s">
-        <v>256</v>
+        <v>2246</v>
       </c>
       <c r="H1400" t="s">
-        <v>540</v>
+        <v>2247</v>
       </c>
       <c r="I1400" t="s">
         <v>23</v>
@@ -68748,7 +68888,7 @@
         <v>19</v>
       </c>
       <c r="K1400" t="s">
-        <v>256</v>
+        <v>2246</v>
       </c>
       <c r="L1400">
         <v>0</v>
@@ -68765,34 +68905,34 @@
         <v>46284</v>
       </c>
       <c r="B1401" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="C1401">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1401">
-        <v>5</v>
-      </c>
-      <c r="E1401" s="3">
-        <v>0.83333330000000005</v>
+        <v>0</v>
+      </c>
+      <c r="E1401" s="4">
+        <v>0</v>
       </c>
       <c r="F1401" t="s">
-        <v>2229</v>
+        <v>212</v>
       </c>
       <c r="G1401" t="s">
-        <v>1818</v>
+        <v>2200</v>
       </c>
       <c r="H1401" t="s">
-        <v>2230</v>
+        <v>1044</v>
       </c>
       <c r="I1401" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1401" t="s">
         <v>19</v>
       </c>
       <c r="K1401" t="s">
-        <v>1818</v>
+        <v>2200</v>
       </c>
       <c r="L1401">
         <v>0</v>
@@ -68809,34 +68949,34 @@
         <v>46284</v>
       </c>
       <c r="B1402" t="s">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="C1402">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1402">
-        <v>6</v>
-      </c>
-      <c r="E1402" s="4">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E1402" s="3">
+        <v>0.71428570000000002</v>
       </c>
       <c r="F1402" t="s">
-        <v>453</v>
+        <v>284</v>
       </c>
       <c r="G1402" t="s">
-        <v>2231</v>
+        <v>2116</v>
       </c>
       <c r="H1402" t="s">
-        <v>219</v>
+        <v>442</v>
       </c>
       <c r="I1402" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1402" t="s">
         <v>19</v>
       </c>
       <c r="K1402" t="s">
-        <v>2231</v>
+        <v>2116</v>
       </c>
       <c r="L1402">
         <v>0</v>
@@ -68853,34 +68993,34 @@
         <v>46284</v>
       </c>
       <c r="B1403" t="s">
-        <v>660</v>
+        <v>53</v>
       </c>
       <c r="C1403">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1403">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1403" s="4">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F1403" t="s">
-        <v>294</v>
+        <v>2248</v>
       </c>
       <c r="G1403" t="s">
-        <v>283</v>
+        <v>1209</v>
       </c>
       <c r="H1403" t="s">
-        <v>671</v>
+        <v>1337</v>
       </c>
       <c r="I1403" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1403" t="s">
         <v>19</v>
       </c>
       <c r="K1403" t="s">
-        <v>283</v>
+        <v>1209</v>
       </c>
       <c r="L1403">
         <v>0</v>
@@ -68897,34 +69037,34 @@
         <v>46284</v>
       </c>
       <c r="B1404" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C1404">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1404">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1404" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1404" t="s">
-        <v>507</v>
+        <v>219</v>
       </c>
       <c r="G1404" t="s">
-        <v>284</v>
+        <v>19</v>
       </c>
       <c r="H1404" t="s">
-        <v>518</v>
+        <v>219</v>
       </c>
       <c r="I1404" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1404" t="s">
         <v>19</v>
       </c>
       <c r="K1404" t="s">
-        <v>284</v>
+        <v>19</v>
       </c>
       <c r="L1404">
         <v>0</v>
@@ -68941,25 +69081,25 @@
         <v>46284</v>
       </c>
       <c r="B1405" t="s">
-        <v>183</v>
+        <v>289</v>
       </c>
       <c r="C1405">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1405">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E1405" s="4">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="F1405" t="s">
-        <v>2232</v>
+        <v>453</v>
       </c>
       <c r="G1405" t="s">
-        <v>700</v>
+        <v>2201</v>
       </c>
       <c r="H1405" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="I1405" t="s">
         <v>23</v>
@@ -68968,7 +69108,7 @@
         <v>19</v>
       </c>
       <c r="K1405" t="s">
-        <v>700</v>
+        <v>2201</v>
       </c>
       <c r="L1405">
         <v>0</v>
@@ -68985,34 +69125,34 @@
         <v>46284</v>
       </c>
       <c r="B1406" t="s">
-        <v>152</v>
+        <v>660</v>
       </c>
       <c r="C1406">
+        <v>5</v>
+      </c>
+      <c r="D1406">
         <v>4</v>
       </c>
-      <c r="D1406">
-        <v>0</v>
-      </c>
       <c r="E1406" s="4">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F1406" t="s">
-        <v>1648</v>
+        <v>294</v>
       </c>
       <c r="G1406" t="s">
-        <v>1342</v>
+        <v>283</v>
       </c>
       <c r="H1406" t="s">
-        <v>509</v>
+        <v>671</v>
       </c>
       <c r="I1406" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1406" t="s">
         <v>19</v>
       </c>
       <c r="K1406" t="s">
-        <v>1342</v>
+        <v>283</v>
       </c>
       <c r="L1406">
         <v>0</v>
@@ -69029,25 +69169,25 @@
         <v>46284</v>
       </c>
       <c r="B1407" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="C1407">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1407">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1407" s="4">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F1407" t="s">
-        <v>1827</v>
+        <v>1084</v>
       </c>
       <c r="G1407" t="s">
-        <v>680</v>
+        <v>2249</v>
       </c>
       <c r="H1407" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="I1407" t="s">
         <v>23</v>
@@ -69056,7 +69196,7 @@
         <v>19</v>
       </c>
       <c r="K1407" t="s">
-        <v>680</v>
+        <v>2249</v>
       </c>
       <c r="L1407">
         <v>0</v>
@@ -69073,34 +69213,34 @@
         <v>46284</v>
       </c>
       <c r="B1408" t="s">
-        <v>53</v>
+        <v>237</v>
       </c>
       <c r="C1408">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1408">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E1408" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1408" t="s">
-        <v>2117</v>
+        <v>507</v>
       </c>
       <c r="G1408" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="H1408" t="s">
-        <v>260</v>
+        <v>518</v>
       </c>
       <c r="I1408" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1408" t="s">
         <v>19</v>
       </c>
       <c r="K1408" t="s">
-        <v>473</v>
+        <v>284</v>
       </c>
       <c r="L1408">
         <v>0</v>
@@ -69117,34 +69257,34 @@
         <v>46284</v>
       </c>
       <c r="B1409" t="s">
-        <v>179</v>
+        <v>97</v>
       </c>
       <c r="C1409">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1409">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1409" s="4">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F1409" t="s">
-        <v>2233</v>
+        <v>2250</v>
       </c>
       <c r="G1409" t="s">
-        <v>2234</v>
+        <v>1342</v>
       </c>
       <c r="H1409" t="s">
-        <v>245</v>
+        <v>2251</v>
       </c>
       <c r="I1409" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1409" t="s">
         <v>19</v>
       </c>
       <c r="K1409" t="s">
-        <v>2234</v>
+        <v>1342</v>
       </c>
       <c r="L1409">
         <v>0</v>
@@ -69161,25 +69301,25 @@
         <v>46284</v>
       </c>
       <c r="B1410" t="s">
-        <v>315</v>
+        <v>152</v>
       </c>
       <c r="C1410">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1410">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1410" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1410" t="s">
-        <v>513</v>
+        <v>1648</v>
       </c>
       <c r="G1410" t="s">
-        <v>514</v>
+        <v>1342</v>
       </c>
       <c r="H1410" t="s">
-        <v>284</v>
+        <v>509</v>
       </c>
       <c r="I1410" t="s">
         <v>23</v>
@@ -69188,7 +69328,7 @@
         <v>19</v>
       </c>
       <c r="K1410" t="s">
-        <v>514</v>
+        <v>1342</v>
       </c>
       <c r="L1410">
         <v>0</v>
@@ -69205,25 +69345,25 @@
         <v>46284</v>
       </c>
       <c r="B1411" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="C1411">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1411">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1411" s="4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F1411" t="s">
-        <v>284</v>
+        <v>1827</v>
       </c>
       <c r="G1411" t="s">
+        <v>680</v>
+      </c>
+      <c r="H1411" t="s">
         <v>298</v>
-      </c>
-      <c r="H1411" t="s">
-        <v>453</v>
       </c>
       <c r="I1411" t="s">
         <v>23</v>
@@ -69232,7 +69372,7 @@
         <v>19</v>
       </c>
       <c r="K1411" t="s">
-        <v>298</v>
+        <v>680</v>
       </c>
       <c r="L1411">
         <v>0</v>
@@ -69249,34 +69389,34 @@
         <v>46284</v>
       </c>
       <c r="B1412" t="s">
-        <v>329</v>
+        <v>215</v>
       </c>
       <c r="C1412">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1412">
         <v>2</v>
       </c>
-      <c r="E1412" s="4">
-        <v>1</v>
+      <c r="E1412" s="3">
+        <v>0.66666669999999995</v>
       </c>
       <c r="F1412" t="s">
-        <v>498</v>
+        <v>911</v>
       </c>
       <c r="G1412" t="s">
-        <v>276</v>
+        <v>1000</v>
       </c>
       <c r="H1412" t="s">
-        <v>298</v>
+        <v>245</v>
       </c>
       <c r="I1412" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1412" t="s">
         <v>19</v>
       </c>
       <c r="K1412" t="s">
-        <v>276</v>
+        <v>1000</v>
       </c>
       <c r="L1412">
         <v>0</v>
@@ -69293,25 +69433,25 @@
         <v>46284</v>
       </c>
       <c r="B1413" t="s">
-        <v>1479</v>
+        <v>315</v>
       </c>
       <c r="C1413">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1413">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1413" s="4">
         <v>1</v>
       </c>
       <c r="F1413" t="s">
-        <v>545</v>
+        <v>513</v>
       </c>
       <c r="G1413" t="s">
-        <v>298</v>
+        <v>514</v>
       </c>
       <c r="H1413" t="s">
-        <v>232</v>
+        <v>284</v>
       </c>
       <c r="I1413" t="s">
         <v>23</v>
@@ -69320,7 +69460,7 @@
         <v>19</v>
       </c>
       <c r="K1413" t="s">
-        <v>298</v>
+        <v>514</v>
       </c>
       <c r="L1413">
         <v>0</v>
@@ -69337,7 +69477,7 @@
         <v>46284</v>
       </c>
       <c r="B1414" t="s">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="C1414">
         <v>2</v>
@@ -69349,22 +69489,22 @@
         <v>1</v>
       </c>
       <c r="F1414" t="s">
-        <v>2235</v>
+        <v>284</v>
       </c>
       <c r="G1414" t="s">
-        <v>2236</v>
+        <v>298</v>
       </c>
       <c r="H1414" t="s">
-        <v>700</v>
+        <v>453</v>
       </c>
       <c r="I1414" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1414" t="s">
         <v>19</v>
       </c>
       <c r="K1414" t="s">
-        <v>2236</v>
+        <v>298</v>
       </c>
       <c r="L1414">
         <v>0</v>
@@ -69381,34 +69521,34 @@
         <v>46284</v>
       </c>
       <c r="B1415" t="s">
-        <v>265</v>
+        <v>329</v>
       </c>
       <c r="C1415">
         <v>2</v>
       </c>
       <c r="D1415">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1415" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1415" t="s">
         <v>498</v>
       </c>
       <c r="G1415" t="s">
-        <v>471</v>
+        <v>276</v>
       </c>
       <c r="H1415" t="s">
-        <v>153</v>
+        <v>298</v>
       </c>
       <c r="I1415" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1415" t="s">
         <v>19</v>
       </c>
       <c r="K1415" t="s">
-        <v>471</v>
+        <v>276</v>
       </c>
       <c r="L1415">
         <v>0</v>
@@ -69425,34 +69565,34 @@
         <v>46284</v>
       </c>
       <c r="B1416" t="s">
-        <v>215</v>
+        <v>1479</v>
       </c>
       <c r="C1416">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1416">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1416" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1416" t="s">
-        <v>293</v>
+        <v>545</v>
       </c>
       <c r="G1416" t="s">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="H1416" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="I1416" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1416" t="s">
         <v>19</v>
       </c>
       <c r="K1416" t="s">
-        <v>254</v>
+        <v>298</v>
       </c>
       <c r="L1416">
         <v>0</v>
@@ -69469,34 +69609,34 @@
         <v>46284</v>
       </c>
       <c r="B1417" t="s">
-        <v>708</v>
+        <v>77</v>
       </c>
       <c r="C1417">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1417">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1417" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1417" t="s">
-        <v>286</v>
+        <v>2202</v>
       </c>
       <c r="G1417" t="s">
-        <v>284</v>
+        <v>2203</v>
       </c>
       <c r="H1417" t="s">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="I1417" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1417" t="s">
         <v>19</v>
       </c>
       <c r="K1417" t="s">
-        <v>284</v>
+        <v>2203</v>
       </c>
       <c r="L1417">
         <v>0</v>
@@ -69513,34 +69653,34 @@
         <v>46284</v>
       </c>
       <c r="B1418" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="C1418">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1418">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1418" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1418" t="s">
-        <v>1656</v>
+        <v>498</v>
       </c>
       <c r="G1418" t="s">
-        <v>266</v>
+        <v>471</v>
       </c>
       <c r="H1418" t="s">
-        <v>1474</v>
+        <v>153</v>
       </c>
       <c r="I1418" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1418" t="s">
         <v>19</v>
       </c>
       <c r="K1418" t="s">
-        <v>266</v>
+        <v>471</v>
       </c>
       <c r="L1418">
         <v>0</v>
@@ -69557,25 +69697,25 @@
         <v>46284</v>
       </c>
       <c r="B1419" t="s">
-        <v>529</v>
+        <v>708</v>
       </c>
       <c r="C1419">
         <v>1</v>
       </c>
       <c r="D1419">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1419" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1419" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="G1419" t="s">
-        <v>196</v>
+        <v>284</v>
       </c>
       <c r="H1419" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="I1419" t="s">
         <v>23</v>
@@ -69584,7 +69724,7 @@
         <v>19</v>
       </c>
       <c r="K1419" t="s">
-        <v>196</v>
+        <v>284</v>
       </c>
       <c r="L1419">
         <v>0</v>
@@ -69601,25 +69741,25 @@
         <v>46284</v>
       </c>
       <c r="B1420" t="s">
-        <v>156</v>
+        <v>703</v>
       </c>
       <c r="C1420">
         <v>1</v>
       </c>
       <c r="D1420">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1420" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1420" t="s">
-        <v>296</v>
+        <v>474</v>
       </c>
       <c r="G1420" t="s">
-        <v>254</v>
+        <v>545</v>
       </c>
       <c r="H1420" t="s">
-        <v>208</v>
+        <v>276</v>
       </c>
       <c r="I1420" t="s">
         <v>28</v>
@@ -69628,7 +69768,7 @@
         <v>19</v>
       </c>
       <c r="K1420" t="s">
-        <v>254</v>
+        <v>545</v>
       </c>
       <c r="L1420">
         <v>0</v>
@@ -69645,25 +69785,25 @@
         <v>46284</v>
       </c>
       <c r="B1421" t="s">
-        <v>517</v>
+        <v>271</v>
       </c>
       <c r="C1421">
         <v>1</v>
       </c>
       <c r="D1421">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1421" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1421" t="s">
-        <v>2237</v>
+        <v>1220</v>
       </c>
       <c r="G1421" t="s">
-        <v>700</v>
+        <v>19</v>
       </c>
       <c r="H1421" t="s">
-        <v>524</v>
+        <v>1220</v>
       </c>
       <c r="I1421" t="s">
         <v>23</v>
@@ -69672,7 +69812,7 @@
         <v>19</v>
       </c>
       <c r="K1421" t="s">
-        <v>700</v>
+        <v>19</v>
       </c>
       <c r="L1421">
         <v>0</v>
@@ -69689,7 +69829,7 @@
         <v>46284</v>
       </c>
       <c r="B1422" t="s">
-        <v>89</v>
+        <v>246</v>
       </c>
       <c r="C1422">
         <v>1</v>
@@ -69701,13 +69841,13 @@
         <v>1</v>
       </c>
       <c r="F1422" t="s">
-        <v>303</v>
+        <v>1656</v>
       </c>
       <c r="G1422" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="H1422" t="s">
-        <v>321</v>
+        <v>1474</v>
       </c>
       <c r="I1422" t="s">
         <v>23</v>
@@ -69716,7 +69856,7 @@
         <v>19</v>
       </c>
       <c r="K1422" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="L1422">
         <v>0</v>
@@ -69733,7 +69873,7 @@
         <v>46284</v>
       </c>
       <c r="B1423" t="s">
-        <v>198</v>
+        <v>529</v>
       </c>
       <c r="C1423">
         <v>1</v>
@@ -69745,22 +69885,22 @@
         <v>1</v>
       </c>
       <c r="F1423" t="s">
-        <v>545</v>
+        <v>293</v>
       </c>
       <c r="G1423" t="s">
-        <v>300</v>
+        <v>196</v>
       </c>
       <c r="H1423" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="I1423" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1423" t="s">
         <v>19</v>
       </c>
       <c r="K1423" t="s">
-        <v>300</v>
+        <v>196</v>
       </c>
       <c r="L1423">
         <v>0</v>
@@ -69777,34 +69917,34 @@
         <v>46284</v>
       </c>
       <c r="B1424" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="C1424">
         <v>1</v>
       </c>
       <c r="D1424">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1424" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1424" t="s">
-        <v>1342</v>
+        <v>296</v>
       </c>
       <c r="G1424" t="s">
-        <v>700</v>
+        <v>254</v>
       </c>
       <c r="H1424" t="s">
-        <v>474</v>
+        <v>208</v>
       </c>
       <c r="I1424" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1424" t="s">
         <v>19</v>
       </c>
       <c r="K1424" t="s">
-        <v>700</v>
+        <v>254</v>
       </c>
       <c r="L1424">
         <v>0</v>
@@ -69821,7 +69961,7 @@
         <v>46284</v>
       </c>
       <c r="B1425" t="s">
-        <v>302</v>
+        <v>517</v>
       </c>
       <c r="C1425">
         <v>1</v>
@@ -69833,22 +69973,22 @@
         <v>1</v>
       </c>
       <c r="F1425" t="s">
-        <v>303</v>
+        <v>2204</v>
       </c>
       <c r="G1425" t="s">
-        <v>303</v>
+        <v>700</v>
       </c>
       <c r="H1425" t="s">
-        <v>304</v>
+        <v>524</v>
       </c>
       <c r="I1425" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1425" t="s">
         <v>19</v>
       </c>
       <c r="K1425" t="s">
-        <v>303</v>
+        <v>700</v>
       </c>
       <c r="L1425">
         <v>0</v>
@@ -69865,47 +70005,2115 @@
         <v>46284</v>
       </c>
       <c r="B1426" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1426">
+        <v>1</v>
+      </c>
+      <c r="D1426">
+        <v>1</v>
+      </c>
+      <c r="E1426" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1426" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1426" t="s">
+        <v>258</v>
+      </c>
+      <c r="H1426" t="s">
+        <v>321</v>
+      </c>
+      <c r="I1426" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1426" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1426" t="s">
+        <v>258</v>
+      </c>
+      <c r="L1426">
+        <v>0</v>
+      </c>
+      <c r="M1426" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:14">
+      <c r="A1427" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1427">
+        <v>1</v>
+      </c>
+      <c r="D1427">
+        <v>1</v>
+      </c>
+      <c r="E1427" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1427" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1427" t="s">
+        <v>300</v>
+      </c>
+      <c r="H1427" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1427" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1427" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1427" t="s">
+        <v>300</v>
+      </c>
+      <c r="L1427">
+        <v>0</v>
+      </c>
+      <c r="M1427" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:14">
+      <c r="A1428" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1428">
+        <v>1</v>
+      </c>
+      <c r="D1428">
+        <v>1</v>
+      </c>
+      <c r="E1428" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1428" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1428" t="s">
+        <v>303</v>
+      </c>
+      <c r="H1428" t="s">
+        <v>304</v>
+      </c>
+      <c r="I1428" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1428" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1428" t="s">
+        <v>303</v>
+      </c>
+      <c r="L1428">
+        <v>0</v>
+      </c>
+      <c r="M1428" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:14">
+      <c r="A1429" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1429">
+        <v>1</v>
+      </c>
+      <c r="D1429">
+        <v>1</v>
+      </c>
+      <c r="E1429" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1429" t="s">
+        <v>311</v>
+      </c>
+      <c r="G1429" t="s">
+        <v>312</v>
+      </c>
+      <c r="H1429" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1429" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1429" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1429" t="s">
+        <v>312</v>
+      </c>
+      <c r="L1429">
+        <v>0</v>
+      </c>
+      <c r="M1429" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:14">
+      <c r="A1430" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B1430" t="s">
         <v>525</v>
       </c>
-      <c r="C1426">
-        <v>1</v>
-      </c>
-      <c r="D1426">
-        <v>1</v>
-      </c>
-      <c r="E1426" s="4">
-        <v>1</v>
-      </c>
-      <c r="F1426" t="s">
+      <c r="C1430">
+        <v>1</v>
+      </c>
+      <c r="D1430">
+        <v>1</v>
+      </c>
+      <c r="E1430" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1430" t="s">
         <v>699</v>
       </c>
-      <c r="G1426" t="s">
+      <c r="G1430" t="s">
         <v>700</v>
       </c>
-      <c r="H1426" t="s">
+      <c r="H1430" t="s">
         <v>701</v>
       </c>
-      <c r="I1426" t="s">
+      <c r="I1430" t="s">
         <v>28</v>
       </c>
-      <c r="J1426" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1426" t="s">
+      <c r="J1430" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1430" t="s">
         <v>700</v>
       </c>
-      <c r="L1426">
-        <v>0</v>
-      </c>
-      <c r="M1426" s="4">
-        <v>0</v>
-      </c>
-      <c r="N1426">
+      <c r="L1430">
+        <v>0</v>
+      </c>
+      <c r="M1430" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:14">
+      <c r="A1431" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1431">
+        <v>6261</v>
+      </c>
+      <c r="D1431">
+        <v>6024</v>
+      </c>
+      <c r="E1431" s="3">
+        <v>0.96214659999999996</v>
+      </c>
+      <c r="F1431" t="s">
+        <v>2252</v>
+      </c>
+      <c r="G1431" t="s">
+        <v>2253</v>
+      </c>
+      <c r="H1431" t="s">
+        <v>2254</v>
+      </c>
+      <c r="I1431" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1431" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1431" t="s">
+        <v>2253</v>
+      </c>
+      <c r="L1431">
+        <v>0</v>
+      </c>
+      <c r="M1431" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:14">
+      <c r="A1432" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1432">
+        <v>2261</v>
+      </c>
+      <c r="D1432">
+        <v>2141</v>
+      </c>
+      <c r="E1432" s="3">
+        <v>0.94692609999999999</v>
+      </c>
+      <c r="F1432" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G1432" t="s">
+        <v>2256</v>
+      </c>
+      <c r="H1432" t="s">
+        <v>2257</v>
+      </c>
+      <c r="I1432" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1432" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1432" t="s">
+        <v>2256</v>
+      </c>
+      <c r="L1432">
+        <v>0</v>
+      </c>
+      <c r="M1432" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:14">
+      <c r="A1433" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1433">
+        <v>251</v>
+      </c>
+      <c r="D1433">
+        <v>193</v>
+      </c>
+      <c r="E1433" s="3">
+        <v>0.76892430000000001</v>
+      </c>
+      <c r="F1433" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G1433" t="s">
+        <v>2259</v>
+      </c>
+      <c r="H1433" t="s">
+        <v>2260</v>
+      </c>
+      <c r="I1433" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1433" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1433" t="s">
+        <v>2259</v>
+      </c>
+      <c r="L1433">
+        <v>0</v>
+      </c>
+      <c r="M1433" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:14">
+      <c r="A1434" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1434">
+        <v>198</v>
+      </c>
+      <c r="D1434">
+        <v>198</v>
+      </c>
+      <c r="E1434" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1434" t="s">
+        <v>2198</v>
+      </c>
+      <c r="G1434" t="s">
+        <v>2261</v>
+      </c>
+      <c r="H1434" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I1434" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1434" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1434" t="s">
+        <v>2261</v>
+      </c>
+      <c r="L1434">
+        <v>0</v>
+      </c>
+      <c r="M1434" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:14">
+      <c r="A1435" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1435">
+        <v>114</v>
+      </c>
+      <c r="D1435">
+        <v>94</v>
+      </c>
+      <c r="E1435" s="3">
+        <v>0.8245614</v>
+      </c>
+      <c r="F1435" t="s">
+        <v>2263</v>
+      </c>
+      <c r="G1435" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H1435" t="s">
+        <v>2264</v>
+      </c>
+      <c r="I1435" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1435" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1435" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L1435">
+        <v>0</v>
+      </c>
+      <c r="M1435" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:14">
+      <c r="A1436" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1436">
+        <v>99</v>
+      </c>
+      <c r="D1436">
+        <v>94</v>
+      </c>
+      <c r="E1436" s="3">
+        <v>0.94949490000000003</v>
+      </c>
+      <c r="F1436" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G1436" t="s">
+        <v>2266</v>
+      </c>
+      <c r="H1436" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I1436" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1436" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1436" t="s">
+        <v>2266</v>
+      </c>
+      <c r="L1436">
+        <v>0</v>
+      </c>
+      <c r="M1436" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:14">
+      <c r="A1437" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1437">
+        <v>66</v>
+      </c>
+      <c r="D1437">
+        <v>62</v>
+      </c>
+      <c r="E1437" s="3">
+        <v>0.9393939</v>
+      </c>
+      <c r="F1437" t="s">
+        <v>2066</v>
+      </c>
+      <c r="G1437" t="s">
+        <v>2267</v>
+      </c>
+      <c r="H1437" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I1437" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1437" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1437" t="s">
+        <v>2267</v>
+      </c>
+      <c r="L1437">
+        <v>0</v>
+      </c>
+      <c r="M1437" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:14">
+      <c r="A1438" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1438">
+        <v>38</v>
+      </c>
+      <c r="D1438">
+        <v>0</v>
+      </c>
+      <c r="E1438" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1438" t="s">
+        <v>2268</v>
+      </c>
+      <c r="G1438" t="s">
+        <v>2269</v>
+      </c>
+      <c r="H1438" t="s">
+        <v>2270</v>
+      </c>
+      <c r="I1438" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1438" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1438" t="s">
+        <v>2269</v>
+      </c>
+      <c r="L1438">
+        <v>0</v>
+      </c>
+      <c r="M1438" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:14">
+      <c r="A1439" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1439">
+        <v>31</v>
+      </c>
+      <c r="D1439">
+        <v>27</v>
+      </c>
+      <c r="E1439" s="3">
+        <v>0.87096770000000001</v>
+      </c>
+      <c r="F1439" t="s">
+        <v>893</v>
+      </c>
+      <c r="G1439" t="s">
+        <v>2271</v>
+      </c>
+      <c r="H1439" t="s">
+        <v>2272</v>
+      </c>
+      <c r="I1439" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1439" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1439" t="s">
+        <v>2271</v>
+      </c>
+      <c r="L1439">
+        <v>0</v>
+      </c>
+      <c r="M1439" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:14">
+      <c r="A1440" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1440">
+        <v>17</v>
+      </c>
+      <c r="D1440">
+        <v>16</v>
+      </c>
+      <c r="E1440" s="3">
+        <v>0.94117649999999997</v>
+      </c>
+      <c r="F1440" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G1440" t="s">
+        <v>1790</v>
+      </c>
+      <c r="H1440" t="s">
+        <v>1791</v>
+      </c>
+      <c r="I1440" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1440" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1440" t="s">
+        <v>1790</v>
+      </c>
+      <c r="L1440">
+        <v>0</v>
+      </c>
+      <c r="M1440" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:14">
+      <c r="A1441" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1441">
+        <v>15</v>
+      </c>
+      <c r="D1441">
+        <v>6</v>
+      </c>
+      <c r="E1441" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="F1441" t="s">
+        <v>2273</v>
+      </c>
+      <c r="G1441" t="s">
+        <v>2274</v>
+      </c>
+      <c r="H1441" t="s">
+        <v>2275</v>
+      </c>
+      <c r="I1441" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1441" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1441" t="s">
+        <v>2274</v>
+      </c>
+      <c r="L1441">
+        <v>0</v>
+      </c>
+      <c r="M1441" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:14">
+      <c r="A1442" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1442">
+        <v>15</v>
+      </c>
+      <c r="D1442">
+        <v>8</v>
+      </c>
+      <c r="E1442" s="3">
+        <v>0.53333330000000001</v>
+      </c>
+      <c r="F1442" t="s">
+        <v>2276</v>
+      </c>
+      <c r="G1442" t="s">
+        <v>1483</v>
+      </c>
+      <c r="H1442" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I1442" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1442" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1442" t="s">
+        <v>1483</v>
+      </c>
+      <c r="L1442">
+        <v>0</v>
+      </c>
+      <c r="M1442" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:14">
+      <c r="A1443" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1443">
+        <v>12</v>
+      </c>
+      <c r="D1443">
+        <v>1</v>
+      </c>
+      <c r="E1443" s="3">
+        <v>8.3333299999999999E-2</v>
+      </c>
+      <c r="F1443" t="s">
+        <v>2278</v>
+      </c>
+      <c r="G1443" t="s">
+        <v>2279</v>
+      </c>
+      <c r="H1443" t="s">
+        <v>809</v>
+      </c>
+      <c r="I1443" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1443" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1443" t="s">
+        <v>2279</v>
+      </c>
+      <c r="L1443">
+        <v>0</v>
+      </c>
+      <c r="M1443" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:14">
+      <c r="A1444" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1444">
+        <v>11</v>
+      </c>
+      <c r="D1444">
+        <v>11</v>
+      </c>
+      <c r="E1444" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1444" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G1444" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H1444" t="s">
+        <v>755</v>
+      </c>
+      <c r="I1444" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1444" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1444" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L1444">
+        <v>0</v>
+      </c>
+      <c r="M1444" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:14">
+      <c r="A1445" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1445">
+        <v>8</v>
+      </c>
+      <c r="D1445">
+        <v>8</v>
+      </c>
+      <c r="E1445" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1445" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1445" t="s">
+        <v>2020</v>
+      </c>
+      <c r="H1445" t="s">
+        <v>2280</v>
+      </c>
+      <c r="I1445" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1445" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1445" t="s">
+        <v>2020</v>
+      </c>
+      <c r="L1445">
+        <v>0</v>
+      </c>
+      <c r="M1445" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:14">
+      <c r="A1446" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1446">
+        <v>8</v>
+      </c>
+      <c r="D1446">
+        <v>1</v>
+      </c>
+      <c r="E1446" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="F1446" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G1446" t="s">
+        <v>2282</v>
+      </c>
+      <c r="H1446" t="s">
+        <v>663</v>
+      </c>
+      <c r="I1446" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1446" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1446" t="s">
+        <v>2282</v>
+      </c>
+      <c r="L1446">
+        <v>0</v>
+      </c>
+      <c r="M1446" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:14">
+      <c r="A1447" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1447">
+        <v>5</v>
+      </c>
+      <c r="D1447">
+        <v>5</v>
+      </c>
+      <c r="E1447" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1447" t="s">
+        <v>316</v>
+      </c>
+      <c r="G1447" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1447" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1447" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1447" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1447" t="s">
+        <v>163</v>
+      </c>
+      <c r="L1447">
+        <v>0</v>
+      </c>
+      <c r="M1447" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:14">
+      <c r="A1448" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1448">
+        <v>5</v>
+      </c>
+      <c r="D1448">
+        <v>0</v>
+      </c>
+      <c r="E1448" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1448" t="s">
+        <v>2283</v>
+      </c>
+      <c r="G1448" t="s">
+        <v>2284</v>
+      </c>
+      <c r="H1448" t="s">
+        <v>496</v>
+      </c>
+      <c r="I1448" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1448" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1448" t="s">
+        <v>2284</v>
+      </c>
+      <c r="L1448">
+        <v>0</v>
+      </c>
+      <c r="M1448" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:14">
+      <c r="A1449" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1449">
+        <v>5</v>
+      </c>
+      <c r="D1449">
+        <v>3</v>
+      </c>
+      <c r="E1449" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="F1449" t="s">
+        <v>919</v>
+      </c>
+      <c r="G1449" t="s">
+        <v>2250</v>
+      </c>
+      <c r="H1449" t="s">
+        <v>504</v>
+      </c>
+      <c r="I1449" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1449" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1449" t="s">
+        <v>2250</v>
+      </c>
+      <c r="L1449">
+        <v>0</v>
+      </c>
+      <c r="M1449" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:14">
+      <c r="A1450" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1450">
+        <v>4</v>
+      </c>
+      <c r="D1450">
+        <v>0</v>
+      </c>
+      <c r="E1450" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1450" t="s">
+        <v>251</v>
+      </c>
+      <c r="G1450" t="s">
+        <v>252</v>
+      </c>
+      <c r="H1450" t="s">
+        <v>253</v>
+      </c>
+      <c r="I1450" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1450" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1450" t="s">
+        <v>252</v>
+      </c>
+      <c r="L1450">
+        <v>0</v>
+      </c>
+      <c r="M1450" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:14">
+      <c r="A1451" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>660</v>
+      </c>
+      <c r="C1451">
+        <v>4</v>
+      </c>
+      <c r="D1451">
+        <v>1</v>
+      </c>
+      <c r="E1451" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="F1451" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1451" t="s">
+        <v>527</v>
+      </c>
+      <c r="H1451" t="s">
+        <v>283</v>
+      </c>
+      <c r="I1451" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1451" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1451" t="s">
+        <v>527</v>
+      </c>
+      <c r="L1451">
+        <v>0</v>
+      </c>
+      <c r="M1451" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:14">
+      <c r="A1452" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1452">
+        <v>4</v>
+      </c>
+      <c r="D1452">
+        <v>0</v>
+      </c>
+      <c r="E1452" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1452" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1452" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H1452" t="s">
+        <v>540</v>
+      </c>
+      <c r="I1452" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1452" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1452" t="s">
+        <v>1199</v>
+      </c>
+      <c r="L1452">
+        <v>0</v>
+      </c>
+      <c r="M1452" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:14">
+      <c r="A1453" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1453">
+        <v>4</v>
+      </c>
+      <c r="D1453">
+        <v>3</v>
+      </c>
+      <c r="E1453" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F1453" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1453" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1453" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1453" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1453" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1453" t="s">
+        <v>276</v>
+      </c>
+      <c r="L1453">
+        <v>0</v>
+      </c>
+      <c r="M1453" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:14">
+      <c r="A1454" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1454">
+        <v>3</v>
+      </c>
+      <c r="D1454">
+        <v>3</v>
+      </c>
+      <c r="E1454" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1454" t="s">
+        <v>453</v>
+      </c>
+      <c r="G1454" t="s">
+        <v>495</v>
+      </c>
+      <c r="H1454" t="s">
+        <v>496</v>
+      </c>
+      <c r="I1454" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1454" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1454" t="s">
+        <v>495</v>
+      </c>
+      <c r="L1454">
+        <v>0</v>
+      </c>
+      <c r="M1454" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:14">
+      <c r="A1455" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1455">
+        <v>3</v>
+      </c>
+      <c r="D1455">
+        <v>3</v>
+      </c>
+      <c r="E1455" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1455" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1455" t="s">
+        <v>495</v>
+      </c>
+      <c r="H1455" t="s">
+        <v>281</v>
+      </c>
+      <c r="I1455" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1455" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1455" t="s">
+        <v>495</v>
+      </c>
+      <c r="L1455">
+        <v>0</v>
+      </c>
+      <c r="M1455" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:14">
+      <c r="A1456" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1456">
+        <v>3</v>
+      </c>
+      <c r="D1456">
+        <v>1</v>
+      </c>
+      <c r="E1456" s="3">
+        <v>0.3333333</v>
+      </c>
+      <c r="F1456" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1456" t="s">
+        <v>303</v>
+      </c>
+      <c r="H1456" t="s">
+        <v>304</v>
+      </c>
+      <c r="I1456" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1456" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1456" t="s">
+        <v>303</v>
+      </c>
+      <c r="L1456">
+        <v>0</v>
+      </c>
+      <c r="M1456" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:14">
+      <c r="A1457" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1457" t="s">
+        <v>708</v>
+      </c>
+      <c r="C1457">
+        <v>3</v>
+      </c>
+      <c r="D1457">
+        <v>0</v>
+      </c>
+      <c r="E1457" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1457" t="s">
+        <v>293</v>
+      </c>
+      <c r="G1457" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1457" t="s">
+        <v>314</v>
+      </c>
+      <c r="I1457" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1457" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1457" t="s">
+        <v>276</v>
+      </c>
+      <c r="L1457">
+        <v>0</v>
+      </c>
+      <c r="M1457" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:14">
+      <c r="A1458" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1458">
+        <v>2</v>
+      </c>
+      <c r="D1458">
+        <v>0</v>
+      </c>
+      <c r="E1458" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1458" t="s">
+        <v>538</v>
+      </c>
+      <c r="G1458" t="s">
+        <v>210</v>
+      </c>
+      <c r="H1458" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1458" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1458" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1458" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1458">
+        <v>0</v>
+      </c>
+      <c r="M1458" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:14">
+      <c r="A1459" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1459" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1459">
+        <v>2</v>
+      </c>
+      <c r="D1459">
+        <v>0</v>
+      </c>
+      <c r="E1459" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1459" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1459" t="s">
+        <v>929</v>
+      </c>
+      <c r="H1459" t="s">
+        <v>504</v>
+      </c>
+      <c r="I1459" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1459" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1459" t="s">
+        <v>929</v>
+      </c>
+      <c r="L1459">
+        <v>0</v>
+      </c>
+      <c r="M1459" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:14">
+      <c r="A1460" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1460" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1460">
+        <v>2</v>
+      </c>
+      <c r="D1460">
+        <v>2</v>
+      </c>
+      <c r="E1460" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1460" t="s">
+        <v>507</v>
+      </c>
+      <c r="G1460" t="s">
+        <v>293</v>
+      </c>
+      <c r="H1460" t="s">
+        <v>514</v>
+      </c>
+      <c r="I1460" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1460" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1460" t="s">
+        <v>293</v>
+      </c>
+      <c r="L1460">
+        <v>0</v>
+      </c>
+      <c r="M1460" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:14">
+      <c r="A1461" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1461" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1461">
+        <v>2</v>
+      </c>
+      <c r="D1461">
+        <v>1</v>
+      </c>
+      <c r="E1461" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1461" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1461" t="s">
+        <v>311</v>
+      </c>
+      <c r="H1461" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1461" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1461" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1461" t="s">
+        <v>311</v>
+      </c>
+      <c r="L1461">
+        <v>0</v>
+      </c>
+      <c r="M1461" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:14">
+      <c r="A1462" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1462">
+        <v>2</v>
+      </c>
+      <c r="D1462">
+        <v>2</v>
+      </c>
+      <c r="E1462" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1462" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1462" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1462" t="s">
+        <v>1220</v>
+      </c>
+      <c r="I1462" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1462" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1462" t="s">
+        <v>698</v>
+      </c>
+      <c r="L1462">
+        <v>0</v>
+      </c>
+      <c r="M1462" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:14">
+      <c r="A1463" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>493</v>
+      </c>
+      <c r="C1463">
+        <v>2</v>
+      </c>
+      <c r="D1463">
+        <v>2</v>
+      </c>
+      <c r="E1463" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1463" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1463" t="s">
+        <v>205</v>
+      </c>
+      <c r="H1463" t="s">
+        <v>457</v>
+      </c>
+      <c r="I1463" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1463" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1463" t="s">
+        <v>205</v>
+      </c>
+      <c r="L1463">
+        <v>0</v>
+      </c>
+      <c r="M1463" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:14">
+      <c r="A1464" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1464">
+        <v>2</v>
+      </c>
+      <c r="D1464">
+        <v>2</v>
+      </c>
+      <c r="E1464" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1464" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1464" t="s">
+        <v>304</v>
+      </c>
+      <c r="H1464" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1464" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1464" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1464" t="s">
+        <v>304</v>
+      </c>
+      <c r="L1464">
+        <v>0</v>
+      </c>
+      <c r="M1464" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:14">
+      <c r="A1465" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1465">
+        <v>1</v>
+      </c>
+      <c r="D1465">
+        <v>1</v>
+      </c>
+      <c r="E1465" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1465" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G1465" t="s">
+        <v>698</v>
+      </c>
+      <c r="H1465" t="s">
+        <v>541</v>
+      </c>
+      <c r="I1465" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1465" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1465" t="s">
+        <v>698</v>
+      </c>
+      <c r="L1465">
+        <v>0</v>
+      </c>
+      <c r="M1465" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:14">
+      <c r="A1466" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1466">
+        <v>1</v>
+      </c>
+      <c r="D1466">
+        <v>0</v>
+      </c>
+      <c r="E1466" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1466" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G1466" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1466" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1466" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1466" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1466" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1466">
+        <v>0</v>
+      </c>
+      <c r="M1466" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:14">
+      <c r="A1467" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1467">
+        <v>1</v>
+      </c>
+      <c r="D1467">
+        <v>1</v>
+      </c>
+      <c r="E1467" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1467" t="s">
+        <v>849</v>
+      </c>
+      <c r="G1467" t="s">
+        <v>306</v>
+      </c>
+      <c r="H1467" t="s">
+        <v>850</v>
+      </c>
+      <c r="I1467" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1467" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1467" t="s">
+        <v>306</v>
+      </c>
+      <c r="L1467">
+        <v>0</v>
+      </c>
+      <c r="M1467" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:14">
+      <c r="A1468" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1468">
+        <v>1</v>
+      </c>
+      <c r="D1468">
+        <v>0</v>
+      </c>
+      <c r="E1468" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1468" t="s">
+        <v>254</v>
+      </c>
+      <c r="G1468" t="s">
+        <v>803</v>
+      </c>
+      <c r="H1468" t="s">
+        <v>541</v>
+      </c>
+      <c r="I1468" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1468" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1468" t="s">
+        <v>803</v>
+      </c>
+      <c r="L1468">
+        <v>0</v>
+      </c>
+      <c r="M1468" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:14">
+      <c r="A1469" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1469">
+        <v>1</v>
+      </c>
+      <c r="D1469">
+        <v>1</v>
+      </c>
+      <c r="E1469" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1469" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1469" t="s">
+        <v>314</v>
+      </c>
+      <c r="H1469" t="s">
+        <v>297</v>
+      </c>
+      <c r="I1469" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1469" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1469" t="s">
+        <v>314</v>
+      </c>
+      <c r="L1469">
+        <v>0</v>
+      </c>
+      <c r="M1469" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:14">
+      <c r="A1470" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C1470">
+        <v>1</v>
+      </c>
+      <c r="D1470">
+        <v>1</v>
+      </c>
+      <c r="E1470" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1470" t="s">
+        <v>300</v>
+      </c>
+      <c r="G1470" t="s">
+        <v>293</v>
+      </c>
+      <c r="H1470" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1470" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1470" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1470" t="s">
+        <v>293</v>
+      </c>
+      <c r="L1470">
+        <v>0</v>
+      </c>
+      <c r="M1470" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:14">
+      <c r="A1471" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1471">
+        <v>1</v>
+      </c>
+      <c r="D1471">
+        <v>1</v>
+      </c>
+      <c r="E1471" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1471" t="s">
+        <v>284</v>
+      </c>
+      <c r="G1471" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1471" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1471" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1471" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1471" t="s">
+        <v>235</v>
+      </c>
+      <c r="L1471">
+        <v>0</v>
+      </c>
+      <c r="M1471" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:14">
+      <c r="A1472" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1472">
+        <v>1</v>
+      </c>
+      <c r="D1472">
+        <v>0</v>
+      </c>
+      <c r="E1472" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1472" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G1472" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1472" t="s">
+        <v>314</v>
+      </c>
+      <c r="I1472" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1472" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1472" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1472">
+        <v>0</v>
+      </c>
+      <c r="M1472" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:14">
+      <c r="A1473" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C1473">
+        <v>1</v>
+      </c>
+      <c r="D1473">
+        <v>1</v>
+      </c>
+      <c r="E1473" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1473" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1473" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1473" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1473" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1473" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1473" t="s">
+        <v>254</v>
+      </c>
+      <c r="L1473">
+        <v>0</v>
+      </c>
+      <c r="M1473" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1473">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1373"/>
+  <autoFilter ref="A1:N1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\new clone\Salefile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9C5B0F-A56F-4A57-8D2B-E3E8385ADF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4B8AA9-CECA-4135-8A69-6D509664554F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10318" uniqueCount="2285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11473" uniqueCount="2457">
   <si>
     <t>Date</t>
   </si>
@@ -6807,94 +6807,610 @@
     <t>16.59165 EUR</t>
   </si>
   <si>
-    <t>14.1015 EUR</t>
-  </si>
-  <si>
-    <t>8.5085 EUR</t>
-  </si>
-  <si>
-    <t>22.61 EUR</t>
-  </si>
-  <si>
-    <t>5.28104 EUR</t>
-  </si>
-  <si>
-    <t>12.4998 EUR</t>
-  </si>
-  <si>
-    <t>17.78084 EUR</t>
-  </si>
-  <si>
-    <t>1.4652 EUR</t>
-  </si>
-  <si>
-    <t>1.584 EUR</t>
-  </si>
-  <si>
-    <t>1.0172 EUR</t>
-  </si>
-  <si>
-    <t>3.4364 EUR</t>
-  </si>
-  <si>
     <t>0.5445 EUR</t>
   </si>
   <si>
     <t>0.4455 EUR</t>
   </si>
   <si>
-    <t>0.3136 EUR</t>
-  </si>
-  <si>
-    <t>0.48688 EUR</t>
-  </si>
-  <si>
-    <t>0.12113 EUR</t>
-  </si>
-  <si>
-    <t>0.608 EUR</t>
-  </si>
-  <si>
-    <t>2.12 EUR</t>
-  </si>
-  <si>
-    <t>2.57 EUR</t>
-  </si>
-  <si>
-    <t>0.2131 EUR</t>
-  </si>
-  <si>
-    <t>0.1736 EUR</t>
-  </si>
-  <si>
-    <t>0.3867 EUR</t>
-  </si>
-  <si>
     <t>0.3082 EUR</t>
   </si>
   <si>
     <t>0.3126 EUR</t>
   </si>
   <si>
-    <t>0.03581 EUR</t>
-  </si>
-  <si>
-    <t>0.16819 EUR</t>
-  </si>
-  <si>
     <t>0.3168 EUR</t>
   </si>
   <si>
-    <t>0.1286 EUR</t>
-  </si>
-  <si>
-    <t>0.0694 EUR</t>
-  </si>
-  <si>
     <t>0.02681 EUR</t>
   </si>
   <si>
     <t>0.06319 EUR</t>
+  </si>
+  <si>
+    <t>16.8115 EUR</t>
+  </si>
+  <si>
+    <t>10.1185 EUR</t>
+  </si>
+  <si>
+    <t>26.93 EUR</t>
+  </si>
+  <si>
+    <t>4.90245 EUR</t>
+  </si>
+  <si>
+    <t>4.08535 EUR</t>
+  </si>
+  <si>
+    <t>8.9878 EUR</t>
+  </si>
+  <si>
+    <t>6.66968 EUR</t>
+  </si>
+  <si>
+    <t>15.7866 EUR</t>
+  </si>
+  <si>
+    <t>22.45628 EUR</t>
+  </si>
+  <si>
+    <t>0.1296 EUR</t>
+  </si>
+  <si>
+    <t>1.5984 EUR</t>
+  </si>
+  <si>
+    <t>1.728 EUR</t>
+  </si>
+  <si>
+    <t>1.2162 EUR</t>
+  </si>
+  <si>
+    <t>2.6852 EUR</t>
+  </si>
+  <si>
+    <t>3.9014 EUR</t>
+  </si>
+  <si>
+    <t>0.293 EUR</t>
+  </si>
+  <si>
+    <t>0.621 EUR</t>
+  </si>
+  <si>
+    <t>0.814 EUR</t>
+  </si>
+  <si>
+    <t>3.576 EUR</t>
+  </si>
+  <si>
+    <t>4.39 EUR</t>
+  </si>
+  <si>
+    <t>0.52531 EUR</t>
+  </si>
+  <si>
+    <t>0.13069 EUR</t>
+  </si>
+  <si>
+    <t>0.656 EUR</t>
+  </si>
+  <si>
+    <t>0.504 EUR</t>
+  </si>
+  <si>
+    <t>2.412 EUR</t>
+  </si>
+  <si>
+    <t>0.3288 EUR</t>
+  </si>
+  <si>
+    <t>0.1452 EUR</t>
+  </si>
+  <si>
+    <t>0.474 EUR</t>
+  </si>
+  <si>
+    <t>0.2711 EUR</t>
+  </si>
+  <si>
+    <t>0.1966 EUR</t>
+  </si>
+  <si>
+    <t>0.4677 EUR</t>
+  </si>
+  <si>
+    <t>0.03981 EUR</t>
+  </si>
+  <si>
+    <t>0.19819 EUR</t>
+  </si>
+  <si>
+    <t>0.0822 EUR</t>
+  </si>
+  <si>
+    <t>0.1062 EUR</t>
+  </si>
+  <si>
+    <t>0.0318 EUR</t>
+  </si>
+  <si>
+    <t>0.00186 EUR</t>
+  </si>
+  <si>
+    <t>0.02886 EUR</t>
+  </si>
+  <si>
+    <t>9.89 EUR</t>
+  </si>
+  <si>
+    <t>5.93 EUR</t>
+  </si>
+  <si>
+    <t>15.82 EUR</t>
+  </si>
+  <si>
+    <t>0.828 EUR</t>
+  </si>
+  <si>
+    <t>10.212 EUR</t>
+  </si>
+  <si>
+    <t>11.04 EUR</t>
+  </si>
+  <si>
+    <t>0.48535 EUR</t>
+  </si>
+  <si>
+    <t>1.05525 EUR</t>
+  </si>
+  <si>
+    <t>1.5406 EUR</t>
+  </si>
+  <si>
+    <t>1 EUR</t>
+  </si>
+  <si>
+    <t>0.4388 EUR</t>
+  </si>
+  <si>
+    <t>0.3548 EUR</t>
+  </si>
+  <si>
+    <t>1.098 EUR</t>
+  </si>
+  <si>
+    <t>4.792 EUR</t>
+  </si>
+  <si>
+    <t>5.89 EUR</t>
+  </si>
+  <si>
+    <t>0.3222 EUR</t>
+  </si>
+  <si>
+    <t>0.639 EUR</t>
+  </si>
+  <si>
+    <t>0.6696 EUR</t>
+  </si>
+  <si>
+    <t>1.4384 EUR</t>
+  </si>
+  <si>
+    <t>2.108 EUR</t>
+  </si>
+  <si>
+    <t>0.1885 EUR</t>
+  </si>
+  <si>
+    <t>0.4307 EUR</t>
+  </si>
+  <si>
+    <t>0.6192 EUR</t>
+  </si>
+  <si>
+    <t>1.07382 EUR</t>
+  </si>
+  <si>
+    <t>2.5443 EUR</t>
+  </si>
+  <si>
+    <t>3.61812 EUR</t>
+  </si>
+  <si>
+    <t>0.7048 EUR</t>
+  </si>
+  <si>
+    <t>0.3252 EUR</t>
+  </si>
+  <si>
+    <t>1.03 EUR</t>
+  </si>
+  <si>
+    <t>1.222 EUR</t>
+  </si>
+  <si>
+    <t>1.296 EUR</t>
+  </si>
+  <si>
+    <t>0.821 EUR</t>
+  </si>
+  <si>
+    <t>1.114 EUR</t>
+  </si>
+  <si>
+    <t>0.49969 EUR</t>
+  </si>
+  <si>
+    <t>0.12431 EUR</t>
+  </si>
+  <si>
+    <t>0.624 EUR</t>
+  </si>
+  <si>
+    <t>0.0918 EUR</t>
+  </si>
+  <si>
+    <t>0.2054 EUR</t>
+  </si>
+  <si>
+    <t>0.05406 EUR</t>
+  </si>
+  <si>
+    <t>0.783 EUR</t>
+  </si>
+  <si>
+    <t>0.83706 EUR</t>
+  </si>
+  <si>
+    <t>0.65 EUR</t>
+  </si>
+  <si>
+    <t>2.08 EUR</t>
+  </si>
+  <si>
+    <t>2.73 EUR</t>
+  </si>
+  <si>
+    <t>0.28283 EUR</t>
+  </si>
+  <si>
+    <t>0.17118 EUR</t>
+  </si>
+  <si>
+    <t>0.454 EUR</t>
+  </si>
+  <si>
+    <t>0.552 EUR</t>
+  </si>
+  <si>
+    <t>0.0728 EUR</t>
+  </si>
+  <si>
+    <t>0.0149 EUR</t>
+  </si>
+  <si>
+    <t>0.0399 EUR</t>
+  </si>
+  <si>
+    <t>0.284 EUR</t>
+  </si>
+  <si>
+    <t>0.0841 EUR</t>
+  </si>
+  <si>
+    <t>0.3366 EUR</t>
+  </si>
+  <si>
+    <t>0.0544 EUR</t>
+  </si>
+  <si>
+    <t>0.938 EUR</t>
+  </si>
+  <si>
+    <t>0.06595 EUR</t>
+  </si>
+  <si>
+    <t>0.03545 EUR</t>
+  </si>
+  <si>
+    <t>0.1014 EUR</t>
+  </si>
+  <si>
+    <t>0.1525 EUR</t>
+  </si>
+  <si>
+    <t>0.0605 EUR</t>
+  </si>
+  <si>
+    <t>0.0512 EUR</t>
+  </si>
+  <si>
+    <t>0.0472 EUR</t>
+  </si>
+  <si>
+    <t>0.0984 EUR</t>
+  </si>
+  <si>
+    <t>0.1962 EUR</t>
+  </si>
+  <si>
+    <t>0.248 EUR</t>
+  </si>
+  <si>
+    <t>0.00875 EUR</t>
+  </si>
+  <si>
+    <t>0.0435 EUR</t>
+  </si>
+  <si>
+    <t>0.05225 EUR</t>
+  </si>
+  <si>
+    <t>0.1005 EUR</t>
+  </si>
+  <si>
+    <t>0.0545 EUR</t>
+  </si>
+  <si>
+    <t>0.155 EUR</t>
+  </si>
+  <si>
+    <t>WII_WHS(Client)</t>
+  </si>
+  <si>
+    <t>0.0534 EUR</t>
+  </si>
+  <si>
+    <t>0.17 EUR</t>
+  </si>
+  <si>
+    <t>0.00445 EUR</t>
+  </si>
+  <si>
+    <t>0.01155 EUR</t>
+  </si>
+  <si>
+    <t>0.0845 EUR</t>
+  </si>
+  <si>
+    <t>0.0712 EUR</t>
+  </si>
+  <si>
+    <t>BroadNet_WS(Client)</t>
+  </si>
+  <si>
+    <t>0.0328 EUR</t>
+  </si>
+  <si>
+    <t>0.0218 EUR</t>
+  </si>
+  <si>
+    <t>0.0095 EUR</t>
+  </si>
+  <si>
+    <t>24.9665 EUR</t>
+  </si>
+  <si>
+    <t>49.933 EUR</t>
+  </si>
+  <si>
+    <t>10.8785 EUR</t>
+  </si>
+  <si>
+    <t>6.5015 EUR</t>
+  </si>
+  <si>
+    <t>17.38 EUR</t>
+  </si>
+  <si>
+    <t>1.1415 EUR</t>
+  </si>
+  <si>
+    <t>15.981 EUR</t>
+  </si>
+  <si>
+    <t>17.1225 EUR</t>
+  </si>
+  <si>
+    <t>1.811 EUR</t>
+  </si>
+  <si>
+    <t>1.595 EUR</t>
+  </si>
+  <si>
+    <t>3.406 EUR</t>
+  </si>
+  <si>
+    <t>KiteTel Comm_Dir_(Client)</t>
+  </si>
+  <si>
+    <t>2.166 EUR</t>
+  </si>
+  <si>
+    <t>16.534 EUR</t>
+  </si>
+  <si>
+    <t>18.7 EUR</t>
+  </si>
+  <si>
+    <t>2.0987 EUR</t>
+  </si>
+  <si>
+    <t>2.276 EUR</t>
+  </si>
+  <si>
+    <t>0.1301 EUR</t>
+  </si>
+  <si>
+    <t>0.3219 EUR</t>
+  </si>
+  <si>
+    <t>0.452 EUR</t>
+  </si>
+  <si>
+    <t>0.3731 EUR</t>
+  </si>
+  <si>
+    <t>0.6293 EUR</t>
+  </si>
+  <si>
+    <t>1.0024 EUR</t>
+  </si>
+  <si>
+    <t>0.4345 EUR</t>
+  </si>
+  <si>
+    <t>0.3555 EUR</t>
+  </si>
+  <si>
+    <t>2.25 EUR</t>
+  </si>
+  <si>
+    <t>2.97 EUR</t>
+  </si>
+  <si>
+    <t>0.779 EUR</t>
+  </si>
+  <si>
+    <t>1.4352 EUR</t>
+  </si>
+  <si>
+    <t>2.2142 EUR</t>
+  </si>
+  <si>
+    <t>0.51788 EUR</t>
+  </si>
+  <si>
+    <t>0.58613 EUR</t>
+  </si>
+  <si>
+    <t>0.972 EUR</t>
+  </si>
+  <si>
+    <t>0.604 EUR</t>
+  </si>
+  <si>
+    <t>1.576 EUR</t>
+  </si>
+  <si>
+    <t>3.28 EUR</t>
+  </si>
+  <si>
+    <t>4.305 EUR</t>
+  </si>
+  <si>
+    <t>0.1872 EUR</t>
+  </si>
+  <si>
+    <t>0.7944 EUR</t>
+  </si>
+  <si>
+    <t>1.7928 EUR</t>
+  </si>
+  <si>
+    <t>2.5872 EUR</t>
+  </si>
+  <si>
+    <t>0.434 EUR</t>
+  </si>
+  <si>
+    <t>1.736 EUR</t>
+  </si>
+  <si>
+    <t>2.17 EUR</t>
+  </si>
+  <si>
+    <t>0.1127 EUR</t>
+  </si>
+  <si>
+    <t>0.2419 EUR</t>
+  </si>
+  <si>
+    <t>0.0257 EUR</t>
+  </si>
+  <si>
+    <t>0.4785 EUR</t>
+  </si>
+  <si>
+    <t>0.5042 EUR</t>
+  </si>
+  <si>
+    <t>0.2476 EUR</t>
+  </si>
+  <si>
+    <t>0.2034 EUR</t>
+  </si>
+  <si>
+    <t>0.451 EUR</t>
+  </si>
+  <si>
+    <t>0.1374 EUR</t>
+  </si>
+  <si>
+    <t>0.0816 EUR</t>
+  </si>
+  <si>
+    <t>0.219 EUR</t>
+  </si>
+  <si>
+    <t>0.0834 EUR</t>
+  </si>
+  <si>
+    <t>0.408 EUR</t>
+  </si>
+  <si>
+    <t>0.05496 EUR</t>
+  </si>
+  <si>
+    <t>0.43296 EUR</t>
+  </si>
+  <si>
+    <t>0.3305 EUR</t>
+  </si>
+  <si>
+    <t>0.3598 EUR</t>
+  </si>
+  <si>
+    <t>0.0566 EUR</t>
+  </si>
+  <si>
+    <t>0.09285 EUR</t>
+  </si>
+  <si>
+    <t>0.05805 EUR</t>
+  </si>
+  <si>
+    <t>0.1509 EUR</t>
+  </si>
+  <si>
+    <t>0.0944 EUR</t>
+  </si>
+  <si>
+    <t>0.0237 EUR</t>
+  </si>
+  <si>
+    <t>0.0518 EUR</t>
+  </si>
+  <si>
+    <t>Green_Packet_Dir_Sec(Client)</t>
+  </si>
+  <si>
+    <t>Vihat_HQ(Client)</t>
+  </si>
+  <si>
+    <t>0.0265 EUR</t>
+  </si>
+  <si>
+    <t>0.0438 EUR</t>
+  </si>
+  <si>
+    <t>Digiwhiff_HQ(Client)</t>
+  </si>
+  <si>
+    <t>TokyDig._SiM(Client)</t>
   </si>
 </sst>
 </file>
@@ -7282,7 +7798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1473"/>
+  <dimension ref="A1:N1638"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -70272,22 +70788,22 @@
         <v>24</v>
       </c>
       <c r="C1432">
-        <v>2261</v>
+        <v>2693</v>
       </c>
       <c r="D1432">
-        <v>2141</v>
+        <v>2555</v>
       </c>
       <c r="E1432" s="3">
-        <v>0.94692609999999999</v>
+        <v>0.94875600000000004</v>
       </c>
       <c r="F1432" t="s">
-        <v>2255</v>
+        <v>2262</v>
       </c>
       <c r="G1432" t="s">
-        <v>2256</v>
+        <v>2263</v>
       </c>
       <c r="H1432" t="s">
-        <v>2257</v>
+        <v>2264</v>
       </c>
       <c r="I1432" t="s">
         <v>28</v>
@@ -70296,7 +70812,7 @@
         <v>19</v>
       </c>
       <c r="K1432" t="s">
-        <v>2256</v>
+        <v>2263</v>
       </c>
       <c r="L1432">
         <v>0</v>
@@ -70313,34 +70829,34 @@
         <v>46285</v>
       </c>
       <c r="B1433" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="C1433">
-        <v>251</v>
+        <v>1023</v>
       </c>
       <c r="D1433">
-        <v>193</v>
+        <v>896</v>
       </c>
       <c r="E1433" s="3">
-        <v>0.76892430000000001</v>
+        <v>0.8758553</v>
       </c>
       <c r="F1433" t="s">
-        <v>2258</v>
+        <v>2265</v>
       </c>
       <c r="G1433" t="s">
-        <v>2259</v>
+        <v>2266</v>
       </c>
       <c r="H1433" t="s">
-        <v>2260</v>
+        <v>2267</v>
       </c>
       <c r="I1433" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1433" t="s">
         <v>19</v>
       </c>
       <c r="K1433" t="s">
-        <v>2259</v>
+        <v>2266</v>
       </c>
       <c r="L1433">
         <v>0</v>
@@ -70357,34 +70873,34 @@
         <v>46285</v>
       </c>
       <c r="B1434" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
       <c r="C1434">
-        <v>198</v>
+        <v>317</v>
       </c>
       <c r="D1434">
-        <v>198</v>
-      </c>
-      <c r="E1434" s="4">
-        <v>1</v>
+        <v>238</v>
+      </c>
+      <c r="E1434" s="3">
+        <v>0.75078860000000003</v>
       </c>
       <c r="F1434" t="s">
-        <v>2198</v>
+        <v>2268</v>
       </c>
       <c r="G1434" t="s">
-        <v>2261</v>
+        <v>2269</v>
       </c>
       <c r="H1434" t="s">
-        <v>2262</v>
+        <v>2270</v>
       </c>
       <c r="I1434" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1434" t="s">
         <v>19</v>
       </c>
       <c r="K1434" t="s">
-        <v>2261</v>
+        <v>2269</v>
       </c>
       <c r="L1434">
         <v>0</v>
@@ -70401,34 +70917,34 @@
         <v>46285</v>
       </c>
       <c r="B1435" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C1435">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="D1435">
-        <v>94</v>
-      </c>
-      <c r="E1435" s="3">
-        <v>0.8245614</v>
+        <v>216</v>
+      </c>
+      <c r="E1435" s="4">
+        <v>1</v>
       </c>
       <c r="F1435" t="s">
-        <v>2263</v>
+        <v>2271</v>
       </c>
       <c r="G1435" t="s">
-        <v>1038</v>
+        <v>2272</v>
       </c>
       <c r="H1435" t="s">
-        <v>2264</v>
+        <v>2273</v>
       </c>
       <c r="I1435" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1435" t="s">
         <v>19</v>
       </c>
       <c r="K1435" t="s">
-        <v>1038</v>
+        <v>2272</v>
       </c>
       <c r="L1435">
         <v>0</v>
@@ -70445,34 +70961,34 @@
         <v>46285</v>
       </c>
       <c r="B1436" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="C1436">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="D1436">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="E1436" s="3">
-        <v>0.94949490000000003</v>
+        <v>0.82170540000000003</v>
       </c>
       <c r="F1436" t="s">
-        <v>2265</v>
+        <v>2274</v>
       </c>
       <c r="G1436" t="s">
-        <v>2266</v>
+        <v>2275</v>
       </c>
       <c r="H1436" t="s">
-        <v>1030</v>
+        <v>2276</v>
       </c>
       <c r="I1436" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1436" t="s">
         <v>19</v>
       </c>
       <c r="K1436" t="s">
-        <v>2266</v>
+        <v>2275</v>
       </c>
       <c r="L1436">
         <v>0</v>
@@ -70489,25 +71005,25 @@
         <v>46285</v>
       </c>
       <c r="B1437" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C1437">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="D1437">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E1437" s="3">
-        <v>0.9393939</v>
+        <v>0.94949490000000003</v>
       </c>
       <c r="F1437" t="s">
-        <v>2066</v>
+        <v>2255</v>
       </c>
       <c r="G1437" t="s">
-        <v>2267</v>
+        <v>2256</v>
       </c>
       <c r="H1437" t="s">
-        <v>2178</v>
+        <v>1030</v>
       </c>
       <c r="I1437" t="s">
         <v>23</v>
@@ -70516,7 +71032,7 @@
         <v>19</v>
       </c>
       <c r="K1437" t="s">
-        <v>2267</v>
+        <v>2256</v>
       </c>
       <c r="L1437">
         <v>0</v>
@@ -70533,34 +71049,34 @@
         <v>46285</v>
       </c>
       <c r="B1438" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1438">
+        <v>69</v>
+      </c>
+      <c r="D1438">
         <v>65</v>
       </c>
-      <c r="C1438">
-        <v>38</v>
-      </c>
-      <c r="D1438">
-        <v>0</v>
-      </c>
-      <c r="E1438" s="4">
-        <v>0</v>
+      <c r="E1438" s="3">
+        <v>0.94202900000000001</v>
       </c>
       <c r="F1438" t="s">
-        <v>2268</v>
+        <v>2277</v>
       </c>
       <c r="G1438" t="s">
-        <v>2269</v>
+        <v>889</v>
       </c>
       <c r="H1438" t="s">
-        <v>2270</v>
+        <v>2278</v>
       </c>
       <c r="I1438" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1438" t="s">
         <v>19</v>
       </c>
       <c r="K1438" t="s">
-        <v>2269</v>
+        <v>889</v>
       </c>
       <c r="L1438">
         <v>0</v>
@@ -70580,22 +71096,22 @@
         <v>105</v>
       </c>
       <c r="C1439">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D1439">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E1439" s="3">
-        <v>0.87096770000000001</v>
+        <v>0.8245614</v>
       </c>
       <c r="F1439" t="s">
-        <v>893</v>
+        <v>2279</v>
       </c>
       <c r="G1439" t="s">
-        <v>2271</v>
+        <v>2280</v>
       </c>
       <c r="H1439" t="s">
-        <v>2272</v>
+        <v>2281</v>
       </c>
       <c r="I1439" t="s">
         <v>28</v>
@@ -70604,7 +71120,7 @@
         <v>19</v>
       </c>
       <c r="K1439" t="s">
-        <v>2271</v>
+        <v>2280</v>
       </c>
       <c r="L1439">
         <v>0</v>
@@ -70621,34 +71137,34 @@
         <v>46285</v>
       </c>
       <c r="B1440" t="s">
-        <v>172</v>
+        <v>65</v>
       </c>
       <c r="C1440">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D1440">
-        <v>16</v>
-      </c>
-      <c r="E1440" s="3">
-        <v>0.94117649999999997</v>
+        <v>0</v>
+      </c>
+      <c r="E1440" s="4">
+        <v>0</v>
       </c>
       <c r="F1440" t="s">
-        <v>1195</v>
+        <v>2282</v>
       </c>
       <c r="G1440" t="s">
-        <v>1790</v>
+        <v>2283</v>
       </c>
       <c r="H1440" t="s">
-        <v>1791</v>
+        <v>2284</v>
       </c>
       <c r="I1440" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1440" t="s">
         <v>19</v>
       </c>
       <c r="K1440" t="s">
-        <v>1790</v>
+        <v>2283</v>
       </c>
       <c r="L1440">
         <v>0</v>
@@ -70665,34 +71181,34 @@
         <v>46285</v>
       </c>
       <c r="B1441" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="C1441">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D1441">
-        <v>6</v>
-      </c>
-      <c r="E1441" s="4">
-        <v>0.4</v>
+        <v>35</v>
+      </c>
+      <c r="E1441" s="3">
+        <v>0.97222220000000004</v>
       </c>
       <c r="F1441" t="s">
-        <v>2273</v>
+        <v>2285</v>
       </c>
       <c r="G1441" t="s">
-        <v>2274</v>
+        <v>1738</v>
       </c>
       <c r="H1441" t="s">
-        <v>2275</v>
+        <v>2286</v>
       </c>
       <c r="I1441" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1441" t="s">
         <v>19</v>
       </c>
       <c r="K1441" t="s">
-        <v>2274</v>
+        <v>1738</v>
       </c>
       <c r="L1441">
         <v>0</v>
@@ -70709,34 +71225,34 @@
         <v>46285</v>
       </c>
       <c r="B1442" t="s">
-        <v>211</v>
+        <v>57</v>
       </c>
       <c r="C1442">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D1442">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E1442" s="3">
-        <v>0.53333330000000001</v>
+        <v>0.1052632</v>
       </c>
       <c r="F1442" t="s">
-        <v>2276</v>
+        <v>2287</v>
       </c>
       <c r="G1442" t="s">
-        <v>1483</v>
+        <v>2288</v>
       </c>
       <c r="H1442" t="s">
-        <v>2277</v>
+        <v>2289</v>
       </c>
       <c r="I1442" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1442" t="s">
         <v>19</v>
       </c>
       <c r="K1442" t="s">
-        <v>1483</v>
+        <v>2288</v>
       </c>
       <c r="L1442">
         <v>0</v>
@@ -70753,25 +71269,25 @@
         <v>46285</v>
       </c>
       <c r="B1443" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="C1443">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D1443">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E1443" s="3">
-        <v>8.3333299999999999E-2</v>
+        <v>0.38888889999999998</v>
       </c>
       <c r="F1443" t="s">
-        <v>2278</v>
+        <v>2290</v>
       </c>
       <c r="G1443" t="s">
-        <v>2279</v>
+        <v>2291</v>
       </c>
       <c r="H1443" t="s">
-        <v>809</v>
+        <v>2292</v>
       </c>
       <c r="I1443" t="s">
         <v>18</v>
@@ -70780,7 +71296,7 @@
         <v>19</v>
       </c>
       <c r="K1443" t="s">
-        <v>2279</v>
+        <v>2291</v>
       </c>
       <c r="L1443">
         <v>0</v>
@@ -70797,25 +71313,25 @@
         <v>46285</v>
       </c>
       <c r="B1444" t="s">
-        <v>409</v>
+        <v>211</v>
       </c>
       <c r="C1444">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D1444">
-        <v>11</v>
-      </c>
-      <c r="E1444" s="4">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="E1444" s="3">
+        <v>0.53333330000000001</v>
       </c>
       <c r="F1444" t="s">
-        <v>1220</v>
+        <v>2257</v>
       </c>
       <c r="G1444" t="s">
-        <v>1553</v>
+        <v>1483</v>
       </c>
       <c r="H1444" t="s">
-        <v>755</v>
+        <v>2258</v>
       </c>
       <c r="I1444" t="s">
         <v>18</v>
@@ -70824,7 +71340,7 @@
         <v>19</v>
       </c>
       <c r="K1444" t="s">
-        <v>1553</v>
+        <v>1483</v>
       </c>
       <c r="L1444">
         <v>0</v>
@@ -70841,25 +71357,25 @@
         <v>46285</v>
       </c>
       <c r="B1445" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="C1445">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D1445">
-        <v>8</v>
-      </c>
-      <c r="E1445" s="4">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="E1445" s="3">
+        <v>7.1428599999999995E-2</v>
       </c>
       <c r="F1445" t="s">
-        <v>1896</v>
+        <v>2293</v>
       </c>
       <c r="G1445" t="s">
-        <v>2020</v>
+        <v>2294</v>
       </c>
       <c r="H1445" t="s">
-        <v>2280</v>
+        <v>1195</v>
       </c>
       <c r="I1445" t="s">
         <v>18</v>
@@ -70868,7 +71384,7 @@
         <v>19</v>
       </c>
       <c r="K1445" t="s">
-        <v>2020</v>
+        <v>2294</v>
       </c>
       <c r="L1445">
         <v>0</v>
@@ -70885,34 +71401,34 @@
         <v>46285</v>
       </c>
       <c r="B1446" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="C1446">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D1446">
-        <v>1</v>
-      </c>
-      <c r="E1446" s="3">
-        <v>0.125</v>
+        <v>12</v>
+      </c>
+      <c r="E1446" s="4">
+        <v>1</v>
       </c>
       <c r="F1446" t="s">
-        <v>2281</v>
+        <v>1554</v>
       </c>
       <c r="G1446" t="s">
-        <v>2282</v>
+        <v>797</v>
       </c>
       <c r="H1446" t="s">
-        <v>663</v>
+        <v>1555</v>
       </c>
       <c r="I1446" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1446" t="s">
         <v>19</v>
       </c>
       <c r="K1446" t="s">
-        <v>2282</v>
+        <v>797</v>
       </c>
       <c r="L1446">
         <v>0</v>
@@ -70929,25 +71445,25 @@
         <v>46285</v>
       </c>
       <c r="B1447" t="s">
-        <v>308</v>
+        <v>409</v>
       </c>
       <c r="C1447">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D1447">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1447" s="4">
         <v>1</v>
       </c>
       <c r="F1447" t="s">
-        <v>316</v>
+        <v>1220</v>
       </c>
       <c r="G1447" t="s">
-        <v>163</v>
+        <v>1553</v>
       </c>
       <c r="H1447" t="s">
-        <v>236</v>
+        <v>755</v>
       </c>
       <c r="I1447" t="s">
         <v>18</v>
@@ -70956,7 +71472,7 @@
         <v>19</v>
       </c>
       <c r="K1447" t="s">
-        <v>163</v>
+        <v>1553</v>
       </c>
       <c r="L1447">
         <v>0</v>
@@ -70973,34 +71489,34 @@
         <v>46285</v>
       </c>
       <c r="B1448" t="s">
-        <v>215</v>
+        <v>461</v>
       </c>
       <c r="C1448">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1448">
-        <v>0</v>
-      </c>
-      <c r="E1448" s="4">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E1448" s="3">
+        <v>0.66666669999999995</v>
       </c>
       <c r="F1448" t="s">
-        <v>2283</v>
+        <v>1467</v>
       </c>
       <c r="G1448" t="s">
-        <v>2284</v>
+        <v>2295</v>
       </c>
       <c r="H1448" t="s">
-        <v>496</v>
+        <v>540</v>
       </c>
       <c r="I1448" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1448" t="s">
         <v>19</v>
       </c>
       <c r="K1448" t="s">
-        <v>2284</v>
+        <v>2295</v>
       </c>
       <c r="L1448">
         <v>0</v>
@@ -71017,25 +71533,25 @@
         <v>46285</v>
       </c>
       <c r="B1449" t="s">
-        <v>461</v>
+        <v>152</v>
       </c>
       <c r="C1449">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D1449">
-        <v>3</v>
-      </c>
-      <c r="E1449" s="4">
-        <v>0.6</v>
+        <v>1</v>
+      </c>
+      <c r="E1449" s="3">
+        <v>0.1666667</v>
       </c>
       <c r="F1449" t="s">
-        <v>919</v>
+        <v>2296</v>
       </c>
       <c r="G1449" t="s">
-        <v>2250</v>
+        <v>2297</v>
       </c>
       <c r="H1449" t="s">
-        <v>504</v>
+        <v>218</v>
       </c>
       <c r="I1449" t="s">
         <v>23</v>
@@ -71044,7 +71560,7 @@
         <v>19</v>
       </c>
       <c r="K1449" t="s">
-        <v>2250</v>
+        <v>2297</v>
       </c>
       <c r="L1449">
         <v>0</v>
@@ -71061,10 +71577,10 @@
         <v>46285</v>
       </c>
       <c r="B1450" t="s">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="C1450">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1450">
         <v>0</v>
@@ -71073,22 +71589,22 @@
         <v>0</v>
       </c>
       <c r="F1450" t="s">
-        <v>251</v>
+        <v>675</v>
       </c>
       <c r="G1450" t="s">
-        <v>252</v>
+        <v>2114</v>
       </c>
       <c r="H1450" t="s">
-        <v>253</v>
+        <v>1438</v>
       </c>
       <c r="I1450" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1450" t="s">
         <v>19</v>
       </c>
       <c r="K1450" t="s">
-        <v>252</v>
+        <v>2114</v>
       </c>
       <c r="L1450">
         <v>0</v>
@@ -71105,34 +71621,34 @@
         <v>46285</v>
       </c>
       <c r="B1451" t="s">
-        <v>660</v>
+        <v>215</v>
       </c>
       <c r="C1451">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1451">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1451" s="4">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F1451" t="s">
-        <v>327</v>
+        <v>2260</v>
       </c>
       <c r="G1451" t="s">
-        <v>527</v>
+        <v>2261</v>
       </c>
       <c r="H1451" t="s">
-        <v>283</v>
+        <v>496</v>
       </c>
       <c r="I1451" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1451" t="s">
         <v>19</v>
       </c>
       <c r="K1451" t="s">
-        <v>527</v>
+        <v>2261</v>
       </c>
       <c r="L1451">
         <v>0</v>
@@ -71149,34 +71665,34 @@
         <v>46285</v>
       </c>
       <c r="B1452" t="s">
-        <v>265</v>
+        <v>308</v>
       </c>
       <c r="C1452">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1452">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E1452" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1452" t="s">
-        <v>258</v>
+        <v>316</v>
       </c>
       <c r="G1452" t="s">
-        <v>1199</v>
+        <v>163</v>
       </c>
       <c r="H1452" t="s">
-        <v>540</v>
+        <v>236</v>
       </c>
       <c r="I1452" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1452" t="s">
         <v>19</v>
       </c>
       <c r="K1452" t="s">
-        <v>1199</v>
+        <v>163</v>
       </c>
       <c r="L1452">
         <v>0</v>
@@ -71193,34 +71709,34 @@
         <v>46285</v>
       </c>
       <c r="B1453" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C1453">
         <v>4</v>
       </c>
       <c r="D1453">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1453" s="4">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F1453" t="s">
-        <v>545</v>
+        <v>251</v>
       </c>
       <c r="G1453" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="H1453" t="s">
-        <v>208</v>
+        <v>253</v>
       </c>
       <c r="I1453" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1453" t="s">
         <v>19</v>
       </c>
       <c r="K1453" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="L1453">
         <v>0</v>
@@ -71237,34 +71753,34 @@
         <v>46285</v>
       </c>
       <c r="B1454" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="C1454">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1454">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1454" s="4">
         <v>1</v>
       </c>
       <c r="F1454" t="s">
-        <v>453</v>
+        <v>549</v>
       </c>
       <c r="G1454" t="s">
-        <v>495</v>
+        <v>284</v>
       </c>
       <c r="H1454" t="s">
-        <v>496</v>
+        <v>519</v>
       </c>
       <c r="I1454" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1454" t="s">
         <v>19</v>
       </c>
       <c r="K1454" t="s">
-        <v>495</v>
+        <v>284</v>
       </c>
       <c r="L1454">
         <v>0</v>
@@ -71281,25 +71797,25 @@
         <v>46285</v>
       </c>
       <c r="B1455" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="C1455">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1455">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1455" s="4">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F1455" t="s">
-        <v>498</v>
+        <v>304</v>
       </c>
       <c r="G1455" t="s">
-        <v>495</v>
+        <v>304</v>
       </c>
       <c r="H1455" t="s">
-        <v>281</v>
+        <v>474</v>
       </c>
       <c r="I1455" t="s">
         <v>23</v>
@@ -71308,7 +71824,7 @@
         <v>19</v>
       </c>
       <c r="K1455" t="s">
-        <v>495</v>
+        <v>304</v>
       </c>
       <c r="L1455">
         <v>0</v>
@@ -71325,34 +71841,34 @@
         <v>46285</v>
       </c>
       <c r="B1456" t="s">
-        <v>220</v>
+        <v>660</v>
       </c>
       <c r="C1456">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1456">
         <v>1</v>
       </c>
-      <c r="E1456" s="3">
-        <v>0.3333333</v>
+      <c r="E1456" s="4">
+        <v>0.25</v>
       </c>
       <c r="F1456" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="G1456" t="s">
-        <v>303</v>
+        <v>527</v>
       </c>
       <c r="H1456" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="I1456" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1456" t="s">
         <v>19</v>
       </c>
       <c r="K1456" t="s">
-        <v>303</v>
+        <v>527</v>
       </c>
       <c r="L1456">
         <v>0</v>
@@ -71369,10 +71885,10 @@
         <v>46285</v>
       </c>
       <c r="B1457" t="s">
-        <v>708</v>
+        <v>265</v>
       </c>
       <c r="C1457">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1457">
         <v>0</v>
@@ -71381,22 +71897,22 @@
         <v>0</v>
       </c>
       <c r="F1457" t="s">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="G1457" t="s">
-        <v>276</v>
+        <v>1199</v>
       </c>
       <c r="H1457" t="s">
-        <v>314</v>
+        <v>540</v>
       </c>
       <c r="I1457" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1457" t="s">
         <v>19</v>
       </c>
       <c r="K1457" t="s">
-        <v>276</v>
+        <v>1199</v>
       </c>
       <c r="L1457">
         <v>0</v>
@@ -71413,34 +71929,34 @@
         <v>46285</v>
       </c>
       <c r="B1458" t="s">
-        <v>85</v>
+        <v>241</v>
       </c>
       <c r="C1458">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1458">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1458" s="4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F1458" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
       <c r="G1458" t="s">
-        <v>210</v>
+        <v>276</v>
       </c>
       <c r="H1458" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
       <c r="I1458" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1458" t="s">
         <v>19</v>
       </c>
       <c r="K1458" t="s">
-        <v>210</v>
+        <v>276</v>
       </c>
       <c r="L1458">
         <v>0</v>
@@ -71457,25 +71973,25 @@
         <v>46285</v>
       </c>
       <c r="B1459" t="s">
-        <v>289</v>
+        <v>204</v>
       </c>
       <c r="C1459">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1459">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1459" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1459" t="s">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="G1459" t="s">
-        <v>929</v>
+        <v>495</v>
       </c>
       <c r="H1459" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="I1459" t="s">
         <v>23</v>
@@ -71484,7 +72000,7 @@
         <v>19</v>
       </c>
       <c r="K1459" t="s">
-        <v>929</v>
+        <v>495</v>
       </c>
       <c r="L1459">
         <v>0</v>
@@ -71501,34 +72017,34 @@
         <v>46285</v>
       </c>
       <c r="B1460" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="C1460">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1460">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1460" s="4">
         <v>1</v>
       </c>
       <c r="F1460" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="G1460" t="s">
-        <v>293</v>
+        <v>495</v>
       </c>
       <c r="H1460" t="s">
-        <v>514</v>
+        <v>281</v>
       </c>
       <c r="I1460" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1460" t="s">
         <v>19</v>
       </c>
       <c r="K1460" t="s">
-        <v>293</v>
+        <v>495</v>
       </c>
       <c r="L1460">
         <v>0</v>
@@ -71545,25 +72061,25 @@
         <v>46285</v>
       </c>
       <c r="B1461" t="s">
-        <v>152</v>
+        <v>329</v>
       </c>
       <c r="C1461">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1461">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1461" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F1461" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1461" t="s">
         <v>277</v>
       </c>
-      <c r="G1461" t="s">
-        <v>311</v>
-      </c>
       <c r="H1461" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="I1461" t="s">
         <v>23</v>
@@ -71572,7 +72088,7 @@
         <v>19</v>
       </c>
       <c r="K1461" t="s">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="L1461">
         <v>0</v>
@@ -71589,25 +72105,25 @@
         <v>46285</v>
       </c>
       <c r="B1462" t="s">
-        <v>333</v>
+        <v>708</v>
       </c>
       <c r="C1462">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1462">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1462" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1462" t="s">
-        <v>202</v>
+        <v>293</v>
       </c>
       <c r="G1462" t="s">
-        <v>698</v>
+        <v>276</v>
       </c>
       <c r="H1462" t="s">
-        <v>1220</v>
+        <v>314</v>
       </c>
       <c r="I1462" t="s">
         <v>23</v>
@@ -71616,7 +72132,7 @@
         <v>19</v>
       </c>
       <c r="K1462" t="s">
-        <v>698</v>
+        <v>276</v>
       </c>
       <c r="L1462">
         <v>0</v>
@@ -71633,25 +72149,25 @@
         <v>46285</v>
       </c>
       <c r="B1463" t="s">
-        <v>493</v>
+        <v>289</v>
       </c>
       <c r="C1463">
         <v>2</v>
       </c>
       <c r="D1463">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1463" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1463" t="s">
-        <v>304</v>
+        <v>498</v>
       </c>
       <c r="G1463" t="s">
-        <v>205</v>
+        <v>929</v>
       </c>
       <c r="H1463" t="s">
-        <v>457</v>
+        <v>504</v>
       </c>
       <c r="I1463" t="s">
         <v>23</v>
@@ -71660,7 +72176,7 @@
         <v>19</v>
       </c>
       <c r="K1463" t="s">
-        <v>205</v>
+        <v>929</v>
       </c>
       <c r="L1463">
         <v>0</v>
@@ -71677,7 +72193,7 @@
         <v>46285</v>
       </c>
       <c r="B1464" t="s">
-        <v>302</v>
+        <v>140</v>
       </c>
       <c r="C1464">
         <v>2</v>
@@ -71689,13 +72205,13 @@
         <v>1</v>
       </c>
       <c r="F1464" t="s">
-        <v>304</v>
+        <v>549</v>
       </c>
       <c r="G1464" t="s">
-        <v>304</v>
+        <v>706</v>
       </c>
       <c r="H1464" t="s">
-        <v>474</v>
+        <v>323</v>
       </c>
       <c r="I1464" t="s">
         <v>18</v>
@@ -71704,7 +72220,7 @@
         <v>19</v>
       </c>
       <c r="K1464" t="s">
-        <v>304</v>
+        <v>706</v>
       </c>
       <c r="L1464">
         <v>0</v>
@@ -71721,28 +72237,28 @@
         <v>46285</v>
       </c>
       <c r="B1465" t="s">
-        <v>61</v>
+        <v>333</v>
       </c>
       <c r="C1465">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1465">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1465" s="4">
         <v>1</v>
       </c>
       <c r="F1465" t="s">
-        <v>1112</v>
+        <v>202</v>
       </c>
       <c r="G1465" t="s">
         <v>698</v>
       </c>
       <c r="H1465" t="s">
-        <v>541</v>
+        <v>1220</v>
       </c>
       <c r="I1465" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1465" t="s">
         <v>19</v>
@@ -71765,34 +72281,34 @@
         <v>46285</v>
       </c>
       <c r="B1466" t="s">
-        <v>201</v>
+        <v>144</v>
       </c>
       <c r="C1466">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1466">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1466" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1466" t="s">
-        <v>1836</v>
+        <v>1001</v>
       </c>
       <c r="G1466" t="s">
-        <v>700</v>
+        <v>513</v>
       </c>
       <c r="H1466" t="s">
-        <v>196</v>
+        <v>323</v>
       </c>
       <c r="I1466" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1466" t="s">
         <v>19</v>
       </c>
       <c r="K1466" t="s">
-        <v>700</v>
+        <v>513</v>
       </c>
       <c r="L1466">
         <v>0</v>
@@ -71809,34 +72325,34 @@
         <v>46285</v>
       </c>
       <c r="B1467" t="s">
-        <v>291</v>
+        <v>493</v>
       </c>
       <c r="C1467">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1467">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1467" s="4">
         <v>1</v>
       </c>
       <c r="F1467" t="s">
-        <v>849</v>
+        <v>304</v>
       </c>
       <c r="G1467" t="s">
-        <v>306</v>
+        <v>205</v>
       </c>
       <c r="H1467" t="s">
-        <v>850</v>
+        <v>457</v>
       </c>
       <c r="I1467" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1467" t="s">
         <v>19</v>
       </c>
       <c r="K1467" t="s">
-        <v>306</v>
+        <v>205</v>
       </c>
       <c r="L1467">
         <v>0</v>
@@ -71853,34 +72369,34 @@
         <v>46285</v>
       </c>
       <c r="B1468" t="s">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="C1468">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1468">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1468" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1468" t="s">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="G1468" t="s">
-        <v>803</v>
+        <v>304</v>
       </c>
       <c r="H1468" t="s">
-        <v>541</v>
+        <v>474</v>
       </c>
       <c r="I1468" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1468" t="s">
         <v>19</v>
       </c>
       <c r="K1468" t="s">
-        <v>803</v>
+        <v>304</v>
       </c>
       <c r="L1468">
         <v>0</v>
@@ -71897,25 +72413,25 @@
         <v>46285</v>
       </c>
       <c r="B1469" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="C1469">
         <v>1</v>
       </c>
       <c r="D1469">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1469" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1469" t="s">
-        <v>296</v>
+        <v>1836</v>
       </c>
       <c r="G1469" t="s">
-        <v>314</v>
+        <v>700</v>
       </c>
       <c r="H1469" t="s">
-        <v>297</v>
+        <v>196</v>
       </c>
       <c r="I1469" t="s">
         <v>18</v>
@@ -71924,7 +72440,7 @@
         <v>19</v>
       </c>
       <c r="K1469" t="s">
-        <v>314</v>
+        <v>700</v>
       </c>
       <c r="L1469">
         <v>0</v>
@@ -71941,34 +72457,34 @@
         <v>46285</v>
       </c>
       <c r="B1470" t="s">
-        <v>1113</v>
+        <v>261</v>
       </c>
       <c r="C1470">
         <v>1</v>
       </c>
       <c r="D1470">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1470" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1470" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="G1470" t="s">
-        <v>293</v>
+        <v>803</v>
       </c>
       <c r="H1470" t="s">
-        <v>202</v>
+        <v>541</v>
       </c>
       <c r="I1470" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1470" t="s">
         <v>19</v>
       </c>
       <c r="K1470" t="s">
-        <v>293</v>
+        <v>803</v>
       </c>
       <c r="L1470">
         <v>0</v>
@@ -71985,7 +72501,7 @@
         <v>46285</v>
       </c>
       <c r="B1471" t="s">
-        <v>329</v>
+        <v>61</v>
       </c>
       <c r="C1471">
         <v>1</v>
@@ -71997,22 +72513,22 @@
         <v>1</v>
       </c>
       <c r="F1471" t="s">
-        <v>284</v>
+        <v>1112</v>
       </c>
       <c r="G1471" t="s">
-        <v>235</v>
+        <v>698</v>
       </c>
       <c r="H1471" t="s">
-        <v>254</v>
+        <v>541</v>
       </c>
       <c r="I1471" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1471" t="s">
         <v>19</v>
       </c>
       <c r="K1471" t="s">
-        <v>235</v>
+        <v>698</v>
       </c>
       <c r="L1471">
         <v>0</v>
@@ -72029,34 +72545,34 @@
         <v>46285</v>
       </c>
       <c r="B1472" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="C1472">
         <v>1</v>
       </c>
       <c r="D1472">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1472" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1472" t="s">
-        <v>1093</v>
+        <v>296</v>
       </c>
       <c r="G1472" t="s">
-        <v>700</v>
+        <v>314</v>
       </c>
       <c r="H1472" t="s">
+        <v>297</v>
+      </c>
+      <c r="I1472" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1472" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1472" t="s">
         <v>314</v>
-      </c>
-      <c r="I1472" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1472" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1472" t="s">
-        <v>700</v>
       </c>
       <c r="L1472">
         <v>0</v>
@@ -72073,42 +72589,7302 @@
         <v>46285</v>
       </c>
       <c r="B1473" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C1473">
+        <v>1</v>
+      </c>
+      <c r="D1473">
+        <v>1</v>
+      </c>
+      <c r="E1473" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1473" t="s">
+        <v>300</v>
+      </c>
+      <c r="G1473" t="s">
+        <v>293</v>
+      </c>
+      <c r="H1473" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1473" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1473" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1473" t="s">
+        <v>293</v>
+      </c>
+      <c r="L1473">
+        <v>0</v>
+      </c>
+      <c r="M1473" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:14">
+      <c r="A1474" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1474" t="s">
         <v>1479</v>
       </c>
-      <c r="C1473">
-        <v>1</v>
-      </c>
-      <c r="D1473">
-        <v>1</v>
-      </c>
-      <c r="E1473" s="4">
-        <v>1</v>
-      </c>
-      <c r="F1473" t="s">
+      <c r="C1474">
+        <v>1</v>
+      </c>
+      <c r="D1474">
+        <v>1</v>
+      </c>
+      <c r="E1474" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1474" t="s">
         <v>286</v>
       </c>
-      <c r="G1473" t="s">
+      <c r="G1474" t="s">
         <v>254</v>
       </c>
-      <c r="H1473" t="s">
+      <c r="H1474" t="s">
         <v>474</v>
       </c>
-      <c r="I1473" t="s">
+      <c r="I1474" t="s">
         <v>23</v>
       </c>
-      <c r="J1473" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1473" t="s">
+      <c r="J1474" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1474" t="s">
         <v>254</v>
       </c>
-      <c r="L1473">
-        <v>0</v>
-      </c>
-      <c r="M1473" s="4">
-        <v>0</v>
-      </c>
-      <c r="N1473">
+      <c r="L1474">
+        <v>0</v>
+      </c>
+      <c r="M1474" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:14">
+      <c r="A1475" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1475">
+        <v>1</v>
+      </c>
+      <c r="D1475">
+        <v>1</v>
+      </c>
+      <c r="E1475" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1475" t="s">
+        <v>311</v>
+      </c>
+      <c r="G1475" t="s">
+        <v>312</v>
+      </c>
+      <c r="H1475" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1475" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1475" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1475" t="s">
+        <v>312</v>
+      </c>
+      <c r="L1475">
+        <v>0</v>
+      </c>
+      <c r="M1475" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:14">
+      <c r="A1476" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>670</v>
+      </c>
+      <c r="C1476">
+        <v>1</v>
+      </c>
+      <c r="D1476">
+        <v>1</v>
+      </c>
+      <c r="E1476" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1476" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1476" t="s">
+        <v>306</v>
+      </c>
+      <c r="H1476" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1476" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1476" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1476" t="s">
+        <v>306</v>
+      </c>
+      <c r="L1476">
+        <v>0</v>
+      </c>
+      <c r="M1476" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:14">
+      <c r="A1477" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1477">
+        <v>1</v>
+      </c>
+      <c r="D1477">
+        <v>0</v>
+      </c>
+      <c r="E1477" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1477" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G1477" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1477" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1477" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1477" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1477" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1477">
+        <v>0</v>
+      </c>
+      <c r="M1477" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:14">
+      <c r="A1478" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1478">
+        <v>1</v>
+      </c>
+      <c r="D1478">
+        <v>1</v>
+      </c>
+      <c r="E1478" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1478" t="s">
+        <v>849</v>
+      </c>
+      <c r="G1478" t="s">
+        <v>306</v>
+      </c>
+      <c r="H1478" t="s">
+        <v>850</v>
+      </c>
+      <c r="I1478" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1478" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1478" t="s">
+        <v>306</v>
+      </c>
+      <c r="L1478">
+        <v>0</v>
+      </c>
+      <c r="M1478" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:14">
+      <c r="A1479" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1479">
+        <v>1</v>
+      </c>
+      <c r="D1479">
+        <v>1</v>
+      </c>
+      <c r="E1479" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1479" t="s">
+        <v>2298</v>
+      </c>
+      <c r="G1479" t="s">
+        <v>277</v>
+      </c>
+      <c r="H1479" t="s">
+        <v>2299</v>
+      </c>
+      <c r="I1479" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1479" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1479" t="s">
+        <v>277</v>
+      </c>
+      <c r="L1479">
+        <v>0</v>
+      </c>
+      <c r="M1479" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:14">
+      <c r="A1480" s="2">
+        <v>46285</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1480">
+        <v>1</v>
+      </c>
+      <c r="D1480">
+        <v>0</v>
+      </c>
+      <c r="E1480" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1480" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G1480" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1480" t="s">
+        <v>314</v>
+      </c>
+      <c r="I1480" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1480" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1480" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1480">
+        <v>0</v>
+      </c>
+      <c r="M1480" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:14">
+      <c r="A1481" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1481">
+        <v>1582</v>
+      </c>
+      <c r="D1481">
+        <v>1493</v>
+      </c>
+      <c r="E1481" s="3">
+        <v>0.94374210000000003</v>
+      </c>
+      <c r="F1481" t="s">
+        <v>2300</v>
+      </c>
+      <c r="G1481" t="s">
+        <v>2301</v>
+      </c>
+      <c r="H1481" t="s">
+        <v>2302</v>
+      </c>
+      <c r="I1481" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1481" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1481" t="s">
+        <v>2301</v>
+      </c>
+      <c r="L1481">
+        <v>0</v>
+      </c>
+      <c r="M1481" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:14">
+      <c r="A1482" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1482">
+        <v>1383</v>
+      </c>
+      <c r="D1482">
+        <v>1377</v>
+      </c>
+      <c r="E1482" s="3">
+        <v>0.99566160000000004</v>
+      </c>
+      <c r="F1482" t="s">
+        <v>2303</v>
+      </c>
+      <c r="G1482" t="s">
+        <v>2304</v>
+      </c>
+      <c r="H1482" t="s">
+        <v>2305</v>
+      </c>
+      <c r="I1482" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1482" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1482" t="s">
+        <v>2304</v>
+      </c>
+      <c r="L1482">
+        <v>0</v>
+      </c>
+      <c r="M1482" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:14">
+      <c r="A1483" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1483">
+        <v>149</v>
+      </c>
+      <c r="D1483">
+        <v>139</v>
+      </c>
+      <c r="E1483" s="3">
+        <v>0.93288590000000005</v>
+      </c>
+      <c r="F1483" t="s">
+        <v>2306</v>
+      </c>
+      <c r="G1483" t="s">
+        <v>2307</v>
+      </c>
+      <c r="H1483" t="s">
+        <v>2308</v>
+      </c>
+      <c r="I1483" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1483" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1483" t="s">
+        <v>2307</v>
+      </c>
+      <c r="L1483">
+        <v>0</v>
+      </c>
+      <c r="M1483" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:14">
+      <c r="A1484" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1484">
+        <v>125</v>
+      </c>
+      <c r="D1484">
+        <v>102</v>
+      </c>
+      <c r="E1484" s="3">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="F1484" t="s">
+        <v>358</v>
+      </c>
+      <c r="G1484" t="s">
+        <v>358</v>
+      </c>
+      <c r="H1484" t="s">
+        <v>2309</v>
+      </c>
+      <c r="I1484" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1484" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1484" t="s">
+        <v>358</v>
+      </c>
+      <c r="L1484">
+        <v>0</v>
+      </c>
+      <c r="M1484" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:14">
+      <c r="A1485" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1485">
+        <v>81</v>
+      </c>
+      <c r="D1485">
+        <v>74</v>
+      </c>
+      <c r="E1485" s="3">
+        <v>0.91358019999999995</v>
+      </c>
+      <c r="F1485" t="s">
+        <v>2310</v>
+      </c>
+      <c r="G1485" t="s">
+        <v>2311</v>
+      </c>
+      <c r="H1485" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I1485" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1485" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1485" t="s">
+        <v>2311</v>
+      </c>
+      <c r="L1485">
+        <v>0</v>
+      </c>
+      <c r="M1485" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:14">
+      <c r="A1486" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1486">
+        <v>77</v>
+      </c>
+      <c r="D1486">
+        <v>68</v>
+      </c>
+      <c r="E1486" s="3">
+        <v>0.88311689999999998</v>
+      </c>
+      <c r="F1486" t="s">
+        <v>2312</v>
+      </c>
+      <c r="G1486" t="s">
+        <v>2313</v>
+      </c>
+      <c r="H1486" t="s">
+        <v>2314</v>
+      </c>
+      <c r="I1486" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1486" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1486" t="s">
+        <v>2313</v>
+      </c>
+      <c r="L1486">
+        <v>0</v>
+      </c>
+      <c r="M1486" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:14">
+      <c r="A1487" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1487">
+        <v>71</v>
+      </c>
+      <c r="D1487">
+        <v>61</v>
+      </c>
+      <c r="E1487" s="3">
+        <v>0.85915490000000005</v>
+      </c>
+      <c r="F1487" t="s">
+        <v>2315</v>
+      </c>
+      <c r="G1487" t="s">
+        <v>2259</v>
+      </c>
+      <c r="H1487" t="s">
+        <v>2316</v>
+      </c>
+      <c r="I1487" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1487" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1487" t="s">
+        <v>2259</v>
+      </c>
+      <c r="L1487">
+        <v>0</v>
+      </c>
+      <c r="M1487" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:14">
+      <c r="A1488" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1488">
+        <v>68</v>
+      </c>
+      <c r="D1488">
+        <v>56</v>
+      </c>
+      <c r="E1488" s="3">
+        <v>0.82352939999999997</v>
+      </c>
+      <c r="F1488" t="s">
+        <v>2317</v>
+      </c>
+      <c r="G1488" t="s">
+        <v>2318</v>
+      </c>
+      <c r="H1488" t="s">
+        <v>2319</v>
+      </c>
+      <c r="I1488" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1488" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1488" t="s">
+        <v>2318</v>
+      </c>
+      <c r="L1488">
+        <v>0</v>
+      </c>
+      <c r="M1488" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:14">
+      <c r="A1489" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1489">
+        <v>65</v>
+      </c>
+      <c r="D1489">
+        <v>60</v>
+      </c>
+      <c r="E1489" s="3">
+        <v>0.92307689999999998</v>
+      </c>
+      <c r="F1489" t="s">
+        <v>2320</v>
+      </c>
+      <c r="G1489" t="s">
+        <v>2321</v>
+      </c>
+      <c r="H1489" t="s">
+        <v>2322</v>
+      </c>
+      <c r="I1489" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1489" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1489" t="s">
+        <v>2321</v>
+      </c>
+      <c r="L1489">
+        <v>0</v>
+      </c>
+      <c r="M1489" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:14">
+      <c r="A1490" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1490">
+        <v>54</v>
+      </c>
+      <c r="D1490">
+        <v>21</v>
+      </c>
+      <c r="E1490" s="3">
+        <v>0.38888889999999998</v>
+      </c>
+      <c r="F1490" t="s">
+        <v>2323</v>
+      </c>
+      <c r="G1490" t="s">
+        <v>2324</v>
+      </c>
+      <c r="H1490" t="s">
+        <v>2325</v>
+      </c>
+      <c r="I1490" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1490" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1490" t="s">
+        <v>2324</v>
+      </c>
+      <c r="L1490">
+        <v>0</v>
+      </c>
+      <c r="M1490" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:14">
+      <c r="A1491" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1491">
+        <v>50</v>
+      </c>
+      <c r="D1491">
+        <v>1</v>
+      </c>
+      <c r="E1491" s="4">
+        <v>0.02</v>
+      </c>
+      <c r="F1491" t="s">
+        <v>2326</v>
+      </c>
+      <c r="G1491" t="s">
+        <v>2327</v>
+      </c>
+      <c r="H1491" t="s">
+        <v>2328</v>
+      </c>
+      <c r="I1491" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1491" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1491" t="s">
+        <v>2327</v>
+      </c>
+      <c r="L1491">
+        <v>0</v>
+      </c>
+      <c r="M1491" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:14">
+      <c r="A1492" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1492">
+        <v>48</v>
+      </c>
+      <c r="D1492">
+        <v>46</v>
+      </c>
+      <c r="E1492" s="3">
+        <v>0.95833330000000005</v>
+      </c>
+      <c r="F1492" t="s">
+        <v>933</v>
+      </c>
+      <c r="G1492" t="s">
+        <v>2329</v>
+      </c>
+      <c r="H1492" t="s">
+        <v>2330</v>
+      </c>
+      <c r="I1492" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1492" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1492" t="s">
+        <v>2329</v>
+      </c>
+      <c r="L1492">
+        <v>0</v>
+      </c>
+      <c r="M1492" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:14">
+      <c r="A1493" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1493">
+        <v>44</v>
+      </c>
+      <c r="D1493">
+        <v>2</v>
+      </c>
+      <c r="E1493" s="3">
+        <v>4.5454500000000002E-2</v>
+      </c>
+      <c r="F1493" t="s">
+        <v>2331</v>
+      </c>
+      <c r="G1493" t="s">
+        <v>2277</v>
+      </c>
+      <c r="H1493" t="s">
+        <v>2332</v>
+      </c>
+      <c r="I1493" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1493" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1493" t="s">
+        <v>2277</v>
+      </c>
+      <c r="L1493">
+        <v>0</v>
+      </c>
+      <c r="M1493" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:14">
+      <c r="A1494" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1494">
+        <v>39</v>
+      </c>
+      <c r="D1494">
+        <v>0</v>
+      </c>
+      <c r="E1494" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1494" t="s">
+        <v>2333</v>
+      </c>
+      <c r="G1494" t="s">
+        <v>2334</v>
+      </c>
+      <c r="H1494" t="s">
+        <v>2335</v>
+      </c>
+      <c r="I1494" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1494" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1494" t="s">
+        <v>2334</v>
+      </c>
+      <c r="L1494">
+        <v>0</v>
+      </c>
+      <c r="M1494" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:14">
+      <c r="A1495" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1495">
+        <v>34</v>
+      </c>
+      <c r="D1495">
+        <v>27</v>
+      </c>
+      <c r="E1495" s="3">
+        <v>0.79411759999999998</v>
+      </c>
+      <c r="F1495" t="s">
+        <v>2336</v>
+      </c>
+      <c r="G1495" t="s">
+        <v>466</v>
+      </c>
+      <c r="H1495" t="s">
+        <v>2337</v>
+      </c>
+      <c r="I1495" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1495" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1495" t="s">
+        <v>466</v>
+      </c>
+      <c r="L1495">
+        <v>0</v>
+      </c>
+      <c r="M1495" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:14">
+      <c r="A1496" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1496">
+        <v>29</v>
+      </c>
+      <c r="D1496">
+        <v>26</v>
+      </c>
+      <c r="E1496" s="3">
+        <v>0.89655169999999995</v>
+      </c>
+      <c r="F1496" t="s">
+        <v>2338</v>
+      </c>
+      <c r="G1496" t="s">
+        <v>2339</v>
+      </c>
+      <c r="H1496" t="s">
+        <v>2340</v>
+      </c>
+      <c r="I1496" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1496" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1496" t="s">
+        <v>2339</v>
+      </c>
+      <c r="L1496">
+        <v>0</v>
+      </c>
+      <c r="M1496" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:14">
+      <c r="A1497" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1497">
+        <v>27</v>
+      </c>
+      <c r="D1497">
+        <v>19</v>
+      </c>
+      <c r="E1497" s="3">
+        <v>0.70370370000000004</v>
+      </c>
+      <c r="F1497" t="s">
+        <v>270</v>
+      </c>
+      <c r="G1497" t="s">
+        <v>2178</v>
+      </c>
+      <c r="H1497" t="s">
+        <v>901</v>
+      </c>
+      <c r="I1497" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1497" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1497" t="s">
+        <v>2178</v>
+      </c>
+      <c r="L1497">
+        <v>0</v>
+      </c>
+      <c r="M1497" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:14">
+      <c r="A1498" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1498">
+        <v>26</v>
+      </c>
+      <c r="D1498">
+        <v>14</v>
+      </c>
+      <c r="E1498" s="3">
+        <v>0.53846150000000004</v>
+      </c>
+      <c r="F1498" t="s">
+        <v>2341</v>
+      </c>
+      <c r="G1498" t="s">
+        <v>2342</v>
+      </c>
+      <c r="H1498" t="s">
+        <v>2343</v>
+      </c>
+      <c r="I1498" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1498" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1498" t="s">
+        <v>2342</v>
+      </c>
+      <c r="L1498">
+        <v>0</v>
+      </c>
+      <c r="M1498" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:14">
+      <c r="A1499" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1499">
+        <v>24</v>
+      </c>
+      <c r="D1499">
+        <v>9</v>
+      </c>
+      <c r="E1499" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="F1499" t="s">
+        <v>2344</v>
+      </c>
+      <c r="G1499" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H1499" t="s">
+        <v>2346</v>
+      </c>
+      <c r="I1499" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1499" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1499" t="s">
+        <v>2345</v>
+      </c>
+      <c r="L1499">
+        <v>0</v>
+      </c>
+      <c r="M1499" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:14">
+      <c r="A1500" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1500">
+        <v>23</v>
+      </c>
+      <c r="D1500">
+        <v>19</v>
+      </c>
+      <c r="E1500" s="3">
+        <v>0.82608700000000002</v>
+      </c>
+      <c r="F1500" t="s">
+        <v>2065</v>
+      </c>
+      <c r="G1500" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H1500" t="s">
+        <v>2347</v>
+      </c>
+      <c r="I1500" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1500" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1500" t="s">
+        <v>1435</v>
+      </c>
+      <c r="L1500">
+        <v>0</v>
+      </c>
+      <c r="M1500" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:14">
+      <c r="A1501" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>325</v>
+      </c>
+      <c r="C1501">
+        <v>22</v>
+      </c>
+      <c r="D1501">
+        <v>21</v>
+      </c>
+      <c r="E1501" s="3">
+        <v>0.95454550000000005</v>
+      </c>
+      <c r="F1501" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G1501" t="s">
+        <v>687</v>
+      </c>
+      <c r="H1501" t="s">
+        <v>2348</v>
+      </c>
+      <c r="I1501" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1501" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1501" t="s">
+        <v>687</v>
+      </c>
+      <c r="L1501">
+        <v>0</v>
+      </c>
+      <c r="M1501" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:14">
+      <c r="A1502" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1502" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1502">
+        <v>21</v>
+      </c>
+      <c r="D1502">
+        <v>19</v>
+      </c>
+      <c r="E1502" s="3">
+        <v>0.90476190000000001</v>
+      </c>
+      <c r="F1502" t="s">
+        <v>2349</v>
+      </c>
+      <c r="G1502" t="s">
+        <v>244</v>
+      </c>
+      <c r="H1502" t="s">
+        <v>2350</v>
+      </c>
+      <c r="I1502" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1502" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1502" t="s">
+        <v>244</v>
+      </c>
+      <c r="L1502">
+        <v>0</v>
+      </c>
+      <c r="M1502" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:14">
+      <c r="A1503" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1503" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1503">
+        <v>19</v>
+      </c>
+      <c r="D1503">
+        <v>14</v>
+      </c>
+      <c r="E1503" s="3">
+        <v>0.73684210000000006</v>
+      </c>
+      <c r="F1503" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1503" t="s">
+        <v>2351</v>
+      </c>
+      <c r="H1503" t="s">
+        <v>624</v>
+      </c>
+      <c r="I1503" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1503" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1503" t="s">
+        <v>2351</v>
+      </c>
+      <c r="L1503">
+        <v>0</v>
+      </c>
+      <c r="M1503" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:14">
+      <c r="A1504" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1504" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1504">
+        <v>19</v>
+      </c>
+      <c r="D1504">
+        <v>19</v>
+      </c>
+      <c r="E1504" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1504" t="s">
+        <v>1580</v>
+      </c>
+      <c r="G1504" t="s">
+        <v>2104</v>
+      </c>
+      <c r="H1504" t="s">
+        <v>2352</v>
+      </c>
+      <c r="I1504" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1504" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1504" t="s">
+        <v>2104</v>
+      </c>
+      <c r="L1504">
+        <v>0</v>
+      </c>
+      <c r="M1504" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:14">
+      <c r="A1505" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1505" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1505">
+        <v>17</v>
+      </c>
+      <c r="D1505">
+        <v>15</v>
+      </c>
+      <c r="E1505" s="3">
+        <v>0.8823529</v>
+      </c>
+      <c r="F1505" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1505" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H1505" t="s">
+        <v>1075</v>
+      </c>
+      <c r="I1505" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1505" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1505" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L1505">
+        <v>0</v>
+      </c>
+      <c r="M1505" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:14">
+      <c r="A1506" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1506" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1506">
+        <v>17</v>
+      </c>
+      <c r="D1506">
+        <v>0</v>
+      </c>
+      <c r="E1506" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1506" t="s">
+        <v>2353</v>
+      </c>
+      <c r="G1506" t="s">
+        <v>2354</v>
+      </c>
+      <c r="H1506" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I1506" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1506" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1506" t="s">
+        <v>2354</v>
+      </c>
+      <c r="L1506">
+        <v>0</v>
+      </c>
+      <c r="M1506" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:14">
+      <c r="A1507" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1507" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1507">
+        <v>17</v>
+      </c>
+      <c r="D1507">
+        <v>8</v>
+      </c>
+      <c r="E1507" s="3">
+        <v>0.47058820000000001</v>
+      </c>
+      <c r="F1507" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1507" t="s">
+        <v>203</v>
+      </c>
+      <c r="H1507" t="s">
+        <v>791</v>
+      </c>
+      <c r="I1507" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1507" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1507" t="s">
+        <v>203</v>
+      </c>
+      <c r="L1507">
+        <v>0</v>
+      </c>
+      <c r="M1507" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:14">
+      <c r="A1508" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1508" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1508">
+        <v>14</v>
+      </c>
+      <c r="D1508">
+        <v>14</v>
+      </c>
+      <c r="E1508" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1508" t="s">
+        <v>489</v>
+      </c>
+      <c r="G1508" t="s">
+        <v>1632</v>
+      </c>
+      <c r="H1508" t="s">
+        <v>2355</v>
+      </c>
+      <c r="I1508" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1508" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1508" t="s">
+        <v>1632</v>
+      </c>
+      <c r="L1508">
+        <v>0</v>
+      </c>
+      <c r="M1508" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:14">
+      <c r="A1509" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1509" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1509">
+        <v>11</v>
+      </c>
+      <c r="D1509">
+        <v>11</v>
+      </c>
+      <c r="E1509" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1509" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1509" t="s">
+        <v>809</v>
+      </c>
+      <c r="H1509" t="s">
+        <v>1986</v>
+      </c>
+      <c r="I1509" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1509" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1509" t="s">
+        <v>809</v>
+      </c>
+      <c r="L1509">
+        <v>0</v>
+      </c>
+      <c r="M1509" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:14">
+      <c r="A1510" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1510" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1510">
+        <v>11</v>
+      </c>
+      <c r="D1510">
+        <v>9</v>
+      </c>
+      <c r="E1510" s="3">
+        <v>0.81818179999999996</v>
+      </c>
+      <c r="F1510" t="s">
+        <v>2356</v>
+      </c>
+      <c r="G1510" t="s">
+        <v>2357</v>
+      </c>
+      <c r="H1510" t="s">
+        <v>2358</v>
+      </c>
+      <c r="I1510" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1510" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1510" t="s">
+        <v>2357</v>
+      </c>
+      <c r="L1510">
+        <v>0</v>
+      </c>
+      <c r="M1510" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:14">
+      <c r="A1511" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1511" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1511">
+        <v>11</v>
+      </c>
+      <c r="D1511">
+        <v>11</v>
+      </c>
+      <c r="E1511" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1511" t="s">
+        <v>2359</v>
+      </c>
+      <c r="G1511" t="s">
+        <v>2360</v>
+      </c>
+      <c r="H1511" t="s">
+        <v>1549</v>
+      </c>
+      <c r="I1511" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1511" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1511" t="s">
+        <v>2360</v>
+      </c>
+      <c r="L1511">
+        <v>0</v>
+      </c>
+      <c r="M1511" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:14">
+      <c r="A1512" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1512" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1512">
+        <v>10</v>
+      </c>
+      <c r="D1512">
+        <v>1</v>
+      </c>
+      <c r="E1512" s="4">
+        <v>0.1</v>
+      </c>
+      <c r="F1512" t="s">
+        <v>538</v>
+      </c>
+      <c r="G1512" t="s">
+        <v>499</v>
+      </c>
+      <c r="H1512" t="s">
+        <v>804</v>
+      </c>
+      <c r="I1512" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1512" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1512" t="s">
+        <v>499</v>
+      </c>
+      <c r="L1512">
+        <v>0</v>
+      </c>
+      <c r="M1512" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:14">
+      <c r="A1513" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1513" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1513">
+        <v>10</v>
+      </c>
+      <c r="D1513">
+        <v>6</v>
+      </c>
+      <c r="E1513" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="F1513" t="s">
+        <v>2361</v>
+      </c>
+      <c r="G1513" t="s">
+        <v>2362</v>
+      </c>
+      <c r="H1513" t="s">
+        <v>2363</v>
+      </c>
+      <c r="I1513" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1513" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1513" t="s">
+        <v>2362</v>
+      </c>
+      <c r="L1513">
+        <v>0</v>
+      </c>
+      <c r="M1513" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:14">
+      <c r="A1514" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1514" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1514">
+        <v>9</v>
+      </c>
+      <c r="D1514">
+        <v>0</v>
+      </c>
+      <c r="E1514" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1514" t="s">
+        <v>2364</v>
+      </c>
+      <c r="G1514" t="s">
+        <v>912</v>
+      </c>
+      <c r="H1514" t="s">
+        <v>1071</v>
+      </c>
+      <c r="I1514" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1514" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1514" t="s">
+        <v>912</v>
+      </c>
+      <c r="L1514">
+        <v>0</v>
+      </c>
+      <c r="M1514" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:14">
+      <c r="A1515" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1515" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1515">
+        <v>9</v>
+      </c>
+      <c r="D1515">
+        <v>5</v>
+      </c>
+      <c r="E1515" s="3">
+        <v>0.55555560000000004</v>
+      </c>
+      <c r="F1515" t="s">
+        <v>538</v>
+      </c>
+      <c r="G1515" t="s">
+        <v>991</v>
+      </c>
+      <c r="H1515" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1515" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1515" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1515" t="s">
+        <v>991</v>
+      </c>
+      <c r="L1515">
+        <v>0</v>
+      </c>
+      <c r="M1515" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:14">
+      <c r="A1516" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1516" t="s">
+        <v>660</v>
+      </c>
+      <c r="C1516">
+        <v>8</v>
+      </c>
+      <c r="D1516">
+        <v>8</v>
+      </c>
+      <c r="E1516" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1516" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1516" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1516" t="s">
+        <v>321</v>
+      </c>
+      <c r="I1516" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1516" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1516" t="s">
+        <v>1209</v>
+      </c>
+      <c r="L1516">
+        <v>0</v>
+      </c>
+      <c r="M1516" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:14">
+      <c r="A1517" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1517" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C1517">
+        <v>8</v>
+      </c>
+      <c r="D1517">
+        <v>0</v>
+      </c>
+      <c r="E1517" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1517" t="s">
+        <v>474</v>
+      </c>
+      <c r="G1517" t="s">
+        <v>801</v>
+      </c>
+      <c r="H1517" t="s">
+        <v>2365</v>
+      </c>
+      <c r="I1517" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1517" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1517" t="s">
+        <v>801</v>
+      </c>
+      <c r="L1517">
+        <v>0</v>
+      </c>
+      <c r="M1517" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:14">
+      <c r="A1518" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1518" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1518">
+        <v>8</v>
+      </c>
+      <c r="D1518">
+        <v>0</v>
+      </c>
+      <c r="E1518" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1518" t="s">
+        <v>1569</v>
+      </c>
+      <c r="G1518" t="s">
+        <v>309</v>
+      </c>
+      <c r="H1518" t="s">
+        <v>1570</v>
+      </c>
+      <c r="I1518" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1518" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1518" t="s">
+        <v>309</v>
+      </c>
+      <c r="L1518">
+        <v>0</v>
+      </c>
+      <c r="M1518" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:14">
+      <c r="A1519" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1519" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1519">
+        <v>7</v>
+      </c>
+      <c r="D1519">
+        <v>6</v>
+      </c>
+      <c r="E1519" s="3">
+        <v>0.85714290000000004</v>
+      </c>
+      <c r="F1519" t="s">
+        <v>2366</v>
+      </c>
+      <c r="G1519" t="s">
+        <v>2367</v>
+      </c>
+      <c r="H1519" t="s">
+        <v>2368</v>
+      </c>
+      <c r="I1519" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1519" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1519" t="s">
+        <v>2367</v>
+      </c>
+      <c r="L1519">
+        <v>0</v>
+      </c>
+      <c r="M1519" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:14">
+      <c r="A1520" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1520" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1520">
+        <v>7</v>
+      </c>
+      <c r="D1520">
+        <v>3</v>
+      </c>
+      <c r="E1520" s="3">
+        <v>0.42857139999999999</v>
+      </c>
+      <c r="F1520" t="s">
+        <v>2369</v>
+      </c>
+      <c r="G1520" t="s">
+        <v>2370</v>
+      </c>
+      <c r="H1520" t="s">
+        <v>2371</v>
+      </c>
+      <c r="I1520" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1520" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1520" t="s">
+        <v>2370</v>
+      </c>
+      <c r="L1520">
+        <v>0</v>
+      </c>
+      <c r="M1520" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:14">
+      <c r="A1521" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1521" t="s">
+        <v>670</v>
+      </c>
+      <c r="C1521">
+        <v>6</v>
+      </c>
+      <c r="D1521">
+        <v>6</v>
+      </c>
+      <c r="E1521" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1521" t="s">
+        <v>284</v>
+      </c>
+      <c r="G1521" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1521" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1521" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1521" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1521" t="s">
+        <v>235</v>
+      </c>
+      <c r="L1521">
+        <v>0</v>
+      </c>
+      <c r="M1521" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:14">
+      <c r="A1522" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1522" t="s">
+        <v>2372</v>
+      </c>
+      <c r="C1522">
+        <v>6</v>
+      </c>
+      <c r="D1522">
+        <v>5</v>
+      </c>
+      <c r="E1522" s="3">
+        <v>0.83333330000000005</v>
+      </c>
+      <c r="F1522" t="s">
+        <v>680</v>
+      </c>
+      <c r="G1522" t="s">
+        <v>2373</v>
+      </c>
+      <c r="H1522" t="s">
+        <v>448</v>
+      </c>
+      <c r="I1522" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1522" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1522" t="s">
+        <v>2373</v>
+      </c>
+      <c r="L1522">
+        <v>0</v>
+      </c>
+      <c r="M1522" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:14">
+      <c r="A1523" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1523" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1523">
+        <v>6</v>
+      </c>
+      <c r="D1523">
+        <v>6</v>
+      </c>
+      <c r="E1523" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1523" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1523" t="s">
+        <v>236</v>
+      </c>
+      <c r="H1523" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1523" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1523" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1523" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1523">
+        <v>0</v>
+      </c>
+      <c r="M1523" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:14">
+      <c r="A1524" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1524" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1524">
+        <v>6</v>
+      </c>
+      <c r="D1524">
+        <v>0</v>
+      </c>
+      <c r="E1524" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1524" t="s">
+        <v>311</v>
+      </c>
+      <c r="G1524" t="s">
+        <v>429</v>
+      </c>
+      <c r="H1524" t="s">
+        <v>239</v>
+      </c>
+      <c r="I1524" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1524" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1524" t="s">
+        <v>429</v>
+      </c>
+      <c r="L1524">
+        <v>0</v>
+      </c>
+      <c r="M1524" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:14">
+      <c r="A1525" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1525" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C1525">
+        <v>5</v>
+      </c>
+      <c r="D1525">
+        <v>5</v>
+      </c>
+      <c r="E1525" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1525" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1525" t="s">
+        <v>2374</v>
+      </c>
+      <c r="H1525" t="s">
+        <v>662</v>
+      </c>
+      <c r="I1525" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1525" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1525" t="s">
+        <v>2374</v>
+      </c>
+      <c r="L1525">
+        <v>0</v>
+      </c>
+      <c r="M1525" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:14">
+      <c r="A1526" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1526" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1526">
+        <v>4</v>
+      </c>
+      <c r="D1526">
+        <v>0</v>
+      </c>
+      <c r="E1526" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1526" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G1526" t="s">
+        <v>1342</v>
+      </c>
+      <c r="H1526" t="s">
+        <v>509</v>
+      </c>
+      <c r="I1526" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1526" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1526" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L1526">
+        <v>0</v>
+      </c>
+      <c r="M1526" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:14">
+      <c r="A1527" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1527" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1527">
+        <v>4</v>
+      </c>
+      <c r="D1527">
+        <v>4</v>
+      </c>
+      <c r="E1527" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1527" t="s">
+        <v>2375</v>
+      </c>
+      <c r="G1527" t="s">
+        <v>2376</v>
+      </c>
+      <c r="H1527" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1527" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1527" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1527" t="s">
+        <v>2376</v>
+      </c>
+      <c r="L1527">
+        <v>0</v>
+      </c>
+      <c r="M1527" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:14">
+      <c r="A1528" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1528" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1528">
+        <v>4</v>
+      </c>
+      <c r="D1528">
+        <v>3</v>
+      </c>
+      <c r="E1528" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F1528" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1528" t="s">
+        <v>474</v>
+      </c>
+      <c r="H1528" t="s">
+        <v>840</v>
+      </c>
+      <c r="I1528" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1528" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1528" t="s">
+        <v>474</v>
+      </c>
+      <c r="L1528">
+        <v>0</v>
+      </c>
+      <c r="M1528" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:14">
+      <c r="A1529" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1529" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1529">
+        <v>4</v>
+      </c>
+      <c r="D1529">
+        <v>4</v>
+      </c>
+      <c r="E1529" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1529" t="s">
+        <v>254</v>
+      </c>
+      <c r="G1529" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H1529" t="s">
+        <v>2377</v>
+      </c>
+      <c r="I1529" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1529" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1529" t="s">
+        <v>1813</v>
+      </c>
+      <c r="L1529">
+        <v>0</v>
+      </c>
+      <c r="M1529" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:14">
+      <c r="A1530" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1530" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1530">
+        <v>4</v>
+      </c>
+      <c r="D1530">
+        <v>2</v>
+      </c>
+      <c r="E1530" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1530" t="s">
+        <v>307</v>
+      </c>
+      <c r="G1530" t="s">
+        <v>281</v>
+      </c>
+      <c r="H1530" t="s">
+        <v>1345</v>
+      </c>
+      <c r="I1530" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1530" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1530" t="s">
+        <v>281</v>
+      </c>
+      <c r="L1530">
+        <v>0</v>
+      </c>
+      <c r="M1530" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:14">
+      <c r="A1531" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1531" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1531">
+        <v>4</v>
+      </c>
+      <c r="D1531">
+        <v>0</v>
+      </c>
+      <c r="E1531" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1531" t="s">
+        <v>2378</v>
+      </c>
+      <c r="G1531" t="s">
+        <v>1342</v>
+      </c>
+      <c r="H1531" t="s">
+        <v>508</v>
+      </c>
+      <c r="I1531" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1531" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1531" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L1531">
+        <v>0</v>
+      </c>
+      <c r="M1531" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:14">
+      <c r="A1532" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1532" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1532">
+        <v>4</v>
+      </c>
+      <c r="D1532">
+        <v>0</v>
+      </c>
+      <c r="E1532" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1532" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1532" t="s">
+        <v>239</v>
+      </c>
+      <c r="H1532" t="s">
+        <v>2105</v>
+      </c>
+      <c r="I1532" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1532" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1532" t="s">
+        <v>239</v>
+      </c>
+      <c r="L1532">
+        <v>0</v>
+      </c>
+      <c r="M1532" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:14">
+      <c r="A1533" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1533" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1533">
+        <v>4</v>
+      </c>
+      <c r="D1533">
+        <v>2</v>
+      </c>
+      <c r="E1533" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1533" t="s">
+        <v>2362</v>
+      </c>
+      <c r="G1533" t="s">
+        <v>928</v>
+      </c>
+      <c r="H1533" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1533" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1533" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1533" t="s">
+        <v>928</v>
+      </c>
+      <c r="L1533">
+        <v>0</v>
+      </c>
+      <c r="M1533" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:14">
+      <c r="A1534" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1534" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1534">
+        <v>4</v>
+      </c>
+      <c r="D1534">
+        <v>0</v>
+      </c>
+      <c r="E1534" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1534" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1534" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1534" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1534" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1534" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1534" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1534">
+        <v>0</v>
+      </c>
+      <c r="M1534" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:14">
+      <c r="A1535" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1535" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C1535">
+        <v>4</v>
+      </c>
+      <c r="D1535">
+        <v>0</v>
+      </c>
+      <c r="E1535" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1535" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1535" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1535" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1535" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1535" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1535" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1535">
+        <v>0</v>
+      </c>
+      <c r="M1535" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:14">
+      <c r="A1536" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1536" t="s">
+        <v>2379</v>
+      </c>
+      <c r="C1536">
+        <v>4</v>
+      </c>
+      <c r="D1536">
+        <v>0</v>
+      </c>
+      <c r="E1536" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1536" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1536" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1536" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1536" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1536" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1536" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1536">
+        <v>0</v>
+      </c>
+      <c r="M1536" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:14">
+      <c r="A1537" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1537" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C1537">
+        <v>4</v>
+      </c>
+      <c r="D1537">
+        <v>0</v>
+      </c>
+      <c r="E1537" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1537" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1537" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1537" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1537" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1537" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1537" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1537">
+        <v>0</v>
+      </c>
+      <c r="M1537" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:14">
+      <c r="A1538" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C1538">
+        <v>3</v>
+      </c>
+      <c r="D1538">
+        <v>0</v>
+      </c>
+      <c r="E1538" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1538" t="s">
+        <v>298</v>
+      </c>
+      <c r="G1538" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1538" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I1538" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1538" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1538" t="s">
+        <v>181</v>
+      </c>
+      <c r="L1538">
+        <v>0</v>
+      </c>
+      <c r="M1538" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:14">
+      <c r="A1539" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>2030</v>
+      </c>
+      <c r="C1539">
+        <v>3</v>
+      </c>
+      <c r="D1539">
+        <v>0</v>
+      </c>
+      <c r="E1539" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1539" t="s">
+        <v>284</v>
+      </c>
+      <c r="G1539" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1539" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I1539" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1539" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1539" t="s">
+        <v>259</v>
+      </c>
+      <c r="L1539">
+        <v>0</v>
+      </c>
+      <c r="M1539" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:14">
+      <c r="A1540" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1540" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1540">
+        <v>3</v>
+      </c>
+      <c r="D1540">
+        <v>0</v>
+      </c>
+      <c r="E1540" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1540" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G1540" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1540" t="s">
+        <v>503</v>
+      </c>
+      <c r="I1540" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1540" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1540" t="s">
+        <v>473</v>
+      </c>
+      <c r="L1540">
+        <v>0</v>
+      </c>
+      <c r="M1540" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:14">
+      <c r="A1541" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1541" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1541">
+        <v>3</v>
+      </c>
+      <c r="D1541">
+        <v>3</v>
+      </c>
+      <c r="E1541" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1541" t="s">
+        <v>2024</v>
+      </c>
+      <c r="G1541" t="s">
+        <v>1656</v>
+      </c>
+      <c r="H1541" t="s">
+        <v>300</v>
+      </c>
+      <c r="I1541" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1541" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1541" t="s">
+        <v>1656</v>
+      </c>
+      <c r="L1541">
+        <v>0</v>
+      </c>
+      <c r="M1541" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:14">
+      <c r="A1542" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1542" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1542">
+        <v>3</v>
+      </c>
+      <c r="D1542">
+        <v>3</v>
+      </c>
+      <c r="E1542" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1542" t="s">
+        <v>259</v>
+      </c>
+      <c r="G1542" t="s">
+        <v>662</v>
+      </c>
+      <c r="H1542" t="s">
+        <v>1071</v>
+      </c>
+      <c r="I1542" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1542" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1542" t="s">
+        <v>662</v>
+      </c>
+      <c r="L1542">
+        <v>0</v>
+      </c>
+      <c r="M1542" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:14">
+      <c r="A1543" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1543" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1543">
+        <v>3</v>
+      </c>
+      <c r="D1543">
+        <v>0</v>
+      </c>
+      <c r="E1543" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1543" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G1543" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1543" t="s">
+        <v>281</v>
+      </c>
+      <c r="I1543" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1543" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1543" t="s">
+        <v>473</v>
+      </c>
+      <c r="L1543">
+        <v>0</v>
+      </c>
+      <c r="M1543" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:14">
+      <c r="A1544" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1544" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1544">
+        <v>2</v>
+      </c>
+      <c r="D1544">
+        <v>2</v>
+      </c>
+      <c r="E1544" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1544" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1544" t="s">
+        <v>528</v>
+      </c>
+      <c r="H1544" t="s">
+        <v>408</v>
+      </c>
+      <c r="I1544" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1544" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1544" t="s">
+        <v>528</v>
+      </c>
+      <c r="L1544">
+        <v>0</v>
+      </c>
+      <c r="M1544" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:14">
+      <c r="A1545" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1545" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1545">
+        <v>2</v>
+      </c>
+      <c r="D1545">
+        <v>0</v>
+      </c>
+      <c r="E1545" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1545" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1545" t="s">
+        <v>471</v>
+      </c>
+      <c r="H1545" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1545" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1545" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1545" t="s">
+        <v>471</v>
+      </c>
+      <c r="L1545">
+        <v>0</v>
+      </c>
+      <c r="M1545" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:14">
+      <c r="A1546" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1546" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1546">
+        <v>2</v>
+      </c>
+      <c r="D1546">
+        <v>0</v>
+      </c>
+      <c r="E1546" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1546" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1546" t="s">
+        <v>287</v>
+      </c>
+      <c r="H1546" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1546" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1546" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1546" t="s">
+        <v>287</v>
+      </c>
+      <c r="L1546">
+        <v>0</v>
+      </c>
+      <c r="M1546" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:14">
+      <c r="A1547" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1547" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C1547">
+        <v>2</v>
+      </c>
+      <c r="D1547">
+        <v>1</v>
+      </c>
+      <c r="E1547" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1547" t="s">
+        <v>2380</v>
+      </c>
+      <c r="G1547" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1547" t="s">
+        <v>1803</v>
+      </c>
+      <c r="I1547" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1547" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1547" t="s">
+        <v>196</v>
+      </c>
+      <c r="L1547">
+        <v>0</v>
+      </c>
+      <c r="M1547" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:14">
+      <c r="A1548" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1548">
+        <v>2</v>
+      </c>
+      <c r="D1548">
+        <v>2</v>
+      </c>
+      <c r="E1548" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1548" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1548" t="s">
+        <v>929</v>
+      </c>
+      <c r="H1548" t="s">
+        <v>504</v>
+      </c>
+      <c r="I1548" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1548" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1548" t="s">
+        <v>929</v>
+      </c>
+      <c r="L1548">
+        <v>0</v>
+      </c>
+      <c r="M1548" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:14">
+      <c r="A1549" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1549" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1549">
+        <v>2</v>
+      </c>
+      <c r="D1549">
+        <v>2</v>
+      </c>
+      <c r="E1549" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1549" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1549" t="s">
+        <v>408</v>
+      </c>
+      <c r="H1549" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1549" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1549" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1549" t="s">
+        <v>408</v>
+      </c>
+      <c r="L1549">
+        <v>0</v>
+      </c>
+      <c r="M1549" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:14">
+      <c r="A1550" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1550" t="s">
+        <v>703</v>
+      </c>
+      <c r="C1550">
+        <v>2</v>
+      </c>
+      <c r="D1550">
+        <v>1</v>
+      </c>
+      <c r="E1550" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1550" t="s">
+        <v>232</v>
+      </c>
+      <c r="G1550" t="s">
+        <v>303</v>
+      </c>
+      <c r="H1550" t="s">
+        <v>453</v>
+      </c>
+      <c r="I1550" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1550" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1550" t="s">
+        <v>303</v>
+      </c>
+      <c r="L1550">
+        <v>0</v>
+      </c>
+      <c r="M1550" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:14">
+      <c r="A1551" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1551" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C1551">
+        <v>2</v>
+      </c>
+      <c r="D1551">
+        <v>1</v>
+      </c>
+      <c r="E1551" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1551" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1551" t="s">
+        <v>284</v>
+      </c>
+      <c r="H1551" t="s">
+        <v>304</v>
+      </c>
+      <c r="I1551" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1551" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1551" t="s">
+        <v>284</v>
+      </c>
+      <c r="L1551">
+        <v>0</v>
+      </c>
+      <c r="M1551" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:14">
+      <c r="A1552" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1552" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1552">
+        <v>1</v>
+      </c>
+      <c r="D1552">
+        <v>1</v>
+      </c>
+      <c r="E1552" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1552" t="s">
+        <v>830</v>
+      </c>
+      <c r="G1552" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1552" t="s">
+        <v>830</v>
+      </c>
+      <c r="I1552" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1552" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1552" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1552">
+        <v>0</v>
+      </c>
+      <c r="M1552" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:14">
+      <c r="A1553" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1553" t="s">
+        <v>544</v>
+      </c>
+      <c r="C1553">
+        <v>1</v>
+      </c>
+      <c r="D1553">
+        <v>1</v>
+      </c>
+      <c r="E1553" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1553" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1553" t="s">
+        <v>208</v>
+      </c>
+      <c r="H1553" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1553" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1553" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1553" t="s">
+        <v>208</v>
+      </c>
+      <c r="L1553">
+        <v>0</v>
+      </c>
+      <c r="M1553" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:14">
+      <c r="A1554" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1554" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C1554">
+        <v>1</v>
+      </c>
+      <c r="D1554">
+        <v>0</v>
+      </c>
+      <c r="E1554" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1554" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1554" t="s">
+        <v>845</v>
+      </c>
+      <c r="H1554" t="s">
+        <v>2121</v>
+      </c>
+      <c r="I1554" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1554" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1554" t="s">
+        <v>845</v>
+      </c>
+      <c r="L1554">
+        <v>0</v>
+      </c>
+      <c r="M1554" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:14">
+      <c r="A1555" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1555" t="s">
+        <v>485</v>
+      </c>
+      <c r="C1555">
+        <v>1</v>
+      </c>
+      <c r="D1555">
+        <v>0</v>
+      </c>
+      <c r="E1555" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1555" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1555" t="s">
+        <v>637</v>
+      </c>
+      <c r="H1555" t="s">
+        <v>290</v>
+      </c>
+      <c r="I1555" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1555" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1555" t="s">
+        <v>637</v>
+      </c>
+      <c r="L1555">
+        <v>0</v>
+      </c>
+      <c r="M1555" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:14">
+      <c r="A1556" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1556" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1556">
+        <v>1</v>
+      </c>
+      <c r="D1556">
+        <v>0</v>
+      </c>
+      <c r="E1556" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1556" t="s">
+        <v>2381</v>
+      </c>
+      <c r="G1556" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1556" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1556" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1556" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1556" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1556">
+        <v>0</v>
+      </c>
+      <c r="M1556" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:14">
+      <c r="A1557" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1557" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1557">
+        <v>1</v>
+      </c>
+      <c r="D1557">
+        <v>1</v>
+      </c>
+      <c r="E1557" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1557" t="s">
+        <v>238</v>
+      </c>
+      <c r="G1557" t="s">
+        <v>524</v>
+      </c>
+      <c r="H1557" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1557" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1557" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1557" t="s">
+        <v>524</v>
+      </c>
+      <c r="L1557">
+        <v>0</v>
+      </c>
+      <c r="M1557" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:14">
+      <c r="A1558" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1558" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1558">
+        <v>1</v>
+      </c>
+      <c r="D1558">
+        <v>1</v>
+      </c>
+      <c r="E1558" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1558" t="s">
+        <v>311</v>
+      </c>
+      <c r="G1558" t="s">
+        <v>312</v>
+      </c>
+      <c r="H1558" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1558" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1558" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1558" t="s">
+        <v>312</v>
+      </c>
+      <c r="L1558">
+        <v>0</v>
+      </c>
+      <c r="M1558" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:14">
+      <c r="A1559" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1559" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C1559">
+        <v>1</v>
+      </c>
+      <c r="D1559">
+        <v>1</v>
+      </c>
+      <c r="E1559" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1559" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1559" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1559" t="s">
+        <v>258</v>
+      </c>
+      <c r="I1559" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1559" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1559" t="s">
+        <v>254</v>
+      </c>
+      <c r="L1559">
+        <v>0</v>
+      </c>
+      <c r="M1559" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:14">
+      <c r="A1560" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1560" t="s">
+        <v>708</v>
+      </c>
+      <c r="C1560">
+        <v>1</v>
+      </c>
+      <c r="D1560">
+        <v>0</v>
+      </c>
+      <c r="E1560" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1560" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1560" t="s">
+        <v>284</v>
+      </c>
+      <c r="H1560" t="s">
+        <v>300</v>
+      </c>
+      <c r="I1560" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1560" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1560" t="s">
+        <v>284</v>
+      </c>
+      <c r="L1560">
+        <v>0</v>
+      </c>
+      <c r="M1560" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:14">
+      <c r="A1561" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1561" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1561">
+        <v>1</v>
+      </c>
+      <c r="D1561">
+        <v>1</v>
+      </c>
+      <c r="E1561" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1561" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1561" t="s">
+        <v>297</v>
+      </c>
+      <c r="H1561" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1561" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1561" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1561" t="s">
+        <v>297</v>
+      </c>
+      <c r="L1561">
+        <v>0</v>
+      </c>
+      <c r="M1561" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:14">
+      <c r="A1562" s="2">
+        <v>46286</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>529</v>
+      </c>
+      <c r="C1562">
+        <v>1</v>
+      </c>
+      <c r="D1562">
+        <v>0</v>
+      </c>
+      <c r="E1562" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1562" t="s">
+        <v>2382</v>
+      </c>
+      <c r="G1562" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1562" t="s">
+        <v>2382</v>
+      </c>
+      <c r="I1562" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1562" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1562" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1562">
+        <v>0</v>
+      </c>
+      <c r="M1562" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:14">
+      <c r="A1563" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1563">
+        <v>3841</v>
+      </c>
+      <c r="D1563">
+        <v>3450</v>
+      </c>
+      <c r="E1563" s="3">
+        <v>0.89820359999999999</v>
+      </c>
+      <c r="F1563" t="s">
+        <v>2383</v>
+      </c>
+      <c r="G1563" t="s">
+        <v>2383</v>
+      </c>
+      <c r="H1563" t="s">
+        <v>2384</v>
+      </c>
+      <c r="I1563" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1563" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1563" t="s">
+        <v>2383</v>
+      </c>
+      <c r="L1563">
+        <v>0</v>
+      </c>
+      <c r="M1563" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:14">
+      <c r="A1564" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1564">
+        <v>1739</v>
+      </c>
+      <c r="D1564">
+        <v>1651</v>
+      </c>
+      <c r="E1564" s="3">
+        <v>0.94939620000000002</v>
+      </c>
+      <c r="F1564" t="s">
+        <v>2385</v>
+      </c>
+      <c r="G1564" t="s">
+        <v>2386</v>
+      </c>
+      <c r="H1564" t="s">
+        <v>2387</v>
+      </c>
+      <c r="I1564" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1564" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1564" t="s">
+        <v>2386</v>
+      </c>
+      <c r="L1564">
+        <v>0</v>
+      </c>
+      <c r="M1564" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:14">
+      <c r="A1565" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1565">
+        <v>761</v>
+      </c>
+      <c r="D1565">
+        <v>752</v>
+      </c>
+      <c r="E1565" s="3">
+        <v>0.98817350000000004</v>
+      </c>
+      <c r="F1565" t="s">
+        <v>2388</v>
+      </c>
+      <c r="G1565" t="s">
+        <v>2389</v>
+      </c>
+      <c r="H1565" t="s">
+        <v>2390</v>
+      </c>
+      <c r="I1565" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1565" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1565" t="s">
+        <v>2389</v>
+      </c>
+      <c r="L1565">
+        <v>0</v>
+      </c>
+      <c r="M1565" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:14">
+      <c r="A1566" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1566">
+        <v>425</v>
+      </c>
+      <c r="D1566">
+        <v>334</v>
+      </c>
+      <c r="E1566" s="3">
+        <v>0.78588239999999998</v>
+      </c>
+      <c r="F1566" t="s">
+        <v>2391</v>
+      </c>
+      <c r="G1566" t="s">
+        <v>2392</v>
+      </c>
+      <c r="H1566" t="s">
+        <v>2393</v>
+      </c>
+      <c r="I1566" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1566" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1566" t="s">
+        <v>2392</v>
+      </c>
+      <c r="L1566">
+        <v>0</v>
+      </c>
+      <c r="M1566" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:14">
+      <c r="A1567" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>2394</v>
+      </c>
+      <c r="C1567">
+        <v>352</v>
+      </c>
+      <c r="D1567">
+        <v>335</v>
+      </c>
+      <c r="E1567" s="3">
+        <v>0.95170449999999995</v>
+      </c>
+      <c r="F1567" t="s">
+        <v>2395</v>
+      </c>
+      <c r="G1567" t="s">
+        <v>2396</v>
+      </c>
+      <c r="H1567" t="s">
+        <v>2397</v>
+      </c>
+      <c r="I1567" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1567" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1567" t="s">
+        <v>2396</v>
+      </c>
+      <c r="L1567">
+        <v>0</v>
+      </c>
+      <c r="M1567" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:14">
+      <c r="A1568" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1568">
+        <v>286</v>
+      </c>
+      <c r="D1568">
+        <v>286</v>
+      </c>
+      <c r="E1568" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1568" t="s">
+        <v>2152</v>
+      </c>
+      <c r="G1568" t="s">
+        <v>2398</v>
+      </c>
+      <c r="H1568" t="s">
+        <v>2399</v>
+      </c>
+      <c r="I1568" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1568" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1568" t="s">
+        <v>2398</v>
+      </c>
+      <c r="L1568">
+        <v>0</v>
+      </c>
+      <c r="M1568" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:14">
+      <c r="A1569" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1569">
+        <v>113</v>
+      </c>
+      <c r="D1569">
+        <v>107</v>
+      </c>
+      <c r="E1569" s="3">
+        <v>0.94690269999999999</v>
+      </c>
+      <c r="F1569" t="s">
+        <v>2400</v>
+      </c>
+      <c r="G1569" t="s">
+        <v>2401</v>
+      </c>
+      <c r="H1569" t="s">
+        <v>2402</v>
+      </c>
+      <c r="I1569" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1569" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1569" t="s">
+        <v>2401</v>
+      </c>
+      <c r="L1569">
+        <v>0</v>
+      </c>
+      <c r="M1569" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:14">
+      <c r="A1570" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1570">
+        <v>112</v>
+      </c>
+      <c r="D1570">
+        <v>97</v>
+      </c>
+      <c r="E1570" s="3">
+        <v>0.86607140000000005</v>
+      </c>
+      <c r="F1570" t="s">
+        <v>2403</v>
+      </c>
+      <c r="G1570" t="s">
+        <v>2404</v>
+      </c>
+      <c r="H1570" t="s">
+        <v>2405</v>
+      </c>
+      <c r="I1570" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1570" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1570" t="s">
+        <v>2404</v>
+      </c>
+      <c r="L1570">
+        <v>0</v>
+      </c>
+      <c r="M1570" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:14">
+      <c r="A1571" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1571">
+        <v>79</v>
+      </c>
+      <c r="D1571">
+        <v>73</v>
+      </c>
+      <c r="E1571" s="3">
+        <v>0.92405060000000006</v>
+      </c>
+      <c r="F1571" t="s">
+        <v>2406</v>
+      </c>
+      <c r="G1571" t="s">
+        <v>2407</v>
+      </c>
+      <c r="H1571" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1571" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1571" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1571" t="s">
+        <v>2407</v>
+      </c>
+      <c r="L1571">
+        <v>0</v>
+      </c>
+      <c r="M1571" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:14">
+      <c r="A1572" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1572">
+        <v>75</v>
+      </c>
+      <c r="D1572">
+        <v>70</v>
+      </c>
+      <c r="E1572" s="3">
+        <v>0.93333330000000003</v>
+      </c>
+      <c r="F1572" t="s">
+        <v>784</v>
+      </c>
+      <c r="G1572" t="s">
+        <v>2408</v>
+      </c>
+      <c r="H1572" t="s">
+        <v>2409</v>
+      </c>
+      <c r="I1572" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1572" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1572" t="s">
+        <v>2408</v>
+      </c>
+      <c r="L1572">
+        <v>0</v>
+      </c>
+      <c r="M1572" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:14">
+      <c r="A1573" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1573">
+        <v>73</v>
+      </c>
+      <c r="D1573">
+        <v>64</v>
+      </c>
+      <c r="E1573" s="3">
+        <v>0.8767123</v>
+      </c>
+      <c r="F1573" t="s">
+        <v>2410</v>
+      </c>
+      <c r="G1573" t="s">
+        <v>2411</v>
+      </c>
+      <c r="H1573" t="s">
+        <v>2412</v>
+      </c>
+      <c r="I1573" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1573" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1573" t="s">
+        <v>2411</v>
+      </c>
+      <c r="L1573">
+        <v>0</v>
+      </c>
+      <c r="M1573" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:14">
+      <c r="A1574" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1574">
+        <v>69</v>
+      </c>
+      <c r="D1574">
+        <v>27</v>
+      </c>
+      <c r="E1574" s="3">
+        <v>0.39130429999999999</v>
+      </c>
+      <c r="F1574" t="s">
+        <v>2413</v>
+      </c>
+      <c r="G1574" t="s">
+        <v>2414</v>
+      </c>
+      <c r="H1574" t="s">
+        <v>1968</v>
+      </c>
+      <c r="I1574" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1574" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1574" t="s">
+        <v>2414</v>
+      </c>
+      <c r="L1574">
+        <v>0</v>
+      </c>
+      <c r="M1574" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:14">
+      <c r="A1575" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1575">
+        <v>64</v>
+      </c>
+      <c r="D1575">
+        <v>14</v>
+      </c>
+      <c r="E1575" s="3">
+        <v>0.21875</v>
+      </c>
+      <c r="F1575" t="s">
+        <v>2415</v>
+      </c>
+      <c r="G1575" t="s">
+        <v>2416</v>
+      </c>
+      <c r="H1575" t="s">
+        <v>2417</v>
+      </c>
+      <c r="I1575" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1575" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1575" t="s">
+        <v>2416</v>
+      </c>
+      <c r="L1575">
+        <v>0</v>
+      </c>
+      <c r="M1575" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:14">
+      <c r="A1576" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1576">
+        <v>41</v>
+      </c>
+      <c r="D1576">
+        <v>41</v>
+      </c>
+      <c r="E1576" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1576" t="s">
+        <v>412</v>
+      </c>
+      <c r="G1576" t="s">
+        <v>2418</v>
+      </c>
+      <c r="H1576" t="s">
+        <v>2419</v>
+      </c>
+      <c r="I1576" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1576" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1576" t="s">
+        <v>2418</v>
+      </c>
+      <c r="L1576">
+        <v>0</v>
+      </c>
+      <c r="M1576" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:14">
+      <c r="A1577" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1577">
+        <v>40</v>
+      </c>
+      <c r="D1577">
+        <v>37</v>
+      </c>
+      <c r="E1577" s="3">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="F1577" t="s">
+        <v>1459</v>
+      </c>
+      <c r="G1577" t="s">
+        <v>2420</v>
+      </c>
+      <c r="H1577" t="s">
+        <v>797</v>
+      </c>
+      <c r="I1577" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1577" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1577" t="s">
+        <v>2420</v>
+      </c>
+      <c r="L1577">
+        <v>0</v>
+      </c>
+      <c r="M1577" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:14">
+      <c r="A1578" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1578">
+        <v>37</v>
+      </c>
+      <c r="D1578">
+        <v>22</v>
+      </c>
+      <c r="E1578" s="3">
+        <v>0.59459459999999997</v>
+      </c>
+      <c r="F1578" t="s">
+        <v>2421</v>
+      </c>
+      <c r="G1578" t="s">
+        <v>2422</v>
+      </c>
+      <c r="H1578" t="s">
+        <v>2423</v>
+      </c>
+      <c r="I1578" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1578" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1578" t="s">
+        <v>2422</v>
+      </c>
+      <c r="L1578">
+        <v>0</v>
+      </c>
+      <c r="M1578" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:14">
+      <c r="A1579" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1579">
+        <v>31</v>
+      </c>
+      <c r="D1579">
+        <v>27</v>
+      </c>
+      <c r="E1579" s="3">
+        <v>0.87096770000000001</v>
+      </c>
+      <c r="F1579" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G1579" t="s">
+        <v>2425</v>
+      </c>
+      <c r="H1579" t="s">
+        <v>2426</v>
+      </c>
+      <c r="I1579" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1579" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1579" t="s">
+        <v>2425</v>
+      </c>
+      <c r="L1579">
+        <v>0</v>
+      </c>
+      <c r="M1579" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:14">
+      <c r="A1580" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1580">
+        <v>30</v>
+      </c>
+      <c r="D1580">
+        <v>27</v>
+      </c>
+      <c r="E1580" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F1580" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1580" t="s">
+        <v>2427</v>
+      </c>
+      <c r="H1580" t="s">
+        <v>2428</v>
+      </c>
+      <c r="I1580" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1580" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1580" t="s">
+        <v>2427</v>
+      </c>
+      <c r="L1580">
+        <v>0</v>
+      </c>
+      <c r="M1580" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:14">
+      <c r="A1581" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1581">
+        <v>29</v>
+      </c>
+      <c r="D1581">
+        <v>20</v>
+      </c>
+      <c r="E1581" s="3">
+        <v>0.68965520000000002</v>
+      </c>
+      <c r="F1581" t="s">
+        <v>2429</v>
+      </c>
+      <c r="G1581" t="s">
+        <v>2430</v>
+      </c>
+      <c r="H1581" t="s">
+        <v>2431</v>
+      </c>
+      <c r="I1581" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1581" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1581" t="s">
+        <v>2430</v>
+      </c>
+      <c r="L1581">
+        <v>0</v>
+      </c>
+      <c r="M1581" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:14">
+      <c r="A1582" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1582">
+        <v>26</v>
+      </c>
+      <c r="D1582">
+        <v>22</v>
+      </c>
+      <c r="E1582" s="3">
+        <v>0.84615379999999996</v>
+      </c>
+      <c r="F1582" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G1582" t="s">
+        <v>2002</v>
+      </c>
+      <c r="H1582" t="s">
+        <v>2241</v>
+      </c>
+      <c r="I1582" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1582" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1582" t="s">
+        <v>2002</v>
+      </c>
+      <c r="L1582">
+        <v>0</v>
+      </c>
+      <c r="M1582" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:14">
+      <c r="A1583" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1583">
+        <v>24</v>
+      </c>
+      <c r="D1583">
+        <v>22</v>
+      </c>
+      <c r="E1583" s="3">
+        <v>0.91666669999999995</v>
+      </c>
+      <c r="F1583" t="s">
+        <v>2424</v>
+      </c>
+      <c r="G1583" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1583" t="s">
+        <v>975</v>
+      </c>
+      <c r="I1583" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1583" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1583" t="s">
+        <v>90</v>
+      </c>
+      <c r="L1583">
+        <v>0</v>
+      </c>
+      <c r="M1583" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:14">
+      <c r="A1584" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1584">
+        <v>23</v>
+      </c>
+      <c r="D1584">
+        <v>10</v>
+      </c>
+      <c r="E1584" s="3">
+        <v>0.43478260000000002</v>
+      </c>
+      <c r="F1584" t="s">
+        <v>2432</v>
+      </c>
+      <c r="G1584" t="s">
+        <v>2433</v>
+      </c>
+      <c r="H1584" t="s">
+        <v>2434</v>
+      </c>
+      <c r="I1584" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1584" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1584" t="s">
+        <v>2433</v>
+      </c>
+      <c r="L1584">
+        <v>0</v>
+      </c>
+      <c r="M1584" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:14">
+      <c r="A1585" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1585">
+        <v>21</v>
+      </c>
+      <c r="D1585">
+        <v>13</v>
+      </c>
+      <c r="E1585" s="3">
+        <v>0.61904760000000003</v>
+      </c>
+      <c r="F1585" t="s">
+        <v>2435</v>
+      </c>
+      <c r="G1585" t="s">
+        <v>2436</v>
+      </c>
+      <c r="H1585" t="s">
+        <v>2437</v>
+      </c>
+      <c r="I1585" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1585" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1585" t="s">
+        <v>2436</v>
+      </c>
+      <c r="L1585">
+        <v>0</v>
+      </c>
+      <c r="M1585" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:14">
+      <c r="A1586" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1586">
+        <v>20</v>
+      </c>
+      <c r="D1586">
+        <v>20</v>
+      </c>
+      <c r="E1586" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1586" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G1586" t="s">
+        <v>255</v>
+      </c>
+      <c r="H1586" t="s">
+        <v>2438</v>
+      </c>
+      <c r="I1586" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1586" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1586" t="s">
+        <v>255</v>
+      </c>
+      <c r="L1586">
+        <v>0</v>
+      </c>
+      <c r="M1586" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:14">
+      <c r="A1587" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1587">
+        <v>17</v>
+      </c>
+      <c r="D1587">
+        <v>17</v>
+      </c>
+      <c r="E1587" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1587" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G1587" t="s">
+        <v>1790</v>
+      </c>
+      <c r="H1587" t="s">
+        <v>1791</v>
+      </c>
+      <c r="I1587" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1587" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1587" t="s">
+        <v>1790</v>
+      </c>
+      <c r="L1587">
+        <v>0</v>
+      </c>
+      <c r="M1587" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:14">
+      <c r="A1588" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1588">
+        <v>16</v>
+      </c>
+      <c r="D1588">
+        <v>10</v>
+      </c>
+      <c r="E1588" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="F1588" t="s">
+        <v>471</v>
+      </c>
+      <c r="G1588" t="s">
+        <v>644</v>
+      </c>
+      <c r="H1588" t="s">
+        <v>2114</v>
+      </c>
+      <c r="I1588" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1588" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1588" t="s">
+        <v>644</v>
+      </c>
+      <c r="L1588">
+        <v>0</v>
+      </c>
+      <c r="M1588" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1588">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:14">
+      <c r="A1589" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1589" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1589">
+        <v>16</v>
+      </c>
+      <c r="D1589">
+        <v>16</v>
+      </c>
+      <c r="E1589" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1589" t="s">
+        <v>528</v>
+      </c>
+      <c r="G1589" t="s">
+        <v>2439</v>
+      </c>
+      <c r="H1589" t="s">
+        <v>1513</v>
+      </c>
+      <c r="I1589" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1589" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1589" t="s">
+        <v>2439</v>
+      </c>
+      <c r="L1589">
+        <v>0</v>
+      </c>
+      <c r="M1589" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:14">
+      <c r="A1590" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1590" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1590">
+        <v>15</v>
+      </c>
+      <c r="D1590">
+        <v>14</v>
+      </c>
+      <c r="E1590" s="3">
+        <v>0.93333330000000003</v>
+      </c>
+      <c r="F1590" t="s">
+        <v>2440</v>
+      </c>
+      <c r="G1590" t="s">
+        <v>793</v>
+      </c>
+      <c r="H1590" t="s">
+        <v>2441</v>
+      </c>
+      <c r="I1590" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1590" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1590" t="s">
+        <v>793</v>
+      </c>
+      <c r="L1590">
+        <v>0</v>
+      </c>
+      <c r="M1590" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:14">
+      <c r="A1591" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1591" t="s">
+        <v>325</v>
+      </c>
+      <c r="C1591">
+        <v>14</v>
+      </c>
+      <c r="D1591">
+        <v>14</v>
+      </c>
+      <c r="E1591" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1591" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G1591" t="s">
+        <v>648</v>
+      </c>
+      <c r="H1591" t="s">
+        <v>321</v>
+      </c>
+      <c r="I1591" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1591" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1591" t="s">
+        <v>648</v>
+      </c>
+      <c r="L1591">
+        <v>0</v>
+      </c>
+      <c r="M1591" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1591">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:14">
+      <c r="A1592" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1592">
+        <v>14</v>
+      </c>
+      <c r="D1592">
+        <v>9</v>
+      </c>
+      <c r="E1592" s="3">
+        <v>0.64285709999999996</v>
+      </c>
+      <c r="F1592" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G1592" t="s">
+        <v>2442</v>
+      </c>
+      <c r="H1592" t="s">
+        <v>2443</v>
+      </c>
+      <c r="I1592" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1592" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1592" t="s">
+        <v>2442</v>
+      </c>
+      <c r="L1592">
+        <v>0</v>
+      </c>
+      <c r="M1592" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:14">
+      <c r="A1593" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1593">
+        <v>10</v>
+      </c>
+      <c r="D1593">
+        <v>7</v>
+      </c>
+      <c r="E1593" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="F1593" t="s">
+        <v>268</v>
+      </c>
+      <c r="G1593" t="s">
+        <v>656</v>
+      </c>
+      <c r="H1593" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1593" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1593" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1593" t="s">
+        <v>656</v>
+      </c>
+      <c r="L1593">
+        <v>0</v>
+      </c>
+      <c r="M1593" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:14">
+      <c r="A1594" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1594">
+        <v>10</v>
+      </c>
+      <c r="D1594">
+        <v>5</v>
+      </c>
+      <c r="E1594" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1594" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G1594" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1594" t="s">
+        <v>228</v>
+      </c>
+      <c r="I1594" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1594" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1594" t="s">
+        <v>162</v>
+      </c>
+      <c r="L1594">
+        <v>0</v>
+      </c>
+      <c r="M1594" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:14">
+      <c r="A1595" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1595">
+        <v>9</v>
+      </c>
+      <c r="D1595">
+        <v>7</v>
+      </c>
+      <c r="E1595" s="3">
+        <v>0.77777779999999996</v>
+      </c>
+      <c r="F1595" t="s">
+        <v>2097</v>
+      </c>
+      <c r="G1595" t="s">
+        <v>2187</v>
+      </c>
+      <c r="H1595" t="s">
+        <v>488</v>
+      </c>
+      <c r="I1595" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1595" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1595" t="s">
+        <v>2187</v>
+      </c>
+      <c r="L1595">
+        <v>0</v>
+      </c>
+      <c r="M1595" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:14">
+      <c r="A1596" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1596">
+        <v>8</v>
+      </c>
+      <c r="D1596">
+        <v>5</v>
+      </c>
+      <c r="E1596" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="F1596" t="s">
+        <v>1463</v>
+      </c>
+      <c r="G1596" t="s">
+        <v>2444</v>
+      </c>
+      <c r="H1596" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1596" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1596" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1596" t="s">
+        <v>2444</v>
+      </c>
+      <c r="L1596">
+        <v>0</v>
+      </c>
+      <c r="M1596" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:14">
+      <c r="A1597" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1597" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1597">
+        <v>8</v>
+      </c>
+      <c r="D1597">
+        <v>6</v>
+      </c>
+      <c r="E1597" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F1597" t="s">
+        <v>2445</v>
+      </c>
+      <c r="G1597" t="s">
+        <v>2446</v>
+      </c>
+      <c r="H1597" t="s">
+        <v>2447</v>
+      </c>
+      <c r="I1597" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1597" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1597" t="s">
+        <v>2446</v>
+      </c>
+      <c r="L1597">
+        <v>0</v>
+      </c>
+      <c r="M1597" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:14">
+      <c r="A1598" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1598" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1598">
+        <v>8</v>
+      </c>
+      <c r="D1598">
+        <v>4</v>
+      </c>
+      <c r="E1598" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1598" t="s">
+        <v>2188</v>
+      </c>
+      <c r="G1598" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H1598" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1598" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1598" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1598" t="s">
+        <v>2189</v>
+      </c>
+      <c r="L1598">
+        <v>0</v>
+      </c>
+      <c r="M1598" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:14">
+      <c r="A1599" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1599" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1599">
+        <v>7</v>
+      </c>
+      <c r="D1599">
+        <v>7</v>
+      </c>
+      <c r="E1599" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1599" t="s">
+        <v>495</v>
+      </c>
+      <c r="G1599" t="s">
+        <v>236</v>
+      </c>
+      <c r="H1599" t="s">
+        <v>228</v>
+      </c>
+      <c r="I1599" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1599" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1599" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1599">
+        <v>0</v>
+      </c>
+      <c r="M1599" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:14">
+      <c r="A1600" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1600" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1600">
+        <v>7</v>
+      </c>
+      <c r="D1600">
+        <v>5</v>
+      </c>
+      <c r="E1600" s="3">
+        <v>0.71428570000000002</v>
+      </c>
+      <c r="F1600" t="s">
+        <v>1567</v>
+      </c>
+      <c r="G1600" t="s">
+        <v>2448</v>
+      </c>
+      <c r="H1600" t="s">
+        <v>2180</v>
+      </c>
+      <c r="I1600" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1600" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1600" t="s">
+        <v>2448</v>
+      </c>
+      <c r="L1600">
+        <v>0</v>
+      </c>
+      <c r="M1600" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:14">
+      <c r="A1601" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1601">
+        <v>5</v>
+      </c>
+      <c r="D1601">
+        <v>0</v>
+      </c>
+      <c r="E1601" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1601" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1601" t="s">
+        <v>474</v>
+      </c>
+      <c r="H1601" t="s">
+        <v>1652</v>
+      </c>
+      <c r="I1601" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1601" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1601" t="s">
+        <v>474</v>
+      </c>
+      <c r="L1601">
+        <v>0</v>
+      </c>
+      <c r="M1601" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:14">
+      <c r="A1602" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1602">
+        <v>5</v>
+      </c>
+      <c r="D1602">
+        <v>1</v>
+      </c>
+      <c r="E1602" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="F1602" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1602" t="s">
+        <v>826</v>
+      </c>
+      <c r="H1602" t="s">
+        <v>490</v>
+      </c>
+      <c r="I1602" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1602" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1602" t="s">
+        <v>826</v>
+      </c>
+      <c r="L1602">
+        <v>0</v>
+      </c>
+      <c r="M1602" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:14">
+      <c r="A1603" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1603">
+        <v>5</v>
+      </c>
+      <c r="D1603">
+        <v>5</v>
+      </c>
+      <c r="E1603" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1603" t="s">
+        <v>242</v>
+      </c>
+      <c r="G1603" t="s">
+        <v>243</v>
+      </c>
+      <c r="H1603" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1603" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1603" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1603" t="s">
+        <v>243</v>
+      </c>
+      <c r="L1603">
+        <v>0</v>
+      </c>
+      <c r="M1603" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:14">
+      <c r="A1604" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C1604">
+        <v>5</v>
+      </c>
+      <c r="D1604">
+        <v>4</v>
+      </c>
+      <c r="E1604" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="F1604" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1604" t="s">
+        <v>827</v>
+      </c>
+      <c r="H1604" t="s">
+        <v>2371</v>
+      </c>
+      <c r="I1604" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1604" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1604" t="s">
+        <v>827</v>
+      </c>
+      <c r="L1604">
+        <v>0</v>
+      </c>
+      <c r="M1604" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:14">
+      <c r="A1605" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1605">
+        <v>5</v>
+      </c>
+      <c r="D1605">
+        <v>0</v>
+      </c>
+      <c r="E1605" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1605" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1605" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1605" t="s">
+        <v>827</v>
+      </c>
+      <c r="I1605" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1605" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1605" t="s">
+        <v>209</v>
+      </c>
+      <c r="L1605">
+        <v>0</v>
+      </c>
+      <c r="M1605" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:14">
+      <c r="A1606" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>497</v>
+      </c>
+      <c r="C1606">
+        <v>4</v>
+      </c>
+      <c r="D1606">
+        <v>0</v>
+      </c>
+      <c r="E1606" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1606" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1606" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1606" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1606" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1606" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1606" t="s">
+        <v>298</v>
+      </c>
+      <c r="L1606">
+        <v>0</v>
+      </c>
+      <c r="M1606" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:14">
+      <c r="A1607" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1607">
+        <v>4</v>
+      </c>
+      <c r="D1607">
+        <v>4</v>
+      </c>
+      <c r="E1607" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1607" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1607" t="s">
+        <v>321</v>
+      </c>
+      <c r="H1607" t="s">
+        <v>453</v>
+      </c>
+      <c r="I1607" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1607" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1607" t="s">
+        <v>321</v>
+      </c>
+      <c r="L1607">
+        <v>0</v>
+      </c>
+      <c r="M1607" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:14">
+      <c r="A1608" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1608">
+        <v>4</v>
+      </c>
+      <c r="D1608">
+        <v>3</v>
+      </c>
+      <c r="E1608" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="F1608" t="s">
+        <v>2449</v>
+      </c>
+      <c r="G1608" t="s">
+        <v>2450</v>
+      </c>
+      <c r="H1608" t="s">
+        <v>1141</v>
+      </c>
+      <c r="I1608" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1608" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1608" t="s">
+        <v>2450</v>
+      </c>
+      <c r="L1608">
+        <v>0</v>
+      </c>
+      <c r="M1608" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:14">
+      <c r="A1609" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1609">
+        <v>3</v>
+      </c>
+      <c r="D1609">
+        <v>3</v>
+      </c>
+      <c r="E1609" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1609" t="s">
+        <v>932</v>
+      </c>
+      <c r="G1609" t="s">
+        <v>516</v>
+      </c>
+      <c r="H1609" t="s">
+        <v>448</v>
+      </c>
+      <c r="I1609" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1609" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1609" t="s">
+        <v>516</v>
+      </c>
+      <c r="L1609">
+        <v>0</v>
+      </c>
+      <c r="M1609" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:14">
+      <c r="A1610" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>670</v>
+      </c>
+      <c r="C1610">
+        <v>3</v>
+      </c>
+      <c r="D1610">
+        <v>3</v>
+      </c>
+      <c r="E1610" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1610" t="s">
+        <v>453</v>
+      </c>
+      <c r="G1610" t="s">
+        <v>495</v>
+      </c>
+      <c r="H1610" t="s">
+        <v>496</v>
+      </c>
+      <c r="I1610" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1610" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1610" t="s">
+        <v>495</v>
+      </c>
+      <c r="L1610">
+        <v>0</v>
+      </c>
+      <c r="M1610" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:14">
+      <c r="A1611" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1611">
+        <v>3</v>
+      </c>
+      <c r="D1611">
+        <v>3</v>
+      </c>
+      <c r="E1611" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1611" t="s">
+        <v>800</v>
+      </c>
+      <c r="G1611" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H1611" t="s">
+        <v>533</v>
+      </c>
+      <c r="I1611" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1611" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1611" t="s">
+        <v>1356</v>
+      </c>
+      <c r="L1611">
+        <v>0</v>
+      </c>
+      <c r="M1611" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:14">
+      <c r="A1612" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>703</v>
+      </c>
+      <c r="C1612">
+        <v>3</v>
+      </c>
+      <c r="D1612">
+        <v>3</v>
+      </c>
+      <c r="E1612" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1612" t="s">
+        <v>471</v>
+      </c>
+      <c r="G1612" t="s">
+        <v>284</v>
+      </c>
+      <c r="H1612" t="s">
+        <v>495</v>
+      </c>
+      <c r="I1612" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1612" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1612" t="s">
+        <v>284</v>
+      </c>
+      <c r="L1612">
+        <v>0</v>
+      </c>
+      <c r="M1612" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:14">
+      <c r="A1613" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1613">
+        <v>3</v>
+      </c>
+      <c r="D1613">
+        <v>3</v>
+      </c>
+      <c r="E1613" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1613" t="s">
+        <v>293</v>
+      </c>
+      <c r="G1613" t="s">
+        <v>1827</v>
+      </c>
+      <c r="H1613" t="s">
+        <v>516</v>
+      </c>
+      <c r="I1613" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1613" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1613" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L1613">
+        <v>0</v>
+      </c>
+      <c r="M1613" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:14">
+      <c r="A1614" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>2451</v>
+      </c>
+      <c r="C1614">
+        <v>3</v>
+      </c>
+      <c r="D1614">
+        <v>0</v>
+      </c>
+      <c r="E1614" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1614" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G1614" t="s">
+        <v>408</v>
+      </c>
+      <c r="H1614" t="s">
+        <v>2198</v>
+      </c>
+      <c r="I1614" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1614" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1614" t="s">
+        <v>408</v>
+      </c>
+      <c r="L1614">
+        <v>0</v>
+      </c>
+      <c r="M1614" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1614">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:14">
+      <c r="A1615" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>529</v>
+      </c>
+      <c r="C1615">
+        <v>3</v>
+      </c>
+      <c r="D1615">
+        <v>2</v>
+      </c>
+      <c r="E1615" s="3">
+        <v>0.66666669999999995</v>
+      </c>
+      <c r="F1615" t="s">
+        <v>704</v>
+      </c>
+      <c r="G1615" t="s">
+        <v>637</v>
+      </c>
+      <c r="H1615" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I1615" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1615" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1615" t="s">
+        <v>637</v>
+      </c>
+      <c r="L1615">
+        <v>0</v>
+      </c>
+      <c r="M1615" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1615">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:14">
+      <c r="A1616" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>2452</v>
+      </c>
+      <c r="C1616">
+        <v>2</v>
+      </c>
+      <c r="D1616">
+        <v>2</v>
+      </c>
+      <c r="E1616" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1616" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1616" t="s">
+        <v>528</v>
+      </c>
+      <c r="H1616" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I1616" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1616" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1616" t="s">
+        <v>528</v>
+      </c>
+      <c r="L1616">
+        <v>0</v>
+      </c>
+      <c r="M1616" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:14">
+      <c r="A1617" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>695</v>
+      </c>
+      <c r="C1617">
+        <v>2</v>
+      </c>
+      <c r="D1617">
+        <v>2</v>
+      </c>
+      <c r="E1617" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1617" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1617" t="s">
+        <v>268</v>
+      </c>
+      <c r="H1617" t="s">
+        <v>448</v>
+      </c>
+      <c r="I1617" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1617" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1617" t="s">
+        <v>268</v>
+      </c>
+      <c r="L1617">
+        <v>0</v>
+      </c>
+      <c r="M1617" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:14">
+      <c r="A1618" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1618">
+        <v>2</v>
+      </c>
+      <c r="D1618">
+        <v>2</v>
+      </c>
+      <c r="E1618" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1618" t="s">
+        <v>298</v>
+      </c>
+      <c r="G1618" t="s">
+        <v>283</v>
+      </c>
+      <c r="H1618" t="s">
+        <v>539</v>
+      </c>
+      <c r="I1618" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1618" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1618" t="s">
+        <v>283</v>
+      </c>
+      <c r="L1618">
+        <v>0</v>
+      </c>
+      <c r="M1618" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:14">
+      <c r="A1619" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1619">
+        <v>2</v>
+      </c>
+      <c r="D1619">
+        <v>0</v>
+      </c>
+      <c r="E1619" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1619" t="s">
+        <v>1818</v>
+      </c>
+      <c r="G1619" t="s">
+        <v>472</v>
+      </c>
+      <c r="H1619" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1619" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1619" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1619" t="s">
+        <v>472</v>
+      </c>
+      <c r="L1619">
+        <v>0</v>
+      </c>
+      <c r="M1619" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:14">
+      <c r="A1620" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1620">
+        <v>2</v>
+      </c>
+      <c r="D1620">
+        <v>2</v>
+      </c>
+      <c r="E1620" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1620" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G1620" t="s">
+        <v>2453</v>
+      </c>
+      <c r="H1620" t="s">
+        <v>838</v>
+      </c>
+      <c r="I1620" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1620" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1620" t="s">
+        <v>2453</v>
+      </c>
+      <c r="L1620">
+        <v>0</v>
+      </c>
+      <c r="M1620" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:14">
+      <c r="A1621" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1621">
+        <v>2</v>
+      </c>
+      <c r="D1621">
+        <v>0</v>
+      </c>
+      <c r="E1621" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1621" t="s">
+        <v>1803</v>
+      </c>
+      <c r="G1621" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1621" t="s">
+        <v>537</v>
+      </c>
+      <c r="I1621" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1621" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1621" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1621">
+        <v>0</v>
+      </c>
+      <c r="M1621" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:14">
+      <c r="A1622" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1622">
+        <v>2</v>
+      </c>
+      <c r="D1622">
+        <v>1</v>
+      </c>
+      <c r="E1622" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="F1622" t="s">
+        <v>2454</v>
+      </c>
+      <c r="G1622" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1622" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I1622" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1622" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1622" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1622">
+        <v>0</v>
+      </c>
+      <c r="M1622" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:14">
+      <c r="A1623" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1623">
+        <v>2</v>
+      </c>
+      <c r="D1623">
+        <v>2</v>
+      </c>
+      <c r="E1623" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1623" t="s">
+        <v>686</v>
+      </c>
+      <c r="G1623" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H1623" t="s">
+        <v>528</v>
+      </c>
+      <c r="I1623" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1623" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1623" t="s">
+        <v>1322</v>
+      </c>
+      <c r="L1623">
+        <v>0</v>
+      </c>
+      <c r="M1623" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:14">
+      <c r="A1624" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>2455</v>
+      </c>
+      <c r="C1624">
+        <v>2</v>
+      </c>
+      <c r="D1624">
+        <v>2</v>
+      </c>
+      <c r="E1624" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1624" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1624" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1624" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1624" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1624" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1624" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1624">
+        <v>0</v>
+      </c>
+      <c r="M1624" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:14">
+      <c r="A1625" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>187</v>
+      </c>
+      <c r="C1625">
+        <v>2</v>
+      </c>
+      <c r="D1625">
+        <v>2</v>
+      </c>
+      <c r="E1625" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1625" t="s">
+        <v>513</v>
+      </c>
+      <c r="G1625" t="s">
+        <v>519</v>
+      </c>
+      <c r="H1625" t="s">
+        <v>473</v>
+      </c>
+      <c r="I1625" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1625" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1625" t="s">
+        <v>519</v>
+      </c>
+      <c r="L1625">
+        <v>0</v>
+      </c>
+      <c r="M1625" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:14">
+      <c r="A1626" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1626">
+        <v>1</v>
+      </c>
+      <c r="D1626">
+        <v>0</v>
+      </c>
+      <c r="E1626" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1626" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1626" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1626" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1626" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1626" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1626" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1626">
+        <v>0</v>
+      </c>
+      <c r="M1626" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1626">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:14">
+      <c r="A1627" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1627">
+        <v>1</v>
+      </c>
+      <c r="D1627">
+        <v>1</v>
+      </c>
+      <c r="E1627" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1627" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1627" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1627" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1627" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1627" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1627" t="s">
+        <v>254</v>
+      </c>
+      <c r="L1627">
+        <v>0</v>
+      </c>
+      <c r="M1627" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:14">
+      <c r="A1628" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>544</v>
+      </c>
+      <c r="C1628">
+        <v>1</v>
+      </c>
+      <c r="D1628">
+        <v>1</v>
+      </c>
+      <c r="E1628" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1628" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1628" t="s">
+        <v>208</v>
+      </c>
+      <c r="H1628" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1628" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1628" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1628" t="s">
+        <v>208</v>
+      </c>
+      <c r="L1628">
+        <v>0</v>
+      </c>
+      <c r="M1628" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:14">
+      <c r="A1629" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C1629">
+        <v>1</v>
+      </c>
+      <c r="D1629">
+        <v>1</v>
+      </c>
+      <c r="E1629" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1629" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1629" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1629" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1629" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1629" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1629" t="s">
+        <v>254</v>
+      </c>
+      <c r="L1629">
+        <v>0</v>
+      </c>
+      <c r="M1629" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1629">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:14">
+      <c r="A1630" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>2456</v>
+      </c>
+      <c r="C1630">
+        <v>1</v>
+      </c>
+      <c r="D1630">
+        <v>0</v>
+      </c>
+      <c r="E1630" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1630" t="s">
+        <v>284</v>
+      </c>
+      <c r="G1630" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1630" t="s">
+        <v>284</v>
+      </c>
+      <c r="I1630" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1630" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1630" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1630">
+        <v>0</v>
+      </c>
+      <c r="M1630" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:14">
+      <c r="A1631" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1631">
+        <v>1</v>
+      </c>
+      <c r="D1631">
+        <v>1</v>
+      </c>
+      <c r="E1631" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1631" t="s">
+        <v>311</v>
+      </c>
+      <c r="G1631" t="s">
+        <v>312</v>
+      </c>
+      <c r="H1631" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1631" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1631" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1631" t="s">
+        <v>312</v>
+      </c>
+      <c r="L1631">
+        <v>0</v>
+      </c>
+      <c r="M1631" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:14">
+      <c r="A1632" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>550</v>
+      </c>
+      <c r="C1632">
+        <v>1</v>
+      </c>
+      <c r="D1632">
+        <v>0</v>
+      </c>
+      <c r="E1632" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1632" t="s">
+        <v>808</v>
+      </c>
+      <c r="G1632" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1632" t="s">
+        <v>258</v>
+      </c>
+      <c r="I1632" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1632" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1632" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1632">
+        <v>0</v>
+      </c>
+      <c r="M1632" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:14">
+      <c r="A1633" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1633">
+        <v>1</v>
+      </c>
+      <c r="D1633">
+        <v>1</v>
+      </c>
+      <c r="E1633" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1633" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1633" t="s">
+        <v>297</v>
+      </c>
+      <c r="H1633" t="s">
+        <v>321</v>
+      </c>
+      <c r="I1633" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1633" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1633" t="s">
+        <v>297</v>
+      </c>
+      <c r="L1633">
+        <v>0</v>
+      </c>
+      <c r="M1633" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:14">
+      <c r="A1634" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C1634">
+        <v>1</v>
+      </c>
+      <c r="D1634">
+        <v>0</v>
+      </c>
+      <c r="E1634" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1634" t="s">
+        <v>306</v>
+      </c>
+      <c r="G1634" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1634" t="s">
+        <v>524</v>
+      </c>
+      <c r="I1634" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1634" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1634" t="s">
+        <v>254</v>
+      </c>
+      <c r="L1634">
+        <v>0</v>
+      </c>
+      <c r="M1634" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:14">
+      <c r="A1635" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>525</v>
+      </c>
+      <c r="C1635">
+        <v>1</v>
+      </c>
+      <c r="D1635">
+        <v>1</v>
+      </c>
+      <c r="E1635" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1635" t="s">
+        <v>699</v>
+      </c>
+      <c r="G1635" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1635" t="s">
+        <v>701</v>
+      </c>
+      <c r="I1635" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1635" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1635" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1635">
+        <v>0</v>
+      </c>
+      <c r="M1635" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1635">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:14">
+      <c r="A1636" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1636">
+        <v>1</v>
+      </c>
+      <c r="D1636">
+        <v>0</v>
+      </c>
+      <c r="E1636" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1636" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G1636" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1636" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1636" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1636" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1636" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1636">
+        <v>0</v>
+      </c>
+      <c r="M1636" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:14">
+      <c r="A1637" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1637">
+        <v>1</v>
+      </c>
+      <c r="D1637">
+        <v>1</v>
+      </c>
+      <c r="E1637" s="4">
+        <v>1</v>
+      </c>
+      <c r="F1637" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1637" t="s">
+        <v>303</v>
+      </c>
+      <c r="H1637" t="s">
+        <v>312</v>
+      </c>
+      <c r="I1637" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1637" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1637" t="s">
+        <v>303</v>
+      </c>
+      <c r="L1637">
+        <v>0</v>
+      </c>
+      <c r="M1637" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:14">
+      <c r="A1638" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1638">
+        <v>1</v>
+      </c>
+      <c r="D1638">
+        <v>0</v>
+      </c>
+      <c r="E1638" s="4">
+        <v>0</v>
+      </c>
+      <c r="F1638" t="s">
+        <v>2031</v>
+      </c>
+      <c r="G1638" t="s">
+        <v>2032</v>
+      </c>
+      <c r="H1638" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1638" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1638" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1638" t="s">
+        <v>2032</v>
+      </c>
+      <c r="L1638">
+        <v>0</v>
+      </c>
+      <c r="M1638" s="4">
+        <v>0</v>
+      </c>
+      <c r="N1638">
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\new clone\Salefile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A5E411-3ABC-48FF-8609-568F6125365E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AAFA8F-8950-4552-8705-CC0A360401AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12047" uniqueCount="2550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12628" uniqueCount="2633">
   <si>
     <t>Date</t>
   </si>
@@ -7452,24 +7452,6 @@
     <t>0.0925 EUR</t>
   </si>
   <si>
-    <t>17.961 EUR</t>
-  </si>
-  <si>
-    <t>10.879 EUR</t>
-  </si>
-  <si>
-    <t>28.84 EUR</t>
-  </si>
-  <si>
-    <t>21.0866 EUR</t>
-  </si>
-  <si>
-    <t>49.9034 EUR</t>
-  </si>
-  <si>
-    <t>70.99 EUR</t>
-  </si>
-  <si>
     <t>0.43698 EUR</t>
   </si>
   <si>
@@ -7479,24 +7461,6 @@
     <t>4.24795 EUR</t>
   </si>
   <si>
-    <t>0.8103 EUR</t>
-  </si>
-  <si>
-    <t>9.9057 EUR</t>
-  </si>
-  <si>
-    <t>10.716 EUR</t>
-  </si>
-  <si>
-    <t>5.176 EUR</t>
-  </si>
-  <si>
-    <t>44.704 EUR</t>
-  </si>
-  <si>
-    <t>49.88 EUR</t>
-  </si>
-  <si>
     <t>4.4989 EUR</t>
   </si>
   <si>
@@ -7506,114 +7470,18 @@
     <t>8.991 EUR</t>
   </si>
   <si>
-    <t>1.204 EUR</t>
-  </si>
-  <si>
-    <t>3.184 EUR</t>
-  </si>
-  <si>
-    <t>1.0316 EUR</t>
-  </si>
-  <si>
-    <t>1.1104 EUR</t>
-  </si>
-  <si>
-    <t>2.142 EUR</t>
-  </si>
-  <si>
-    <t>0.49865 EUR</t>
-  </si>
-  <si>
-    <t>0.40315 EUR</t>
-  </si>
-  <si>
-    <t>0.9018 EUR</t>
-  </si>
-  <si>
-    <t>1.1712 EUR</t>
-  </si>
-  <si>
-    <t>2.8512 EUR</t>
-  </si>
-  <si>
     <t>0.702 EUR</t>
   </si>
   <si>
-    <t>0.66842 EUR</t>
-  </si>
-  <si>
-    <t>1.4955 EUR</t>
-  </si>
-  <si>
-    <t>2.16392 EUR</t>
-  </si>
-  <si>
-    <t>0.704 EUR</t>
-  </si>
-  <si>
-    <t>2.424 EUR</t>
-  </si>
-  <si>
-    <t>3.3 EUR</t>
-  </si>
-  <si>
-    <t>0.07835 EUR</t>
-  </si>
-  <si>
-    <t>0.22995 EUR</t>
-  </si>
-  <si>
-    <t>0.3083 EUR</t>
-  </si>
-  <si>
-    <t>0.6176 EUR</t>
-  </si>
-  <si>
-    <t>0.1244 EUR</t>
-  </si>
-  <si>
-    <t>0.2825 EUR</t>
-  </si>
-  <si>
-    <t>0.3209 EUR</t>
-  </si>
-  <si>
     <t>0.3652 EUR</t>
   </si>
   <si>
-    <t>0.55 EUR</t>
-  </si>
-  <si>
-    <t>2.31 EUR</t>
-  </si>
-  <si>
     <t>0.3948 EUR</t>
   </si>
   <si>
     <t>0.0672 EUR</t>
   </si>
   <si>
-    <t>0.02995 EUR</t>
-  </si>
-  <si>
-    <t>0.1455 EUR</t>
-  </si>
-  <si>
-    <t>0.17545 EUR</t>
-  </si>
-  <si>
-    <t>0.513 EUR</t>
-  </si>
-  <si>
-    <t>0.07834 EUR</t>
-  </si>
-  <si>
-    <t>0.5645 EUR</t>
-  </si>
-  <si>
-    <t>0.64284 EUR</t>
-  </si>
-  <si>
     <t>-0.124 EUR</t>
   </si>
   <si>
@@ -7635,24 +7503,9 @@
     <t>0.00195 EUR</t>
   </si>
   <si>
-    <t>0.1012 EUR</t>
-  </si>
-  <si>
     <t>0.2256 EUR</t>
   </si>
   <si>
-    <t>0.2528 EUR</t>
-  </si>
-  <si>
-    <t>0.583 EUR</t>
-  </si>
-  <si>
-    <t>0.12619 EUR</t>
-  </si>
-  <si>
-    <t>0.166 EUR</t>
-  </si>
-  <si>
     <t>Avrio Mobility_HQ(Client)</t>
   </si>
   <si>
@@ -7668,9 +7521,6 @@
     <t>0.1272 EUR</t>
   </si>
   <si>
-    <t>0.079 EUR</t>
-  </si>
-  <si>
     <t>0.0222 EUR</t>
   </si>
   <si>
@@ -7690,6 +7540,405 @@
   </si>
   <si>
     <t>0.0416 EUR</t>
+  </si>
+  <si>
+    <t>22.376 EUR</t>
+  </si>
+  <si>
+    <t>13.504 EUR</t>
+  </si>
+  <si>
+    <t>35.88 EUR</t>
+  </si>
+  <si>
+    <t>21.5032 EUR</t>
+  </si>
+  <si>
+    <t>50.8508 EUR</t>
+  </si>
+  <si>
+    <t>72.354 EUR</t>
+  </si>
+  <si>
+    <t>0.8157 EUR</t>
+  </si>
+  <si>
+    <t>9.9723 EUR</t>
+  </si>
+  <si>
+    <t>10.788 EUR</t>
+  </si>
+  <si>
+    <t>5.674 EUR</t>
+  </si>
+  <si>
+    <t>48.522 EUR</t>
+  </si>
+  <si>
+    <t>54.196 EUR</t>
+  </si>
+  <si>
+    <t>1.205 EUR</t>
+  </si>
+  <si>
+    <t>3.2 EUR</t>
+  </si>
+  <si>
+    <t>1.0568 EUR</t>
+  </si>
+  <si>
+    <t>1.1392 EUR</t>
+  </si>
+  <si>
+    <t>2.196 EUR</t>
+  </si>
+  <si>
+    <t>0.50005 EUR</t>
+  </si>
+  <si>
+    <t>0.40355 EUR</t>
+  </si>
+  <si>
+    <t>0.9036 EUR</t>
+  </si>
+  <si>
+    <t>0.13835 EUR</t>
+  </si>
+  <si>
+    <t>0.46125 EUR</t>
+  </si>
+  <si>
+    <t>1.4784 EUR</t>
+  </si>
+  <si>
+    <t>1.848 EUR</t>
+  </si>
+  <si>
+    <t>3.3264 EUR</t>
+  </si>
+  <si>
+    <t>1.655 EUR</t>
+  </si>
+  <si>
+    <t>1.755 EUR</t>
+  </si>
+  <si>
+    <t>0.423 EUR</t>
+  </si>
+  <si>
+    <t>0.87882 EUR</t>
+  </si>
+  <si>
+    <t>1.9935 EUR</t>
+  </si>
+  <si>
+    <t>2.87232 EUR</t>
+  </si>
+  <si>
+    <t>1.044 EUR</t>
+  </si>
+  <si>
+    <t>3.096 EUR</t>
+  </si>
+  <si>
+    <t>4.14 EUR</t>
+  </si>
+  <si>
+    <t>0.6266 EUR</t>
+  </si>
+  <si>
+    <t>0.1394 EUR</t>
+  </si>
+  <si>
+    <t>0.766 EUR</t>
+  </si>
+  <si>
+    <t>0.3344 EUR</t>
+  </si>
+  <si>
+    <t>0.0858 EUR</t>
+  </si>
+  <si>
+    <t>0.6725 EUR</t>
+  </si>
+  <si>
+    <t>0.7583 EUR</t>
+  </si>
+  <si>
+    <t>0.02445 EUR</t>
+  </si>
+  <si>
+    <t>0.02775 EUR</t>
+  </si>
+  <si>
+    <t>0.0522 EUR</t>
+  </si>
+  <si>
+    <t>0.1842 EUR</t>
+  </si>
+  <si>
+    <t>0.2289 EUR</t>
+  </si>
+  <si>
+    <t>0.1094 EUR</t>
+  </si>
+  <si>
+    <t>0.0536 EUR</t>
+  </si>
+  <si>
+    <t>0.163 EUR</t>
+  </si>
+  <si>
+    <t>0.05181 EUR</t>
+  </si>
+  <si>
+    <t>0.18019 EUR</t>
+  </si>
+  <si>
+    <t>0.0091 EUR</t>
+  </si>
+  <si>
+    <t>0.0795 EUR</t>
+  </si>
+  <si>
+    <t>163.4438 EUR</t>
+  </si>
+  <si>
+    <t>338.5962 EUR</t>
+  </si>
+  <si>
+    <t>502.04 EUR</t>
+  </si>
+  <si>
+    <t>16.7155 EUR</t>
+  </si>
+  <si>
+    <t>9.9445 EUR</t>
+  </si>
+  <si>
+    <t>26.66 EUR</t>
+  </si>
+  <si>
+    <t>12.8836 EUR</t>
+  </si>
+  <si>
+    <t>30.9964 EUR</t>
+  </si>
+  <si>
+    <t>43.88 EUR</t>
+  </si>
+  <si>
+    <t>1.7005 EUR</t>
+  </si>
+  <si>
+    <t>28.4315 EUR</t>
+  </si>
+  <si>
+    <t>30.132 EUR</t>
+  </si>
+  <si>
+    <t>3.714 EUR</t>
+  </si>
+  <si>
+    <t>29.278 EUR</t>
+  </si>
+  <si>
+    <t>32.992 EUR</t>
+  </si>
+  <si>
+    <t>3.12998 EUR</t>
+  </si>
+  <si>
+    <t>0.02903 EUR</t>
+  </si>
+  <si>
+    <t>3.159 EUR</t>
+  </si>
+  <si>
+    <t>0.1465 EUR</t>
+  </si>
+  <si>
+    <t>1.7775 EUR</t>
+  </si>
+  <si>
+    <t>1.924 EUR</t>
+  </si>
+  <si>
+    <t>0.515 EUR</t>
+  </si>
+  <si>
+    <t>0.824 EUR</t>
+  </si>
+  <si>
+    <t>1.63751 EUR</t>
+  </si>
+  <si>
+    <t>0.76849 EUR</t>
+  </si>
+  <si>
+    <t>2.406 EUR</t>
+  </si>
+  <si>
+    <t>0.53025 EUR</t>
+  </si>
+  <si>
+    <t>0.42975 EUR</t>
+  </si>
+  <si>
+    <t>2.3808 EUR</t>
+  </si>
+  <si>
+    <t>1.302 EUR</t>
+  </si>
+  <si>
+    <t>3.6828 EUR</t>
+  </si>
+  <si>
+    <t>1.058 EUR</t>
+  </si>
+  <si>
+    <t>3.802 EUR</t>
+  </si>
+  <si>
+    <t>4.86 EUR</t>
+  </si>
+  <si>
+    <t>0.2436 EUR</t>
+  </si>
+  <si>
+    <t>0.82082 EUR</t>
+  </si>
+  <si>
+    <t>1.9437 EUR</t>
+  </si>
+  <si>
+    <t>2.76452 EUR</t>
+  </si>
+  <si>
+    <t>0.837 EUR</t>
+  </si>
+  <si>
+    <t>0.07085 EUR</t>
+  </si>
+  <si>
+    <t>0.30385 EUR</t>
+  </si>
+  <si>
+    <t>0.3747 EUR</t>
+  </si>
+  <si>
+    <t>0.0862 EUR</t>
+  </si>
+  <si>
+    <t>0.0448 EUR</t>
+  </si>
+  <si>
+    <t>0.2652 EUR</t>
+  </si>
+  <si>
+    <t>0.3048 EUR</t>
+  </si>
+  <si>
+    <t>0.13661 EUR</t>
+  </si>
+  <si>
+    <t>0.09739 EUR</t>
+  </si>
+  <si>
+    <t>0.03265 EUR</t>
+  </si>
+  <si>
+    <t>0.21415 EUR</t>
+  </si>
+  <si>
+    <t>0.0126 EUR</t>
+  </si>
+  <si>
+    <t>0.4976 EUR</t>
+  </si>
+  <si>
+    <t>0.42884 EUR</t>
+  </si>
+  <si>
+    <t>0.56116 EUR</t>
+  </si>
+  <si>
+    <t>0.151 EUR</t>
+  </si>
+  <si>
+    <t>0.00695 EUR</t>
+  </si>
+  <si>
+    <t>0.00765 EUR</t>
+  </si>
+  <si>
+    <t>0.0146 EUR</t>
+  </si>
+  <si>
+    <t>0.01305 EUR</t>
+  </si>
+  <si>
+    <t>0.20205 EUR</t>
+  </si>
+  <si>
+    <t>0.2375 EUR</t>
+  </si>
+  <si>
+    <t>0.1025 EUR</t>
+  </si>
+  <si>
+    <t>0.00475 EUR</t>
+  </si>
+  <si>
+    <t>0.00665 EUR</t>
+  </si>
+  <si>
+    <t>0.318 EUR</t>
+  </si>
+  <si>
+    <t>0.402 EUR</t>
+  </si>
+  <si>
+    <t>0.14115 EUR</t>
+  </si>
+  <si>
+    <t>0.00045 EUR</t>
+  </si>
+  <si>
+    <t>0.1416 EUR</t>
+  </si>
+  <si>
+    <t>0.122 EUR</t>
+  </si>
+  <si>
+    <t>0.24406 EUR</t>
+  </si>
+  <si>
+    <t>0.01594 EUR</t>
+  </si>
+  <si>
+    <t>0.01325 EUR</t>
+  </si>
+  <si>
+    <t>0.0928 EUR</t>
+  </si>
+  <si>
+    <t>Cyvora_HQ(Client)</t>
+  </si>
+  <si>
+    <t>0.0708 EUR</t>
+  </si>
+  <si>
+    <t>0.0592 EUR</t>
+  </si>
+  <si>
+    <t>0.0624 EUR</t>
+  </si>
+  <si>
+    <t>0.0481 EUR</t>
+  </si>
+  <si>
+    <t>0.0214 EUR</t>
   </si>
 </sst>
 </file>
@@ -8078,7 +8327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1720"/>
+  <dimension ref="A1:N1803"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -80308,22 +80557,22 @@
         <v>24</v>
       </c>
       <c r="C1642" s="2">
-        <v>2884</v>
+        <v>3588</v>
       </c>
       <c r="D1642" s="2">
-        <v>2736</v>
+        <v>3405</v>
       </c>
       <c r="E1642" s="4">
-        <v>0.94868240000000004</v>
+        <v>0.94899670000000003</v>
       </c>
       <c r="F1642" s="2" t="s">
-        <v>2470</v>
+        <v>2500</v>
       </c>
       <c r="G1642" s="2" t="s">
-        <v>2471</v>
+        <v>2501</v>
       </c>
       <c r="H1642" s="2" t="s">
-        <v>2472</v>
+        <v>2502</v>
       </c>
       <c r="I1642" s="2" t="s">
         <v>28</v>
@@ -80332,7 +80581,7 @@
         <v>19</v>
       </c>
       <c r="K1642" s="2" t="s">
-        <v>2471</v>
+        <v>2501</v>
       </c>
       <c r="L1642" s="2">
         <v>0</v>
@@ -80352,22 +80601,22 @@
         <v>49</v>
       </c>
       <c r="C1643" s="2">
-        <v>2290</v>
+        <v>2334</v>
       </c>
       <c r="D1643" s="2">
-        <v>1973</v>
+        <v>2015</v>
       </c>
       <c r="E1643" s="4">
-        <v>0.86157209999999995</v>
+        <v>0.8633248</v>
       </c>
       <c r="F1643" s="2" t="s">
-        <v>2473</v>
+        <v>2503</v>
       </c>
       <c r="G1643" s="2" t="s">
-        <v>2474</v>
+        <v>2504</v>
       </c>
       <c r="H1643" s="2" t="s">
-        <v>2475</v>
+        <v>2505</v>
       </c>
       <c r="I1643" s="2" t="s">
         <v>28</v>
@@ -80376,7 +80625,7 @@
         <v>19</v>
       </c>
       <c r="K1643" s="2" t="s">
-        <v>2474</v>
+        <v>2504</v>
       </c>
       <c r="L1643" s="2">
         <v>0</v>
@@ -80405,13 +80654,13 @@
         <v>0.95321270000000002</v>
       </c>
       <c r="F1644" s="2" t="s">
-        <v>2476</v>
+        <v>2470</v>
       </c>
       <c r="G1644" s="2" t="s">
-        <v>2477</v>
+        <v>2471</v>
       </c>
       <c r="H1644" s="2" t="s">
-        <v>2478</v>
+        <v>2472</v>
       </c>
       <c r="I1644" s="2" t="s">
         <v>23</v>
@@ -80420,7 +80669,7 @@
         <v>19</v>
       </c>
       <c r="K1644" s="2" t="s">
-        <v>2477</v>
+        <v>2471</v>
       </c>
       <c r="L1644" s="2">
         <v>0</v>
@@ -80440,22 +80689,22 @@
         <v>45</v>
       </c>
       <c r="C1645" s="2">
-        <v>1350</v>
+        <v>1359</v>
       </c>
       <c r="D1645" s="2">
-        <v>1338</v>
+        <v>1347</v>
       </c>
       <c r="E1645" s="4">
-        <v>0.99111110000000002</v>
+        <v>0.99117</v>
       </c>
       <c r="F1645" s="2" t="s">
-        <v>2479</v>
+        <v>2506</v>
       </c>
       <c r="G1645" s="2" t="s">
-        <v>2480</v>
+        <v>2507</v>
       </c>
       <c r="H1645" s="2" t="s">
-        <v>2481</v>
+        <v>2508</v>
       </c>
       <c r="I1645" s="2" t="s">
         <v>23</v>
@@ -80464,7 +80713,7 @@
         <v>19</v>
       </c>
       <c r="K1645" s="2" t="s">
-        <v>2480</v>
+        <v>2507</v>
       </c>
       <c r="L1645" s="2">
         <v>0</v>
@@ -80484,22 +80733,22 @@
         <v>2391</v>
       </c>
       <c r="C1646" s="2">
-        <v>830</v>
+        <v>913</v>
       </c>
       <c r="D1646" s="2">
-        <v>792</v>
+        <v>875</v>
       </c>
       <c r="E1646" s="4">
-        <v>0.95421690000000003</v>
+        <v>0.95837899999999998</v>
       </c>
       <c r="F1646" s="2" t="s">
-        <v>2482</v>
+        <v>2509</v>
       </c>
       <c r="G1646" s="2" t="s">
-        <v>2483</v>
+        <v>2510</v>
       </c>
       <c r="H1646" s="2" t="s">
-        <v>2484</v>
+        <v>2511</v>
       </c>
       <c r="I1646" s="2" t="s">
         <v>28</v>
@@ -80508,7 +80757,7 @@
         <v>19</v>
       </c>
       <c r="K1646" s="2" t="s">
-        <v>2483</v>
+        <v>2510</v>
       </c>
       <c r="L1646" s="2">
         <v>0</v>
@@ -80537,13 +80786,13 @@
         <v>0.89496399999999998</v>
       </c>
       <c r="F1647" s="2" t="s">
-        <v>2485</v>
+        <v>2473</v>
       </c>
       <c r="G1647" s="2" t="s">
-        <v>2486</v>
+        <v>2474</v>
       </c>
       <c r="H1647" s="2" t="s">
-        <v>2487</v>
+        <v>2475</v>
       </c>
       <c r="I1647" s="2" t="s">
         <v>28</v>
@@ -80552,7 +80801,7 @@
         <v>19</v>
       </c>
       <c r="K1647" s="2" t="s">
-        <v>2486</v>
+        <v>2474</v>
       </c>
       <c r="L1647" s="2">
         <v>0</v>
@@ -80572,22 +80821,22 @@
         <v>65</v>
       </c>
       <c r="C1648" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D1648" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E1648" s="4">
-        <v>0.88016530000000004</v>
+        <v>0.88247419999999999</v>
       </c>
       <c r="F1648" s="2" t="s">
-        <v>2488</v>
+        <v>2512</v>
       </c>
       <c r="G1648" s="2" t="s">
-        <v>386</v>
+        <v>1183</v>
       </c>
       <c r="H1648" s="2" t="s">
-        <v>2489</v>
+        <v>2513</v>
       </c>
       <c r="I1648" s="2" t="s">
         <v>18</v>
@@ -80596,7 +80845,7 @@
         <v>19</v>
       </c>
       <c r="K1648" s="2" t="s">
-        <v>386</v>
+        <v>1183</v>
       </c>
       <c r="L1648" s="2">
         <v>0</v>
@@ -80616,22 +80865,22 @@
         <v>124</v>
       </c>
       <c r="C1649" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D1649" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E1649" s="4">
-        <v>0.86134449999999996</v>
+        <v>0.86475409999999997</v>
       </c>
       <c r="F1649" s="2" t="s">
-        <v>2490</v>
+        <v>2514</v>
       </c>
       <c r="G1649" s="2" t="s">
-        <v>2491</v>
+        <v>2515</v>
       </c>
       <c r="H1649" s="2" t="s">
-        <v>2492</v>
+        <v>2516</v>
       </c>
       <c r="I1649" s="2" t="s">
         <v>23</v>
@@ -80640,7 +80889,7 @@
         <v>19</v>
       </c>
       <c r="K1649" s="2" t="s">
-        <v>2491</v>
+        <v>2515</v>
       </c>
       <c r="L1649" s="2">
         <v>0</v>
@@ -80660,22 +80909,22 @@
         <v>101</v>
       </c>
       <c r="C1650" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1650" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E1650" s="4">
-        <v>0.92307689999999998</v>
+        <v>0.92391299999999998</v>
       </c>
       <c r="F1650" s="2" t="s">
-        <v>2493</v>
+        <v>2517</v>
       </c>
       <c r="G1650" s="2" t="s">
-        <v>2494</v>
+        <v>2518</v>
       </c>
       <c r="H1650" s="2" t="s">
-        <v>2495</v>
+        <v>2519</v>
       </c>
       <c r="I1650" s="2" t="s">
         <v>23</v>
@@ -80684,7 +80933,7 @@
         <v>19</v>
       </c>
       <c r="K1650" s="2" t="s">
-        <v>2494</v>
+        <v>2518</v>
       </c>
       <c r="L1650" s="2">
         <v>0</v>
@@ -80701,25 +80950,25 @@
         <v>46288</v>
       </c>
       <c r="B1651" s="2" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="C1651" s="2">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D1651" s="2">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="E1651" s="4">
-        <v>0.94444439999999996</v>
+        <v>0.98888889999999996</v>
       </c>
       <c r="F1651" s="2" t="s">
-        <v>2496</v>
+        <v>2520</v>
       </c>
       <c r="G1651" s="2" t="s">
-        <v>1439</v>
+        <v>2521</v>
       </c>
       <c r="H1651" s="2" t="s">
-        <v>2497</v>
+        <v>1398</v>
       </c>
       <c r="I1651" s="2" t="s">
         <v>18</v>
@@ -80728,7 +80977,7 @@
         <v>19</v>
       </c>
       <c r="K1651" s="2" t="s">
-        <v>1439</v>
+        <v>2521</v>
       </c>
       <c r="L1651" s="2">
         <v>0</v>
@@ -80745,34 +80994,34 @@
         <v>46288</v>
       </c>
       <c r="B1652" s="2" t="s">
-        <v>329</v>
+        <v>128</v>
       </c>
       <c r="C1652" s="2">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="D1652" s="2">
-        <v>9</v>
-      </c>
-      <c r="E1652" s="5">
-        <v>0.25</v>
+        <v>80</v>
+      </c>
+      <c r="E1652" s="4">
+        <v>0.95238100000000003</v>
       </c>
       <c r="F1652" s="2" t="s">
-        <v>2498</v>
+        <v>2522</v>
       </c>
       <c r="G1652" s="2" t="s">
-        <v>270</v>
+        <v>2523</v>
       </c>
       <c r="H1652" s="2" t="s">
-        <v>2339</v>
+        <v>2524</v>
       </c>
       <c r="I1652" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1652" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1652" s="2" t="s">
-        <v>270</v>
+        <v>2523</v>
       </c>
       <c r="L1652" s="2">
         <v>0</v>
@@ -80789,34 +81038,34 @@
         <v>46288</v>
       </c>
       <c r="B1653" s="2" t="s">
-        <v>148</v>
+        <v>308</v>
       </c>
       <c r="C1653" s="2">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D1653" s="2">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E1653" s="4">
-        <v>0.78125</v>
+        <v>0.70769230000000005</v>
       </c>
       <c r="F1653" s="2" t="s">
-        <v>2499</v>
+        <v>504</v>
       </c>
       <c r="G1653" s="2" t="s">
-        <v>2500</v>
+        <v>2525</v>
       </c>
       <c r="H1653" s="2" t="s">
-        <v>2501</v>
+        <v>2526</v>
       </c>
       <c r="I1653" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1653" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1653" s="2" t="s">
-        <v>2500</v>
+        <v>2525</v>
       </c>
       <c r="L1653" s="2">
         <v>0</v>
@@ -80833,25 +81082,25 @@
         <v>46288</v>
       </c>
       <c r="B1654" s="2" t="s">
-        <v>409</v>
+        <v>81</v>
       </c>
       <c r="C1654" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D1654" s="2">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E1654" s="4">
-        <v>0.3125</v>
+        <v>0.88888889999999998</v>
       </c>
       <c r="F1654" s="2" t="s">
-        <v>1199</v>
+        <v>1348</v>
       </c>
       <c r="G1654" s="2" t="s">
-        <v>2502</v>
+        <v>158</v>
       </c>
       <c r="H1654" s="2" t="s">
-        <v>771</v>
+        <v>2527</v>
       </c>
       <c r="I1654" s="2" t="s">
         <v>18</v>
@@ -80860,7 +81109,7 @@
         <v>19</v>
       </c>
       <c r="K1654" s="2" t="s">
-        <v>2502</v>
+        <v>158</v>
       </c>
       <c r="L1654" s="2">
         <v>0</v>
@@ -80877,25 +81126,25 @@
         <v>46288</v>
       </c>
       <c r="B1655" s="2" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="C1655" s="2">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D1655" s="2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E1655" s="4">
-        <v>0.66666669999999995</v>
+        <v>0.78571429999999998</v>
       </c>
       <c r="F1655" s="2" t="s">
-        <v>1502</v>
+        <v>2528</v>
       </c>
       <c r="G1655" s="2" t="s">
-        <v>2503</v>
+        <v>2529</v>
       </c>
       <c r="H1655" s="2" t="s">
-        <v>2504</v>
+        <v>2530</v>
       </c>
       <c r="I1655" s="2" t="s">
         <v>28</v>
@@ -80904,7 +81153,7 @@
         <v>19</v>
       </c>
       <c r="K1655" s="2" t="s">
-        <v>2503</v>
+        <v>2529</v>
       </c>
       <c r="L1655" s="2">
         <v>0</v>
@@ -80921,34 +81170,34 @@
         <v>46288</v>
       </c>
       <c r="B1656" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C1656" s="2">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D1656" s="2">
+        <v>30</v>
+      </c>
+      <c r="E1656" s="4">
+        <v>0.71428570000000002</v>
+      </c>
+      <c r="F1656" s="2" t="s">
+        <v>2531</v>
+      </c>
+      <c r="G1656" s="2" t="s">
+        <v>2532</v>
+      </c>
+      <c r="H1656" s="2" t="s">
+        <v>2533</v>
+      </c>
+      <c r="I1656" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E1656" s="4">
-        <v>0.96551719999999996</v>
-      </c>
-      <c r="F1656" s="2" t="s">
-        <v>2505</v>
-      </c>
-      <c r="G1656" s="2" t="s">
-        <v>2506</v>
-      </c>
-      <c r="H1656" s="2" t="s">
-        <v>2507</v>
-      </c>
-      <c r="I1656" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="J1656" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1656" s="2" t="s">
-        <v>2506</v>
+        <v>2532</v>
       </c>
       <c r="L1656" s="2">
         <v>0</v>
@@ -80965,25 +81214,25 @@
         <v>46288</v>
       </c>
       <c r="B1657" s="2" t="s">
-        <v>57</v>
+        <v>329</v>
       </c>
       <c r="C1657" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D1657" s="2">
-        <v>3</v>
-      </c>
-      <c r="E1657" s="4">
-        <v>0.10344830000000001</v>
+        <v>9</v>
+      </c>
+      <c r="E1657" s="5">
+        <v>0.25</v>
       </c>
       <c r="F1657" s="2" t="s">
-        <v>2508</v>
+        <v>2476</v>
       </c>
       <c r="G1657" s="2" t="s">
-        <v>2509</v>
+        <v>270</v>
       </c>
       <c r="H1657" s="2" t="s">
-        <v>1632</v>
+        <v>2339</v>
       </c>
       <c r="I1657" s="2" t="s">
         <v>23</v>
@@ -80992,7 +81241,7 @@
         <v>19</v>
       </c>
       <c r="K1657" s="2" t="s">
-        <v>2509</v>
+        <v>270</v>
       </c>
       <c r="L1657" s="2">
         <v>0</v>
@@ -81009,25 +81258,25 @@
         <v>46288</v>
       </c>
       <c r="B1658" s="2" t="s">
-        <v>81</v>
+        <v>409</v>
       </c>
       <c r="C1658" s="2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D1658" s="2">
-        <v>20</v>
-      </c>
-      <c r="E1658" s="5">
-        <v>0.8</v>
+        <v>11</v>
+      </c>
+      <c r="E1658" s="4">
+        <v>0.3333333</v>
       </c>
       <c r="F1658" s="2" t="s">
-        <v>1228</v>
+        <v>200</v>
       </c>
       <c r="G1658" s="2" t="s">
-        <v>2510</v>
+        <v>2071</v>
       </c>
       <c r="H1658" s="2" t="s">
-        <v>2511</v>
+        <v>1045</v>
       </c>
       <c r="I1658" s="2" t="s">
         <v>18</v>
@@ -81036,7 +81285,7 @@
         <v>19</v>
       </c>
       <c r="K1658" s="2" t="s">
-        <v>2510</v>
+        <v>2071</v>
       </c>
       <c r="L1658" s="2">
         <v>0</v>
@@ -81053,34 +81302,34 @@
         <v>46288</v>
       </c>
       <c r="B1659" s="2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="C1659" s="2">
+        <v>30</v>
+      </c>
+      <c r="D1659" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1659" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="F1659" s="2" t="s">
+        <v>2534</v>
+      </c>
+      <c r="G1659" s="2" t="s">
+        <v>2535</v>
+      </c>
+      <c r="H1659" s="2" t="s">
+        <v>2536</v>
+      </c>
+      <c r="I1659" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D1659" s="2">
-        <v>0</v>
-      </c>
-      <c r="E1659" s="5">
-        <v>0</v>
-      </c>
-      <c r="F1659" s="2" t="s">
-        <v>2512</v>
-      </c>
-      <c r="G1659" s="2" t="s">
-        <v>1699</v>
-      </c>
-      <c r="H1659" s="2" t="s">
-        <v>1631</v>
-      </c>
-      <c r="I1659" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="J1659" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1659" s="2" t="s">
-        <v>1699</v>
+        <v>2535</v>
       </c>
       <c r="L1659" s="2">
         <v>0</v>
@@ -81097,34 +81346,34 @@
         <v>46288</v>
       </c>
       <c r="B1660" s="2" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="C1660" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D1660" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E1660" s="4">
-        <v>0.69565220000000005</v>
+        <v>0.92307689999999998</v>
       </c>
       <c r="F1660" s="2" t="s">
-        <v>248</v>
+        <v>1339</v>
       </c>
       <c r="G1660" s="2" t="s">
-        <v>1337</v>
+        <v>1174</v>
       </c>
       <c r="H1660" s="2" t="s">
-        <v>1088</v>
+        <v>2537</v>
       </c>
       <c r="I1660" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1660" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1660" s="2" t="s">
-        <v>1337</v>
+        <v>1174</v>
       </c>
       <c r="L1660" s="2">
         <v>0</v>
@@ -81144,22 +81393,22 @@
         <v>85</v>
       </c>
       <c r="C1661" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D1661" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1661" s="5">
-        <v>0.5</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F1661" s="2" t="s">
-        <v>2513</v>
+        <v>1061</v>
       </c>
       <c r="G1661" s="2" t="s">
-        <v>1619</v>
+        <v>1062</v>
       </c>
       <c r="H1661" s="2" t="s">
-        <v>2514</v>
+        <v>1063</v>
       </c>
       <c r="I1661" s="2" t="s">
         <v>28</v>
@@ -81168,7 +81417,7 @@
         <v>19</v>
       </c>
       <c r="K1661" s="2" t="s">
-        <v>1619</v>
+        <v>1062</v>
       </c>
       <c r="L1661" s="2">
         <v>0</v>
@@ -81185,34 +81434,34 @@
         <v>46288</v>
       </c>
       <c r="B1662" s="2" t="s">
-        <v>97</v>
+        <v>237</v>
       </c>
       <c r="C1662" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D1662" s="2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E1662" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1662" s="2" t="s">
-        <v>2515</v>
+        <v>1921</v>
       </c>
       <c r="G1662" s="2" t="s">
-        <v>2516</v>
+        <v>819</v>
       </c>
       <c r="H1662" s="2" t="s">
-        <v>154</v>
+        <v>1330</v>
       </c>
       <c r="I1662" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1662" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1662" s="2" t="s">
-        <v>2516</v>
+        <v>819</v>
       </c>
       <c r="L1662" s="2">
         <v>0</v>
@@ -81229,34 +81478,34 @@
         <v>46288</v>
       </c>
       <c r="B1663" s="2" t="s">
-        <v>237</v>
+        <v>73</v>
       </c>
       <c r="C1663" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D1663" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E1663" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1663" s="2" t="s">
-        <v>2517</v>
+        <v>2477</v>
       </c>
       <c r="G1663" s="2" t="s">
-        <v>2518</v>
+        <v>1699</v>
       </c>
       <c r="H1663" s="2" t="s">
-        <v>2519</v>
+        <v>1631</v>
       </c>
       <c r="I1663" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1663" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1663" s="2" t="s">
-        <v>2518</v>
+        <v>1699</v>
       </c>
       <c r="L1663" s="2">
         <v>0</v>
@@ -81273,34 +81522,34 @@
         <v>46288</v>
       </c>
       <c r="B1664" s="2" t="s">
-        <v>308</v>
+        <v>198</v>
       </c>
       <c r="C1664" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D1664" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1664" s="4">
-        <v>0.4210526</v>
+        <v>0.69565220000000005</v>
       </c>
       <c r="F1664" s="2" t="s">
-        <v>1114</v>
+        <v>248</v>
       </c>
       <c r="G1664" s="2" t="s">
-        <v>791</v>
+        <v>1337</v>
       </c>
       <c r="H1664" s="2" t="s">
-        <v>2520</v>
+        <v>1088</v>
       </c>
       <c r="I1664" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1664" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1664" s="2" t="s">
-        <v>791</v>
+        <v>1337</v>
       </c>
       <c r="L1664" s="2">
         <v>0</v>
@@ -81317,25 +81566,25 @@
         <v>46288</v>
       </c>
       <c r="B1665" s="2" t="s">
-        <v>29</v>
+        <v>325</v>
       </c>
       <c r="C1665" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D1665" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E1665" s="4">
-        <v>0.83333330000000005</v>
+        <v>0.95454550000000005</v>
       </c>
       <c r="F1665" s="2" t="s">
-        <v>2521</v>
+        <v>283</v>
       </c>
       <c r="G1665" s="2" t="s">
-        <v>2522</v>
+        <v>298</v>
       </c>
       <c r="H1665" s="2" t="s">
-        <v>2523</v>
+        <v>539</v>
       </c>
       <c r="I1665" s="2" t="s">
         <v>28</v>
@@ -81344,7 +81593,7 @@
         <v>19</v>
       </c>
       <c r="K1665" s="2" t="s">
-        <v>2522</v>
+        <v>298</v>
       </c>
       <c r="L1665" s="2">
         <v>0</v>
@@ -81361,34 +81610,34 @@
         <v>46288</v>
       </c>
       <c r="B1666" s="2" t="s">
-        <v>1117</v>
+        <v>29</v>
       </c>
       <c r="C1666" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D1666" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E1666" s="4">
-        <v>0.55555560000000004</v>
+        <v>0.77272730000000001</v>
       </c>
       <c r="F1666" s="2" t="s">
-        <v>453</v>
+        <v>2538</v>
       </c>
       <c r="G1666" s="2" t="s">
-        <v>155</v>
+        <v>2539</v>
       </c>
       <c r="H1666" s="2" t="s">
-        <v>1635</v>
+        <v>2540</v>
       </c>
       <c r="I1666" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1666" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1666" s="2" t="s">
-        <v>155</v>
+        <v>2539</v>
       </c>
       <c r="L1666" s="2">
         <v>0</v>
@@ -81405,34 +81654,34 @@
         <v>46288</v>
       </c>
       <c r="B1667" s="2" t="s">
-        <v>333</v>
+        <v>144</v>
       </c>
       <c r="C1667" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D1667" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E1667" s="4">
-        <v>0.9375</v>
+        <v>0.95454550000000005</v>
       </c>
       <c r="F1667" s="2" t="s">
-        <v>1199</v>
+        <v>2541</v>
       </c>
       <c r="G1667" s="2" t="s">
-        <v>229</v>
+        <v>2542</v>
       </c>
       <c r="H1667" s="2" t="s">
-        <v>1795</v>
+        <v>2543</v>
       </c>
       <c r="I1667" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1667" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1667" s="2" t="s">
-        <v>229</v>
+        <v>2542</v>
       </c>
       <c r="L1667" s="2">
         <v>0</v>
@@ -81449,25 +81698,25 @@
         <v>46288</v>
       </c>
       <c r="B1668" s="2" t="s">
-        <v>302</v>
+        <v>97</v>
       </c>
       <c r="C1668" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D1668" s="2">
-        <v>11</v>
-      </c>
-      <c r="E1668" s="4">
-        <v>0.6875</v>
+        <v>0</v>
+      </c>
+      <c r="E1668" s="5">
+        <v>0</v>
       </c>
       <c r="F1668" s="2" t="s">
-        <v>287</v>
+        <v>2478</v>
       </c>
       <c r="G1668" s="2" t="s">
-        <v>231</v>
+        <v>2479</v>
       </c>
       <c r="H1668" s="2" t="s">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="I1668" s="2" t="s">
         <v>18</v>
@@ -81476,7 +81725,7 @@
         <v>19</v>
       </c>
       <c r="K1668" s="2" t="s">
-        <v>231</v>
+        <v>2479</v>
       </c>
       <c r="L1668" s="2">
         <v>0</v>
@@ -81493,34 +81742,34 @@
         <v>46288</v>
       </c>
       <c r="B1669" s="2" t="s">
-        <v>525</v>
+        <v>1117</v>
       </c>
       <c r="C1669" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1669" s="2">
-        <v>16</v>
-      </c>
-      <c r="E1669" s="5">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="E1669" s="4">
+        <v>0.55555560000000004</v>
       </c>
       <c r="F1669" s="2" t="s">
-        <v>2524</v>
+        <v>453</v>
       </c>
       <c r="G1669" s="2" t="s">
-        <v>1550</v>
+        <v>155</v>
       </c>
       <c r="H1669" s="2" t="s">
-        <v>492</v>
+        <v>1635</v>
       </c>
       <c r="I1669" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1669" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1669" s="2" t="s">
-        <v>1550</v>
+        <v>155</v>
       </c>
       <c r="L1669" s="2">
         <v>0</v>
@@ -81537,34 +81786,34 @@
         <v>46288</v>
       </c>
       <c r="B1670" s="2" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="C1670" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1670" s="2">
-        <v>6</v>
-      </c>
-      <c r="E1670" s="4">
-        <v>0.375</v>
+        <v>17</v>
+      </c>
+      <c r="E1670" s="5">
+        <v>1</v>
       </c>
       <c r="F1670" s="2" t="s">
-        <v>2525</v>
+        <v>1195</v>
       </c>
       <c r="G1670" s="2" t="s">
-        <v>2526</v>
+        <v>1790</v>
       </c>
       <c r="H1670" s="2" t="s">
-        <v>2527</v>
+        <v>1791</v>
       </c>
       <c r="I1670" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1670" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1670" s="2" t="s">
-        <v>2526</v>
+        <v>1790</v>
       </c>
       <c r="L1670" s="2">
         <v>0</v>
@@ -81581,34 +81830,34 @@
         <v>46288</v>
       </c>
       <c r="B1671" s="2" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="C1671" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D1671" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E1671" s="4">
-        <v>0.71428570000000002</v>
+        <v>0.8823529</v>
       </c>
       <c r="F1671" s="2" t="s">
-        <v>2182</v>
+        <v>1197</v>
       </c>
       <c r="G1671" s="2" t="s">
-        <v>206</v>
+        <v>2544</v>
       </c>
       <c r="H1671" s="2" t="s">
-        <v>2528</v>
+        <v>2545</v>
       </c>
       <c r="I1671" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1671" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1671" s="2" t="s">
-        <v>206</v>
+        <v>2544</v>
       </c>
       <c r="L1671" s="2">
         <v>0</v>
@@ -81625,34 +81874,34 @@
         <v>46288</v>
       </c>
       <c r="B1672" s="2" t="s">
-        <v>77</v>
+        <v>333</v>
       </c>
       <c r="C1672" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D1672" s="2">
-        <v>13</v>
-      </c>
-      <c r="E1672" s="5">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="E1672" s="4">
+        <v>0.9375</v>
       </c>
       <c r="F1672" s="2" t="s">
-        <v>2529</v>
+        <v>1199</v>
       </c>
       <c r="G1672" s="2" t="s">
-        <v>2530</v>
+        <v>229</v>
       </c>
       <c r="H1672" s="2" t="s">
-        <v>808</v>
+        <v>1795</v>
       </c>
       <c r="I1672" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1672" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1672" s="2" t="s">
-        <v>2530</v>
+        <v>229</v>
       </c>
       <c r="L1672" s="2">
         <v>0</v>
@@ -81669,25 +81918,25 @@
         <v>46288</v>
       </c>
       <c r="B1673" s="2" t="s">
-        <v>670</v>
+        <v>302</v>
       </c>
       <c r="C1673" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D1673" s="2">
-        <v>13</v>
-      </c>
-      <c r="E1673" s="5">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="E1673" s="4">
+        <v>0.6875</v>
       </c>
       <c r="F1673" s="2" t="s">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="G1673" s="2" t="s">
-        <v>648</v>
+        <v>231</v>
       </c>
       <c r="H1673" s="2" t="s">
-        <v>458</v>
+        <v>210</v>
       </c>
       <c r="I1673" s="2" t="s">
         <v>18</v>
@@ -81696,7 +81945,7 @@
         <v>19</v>
       </c>
       <c r="K1673" s="2" t="s">
-        <v>648</v>
+        <v>231</v>
       </c>
       <c r="L1673" s="2">
         <v>0</v>
@@ -81713,34 +81962,34 @@
         <v>46288</v>
       </c>
       <c r="B1674" s="2" t="s">
-        <v>204</v>
+        <v>525</v>
       </c>
       <c r="C1674" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D1674" s="2">
-        <v>9</v>
-      </c>
-      <c r="E1674" s="4">
-        <v>0.69230769999999997</v>
+        <v>16</v>
+      </c>
+      <c r="E1674" s="5">
+        <v>1</v>
       </c>
       <c r="F1674" s="2" t="s">
-        <v>2531</v>
+        <v>2480</v>
       </c>
       <c r="G1674" s="2" t="s">
-        <v>972</v>
+        <v>1550</v>
       </c>
       <c r="H1674" s="2" t="s">
-        <v>1938</v>
+        <v>492</v>
       </c>
       <c r="I1674" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1674" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1674" s="2" t="s">
-        <v>972</v>
+        <v>1550</v>
       </c>
       <c r="L1674" s="2">
         <v>0</v>
@@ -81757,34 +82006,34 @@
         <v>46288</v>
       </c>
       <c r="B1675" s="2" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C1675" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D1675" s="2">
-        <v>0</v>
-      </c>
-      <c r="E1675" s="5">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="E1675" s="4">
+        <v>0.375</v>
       </c>
       <c r="F1675" s="2" t="s">
-        <v>2532</v>
+        <v>2481</v>
       </c>
       <c r="G1675" s="2" t="s">
-        <v>1228</v>
+        <v>2482</v>
       </c>
       <c r="H1675" s="2" t="s">
-        <v>2201</v>
+        <v>2483</v>
       </c>
       <c r="I1675" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1675" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1675" s="2" t="s">
-        <v>1228</v>
+        <v>2482</v>
       </c>
       <c r="L1675" s="2">
         <v>0</v>
@@ -81804,22 +82053,22 @@
         <v>220</v>
       </c>
       <c r="C1676" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1676" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1676" s="4">
-        <v>0.4166667</v>
+        <v>0.42857139999999999</v>
       </c>
       <c r="F1676" s="2" t="s">
-        <v>2358</v>
+        <v>2546</v>
       </c>
       <c r="G1676" s="2" t="s">
-        <v>822</v>
+        <v>2547</v>
       </c>
       <c r="H1676" s="2" t="s">
-        <v>1423</v>
+        <v>2548</v>
       </c>
       <c r="I1676" s="2" t="s">
         <v>23</v>
@@ -81828,7 +82077,7 @@
         <v>19</v>
       </c>
       <c r="K1676" s="2" t="s">
-        <v>822</v>
+        <v>2547</v>
       </c>
       <c r="L1676" s="2">
         <v>0</v>
@@ -81845,34 +82094,34 @@
         <v>46288</v>
       </c>
       <c r="B1677" s="2" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C1677" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1677" s="2">
         <v>10</v>
       </c>
       <c r="E1677" s="4">
-        <v>0.83333330000000005</v>
+        <v>0.71428570000000002</v>
       </c>
       <c r="F1677" s="2" t="s">
-        <v>808</v>
+        <v>2182</v>
       </c>
       <c r="G1677" s="2" t="s">
-        <v>801</v>
+        <v>206</v>
       </c>
       <c r="H1677" s="2" t="s">
-        <v>2533</v>
+        <v>2484</v>
       </c>
       <c r="I1677" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1677" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1677" s="2" t="s">
-        <v>801</v>
+        <v>206</v>
       </c>
       <c r="L1677" s="2">
         <v>0</v>
@@ -81889,34 +82138,34 @@
         <v>46288</v>
       </c>
       <c r="B1678" s="2" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="C1678" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D1678" s="2">
-        <v>11</v>
-      </c>
-      <c r="E1678" s="5">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="E1678" s="4">
+        <v>0.71428570000000002</v>
       </c>
       <c r="F1678" s="2" t="s">
-        <v>921</v>
+        <v>205</v>
       </c>
       <c r="G1678" s="2" t="s">
-        <v>2534</v>
+        <v>499</v>
       </c>
       <c r="H1678" s="2" t="s">
-        <v>1611</v>
+        <v>1573</v>
       </c>
       <c r="I1678" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1678" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1678" s="2" t="s">
-        <v>2534</v>
+        <v>499</v>
       </c>
       <c r="L1678" s="2">
         <v>0</v>
@@ -81933,34 +82182,34 @@
         <v>46288</v>
       </c>
       <c r="B1679" s="2" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C1679" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D1679" s="2">
-        <v>7</v>
-      </c>
-      <c r="E1679" s="4">
-        <v>0.77777779999999996</v>
+        <v>13</v>
+      </c>
+      <c r="E1679" s="5">
+        <v>1</v>
       </c>
       <c r="F1679" s="2" t="s">
-        <v>276</v>
+        <v>2485</v>
       </c>
       <c r="G1679" s="2" t="s">
-        <v>228</v>
+        <v>2486</v>
       </c>
       <c r="H1679" s="2" t="s">
-        <v>1088</v>
+        <v>808</v>
       </c>
       <c r="I1679" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1679" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1679" s="2" t="s">
-        <v>228</v>
+        <v>2486</v>
       </c>
       <c r="L1679" s="2">
         <v>0</v>
@@ -81977,25 +82226,25 @@
         <v>46288</v>
       </c>
       <c r="B1680" s="2" t="s">
-        <v>215</v>
+        <v>670</v>
       </c>
       <c r="C1680" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D1680" s="2">
-        <v>1</v>
-      </c>
-      <c r="E1680" s="4">
-        <v>0.1111111</v>
+        <v>13</v>
+      </c>
+      <c r="E1680" s="5">
+        <v>1</v>
       </c>
       <c r="F1680" s="2" t="s">
-        <v>2293</v>
+        <v>312</v>
       </c>
       <c r="G1680" s="2" t="s">
-        <v>2535</v>
+        <v>648</v>
       </c>
       <c r="H1680" s="2" t="s">
-        <v>2536</v>
+        <v>458</v>
       </c>
       <c r="I1680" s="2" t="s">
         <v>18</v>
@@ -82004,7 +82253,7 @@
         <v>19</v>
       </c>
       <c r="K1680" s="2" t="s">
-        <v>2535</v>
+        <v>648</v>
       </c>
       <c r="L1680" s="2">
         <v>0</v>
@@ -82021,25 +82270,25 @@
         <v>46288</v>
       </c>
       <c r="B1681" s="2" t="s">
-        <v>2537</v>
+        <v>201</v>
       </c>
       <c r="C1681" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D1681" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E1681" s="5">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F1681" s="2" t="s">
-        <v>321</v>
+        <v>2487</v>
       </c>
       <c r="G1681" s="2" t="s">
-        <v>508</v>
+        <v>1228</v>
       </c>
       <c r="H1681" s="2" t="s">
-        <v>239</v>
+        <v>2201</v>
       </c>
       <c r="I1681" s="2" t="s">
         <v>23</v>
@@ -82048,7 +82297,7 @@
         <v>19</v>
       </c>
       <c r="K1681" s="2" t="s">
-        <v>508</v>
+        <v>1228</v>
       </c>
       <c r="L1681" s="2">
         <v>0</v>
@@ -82065,25 +82314,25 @@
         <v>46288</v>
       </c>
       <c r="B1682" s="2" t="s">
-        <v>53</v>
+        <v>215</v>
       </c>
       <c r="C1682" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D1682" s="2">
-        <v>0</v>
-      </c>
-      <c r="E1682" s="5">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E1682" s="4">
+        <v>0.3333333</v>
       </c>
       <c r="F1682" s="2" t="s">
-        <v>2538</v>
+        <v>2549</v>
       </c>
       <c r="G1682" s="2" t="s">
-        <v>691</v>
+        <v>2550</v>
       </c>
       <c r="H1682" s="2" t="s">
-        <v>917</v>
+        <v>801</v>
       </c>
       <c r="I1682" s="2" t="s">
         <v>18</v>
@@ -82092,7 +82341,7 @@
         <v>19</v>
       </c>
       <c r="K1682" s="2" t="s">
-        <v>691</v>
+        <v>2550</v>
       </c>
       <c r="L1682" s="2">
         <v>0</v>
@@ -82109,25 +82358,25 @@
         <v>46288</v>
       </c>
       <c r="B1683" s="2" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="C1683" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1683" s="2">
-        <v>4</v>
-      </c>
-      <c r="E1683" s="5">
-        <v>0.5</v>
+        <v>7</v>
+      </c>
+      <c r="E1683" s="4">
+        <v>0.77777779999999996</v>
       </c>
       <c r="F1683" s="2" t="s">
-        <v>2539</v>
+        <v>276</v>
       </c>
       <c r="G1683" s="2" t="s">
-        <v>2540</v>
+        <v>228</v>
       </c>
       <c r="H1683" s="2" t="s">
-        <v>644</v>
+        <v>1088</v>
       </c>
       <c r="I1683" s="2" t="s">
         <v>23</v>
@@ -82136,7 +82385,7 @@
         <v>19</v>
       </c>
       <c r="K1683" s="2" t="s">
-        <v>2540</v>
+        <v>228</v>
       </c>
       <c r="L1683" s="2">
         <v>0</v>
@@ -82153,25 +82402,25 @@
         <v>46288</v>
       </c>
       <c r="B1684" s="2" t="s">
-        <v>818</v>
+        <v>2488</v>
       </c>
       <c r="C1684" s="2">
         <v>8</v>
       </c>
       <c r="D1684" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1684" s="5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F1684" s="2" t="s">
-        <v>453</v>
+        <v>321</v>
       </c>
       <c r="G1684" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="H1684" s="2" t="s">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="I1684" s="2" t="s">
         <v>23</v>
@@ -82180,7 +82429,7 @@
         <v>19</v>
       </c>
       <c r="K1684" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L1684" s="2">
         <v>0</v>
@@ -82197,25 +82446,25 @@
         <v>46288</v>
       </c>
       <c r="B1685" s="2" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C1685" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1685" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E1685" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1685" s="2" t="s">
-        <v>2541</v>
+        <v>2489</v>
       </c>
       <c r="G1685" s="2" t="s">
-        <v>1649</v>
+        <v>691</v>
       </c>
       <c r="H1685" s="2" t="s">
-        <v>819</v>
+        <v>917</v>
       </c>
       <c r="I1685" s="2" t="s">
         <v>18</v>
@@ -82224,7 +82473,7 @@
         <v>19</v>
       </c>
       <c r="K1685" s="2" t="s">
-        <v>1649</v>
+        <v>691</v>
       </c>
       <c r="L1685" s="2">
         <v>0</v>
@@ -82241,25 +82490,25 @@
         <v>46288</v>
       </c>
       <c r="B1686" s="2" t="s">
-        <v>183</v>
+        <v>250</v>
       </c>
       <c r="C1686" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1686" s="2">
         <v>4</v>
       </c>
-      <c r="E1686" s="4">
-        <v>0.57142859999999995</v>
+      <c r="E1686" s="5">
+        <v>0.5</v>
       </c>
       <c r="F1686" s="2" t="s">
-        <v>457</v>
+        <v>2490</v>
       </c>
       <c r="G1686" s="2" t="s">
-        <v>694</v>
+        <v>2491</v>
       </c>
       <c r="H1686" s="2" t="s">
-        <v>483</v>
+        <v>644</v>
       </c>
       <c r="I1686" s="2" t="s">
         <v>23</v>
@@ -82268,7 +82517,7 @@
         <v>19</v>
       </c>
       <c r="K1686" s="2" t="s">
-        <v>694</v>
+        <v>2491</v>
       </c>
       <c r="L1686" s="2">
         <v>0</v>
@@ -82285,34 +82534,34 @@
         <v>46288</v>
       </c>
       <c r="B1687" s="2" t="s">
-        <v>544</v>
+        <v>818</v>
       </c>
       <c r="C1687" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D1687" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1687" s="5">
         <v>1</v>
       </c>
       <c r="F1687" s="2" t="s">
-        <v>243</v>
+        <v>453</v>
       </c>
       <c r="G1687" s="2" t="s">
-        <v>243</v>
+        <v>505</v>
       </c>
       <c r="H1687" s="2" t="s">
-        <v>259</v>
+        <v>194</v>
       </c>
       <c r="I1687" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1687" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1687" s="2" t="s">
-        <v>243</v>
+        <v>505</v>
       </c>
       <c r="L1687" s="2">
         <v>0</v>
@@ -82329,34 +82578,34 @@
         <v>46288</v>
       </c>
       <c r="B1688" s="2" t="s">
-        <v>271</v>
+        <v>140</v>
       </c>
       <c r="C1688" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1688" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E1688" s="5">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F1688" s="2" t="s">
-        <v>2542</v>
+        <v>836</v>
       </c>
       <c r="G1688" s="2" t="s">
-        <v>293</v>
+        <v>2551</v>
       </c>
       <c r="H1688" s="2" t="s">
-        <v>2251</v>
+        <v>2204</v>
       </c>
       <c r="I1688" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1688" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1688" s="2" t="s">
-        <v>293</v>
+        <v>2551</v>
       </c>
       <c r="L1688" s="2">
         <v>0</v>
@@ -82373,34 +82622,34 @@
         <v>46288</v>
       </c>
       <c r="B1689" s="2" t="s">
-        <v>295</v>
+        <v>33</v>
       </c>
       <c r="C1689" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1689" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E1689" s="5">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="F1689" s="2" t="s">
-        <v>845</v>
+        <v>2492</v>
       </c>
       <c r="G1689" s="2" t="s">
-        <v>242</v>
+        <v>1649</v>
       </c>
       <c r="H1689" s="2" t="s">
-        <v>300</v>
+        <v>819</v>
       </c>
       <c r="I1689" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1689" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1689" s="2" t="s">
-        <v>242</v>
+        <v>1649</v>
       </c>
       <c r="L1689" s="2">
         <v>0</v>
@@ -82417,25 +82666,25 @@
         <v>46288</v>
       </c>
       <c r="B1690" s="2" t="s">
-        <v>529</v>
+        <v>183</v>
       </c>
       <c r="C1690" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1690" s="2">
         <v>4</v>
       </c>
-      <c r="D1690" s="2">
-        <v>3</v>
-      </c>
-      <c r="E1690" s="5">
-        <v>0.75</v>
+      <c r="E1690" s="4">
+        <v>0.57142859999999995</v>
       </c>
       <c r="F1690" s="2" t="s">
-        <v>911</v>
+        <v>457</v>
       </c>
       <c r="G1690" s="2" t="s">
-        <v>1449</v>
+        <v>694</v>
       </c>
       <c r="H1690" s="2" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="I1690" s="2" t="s">
         <v>23</v>
@@ -82444,7 +82693,7 @@
         <v>19</v>
       </c>
       <c r="K1690" s="2" t="s">
-        <v>1449</v>
+        <v>694</v>
       </c>
       <c r="L1690" s="2">
         <v>0</v>
@@ -82461,34 +82710,34 @@
         <v>46288</v>
       </c>
       <c r="B1691" s="2" t="s">
-        <v>1111</v>
+        <v>271</v>
       </c>
       <c r="C1691" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1691" s="2">
         <v>3</v>
       </c>
       <c r="E1691" s="5">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="F1691" s="2" t="s">
-        <v>686</v>
+        <v>2552</v>
       </c>
       <c r="G1691" s="2" t="s">
-        <v>2543</v>
+        <v>845</v>
       </c>
       <c r="H1691" s="2" t="s">
-        <v>290</v>
+        <v>508</v>
       </c>
       <c r="I1691" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1691" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1691" s="2" t="s">
-        <v>2543</v>
+        <v>845</v>
       </c>
       <c r="L1691" s="2">
         <v>0</v>
@@ -82505,25 +82754,25 @@
         <v>46288</v>
       </c>
       <c r="B1692" s="2" t="s">
-        <v>660</v>
+        <v>544</v>
       </c>
       <c r="C1692" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1692" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1692" s="5">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="F1692" s="2" t="s">
-        <v>327</v>
+        <v>243</v>
       </c>
       <c r="G1692" s="2" t="s">
-        <v>527</v>
+        <v>243</v>
       </c>
       <c r="H1692" s="2" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="I1692" s="2" t="s">
         <v>28</v>
@@ -82532,7 +82781,7 @@
         <v>19</v>
       </c>
       <c r="K1692" s="2" t="s">
-        <v>527</v>
+        <v>243</v>
       </c>
       <c r="L1692" s="2">
         <v>0</v>
@@ -82549,34 +82798,34 @@
         <v>46288</v>
       </c>
       <c r="B1693" s="2" t="s">
-        <v>69</v>
+        <v>1111</v>
       </c>
       <c r="C1693" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="2">
         <v>3</v>
       </c>
-      <c r="D1693" s="2">
-        <v>2</v>
-      </c>
-      <c r="E1693" s="4">
-        <v>0.66666669999999995</v>
+      <c r="E1693" s="5">
+        <v>0.75</v>
       </c>
       <c r="F1693" s="2" t="s">
-        <v>2544</v>
+        <v>686</v>
       </c>
       <c r="G1693" s="2" t="s">
-        <v>2545</v>
+        <v>2493</v>
       </c>
       <c r="H1693" s="2" t="s">
-        <v>227</v>
+        <v>290</v>
       </c>
       <c r="I1693" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1693" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1693" s="2" t="s">
-        <v>2545</v>
+        <v>2493</v>
       </c>
       <c r="L1693" s="2">
         <v>0</v>
@@ -82593,25 +82842,25 @@
         <v>46288</v>
       </c>
       <c r="B1694" s="2" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="C1694" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1694" s="2">
         <v>3</v>
       </c>
       <c r="E1694" s="5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F1694" s="2" t="s">
-        <v>304</v>
+        <v>911</v>
       </c>
       <c r="G1694" s="2" t="s">
-        <v>429</v>
+        <v>1449</v>
       </c>
       <c r="H1694" s="2" t="s">
-        <v>661</v>
+        <v>490</v>
       </c>
       <c r="I1694" s="2" t="s">
         <v>23</v>
@@ -82620,7 +82869,7 @@
         <v>19</v>
       </c>
       <c r="K1694" s="2" t="s">
-        <v>429</v>
+        <v>1449</v>
       </c>
       <c r="L1694" s="2">
         <v>0</v>
@@ -82637,25 +82886,25 @@
         <v>46288</v>
       </c>
       <c r="B1695" s="2" t="s">
-        <v>1237</v>
+        <v>295</v>
       </c>
       <c r="C1695" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1695" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1695" s="5">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F1695" s="2" t="s">
-        <v>532</v>
+        <v>845</v>
       </c>
       <c r="G1695" s="2" t="s">
-        <v>514</v>
+        <v>242</v>
       </c>
       <c r="H1695" s="2" t="s">
-        <v>533</v>
+        <v>300</v>
       </c>
       <c r="I1695" s="2" t="s">
         <v>23</v>
@@ -82664,7 +82913,7 @@
         <v>19</v>
       </c>
       <c r="K1695" s="2" t="s">
-        <v>514</v>
+        <v>242</v>
       </c>
       <c r="L1695" s="2">
         <v>0</v>
@@ -82681,34 +82930,34 @@
         <v>46288</v>
       </c>
       <c r="B1696" s="2" t="s">
-        <v>179</v>
+        <v>660</v>
       </c>
       <c r="C1696" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1696" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1696" s="5">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F1696" s="2" t="s">
-        <v>2373</v>
+        <v>327</v>
       </c>
       <c r="G1696" s="2" t="s">
-        <v>473</v>
+        <v>527</v>
       </c>
       <c r="H1696" s="2" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="I1696" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1696" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1696" s="2" t="s">
-        <v>473</v>
+        <v>527</v>
       </c>
       <c r="L1696" s="2">
         <v>0</v>
@@ -82725,34 +82974,34 @@
         <v>46288</v>
       </c>
       <c r="B1697" s="2" t="s">
-        <v>938</v>
+        <v>493</v>
       </c>
       <c r="C1697" s="2">
         <v>3</v>
       </c>
       <c r="D1697" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1697" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1697" s="2" t="s">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="G1697" s="2" t="s">
-        <v>19</v>
+        <v>429</v>
       </c>
       <c r="H1697" s="2" t="s">
-        <v>254</v>
+        <v>661</v>
       </c>
       <c r="I1697" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1697" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1697" s="2" t="s">
-        <v>19</v>
+        <v>429</v>
       </c>
       <c r="L1697" s="2">
         <v>0</v>
@@ -82769,7 +83018,7 @@
         <v>46288</v>
       </c>
       <c r="B1698" s="2" t="s">
-        <v>144</v>
+        <v>1360</v>
       </c>
       <c r="C1698" s="2">
         <v>3</v>
@@ -82781,13 +83030,13 @@
         <v>1</v>
       </c>
       <c r="F1698" s="2" t="s">
-        <v>709</v>
+        <v>498</v>
       </c>
       <c r="G1698" s="2" t="s">
-        <v>1356</v>
+        <v>259</v>
       </c>
       <c r="H1698" s="2" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="I1698" s="2" t="s">
         <v>18</v>
@@ -82796,7 +83045,7 @@
         <v>19</v>
       </c>
       <c r="K1698" s="2" t="s">
-        <v>1356</v>
+        <v>259</v>
       </c>
       <c r="L1698" s="2">
         <v>0</v>
@@ -82813,34 +83062,34 @@
         <v>46288</v>
       </c>
       <c r="B1699" s="2" t="s">
-        <v>317</v>
+        <v>69</v>
       </c>
       <c r="C1699" s="2">
         <v>3</v>
       </c>
       <c r="D1699" s="2">
-        <v>0</v>
-      </c>
-      <c r="E1699" s="5">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E1699" s="4">
+        <v>0.66666669999999995</v>
       </c>
       <c r="F1699" s="2" t="s">
-        <v>236</v>
+        <v>2494</v>
       </c>
       <c r="G1699" s="2" t="s">
-        <v>19</v>
+        <v>2495</v>
       </c>
       <c r="H1699" s="2" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I1699" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1699" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1699" s="2" t="s">
-        <v>19</v>
+        <v>2495</v>
       </c>
       <c r="L1699" s="2">
         <v>0</v>
@@ -82857,34 +83106,34 @@
         <v>46288</v>
       </c>
       <c r="B1700" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C1700" s="2">
         <v>3</v>
       </c>
       <c r="D1700" s="2">
-        <v>2</v>
-      </c>
-      <c r="E1700" s="4">
-        <v>0.66666669999999995</v>
+        <v>0</v>
+      </c>
+      <c r="E1700" s="5">
+        <v>0</v>
       </c>
       <c r="F1700" s="2" t="s">
-        <v>2546</v>
+        <v>2373</v>
       </c>
       <c r="G1700" s="2" t="s">
-        <v>153</v>
+        <v>473</v>
       </c>
       <c r="H1700" s="2" t="s">
-        <v>2547</v>
+        <v>255</v>
       </c>
       <c r="I1700" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1700" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1700" s="2" t="s">
-        <v>153</v>
+        <v>473</v>
       </c>
       <c r="L1700" s="2">
         <v>0</v>
@@ -82901,25 +83150,25 @@
         <v>46288</v>
       </c>
       <c r="B1701" s="2" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="C1701" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1701" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1701" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1701" s="2" t="s">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="G1701" s="2" t="s">
-        <v>293</v>
+        <v>19</v>
       </c>
       <c r="H1701" s="2" t="s">
-        <v>303</v>
+        <v>236</v>
       </c>
       <c r="I1701" s="2" t="s">
         <v>28</v>
@@ -82928,7 +83177,7 @@
         <v>19</v>
       </c>
       <c r="K1701" s="2" t="s">
-        <v>293</v>
+        <v>19</v>
       </c>
       <c r="L1701" s="2">
         <v>0</v>
@@ -82945,34 +83194,34 @@
         <v>46288</v>
       </c>
       <c r="B1702" s="2" t="s">
-        <v>61</v>
+        <v>1237</v>
       </c>
       <c r="C1702" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1702" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1702" s="5">
         <v>1</v>
       </c>
       <c r="F1702" s="2" t="s">
-        <v>303</v>
+        <v>532</v>
       </c>
       <c r="G1702" s="2" t="s">
-        <v>196</v>
+        <v>514</v>
       </c>
       <c r="H1702" s="2" t="s">
-        <v>297</v>
+        <v>533</v>
       </c>
       <c r="I1702" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1702" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1702" s="2" t="s">
-        <v>196</v>
+        <v>514</v>
       </c>
       <c r="L1702" s="2">
         <v>0</v>
@@ -82989,34 +83238,34 @@
         <v>46288</v>
       </c>
       <c r="B1703" s="2" t="s">
-        <v>140</v>
+        <v>938</v>
       </c>
       <c r="C1703" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1703" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1703" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1703" s="2" t="s">
-        <v>549</v>
+        <v>254</v>
       </c>
       <c r="G1703" s="2" t="s">
-        <v>706</v>
+        <v>19</v>
       </c>
       <c r="H1703" s="2" t="s">
-        <v>323</v>
+        <v>254</v>
       </c>
       <c r="I1703" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1703" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1703" s="2" t="s">
-        <v>706</v>
+        <v>19</v>
       </c>
       <c r="L1703" s="2">
         <v>0</v>
@@ -83033,34 +83282,34 @@
         <v>46288</v>
       </c>
       <c r="B1704" s="2" t="s">
-        <v>2194</v>
+        <v>187</v>
       </c>
       <c r="C1704" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1704" s="2">
         <v>2</v>
       </c>
-      <c r="E1704" s="5">
-        <v>1</v>
+      <c r="E1704" s="4">
+        <v>0.66666669999999995</v>
       </c>
       <c r="F1704" s="2" t="s">
-        <v>545</v>
+        <v>2496</v>
       </c>
       <c r="G1704" s="2" t="s">
-        <v>637</v>
+        <v>153</v>
       </c>
       <c r="H1704" s="2" t="s">
-        <v>528</v>
+        <v>2497</v>
       </c>
       <c r="I1704" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1704" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1704" s="2" t="s">
-        <v>637</v>
+        <v>153</v>
       </c>
       <c r="L1704" s="2">
         <v>0</v>
@@ -83077,25 +83326,25 @@
         <v>46288</v>
       </c>
       <c r="B1705" s="2" t="s">
-        <v>278</v>
+        <v>550</v>
       </c>
       <c r="C1705" s="2">
         <v>2</v>
       </c>
       <c r="D1705" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1705" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1705" s="2" t="s">
-        <v>2548</v>
+        <v>2499</v>
       </c>
       <c r="G1705" s="2" t="s">
-        <v>2105</v>
+        <v>472</v>
       </c>
       <c r="H1705" s="2" t="s">
-        <v>933</v>
+        <v>471</v>
       </c>
       <c r="I1705" s="2" t="s">
         <v>23</v>
@@ -83104,7 +83353,7 @@
         <v>19</v>
       </c>
       <c r="K1705" s="2" t="s">
-        <v>2105</v>
+        <v>472</v>
       </c>
       <c r="L1705" s="2">
         <v>0</v>
@@ -83121,34 +83370,34 @@
         <v>46288</v>
       </c>
       <c r="B1706" s="2" t="s">
-        <v>550</v>
+        <v>61</v>
       </c>
       <c r="C1706" s="2">
         <v>2</v>
       </c>
       <c r="D1706" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1706" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1706" s="2" t="s">
-        <v>2549</v>
+        <v>303</v>
       </c>
       <c r="G1706" s="2" t="s">
-        <v>472</v>
+        <v>196</v>
       </c>
       <c r="H1706" s="2" t="s">
-        <v>471</v>
+        <v>297</v>
       </c>
       <c r="I1706" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1706" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1706" s="2" t="s">
-        <v>472</v>
+        <v>196</v>
       </c>
       <c r="L1706" s="2">
         <v>0</v>
@@ -83165,7 +83414,7 @@
         <v>46288</v>
       </c>
       <c r="B1707" s="2" t="s">
-        <v>1360</v>
+        <v>269</v>
       </c>
       <c r="C1707" s="2">
         <v>2</v>
@@ -83177,22 +83426,22 @@
         <v>1</v>
       </c>
       <c r="F1707" s="2" t="s">
-        <v>293</v>
+        <v>19</v>
       </c>
       <c r="G1707" s="2" t="s">
-        <v>298</v>
+        <v>495</v>
       </c>
       <c r="H1707" s="2" t="s">
-        <v>1220</v>
+        <v>495</v>
       </c>
       <c r="I1707" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1707" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1707" s="2" t="s">
-        <v>298</v>
+        <v>495</v>
       </c>
       <c r="L1707" s="2">
         <v>0</v>
@@ -83209,7 +83458,7 @@
         <v>46288</v>
       </c>
       <c r="B1708" s="2" t="s">
-        <v>269</v>
+        <v>1232</v>
       </c>
       <c r="C1708" s="2">
         <v>2</v>
@@ -83221,22 +83470,22 @@
         <v>1</v>
       </c>
       <c r="F1708" s="2" t="s">
-        <v>19</v>
+        <v>303</v>
       </c>
       <c r="G1708" s="2" t="s">
-        <v>495</v>
+        <v>453</v>
       </c>
       <c r="H1708" s="2" t="s">
-        <v>495</v>
+        <v>528</v>
       </c>
       <c r="I1708" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1708" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1708" s="2" t="s">
-        <v>495</v>
+        <v>453</v>
       </c>
       <c r="L1708" s="2">
         <v>0</v>
@@ -83253,7 +83502,7 @@
         <v>46288</v>
       </c>
       <c r="B1709" s="2" t="s">
-        <v>1232</v>
+        <v>2194</v>
       </c>
       <c r="C1709" s="2">
         <v>2</v>
@@ -83265,22 +83514,22 @@
         <v>1</v>
       </c>
       <c r="F1709" s="2" t="s">
-        <v>303</v>
+        <v>545</v>
       </c>
       <c r="G1709" s="2" t="s">
-        <v>453</v>
+        <v>637</v>
       </c>
       <c r="H1709" s="2" t="s">
         <v>528</v>
       </c>
       <c r="I1709" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1709" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1709" s="2" t="s">
-        <v>453</v>
+        <v>637</v>
       </c>
       <c r="L1709" s="2">
         <v>0</v>
@@ -83297,7 +83546,7 @@
         <v>46288</v>
       </c>
       <c r="B1710" s="2" t="s">
-        <v>136</v>
+        <v>278</v>
       </c>
       <c r="C1710" s="2">
         <v>2</v>
@@ -83309,22 +83558,22 @@
         <v>1</v>
       </c>
       <c r="F1710" s="2" t="s">
-        <v>303</v>
+        <v>2498</v>
       </c>
       <c r="G1710" s="2" t="s">
-        <v>277</v>
+        <v>2105</v>
       </c>
       <c r="H1710" s="2" t="s">
-        <v>1114</v>
+        <v>933</v>
       </c>
       <c r="I1710" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1710" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1710" s="2" t="s">
-        <v>277</v>
+        <v>2105</v>
       </c>
       <c r="L1710" s="2">
         <v>0</v>
@@ -83385,34 +83634,34 @@
         <v>46288</v>
       </c>
       <c r="B1712" s="2" t="s">
-        <v>521</v>
+        <v>315</v>
       </c>
       <c r="C1712" s="2">
         <v>2</v>
       </c>
       <c r="D1712" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1712" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1712" s="2" t="s">
-        <v>495</v>
+        <v>326</v>
       </c>
       <c r="G1712" s="2" t="s">
-        <v>19</v>
+        <v>513</v>
       </c>
       <c r="H1712" s="2" t="s">
-        <v>495</v>
+        <v>303</v>
       </c>
       <c r="I1712" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1712" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1712" s="2" t="s">
-        <v>19</v>
+        <v>513</v>
       </c>
       <c r="L1712" s="2">
         <v>0</v>
@@ -83429,25 +83678,25 @@
         <v>46288</v>
       </c>
       <c r="B1713" s="2" t="s">
-        <v>703</v>
+        <v>521</v>
       </c>
       <c r="C1713" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1713" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1713" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1713" s="2" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="G1713" s="2" t="s">
-        <v>545</v>
+        <v>19</v>
       </c>
       <c r="H1713" s="2" t="s">
-        <v>276</v>
+        <v>495</v>
       </c>
       <c r="I1713" s="2" t="s">
         <v>28</v>
@@ -83456,7 +83705,7 @@
         <v>19</v>
       </c>
       <c r="K1713" s="2" t="s">
-        <v>545</v>
+        <v>19</v>
       </c>
       <c r="L1713" s="2">
         <v>0</v>
@@ -83473,25 +83722,25 @@
         <v>46288</v>
       </c>
       <c r="B1714" s="2" t="s">
-        <v>1479</v>
+        <v>195</v>
       </c>
       <c r="C1714" s="2">
         <v>1</v>
       </c>
       <c r="D1714" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1714" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1714" s="2" t="s">
-        <v>286</v>
+        <v>1354</v>
       </c>
       <c r="G1714" s="2" t="s">
-        <v>254</v>
+        <v>700</v>
       </c>
       <c r="H1714" s="2" t="s">
-        <v>474</v>
+        <v>698</v>
       </c>
       <c r="I1714" s="2" t="s">
         <v>23</v>
@@ -83500,7 +83749,7 @@
         <v>19</v>
       </c>
       <c r="K1714" s="2" t="s">
-        <v>254</v>
+        <v>700</v>
       </c>
       <c r="L1714" s="2">
         <v>0</v>
@@ -83517,7 +83766,7 @@
         <v>46288</v>
       </c>
       <c r="B1715" s="2" t="s">
-        <v>315</v>
+        <v>241</v>
       </c>
       <c r="C1715" s="2">
         <v>1</v>
@@ -83529,22 +83778,22 @@
         <v>1</v>
       </c>
       <c r="F1715" s="2" t="s">
-        <v>705</v>
+        <v>292</v>
       </c>
       <c r="G1715" s="2" t="s">
-        <v>549</v>
+        <v>845</v>
       </c>
       <c r="H1715" s="2" t="s">
-        <v>545</v>
+        <v>296</v>
       </c>
       <c r="I1715" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1715" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1715" s="2" t="s">
-        <v>549</v>
+        <v>845</v>
       </c>
       <c r="L1715" s="2">
         <v>0</v>
@@ -83561,34 +83810,34 @@
         <v>46288</v>
       </c>
       <c r="B1716" s="2" t="s">
-        <v>175</v>
+        <v>313</v>
       </c>
       <c r="C1716" s="2">
         <v>1</v>
       </c>
       <c r="D1716" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1716" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1716" s="2" t="s">
-        <v>845</v>
+        <v>2381</v>
       </c>
       <c r="G1716" s="2" t="s">
-        <v>303</v>
+        <v>700</v>
       </c>
       <c r="H1716" s="2" t="s">
-        <v>1109</v>
+        <v>244</v>
       </c>
       <c r="I1716" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1716" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1716" s="2" t="s">
-        <v>303</v>
+        <v>700</v>
       </c>
       <c r="L1716" s="2">
         <v>0</v>
@@ -83605,7 +83854,7 @@
         <v>46288</v>
       </c>
       <c r="B1717" s="2" t="s">
-        <v>241</v>
+        <v>1479</v>
       </c>
       <c r="C1717" s="2">
         <v>1</v>
@@ -83617,22 +83866,22 @@
         <v>1</v>
       </c>
       <c r="F1717" s="2" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="G1717" s="2" t="s">
-        <v>845</v>
+        <v>254</v>
       </c>
       <c r="H1717" s="2" t="s">
-        <v>296</v>
+        <v>474</v>
       </c>
       <c r="I1717" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1717" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1717" s="2" t="s">
-        <v>845</v>
+        <v>254</v>
       </c>
       <c r="L1717" s="2">
         <v>0</v>
@@ -83649,34 +83898,34 @@
         <v>46288</v>
       </c>
       <c r="B1718" s="2" t="s">
-        <v>313</v>
+        <v>175</v>
       </c>
       <c r="C1718" s="2">
         <v>1</v>
       </c>
       <c r="D1718" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1718" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1718" s="2" t="s">
-        <v>2381</v>
+        <v>845</v>
       </c>
       <c r="G1718" s="2" t="s">
-        <v>700</v>
+        <v>303</v>
       </c>
       <c r="H1718" s="2" t="s">
-        <v>244</v>
+        <v>1109</v>
       </c>
       <c r="I1718" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1718" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1718" s="2" t="s">
-        <v>700</v>
+        <v>303</v>
       </c>
       <c r="L1718" s="2">
         <v>0</v>
@@ -83693,25 +83942,25 @@
         <v>46288</v>
       </c>
       <c r="B1719" s="2" t="s">
-        <v>195</v>
+        <v>543</v>
       </c>
       <c r="C1719" s="2">
         <v>1</v>
       </c>
       <c r="D1719" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1719" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1719" s="2" t="s">
-        <v>1354</v>
+        <v>911</v>
       </c>
       <c r="G1719" s="2" t="s">
-        <v>700</v>
+        <v>283</v>
       </c>
       <c r="H1719" s="2" t="s">
-        <v>698</v>
+        <v>244</v>
       </c>
       <c r="I1719" s="2" t="s">
         <v>23</v>
@@ -83720,7 +83969,7 @@
         <v>19</v>
       </c>
       <c r="K1719" s="2" t="s">
-        <v>700</v>
+        <v>283</v>
       </c>
       <c r="L1719" s="2">
         <v>0</v>
@@ -83737,7 +83986,7 @@
         <v>46288</v>
       </c>
       <c r="B1720" s="2" t="s">
-        <v>543</v>
+        <v>275</v>
       </c>
       <c r="C1720" s="2">
         <v>1</v>
@@ -83749,30 +83998,3682 @@
         <v>1</v>
       </c>
       <c r="F1720" s="2" t="s">
-        <v>911</v>
+        <v>284</v>
       </c>
       <c r="G1720" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H1720" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1720" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1720" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1720" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="L1720" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1720" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1720" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:14">
+      <c r="A1721" s="3">
+        <v>46288</v>
+      </c>
+      <c r="B1721" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C1721" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1721" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1721" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1721" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="G1721" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="H1721" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1721" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1721" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1721" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="L1721" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1721" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1721" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:14">
+      <c r="A1722" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1722" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1722" s="2">
+        <v>25106</v>
+      </c>
+      <c r="D1722" s="2">
+        <v>15918</v>
+      </c>
+      <c r="E1722" s="4">
+        <v>0.63403169999999998</v>
+      </c>
+      <c r="F1722" s="2" t="s">
+        <v>2553</v>
+      </c>
+      <c r="G1722" s="2" t="s">
+        <v>2554</v>
+      </c>
+      <c r="H1722" s="2" t="s">
+        <v>2555</v>
+      </c>
+      <c r="I1722" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1722" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1722" s="2" t="s">
+        <v>2554</v>
+      </c>
+      <c r="L1722" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1722" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1722" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:14">
+      <c r="A1723" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1723" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1723" s="2">
+        <v>2666</v>
+      </c>
+      <c r="D1723" s="2">
+        <v>2517</v>
+      </c>
+      <c r="E1723" s="4">
+        <v>0.94411100000000003</v>
+      </c>
+      <c r="F1723" s="2" t="s">
+        <v>2556</v>
+      </c>
+      <c r="G1723" s="2" t="s">
+        <v>2557</v>
+      </c>
+      <c r="H1723" s="2" t="s">
+        <v>2558</v>
+      </c>
+      <c r="I1723" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1723" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1723" s="2" t="s">
+        <v>2557</v>
+      </c>
+      <c r="L1723" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1723" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1723" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:14">
+      <c r="A1724" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1724" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1724" s="2">
+        <v>1416</v>
+      </c>
+      <c r="D1724" s="2">
+        <v>1225</v>
+      </c>
+      <c r="E1724" s="4">
+        <v>0.86511300000000002</v>
+      </c>
+      <c r="F1724" s="2" t="s">
+        <v>2559</v>
+      </c>
+      <c r="G1724" s="2" t="s">
+        <v>2560</v>
+      </c>
+      <c r="H1724" s="2" t="s">
+        <v>2561</v>
+      </c>
+      <c r="I1724" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1724" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1724" s="2" t="s">
+        <v>2560</v>
+      </c>
+      <c r="L1724" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1724" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1724" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:14">
+      <c r="A1725" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1725" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1725" s="2">
+        <v>1116</v>
+      </c>
+      <c r="D1725" s="2">
+        <v>935</v>
+      </c>
+      <c r="E1725" s="4">
+        <v>0.83781360000000005</v>
+      </c>
+      <c r="F1725" s="2" t="s">
+        <v>2562</v>
+      </c>
+      <c r="G1725" s="2" t="s">
+        <v>2563</v>
+      </c>
+      <c r="H1725" s="2" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I1725" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1725" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1725" s="2" t="s">
+        <v>2563</v>
+      </c>
+      <c r="L1725" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1725" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1725" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:14">
+      <c r="A1726" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1726" s="2" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C1726" s="2">
+        <v>621</v>
+      </c>
+      <c r="D1726" s="2">
+        <v>610</v>
+      </c>
+      <c r="E1726" s="4">
+        <v>0.98228660000000001</v>
+      </c>
+      <c r="F1726" s="2" t="s">
+        <v>2565</v>
+      </c>
+      <c r="G1726" s="2" t="s">
+        <v>2566</v>
+      </c>
+      <c r="H1726" s="2" t="s">
+        <v>2567</v>
+      </c>
+      <c r="I1726" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1726" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1726" s="2" t="s">
+        <v>2566</v>
+      </c>
+      <c r="L1726" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1726" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1726" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:14">
+      <c r="A1727" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1727" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C1727" s="2">
+        <v>351</v>
+      </c>
+      <c r="D1727" s="2">
+        <v>342</v>
+      </c>
+      <c r="E1727" s="4">
+        <v>0.97435899999999998</v>
+      </c>
+      <c r="F1727" s="2" t="s">
+        <v>2568</v>
+      </c>
+      <c r="G1727" s="2" t="s">
+        <v>2569</v>
+      </c>
+      <c r="H1727" s="2" t="s">
+        <v>2570</v>
+      </c>
+      <c r="I1727" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1727" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1727" s="2" t="s">
+        <v>2569</v>
+      </c>
+      <c r="L1727" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1727" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1727" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:14">
+      <c r="A1728" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1728" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1728" s="2">
+        <v>241</v>
+      </c>
+      <c r="D1728" s="2">
+        <v>241</v>
+      </c>
+      <c r="E1728" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1728" s="2" t="s">
+        <v>2571</v>
+      </c>
+      <c r="G1728" s="2" t="s">
+        <v>2572</v>
+      </c>
+      <c r="H1728" s="2" t="s">
+        <v>2573</v>
+      </c>
+      <c r="I1728" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1728" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1728" s="2" t="s">
+        <v>2572</v>
+      </c>
+      <c r="L1728" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1728" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1728" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:14">
+      <c r="A1729" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1729" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1729" s="2">
+        <v>206</v>
+      </c>
+      <c r="D1729" s="2">
+        <v>198</v>
+      </c>
+      <c r="E1729" s="4">
+        <v>0.96116500000000005</v>
+      </c>
+      <c r="F1729" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="G1729" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="H1729" s="2" t="s">
+        <v>2575</v>
+      </c>
+      <c r="I1729" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1729" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1729" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="L1729" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1729" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1729" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:14">
+      <c r="A1730" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1730" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1730" s="2">
+        <v>97</v>
+      </c>
+      <c r="D1730" s="2">
+        <v>18</v>
+      </c>
+      <c r="E1730" s="4">
+        <v>0.18556700000000001</v>
+      </c>
+      <c r="F1730" s="2" t="s">
+        <v>2576</v>
+      </c>
+      <c r="G1730" s="2" t="s">
+        <v>2577</v>
+      </c>
+      <c r="H1730" s="2" t="s">
+        <v>2578</v>
+      </c>
+      <c r="I1730" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1730" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1730" s="2" t="s">
+        <v>2577</v>
+      </c>
+      <c r="L1730" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1730" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1730" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:14">
+      <c r="A1731" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1731" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1731" s="2">
+        <v>96</v>
+      </c>
+      <c r="D1731" s="2">
+        <v>90</v>
+      </c>
+      <c r="E1731" s="4">
+        <v>0.9375</v>
+      </c>
+      <c r="F1731" s="2" t="s">
+        <v>2579</v>
+      </c>
+      <c r="G1731" s="2" t="s">
+        <v>2580</v>
+      </c>
+      <c r="H1731" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="I1731" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1731" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1731" s="2" t="s">
+        <v>2580</v>
+      </c>
+      <c r="L1731" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1731" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1731" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:14">
+      <c r="A1732" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1732" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1732" s="2">
+        <v>93</v>
+      </c>
+      <c r="D1732" s="2">
+        <v>93</v>
+      </c>
+      <c r="E1732" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1732" s="2" t="s">
+        <v>2581</v>
+      </c>
+      <c r="G1732" s="2" t="s">
+        <v>2582</v>
+      </c>
+      <c r="H1732" s="2" t="s">
+        <v>2583</v>
+      </c>
+      <c r="I1732" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1732" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1732" s="2" t="s">
+        <v>2582</v>
+      </c>
+      <c r="L1732" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1732" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1732" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:14">
+      <c r="A1733" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1733" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1733" s="2">
+        <v>68</v>
+      </c>
+      <c r="D1733" s="2">
+        <v>66</v>
+      </c>
+      <c r="E1733" s="4">
+        <v>0.97058820000000001</v>
+      </c>
+      <c r="F1733" s="2" t="s">
+        <v>2584</v>
+      </c>
+      <c r="G1733" s="2" t="s">
+        <v>2585</v>
+      </c>
+      <c r="H1733" s="2" t="s">
+        <v>2586</v>
+      </c>
+      <c r="I1733" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1733" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1733" s="2" t="s">
+        <v>2585</v>
+      </c>
+      <c r="L1733" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1733" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1733" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:14">
+      <c r="A1734" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1734" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1734" s="2">
+        <v>58</v>
+      </c>
+      <c r="D1734" s="2">
+        <v>51</v>
+      </c>
+      <c r="E1734" s="4">
+        <v>0.87931029999999999</v>
+      </c>
+      <c r="F1734" s="2" t="s">
+        <v>2587</v>
+      </c>
+      <c r="G1734" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1734" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1734" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1734" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1734" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="L1734" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1734" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1734" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:14">
+      <c r="A1735" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1735" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1735" s="2">
+        <v>40</v>
+      </c>
+      <c r="D1735" s="2">
+        <v>27</v>
+      </c>
+      <c r="E1735" s="4">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="F1735" s="2" t="s">
+        <v>2588</v>
+      </c>
+      <c r="G1735" s="2" t="s">
+        <v>2589</v>
+      </c>
+      <c r="H1735" s="2" t="s">
+        <v>2590</v>
+      </c>
+      <c r="I1735" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1735" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1735" s="2" t="s">
+        <v>2589</v>
+      </c>
+      <c r="L1735" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1735" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1735" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:14">
+      <c r="A1736" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1736" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1736" s="2">
+        <v>27</v>
+      </c>
+      <c r="D1736" s="2">
+        <v>8</v>
+      </c>
+      <c r="E1736" s="4">
+        <v>0.29629630000000001</v>
+      </c>
+      <c r="F1736" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1736" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H1736" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I1736" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1736" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1736" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="L1736" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1736" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1736" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:14">
+      <c r="A1737" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1737" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C1737" s="2">
+        <v>27</v>
+      </c>
+      <c r="D1737" s="2">
+        <v>26</v>
+      </c>
+      <c r="E1737" s="4">
+        <v>0.96296300000000001</v>
+      </c>
+      <c r="F1737" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="G1737" s="2" t="s">
+        <v>2339</v>
+      </c>
+      <c r="H1737" s="2" t="s">
+        <v>2591</v>
+      </c>
+      <c r="I1737" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1737" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1737" s="2" t="s">
+        <v>2339</v>
+      </c>
+      <c r="L1737" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1737" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1737" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:14">
+      <c r="A1738" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1738" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1738" s="2">
+        <v>24</v>
+      </c>
+      <c r="D1738" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1738" s="4">
+        <v>0.83333330000000005</v>
+      </c>
+      <c r="F1738" s="2" t="s">
+        <v>2592</v>
+      </c>
+      <c r="G1738" s="2" t="s">
+        <v>2593</v>
+      </c>
+      <c r="H1738" s="2" t="s">
+        <v>2594</v>
+      </c>
+      <c r="I1738" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1738" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1738" s="2" t="s">
+        <v>2593</v>
+      </c>
+      <c r="L1738" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1738" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1738" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:14">
+      <c r="A1739" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1739" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1739" s="2">
+        <v>20</v>
+      </c>
+      <c r="D1739" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1739" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F1739" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1739" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H1739" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I1739" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1739" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1739" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="L1739" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1739" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1739" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:14">
+      <c r="A1740" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1740" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1740" s="2">
+        <v>16</v>
+      </c>
+      <c r="D1740" s="2">
+        <v>15</v>
+      </c>
+      <c r="E1740" s="4">
+        <v>0.9375</v>
+      </c>
+      <c r="F1740" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="G1740" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="H1740" s="2" t="s">
+        <v>2595</v>
+      </c>
+      <c r="I1740" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1740" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1740" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="L1740" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1740" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1740" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:14">
+      <c r="A1741" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1741" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1741" s="2">
+        <v>14</v>
+      </c>
+      <c r="D1741" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1741" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1741" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="G1741" s="2" t="s">
+        <v>2596</v>
+      </c>
+      <c r="H1741" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I1741" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1741" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1741" s="2" t="s">
+        <v>2596</v>
+      </c>
+      <c r="L1741" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1741" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1741" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:14">
+      <c r="A1742" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1742" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1742" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1742" s="2">
+        <v>9</v>
+      </c>
+      <c r="E1742" s="4">
+        <v>0.69230769999999997</v>
+      </c>
+      <c r="F1742" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G1742" s="2" t="s">
+        <v>2238</v>
+      </c>
+      <c r="H1742" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="I1742" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1742" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1742" s="2" t="s">
+        <v>2238</v>
+      </c>
+      <c r="L1742" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1742" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1742" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:14">
+      <c r="A1743" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1743" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1743" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1743" s="2">
+        <v>10</v>
+      </c>
+      <c r="E1743" s="4">
+        <v>0.76923079999999999</v>
+      </c>
+      <c r="F1743" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="G1743" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H1743" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I1743" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1743" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1743" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="L1743" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1743" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1743" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:14">
+      <c r="A1744" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1744" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1744" s="2">
+        <v>12</v>
+      </c>
+      <c r="D1744" s="2">
+        <v>10</v>
+      </c>
+      <c r="E1744" s="4">
+        <v>0.83333330000000005</v>
+      </c>
+      <c r="F1744" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="G1744" s="2" t="s">
+        <v>2597</v>
+      </c>
+      <c r="H1744" s="2" t="s">
+        <v>2598</v>
+      </c>
+      <c r="I1744" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1744" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1744" s="2" t="s">
+        <v>2597</v>
+      </c>
+      <c r="L1744" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1744" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1744" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:14">
+      <c r="A1745" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1745" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1745" s="2">
+        <v>12</v>
+      </c>
+      <c r="D1745" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1745" s="4">
+        <v>0.1666667</v>
+      </c>
+      <c r="F1745" s="2" t="s">
+        <v>2599</v>
+      </c>
+      <c r="G1745" s="2" t="s">
+        <v>2600</v>
+      </c>
+      <c r="H1745" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I1745" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1745" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1745" s="2" t="s">
+        <v>2600</v>
+      </c>
+      <c r="L1745" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1745" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1745" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:14">
+      <c r="A1746" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1746" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C1746" s="2">
+        <v>11</v>
+      </c>
+      <c r="D1746" s="2">
+        <v>11</v>
+      </c>
+      <c r="E1746" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1746" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G1746" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="H1746" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1746" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1746" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1746" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="L1746" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1746" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1746" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:14">
+      <c r="A1747" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1747" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C1747" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1747" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1747" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1747" s="2" t="s">
+        <v>2371</v>
+      </c>
+      <c r="G1747" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1747" s="2" t="s">
+        <v>2371</v>
+      </c>
+      <c r="I1747" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1747" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1747" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1747" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1747" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1747" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:14">
+      <c r="A1748" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1748" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1748" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1748" s="2">
+        <v>9</v>
+      </c>
+      <c r="E1748" s="5">
+        <v>0.9</v>
+      </c>
+      <c r="F1748" s="2" t="s">
+        <v>2601</v>
+      </c>
+      <c r="G1748" s="2" t="s">
+        <v>2412</v>
+      </c>
+      <c r="H1748" s="2" t="s">
+        <v>2602</v>
+      </c>
+      <c r="I1748" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1748" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1748" s="2" t="s">
+        <v>2412</v>
+      </c>
+      <c r="L1748" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1748" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1748" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:14">
+      <c r="A1749" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1749" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="C1749" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1749" s="2">
+        <v>6</v>
+      </c>
+      <c r="E1749" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="F1749" s="2" t="s">
+        <v>2603</v>
+      </c>
+      <c r="G1749" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1749" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I1749" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1749" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1749" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="L1749" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1749" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1749" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:14">
+      <c r="A1750" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1750" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C1750" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1750" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1750" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="F1750" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G1750" s="2" t="s">
+        <v>2604</v>
+      </c>
+      <c r="H1750" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="I1750" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1750" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1750" s="2" t="s">
+        <v>2604</v>
+      </c>
+      <c r="L1750" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1750" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1750" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:14">
+      <c r="A1751" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1751" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1751" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1751" s="2">
+        <v>9</v>
+      </c>
+      <c r="E1751" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1751" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="G1751" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H1751" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1751" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1751" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1751" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="L1751" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1751" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1751" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:14">
+      <c r="A1752" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1752" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C1752" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1752" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1752" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1752" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G1752" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="H1752" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I1752" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1752" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1752" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="L1752" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1752" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1752" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:14">
+      <c r="A1753" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1753" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C1753" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1753" s="2">
+        <v>9</v>
+      </c>
+      <c r="E1753" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1753" s="2" t="s">
+        <v>2605</v>
+      </c>
+      <c r="G1753" s="2" t="s">
+        <v>2606</v>
+      </c>
+      <c r="H1753" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I1753" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1753" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1753" s="2" t="s">
+        <v>2606</v>
+      </c>
+      <c r="L1753" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1753" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1753" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:14">
+      <c r="A1754" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1754" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1754" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1754" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1754" s="4">
+        <v>0.875</v>
+      </c>
+      <c r="F1754" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="G1754" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H1754" s="2" t="s">
+        <v>2607</v>
+      </c>
+      <c r="I1754" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1754" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1754" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="L1754" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1754" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1754" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:14">
+      <c r="A1755" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1755" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1755" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1755" s="2">
+        <v>8</v>
+      </c>
+      <c r="E1755" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1755" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G1755" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H1755" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I1755" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1755" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1755" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="L1755" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1755" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1755" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:14">
+      <c r="A1756" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1756" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1756" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1756" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1756" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1756" s="2" t="s">
+        <v>2608</v>
+      </c>
+      <c r="G1756" s="2" t="s">
+        <v>2609</v>
+      </c>
+      <c r="H1756" s="2" t="s">
+        <v>2610</v>
+      </c>
+      <c r="I1756" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1756" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1756" s="2" t="s">
+        <v>2609</v>
+      </c>
+      <c r="L1756" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1756" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1756" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:14">
+      <c r="A1757" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1757" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1757" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1757" s="2">
+        <v>5</v>
+      </c>
+      <c r="E1757" s="4">
+        <v>0.71428570000000002</v>
+      </c>
+      <c r="F1757" s="2" t="s">
+        <v>2611</v>
+      </c>
+      <c r="G1757" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H1757" s="2" t="s">
+        <v>2612</v>
+      </c>
+      <c r="I1757" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1757" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1757" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L1757" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1757" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1757" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:14">
+      <c r="A1758" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1758" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1758" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1758" s="2">
+        <v>5</v>
+      </c>
+      <c r="E1758" s="4">
+        <v>0.71428570000000002</v>
+      </c>
+      <c r="F1758" s="2" t="s">
+        <v>2613</v>
+      </c>
+      <c r="G1758" s="2" t="s">
+        <v>2614</v>
+      </c>
+      <c r="H1758" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="I1758" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1758" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1758" s="2" t="s">
+        <v>2614</v>
+      </c>
+      <c r="L1758" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1758" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1758" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:14">
+      <c r="A1759" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1759" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1759" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1759" s="2">
+        <v>5</v>
+      </c>
+      <c r="E1759" s="4">
+        <v>0.83333330000000005</v>
+      </c>
+      <c r="F1759" s="2" t="s">
+        <v>2615</v>
+      </c>
+      <c r="G1759" s="2" t="s">
+        <v>2616</v>
+      </c>
+      <c r="H1759" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="I1759" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1759" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1759" s="2" t="s">
+        <v>2616</v>
+      </c>
+      <c r="L1759" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1759" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1759" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:14">
+      <c r="A1760" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1760" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1760" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1760" s="2">
+        <v>6</v>
+      </c>
+      <c r="E1760" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1760" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="G1760" s="2" t="s">
+        <v>2617</v>
+      </c>
+      <c r="H1760" s="2" t="s">
+        <v>2618</v>
+      </c>
+      <c r="I1760" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1760" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1760" s="2" t="s">
+        <v>2617</v>
+      </c>
+      <c r="L1760" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1760" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1760" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:14">
+      <c r="A1761" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1761" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1761" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1761" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1761" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1761" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="G1761" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="H1761" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I1761" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1761" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1761" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="L1761" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1761" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1761" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:14">
+      <c r="A1762" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1762" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1762" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1762" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1762" s="4">
+        <v>0.3333333</v>
+      </c>
+      <c r="F1762" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1762" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H1762" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="I1762" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1762" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1762" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L1762" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1762" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1762" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:14">
+      <c r="A1763" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1763" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1763" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1763" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1763" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1763" s="2" t="s">
+        <v>2619</v>
+      </c>
+      <c r="G1763" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="H1763" s="2" t="s">
+        <v>2621</v>
+      </c>
+      <c r="I1763" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1763" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1763" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="L1763" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1763" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1763" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:14">
+      <c r="A1764" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1764" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1764" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1764" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1764" s="4">
+        <v>0.1666667</v>
+      </c>
+      <c r="F1764" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G1764" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="H1764" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="I1764" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1764" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1764" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="L1764" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1764" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1764" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:14">
+      <c r="A1765" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1765" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1765" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1765" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1765" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1765" s="2" t="s">
+        <v>2623</v>
+      </c>
+      <c r="G1765" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="H1765" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="I1765" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1765" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1765" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="L1765" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1765" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1765" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:14">
+      <c r="A1766" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1766" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1766" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1766" s="2">
+        <v>5</v>
+      </c>
+      <c r="E1766" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1766" s="2" t="s">
+        <v>2120</v>
+      </c>
+      <c r="G1766" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="H1766" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="I1766" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1766" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1766" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L1766" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1766" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1766" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:14">
+      <c r="A1767" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1767" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1767" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1767" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1767" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="F1767" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G1767" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="H1767" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="I1767" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1767" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1767" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="L1767" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1767" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1767" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:14">
+      <c r="A1768" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1768" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1768" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1768" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1768" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1768" s="2" t="s">
+        <v>2626</v>
+      </c>
+      <c r="G1768" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H1768" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1768" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1768" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1768" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="L1768" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1768" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1768" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:14">
+      <c r="A1769" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1769" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1769" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1769" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1769" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F1769" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="G1769" s="2" t="s">
+        <v>2543</v>
+      </c>
+      <c r="H1769" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I1769" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1769" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1769" s="2" t="s">
+        <v>2543</v>
+      </c>
+      <c r="L1769" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1769" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1769" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:14">
+      <c r="A1770" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1770" s="2" t="s">
+        <v>2627</v>
+      </c>
+      <c r="C1770" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1770" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1770" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1770" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1770" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H1770" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="I1770" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1770" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1770" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="L1770" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1770" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1770" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:14">
+      <c r="A1771" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1771" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1771" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1771" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1771" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="F1771" s="2" t="s">
+        <v>2628</v>
+      </c>
+      <c r="G1771" s="2" t="s">
+        <v>2629</v>
+      </c>
+      <c r="H1771" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="I1771" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1771" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1771" s="2" t="s">
+        <v>2629</v>
+      </c>
+      <c r="L1771" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1771" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1771" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:14">
+      <c r="A1772" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1772" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1772" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1772" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1772" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1772" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1772" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1772" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="I1772" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1772" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1772" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1772" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1772" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1772" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:14">
+      <c r="A1773" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1773" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1773" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1773" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1773" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1773" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1773" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1773" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="I1773" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1773" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1773" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="L1773" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1773" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1773" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:14">
+      <c r="A1774" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1774" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C1774" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1774" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1774" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1774" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="G1774" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1774" s="2" t="s">
+        <v>2027</v>
+      </c>
+      <c r="I1774" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1774" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1774" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="L1774" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1774" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1774" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:14">
+      <c r="A1775" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1775" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C1775" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1775" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1775" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1775" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1775" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1775" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="I1775" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1775" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1775" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1775" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1775" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1775" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:14">
+      <c r="A1776" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1776" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C1776" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1776" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1776" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1776" s="2" t="s">
+        <v>2630</v>
+      </c>
+      <c r="G1776" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1776" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="I1776" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1776" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1776" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="L1776" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1776" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1776" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:14">
+      <c r="A1777" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1777" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C1777" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1777" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1777" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1777" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1777" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="H1777" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="I1777" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1777" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1777" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="L1777" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1777" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1777" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:14">
+      <c r="A1778" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1778" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1778" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1778" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1778" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1778" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1778" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H1778" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I1778" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1778" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1778" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L1778" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1778" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1778" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:14">
+      <c r="A1779" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1779" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1779" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1779" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1779" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1779" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="G1779" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1779" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="I1779" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1779" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1779" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1779" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1779" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1779" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:14">
+      <c r="A1780" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1780" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1780" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1780" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1780" s="4">
+        <v>0.3333333</v>
+      </c>
+      <c r="F1780" s="2" t="s">
+        <v>2631</v>
+      </c>
+      <c r="G1780" s="2" t="s">
+        <v>2632</v>
+      </c>
+      <c r="H1780" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="I1780" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1780" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1780" s="2" t="s">
+        <v>2632</v>
+      </c>
+      <c r="L1780" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1780" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1780" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:14">
+      <c r="A1781" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1781" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C1781" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1781" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1781" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1781" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1781" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H1781" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I1781" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1781" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1781" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L1781" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1781" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1781" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:14">
+      <c r="A1782" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1782" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1782" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1782" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1782" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1782" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1782" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="H1782" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="I1782" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1782" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1782" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="L1782" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1782" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1782" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:14">
+      <c r="A1783" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1783" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C1783" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1783" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1783" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1783" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1783" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1783" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1783" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1783" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1783" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="L1783" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1783" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1783" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:14">
+      <c r="A1784" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1784" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1784" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1784" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1784" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1784" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1784" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1784" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I1784" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1784" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1784" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1784" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1784" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1784" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:14">
+      <c r="A1785" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1785" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1785" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1785" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1785" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1785" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="G1785" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="H1785" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="I1785" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1785" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1785" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="L1785" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1785" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1785" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:14">
+      <c r="A1786" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1786" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C1786" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1786" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1786" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1786" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1786" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H1786" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I1786" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1786" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1786" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="L1786" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1786" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1786" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:14">
+      <c r="A1787" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1787" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1787" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1787" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1787" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1787" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G1787" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H1787" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="I1787" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1787" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1787" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="L1787" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1787" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1787" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:14">
+      <c r="A1788" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1788" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1788" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1788" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1788" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1788" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="G1788" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H1788" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1788" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1788" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1788" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="L1788" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1788" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1788" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:14">
+      <c r="A1789" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1789" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C1789" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1789" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1789" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1789" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1789" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1789" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I1789" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1789" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1789" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="L1789" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1789" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1789" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:14">
+      <c r="A1790" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1790" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C1790" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1790" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1790" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1790" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="H1720" s="2" t="s">
+      <c r="G1790" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="H1790" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="I1790" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1790" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1790" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="L1790" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1790" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1790" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:14">
+      <c r="A1791" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1791" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1791" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1791" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1791" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1791" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="G1791" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H1791" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="I1791" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1791" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1791" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="L1791" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1791" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1791" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:14">
+      <c r="A1792" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1792" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1792" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1792" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1792" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1792" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1792" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1792" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="I1792" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1792" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1792" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="L1792" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1792" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1792" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:14">
+      <c r="A1793" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1793" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C1793" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1793" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1793" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1793" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="G1793" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1793" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="I1793" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1793" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1793" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1793" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1793" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1793" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:14">
+      <c r="A1794" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1794" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1794" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1794" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1794" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1794" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G1794" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H1794" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I1794" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1794" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1794" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="L1794" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1794" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1794" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:14">
+      <c r="A1795" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1795" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1795" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1795" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1795" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1795" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="G1795" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1795" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="I1795" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1795" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1795" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1795" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1795" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1795" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:14">
+      <c r="A1796" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1796" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C1796" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1796" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1796" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1796" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="G1796" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="I1720" s="2" t="s">
+      <c r="H1796" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="I1796" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1796" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1796" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="L1796" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1796" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1796" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:14">
+      <c r="A1797" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1797" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1797" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1797" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1797" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1797" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1797" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1797" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1797" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J1720" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1720" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="L1720" s="2">
-        <v>0</v>
-      </c>
-      <c r="M1720" s="5">
-        <v>0</v>
-      </c>
-      <c r="N1720" s="2">
+      <c r="J1797" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1797" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1797" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1797" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1797" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:14">
+      <c r="A1798" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1798" s="2" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C1798" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1798" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1798" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1798" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1798" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H1798" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1798" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1798" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1798" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="L1798" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1798" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1798" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:14">
+      <c r="A1799" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1799" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1799" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1799" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1799" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1799" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="G1799" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1799" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="I1799" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1799" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1799" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1799" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1799" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1799" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:14">
+      <c r="A1800" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1800" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1800" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1800" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1800" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1800" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1800" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H1800" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="I1800" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1800" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1800" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="L1800" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1800" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1800" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:14">
+      <c r="A1801" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1801" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C1801" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1801" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1801" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1801" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G1801" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1801" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I1801" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1801" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1801" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1801" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1801" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1801" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:14">
+      <c r="A1802" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1802" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1802" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1802" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1802" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1802" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G1802" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1802" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="I1802" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1802" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1802" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="L1802" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1802" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1802" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:14">
+      <c r="A1803" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1803" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C1803" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1803" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1803" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1803" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="G1803" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1803" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I1803" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1803" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1803" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1803" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1803" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1803" s="2">
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\new clone\Salefile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AAFA8F-8950-4552-8705-CC0A360401AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DEB99CB-9AE1-4323-B1CF-24CADC902105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12628" uniqueCount="2633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13118" uniqueCount="2696">
   <si>
     <t>Date</t>
   </si>
@@ -7701,150 +7701,12 @@
     <t>0.0795 EUR</t>
   </si>
   <si>
-    <t>163.4438 EUR</t>
-  </si>
-  <si>
-    <t>338.5962 EUR</t>
-  </si>
-  <si>
-    <t>502.04 EUR</t>
-  </si>
-  <si>
-    <t>16.7155 EUR</t>
-  </si>
-  <si>
-    <t>9.9445 EUR</t>
-  </si>
-  <si>
-    <t>26.66 EUR</t>
-  </si>
-  <si>
-    <t>12.8836 EUR</t>
-  </si>
-  <si>
-    <t>30.9964 EUR</t>
-  </si>
-  <si>
-    <t>43.88 EUR</t>
-  </si>
-  <si>
-    <t>1.7005 EUR</t>
-  </si>
-  <si>
-    <t>28.4315 EUR</t>
-  </si>
-  <si>
-    <t>30.132 EUR</t>
-  </si>
-  <si>
-    <t>3.714 EUR</t>
-  </si>
-  <si>
-    <t>29.278 EUR</t>
-  </si>
-  <si>
-    <t>32.992 EUR</t>
-  </si>
-  <si>
-    <t>3.12998 EUR</t>
-  </si>
-  <si>
-    <t>0.02903 EUR</t>
-  </si>
-  <si>
-    <t>3.159 EUR</t>
-  </si>
-  <si>
-    <t>0.1465 EUR</t>
-  </si>
-  <si>
-    <t>1.7775 EUR</t>
-  </si>
-  <si>
-    <t>1.924 EUR</t>
-  </si>
-  <si>
     <t>0.515 EUR</t>
   </si>
   <si>
     <t>0.824 EUR</t>
   </si>
   <si>
-    <t>1.63751 EUR</t>
-  </si>
-  <si>
-    <t>0.76849 EUR</t>
-  </si>
-  <si>
-    <t>2.406 EUR</t>
-  </si>
-  <si>
-    <t>0.53025 EUR</t>
-  </si>
-  <si>
-    <t>0.42975 EUR</t>
-  </si>
-  <si>
-    <t>2.3808 EUR</t>
-  </si>
-  <si>
-    <t>1.302 EUR</t>
-  </si>
-  <si>
-    <t>3.6828 EUR</t>
-  </si>
-  <si>
-    <t>1.058 EUR</t>
-  </si>
-  <si>
-    <t>3.802 EUR</t>
-  </si>
-  <si>
-    <t>4.86 EUR</t>
-  </si>
-  <si>
-    <t>0.2436 EUR</t>
-  </si>
-  <si>
-    <t>0.82082 EUR</t>
-  </si>
-  <si>
-    <t>1.9437 EUR</t>
-  </si>
-  <si>
-    <t>2.76452 EUR</t>
-  </si>
-  <si>
-    <t>0.837 EUR</t>
-  </si>
-  <si>
-    <t>0.07085 EUR</t>
-  </si>
-  <si>
-    <t>0.30385 EUR</t>
-  </si>
-  <si>
-    <t>0.3747 EUR</t>
-  </si>
-  <si>
-    <t>0.0862 EUR</t>
-  </si>
-  <si>
-    <t>0.0448 EUR</t>
-  </si>
-  <si>
-    <t>0.2652 EUR</t>
-  </si>
-  <si>
-    <t>0.3048 EUR</t>
-  </si>
-  <si>
-    <t>0.13661 EUR</t>
-  </si>
-  <si>
-    <t>0.09739 EUR</t>
-  </si>
-  <si>
     <t>0.03265 EUR</t>
   </si>
   <si>
@@ -7866,15 +7728,6 @@
     <t>0.151 EUR</t>
   </si>
   <si>
-    <t>0.00695 EUR</t>
-  </si>
-  <si>
-    <t>0.00765 EUR</t>
-  </si>
-  <si>
-    <t>0.0146 EUR</t>
-  </si>
-  <si>
     <t>0.01305 EUR</t>
   </si>
   <si>
@@ -7887,18 +7740,6 @@
     <t>0.1025 EUR</t>
   </si>
   <si>
-    <t>0.00475 EUR</t>
-  </si>
-  <si>
-    <t>0.00665 EUR</t>
-  </si>
-  <si>
-    <t>0.318 EUR</t>
-  </si>
-  <si>
-    <t>0.402 EUR</t>
-  </si>
-  <si>
     <t>0.14115 EUR</t>
   </si>
   <si>
@@ -7908,9 +7749,6 @@
     <t>0.1416 EUR</t>
   </si>
   <si>
-    <t>0.122 EUR</t>
-  </si>
-  <si>
     <t>0.24406 EUR</t>
   </si>
   <si>
@@ -7926,19 +7764,370 @@
     <t>Cyvora_HQ(Client)</t>
   </si>
   <si>
-    <t>0.0708 EUR</t>
-  </si>
-  <si>
     <t>0.0592 EUR</t>
   </si>
   <si>
     <t>0.0624 EUR</t>
   </si>
   <si>
-    <t>0.0481 EUR</t>
-  </si>
-  <si>
-    <t>0.0214 EUR</t>
+    <t>163.4578 EUR</t>
+  </si>
+  <si>
+    <t>338.6222 EUR</t>
+  </si>
+  <si>
+    <t>502.08 EUR</t>
+  </si>
+  <si>
+    <t>21.1085 EUR</t>
+  </si>
+  <si>
+    <t>12.5815 EUR</t>
+  </si>
+  <si>
+    <t>33.69 EUR</t>
+  </si>
+  <si>
+    <t>2.728 EUR</t>
+  </si>
+  <si>
+    <t>45.899 EUR</t>
+  </si>
+  <si>
+    <t>48.627 EUR</t>
+  </si>
+  <si>
+    <t>13.057 EUR</t>
+  </si>
+  <si>
+    <t>31.381 EUR</t>
+  </si>
+  <si>
+    <t>44.438 EUR</t>
+  </si>
+  <si>
+    <t>4.356 EUR</t>
+  </si>
+  <si>
+    <t>34.2 EUR</t>
+  </si>
+  <si>
+    <t>38.556 EUR</t>
+  </si>
+  <si>
+    <t>3.87308 EUR</t>
+  </si>
+  <si>
+    <t>0.04193 EUR</t>
+  </si>
+  <si>
+    <t>3.915 EUR</t>
+  </si>
+  <si>
+    <t>0.1537 EUR</t>
+  </si>
+  <si>
+    <t>1.8663 EUR</t>
+  </si>
+  <si>
+    <t>2.02 EUR</t>
+  </si>
+  <si>
+    <t>3.24251 EUR</t>
+  </si>
+  <si>
+    <t>1.00749 EUR</t>
+  </si>
+  <si>
+    <t>4.25 EUR</t>
+  </si>
+  <si>
+    <t>3.0976 EUR</t>
+  </si>
+  <si>
+    <t>1.694 EUR</t>
+  </si>
+  <si>
+    <t>4.7916 EUR</t>
+  </si>
+  <si>
+    <t>0.53725 EUR</t>
+  </si>
+  <si>
+    <t>0.43175 EUR</t>
+  </si>
+  <si>
+    <t>0.969 EUR</t>
+  </si>
+  <si>
+    <t>1.478 EUR</t>
+  </si>
+  <si>
+    <t>5.482 EUR</t>
+  </si>
+  <si>
+    <t>0.2856 EUR</t>
+  </si>
+  <si>
+    <t>0.612 EUR</t>
+  </si>
+  <si>
+    <t>0.0979 EUR</t>
+  </si>
+  <si>
+    <t>0.4349 EUR</t>
+  </si>
+  <si>
+    <t>0.5328 EUR</t>
+  </si>
+  <si>
+    <t>0.98914 EUR</t>
+  </si>
+  <si>
+    <t>2.3421 EUR</t>
+  </si>
+  <si>
+    <t>3.33124 EUR</t>
+  </si>
+  <si>
+    <t>0.0696 EUR</t>
+  </si>
+  <si>
+    <t>0.1113 EUR</t>
+  </si>
+  <si>
+    <t>0.3835 EUR</t>
+  </si>
+  <si>
+    <t>0.4948 EUR</t>
+  </si>
+  <si>
+    <t>0.01795 EUR</t>
+  </si>
+  <si>
+    <t>0.03525 EUR</t>
+  </si>
+  <si>
+    <t>0.812 EUR</t>
+  </si>
+  <si>
+    <t>0.3572 EUR</t>
+  </si>
+  <si>
+    <t>0.0931 EUR</t>
+  </si>
+  <si>
+    <t>0.0698 EUR</t>
+  </si>
+  <si>
+    <t>0.1068 EUR</t>
+  </si>
+  <si>
+    <t>0.1766 EUR</t>
+  </si>
+  <si>
+    <t>0.15541 EUR</t>
+  </si>
+  <si>
+    <t>0.10059 EUR</t>
+  </si>
+  <si>
+    <t>0.583 EUR</t>
+  </si>
+  <si>
+    <t>0.1132 EUR</t>
+  </si>
+  <si>
+    <t>0.1772 EUR</t>
+  </si>
+  <si>
+    <t>0.0521 EUR</t>
+  </si>
+  <si>
+    <t>0.0274 EUR</t>
+  </si>
+  <si>
+    <t>0.0734 EUR</t>
+  </si>
+  <si>
+    <t>0.143 EUR</t>
+  </si>
+  <si>
+    <t>0.0028 EUR</t>
+  </si>
+  <si>
+    <t>17.8785 EUR</t>
+  </si>
+  <si>
+    <t>10.7615 EUR</t>
+  </si>
+  <si>
+    <t>28.64 EUR</t>
+  </si>
+  <si>
+    <t>1.6723 EUR</t>
+  </si>
+  <si>
+    <t>20.5957 EUR</t>
+  </si>
+  <si>
+    <t>22.268 EUR</t>
+  </si>
+  <si>
+    <t>9.6189 EUR</t>
+  </si>
+  <si>
+    <t>0.1741 EUR</t>
+  </si>
+  <si>
+    <t>9.793 EUR</t>
+  </si>
+  <si>
+    <t>2.828 EUR</t>
+  </si>
+  <si>
+    <t>7.07 EUR</t>
+  </si>
+  <si>
+    <t>9.898 EUR</t>
+  </si>
+  <si>
+    <t>3.24 EUR</t>
+  </si>
+  <si>
+    <t>24.84 EUR</t>
+  </si>
+  <si>
+    <t>28.08 EUR</t>
+  </si>
+  <si>
+    <t>3.23801 EUR</t>
+  </si>
+  <si>
+    <t>0.71599 EUR</t>
+  </si>
+  <si>
+    <t>3.954 EUR</t>
+  </si>
+  <si>
+    <t>1.156 EUR</t>
+  </si>
+  <si>
+    <t>2.564 EUR</t>
+  </si>
+  <si>
+    <t>3.72 EUR</t>
+  </si>
+  <si>
+    <t>0.56465 EUR</t>
+  </si>
+  <si>
+    <t>0.45715 EUR</t>
+  </si>
+  <si>
+    <t>1.0218 EUR</t>
+  </si>
+  <si>
+    <t>2.048 EUR</t>
+  </si>
+  <si>
+    <t>3.168 EUR</t>
+  </si>
+  <si>
+    <t>0.2352 EUR</t>
+  </si>
+  <si>
+    <t>0.2688 EUR</t>
+  </si>
+  <si>
+    <t>1.65 EUR</t>
+  </si>
+  <si>
+    <t>1.716 EUR</t>
+  </si>
+  <si>
+    <t>0.654 EUR</t>
+  </si>
+  <si>
+    <t>1.5438 EUR</t>
+  </si>
+  <si>
+    <t>2.1978 EUR</t>
+  </si>
+  <si>
+    <t>1.4 EUR</t>
+  </si>
+  <si>
+    <t>0.2484 EUR</t>
+  </si>
+  <si>
+    <t>0.0716 EUR</t>
+  </si>
+  <si>
+    <t>0.2188 EUR</t>
+  </si>
+  <si>
+    <t>0.0276 EUR</t>
+  </si>
+  <si>
+    <t>TDNT_DIR(Client)</t>
+  </si>
+  <si>
+    <t>0.1224 EUR</t>
+  </si>
+  <si>
+    <t>0.03935 EUR</t>
+  </si>
+  <si>
+    <t>0.0559 EUR</t>
+  </si>
+  <si>
+    <t>0.0073 EUR</t>
+  </si>
+  <si>
+    <t>0.0674 EUR</t>
+  </si>
+  <si>
+    <t>0.0305 EUR</t>
+  </si>
+  <si>
+    <t>0.16647 EUR</t>
+  </si>
+  <si>
+    <t>0.10653 EUR</t>
+  </si>
+  <si>
+    <t>0.0652 EUR</t>
+  </si>
+  <si>
+    <t>0.0083 EUR</t>
+  </si>
+  <si>
+    <t>0.0462 EUR</t>
+  </si>
+  <si>
+    <t>0.3816 EUR</t>
+  </si>
+  <si>
+    <t>0.04826 EUR</t>
+  </si>
+  <si>
+    <t>0.10226 EUR</t>
+  </si>
+  <si>
+    <t>0.159 EUR</t>
+  </si>
+  <si>
+    <t>0.201 EUR</t>
+  </si>
+  <si>
+    <t>0.00145 EUR</t>
+  </si>
+  <si>
+    <t>0.00015 EUR</t>
+  </si>
+  <si>
+    <t>0.0013 EUR</t>
   </si>
 </sst>
 </file>
@@ -8327,7 +8516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1803"/>
+  <dimension ref="A1:N1873"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -84077,22 +84266,22 @@
         <v>461</v>
       </c>
       <c r="C1722" s="2">
-        <v>25106</v>
+        <v>25108</v>
       </c>
       <c r="D1722" s="2">
-        <v>15918</v>
+        <v>15965</v>
       </c>
       <c r="E1722" s="4">
-        <v>0.63403169999999998</v>
+        <v>0.63585309999999995</v>
       </c>
       <c r="F1722" s="2" t="s">
-        <v>2553</v>
+        <v>2576</v>
       </c>
       <c r="G1722" s="2" t="s">
-        <v>2554</v>
+        <v>2577</v>
       </c>
       <c r="H1722" s="2" t="s">
-        <v>2555</v>
+        <v>2578</v>
       </c>
       <c r="I1722" s="2" t="s">
         <v>23</v>
@@ -84101,7 +84290,7 @@
         <v>19</v>
       </c>
       <c r="K1722" s="2" t="s">
-        <v>2554</v>
+        <v>2577</v>
       </c>
       <c r="L1722" s="2">
         <v>0</v>
@@ -84121,22 +84310,22 @@
         <v>24</v>
       </c>
       <c r="C1723" s="2">
-        <v>2666</v>
+        <v>3369</v>
       </c>
       <c r="D1723" s="2">
-        <v>2517</v>
+        <v>3183</v>
       </c>
       <c r="E1723" s="4">
-        <v>0.94411100000000003</v>
+        <v>0.94479069999999998</v>
       </c>
       <c r="F1723" s="2" t="s">
-        <v>2556</v>
+        <v>2579</v>
       </c>
       <c r="G1723" s="2" t="s">
-        <v>2557</v>
+        <v>2580</v>
       </c>
       <c r="H1723" s="2" t="s">
-        <v>2558</v>
+        <v>2581</v>
       </c>
       <c r="I1723" s="2" t="s">
         <v>28</v>
@@ -84145,7 +84334,7 @@
         <v>19</v>
       </c>
       <c r="K1723" s="2" t="s">
-        <v>2557</v>
+        <v>2580</v>
       </c>
       <c r="L1723" s="2">
         <v>0</v>
@@ -84162,34 +84351,34 @@
         <v>46289</v>
       </c>
       <c r="B1724" s="2" t="s">
-        <v>49</v>
+        <v>308</v>
       </c>
       <c r="C1724" s="2">
-        <v>1416</v>
+        <v>1801</v>
       </c>
       <c r="D1724" s="2">
-        <v>1225</v>
+        <v>1590</v>
       </c>
       <c r="E1724" s="4">
-        <v>0.86511300000000002</v>
+        <v>0.88284289999999999</v>
       </c>
       <c r="F1724" s="2" t="s">
-        <v>2559</v>
+        <v>2582</v>
       </c>
       <c r="G1724" s="2" t="s">
-        <v>2560</v>
+        <v>2583</v>
       </c>
       <c r="H1724" s="2" t="s">
-        <v>2561</v>
+        <v>2584</v>
       </c>
       <c r="I1724" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1724" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1724" s="2" t="s">
-        <v>2560</v>
+        <v>2583</v>
       </c>
       <c r="L1724" s="2">
         <v>0</v>
@@ -84206,34 +84395,34 @@
         <v>46289</v>
       </c>
       <c r="B1725" s="2" t="s">
-        <v>308</v>
+        <v>49</v>
       </c>
       <c r="C1725" s="2">
-        <v>1116</v>
+        <v>1434</v>
       </c>
       <c r="D1725" s="2">
-        <v>935</v>
+        <v>1243</v>
       </c>
       <c r="E1725" s="4">
-        <v>0.83781360000000005</v>
+        <v>0.86680610000000002</v>
       </c>
       <c r="F1725" s="2" t="s">
-        <v>2562</v>
+        <v>2585</v>
       </c>
       <c r="G1725" s="2" t="s">
-        <v>2563</v>
+        <v>2586</v>
       </c>
       <c r="H1725" s="2" t="s">
-        <v>2564</v>
+        <v>2587</v>
       </c>
       <c r="I1725" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1725" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1725" s="2" t="s">
-        <v>2563</v>
+        <v>2586</v>
       </c>
       <c r="L1725" s="2">
         <v>0</v>
@@ -84253,22 +84442,22 @@
         <v>2391</v>
       </c>
       <c r="C1726" s="2">
-        <v>621</v>
+        <v>728</v>
       </c>
       <c r="D1726" s="2">
-        <v>610</v>
+        <v>714</v>
       </c>
       <c r="E1726" s="4">
-        <v>0.98228660000000001</v>
+        <v>0.98076920000000001</v>
       </c>
       <c r="F1726" s="2" t="s">
-        <v>2565</v>
+        <v>2588</v>
       </c>
       <c r="G1726" s="2" t="s">
-        <v>2566</v>
+        <v>2589</v>
       </c>
       <c r="H1726" s="2" t="s">
-        <v>2567</v>
+        <v>2590</v>
       </c>
       <c r="I1726" s="2" t="s">
         <v>28</v>
@@ -84277,7 +84466,7 @@
         <v>19</v>
       </c>
       <c r="K1726" s="2" t="s">
-        <v>2566</v>
+        <v>2589</v>
       </c>
       <c r="L1726" s="2">
         <v>0</v>
@@ -84297,22 +84486,22 @@
         <v>525</v>
       </c>
       <c r="C1727" s="2">
-        <v>351</v>
+        <v>435</v>
       </c>
       <c r="D1727" s="2">
-        <v>342</v>
+        <v>422</v>
       </c>
       <c r="E1727" s="4">
-        <v>0.97435899999999998</v>
+        <v>0.9701149</v>
       </c>
       <c r="F1727" s="2" t="s">
-        <v>2568</v>
+        <v>2591</v>
       </c>
       <c r="G1727" s="2" t="s">
-        <v>2569</v>
+        <v>2592</v>
       </c>
       <c r="H1727" s="2" t="s">
-        <v>2570</v>
+        <v>2593</v>
       </c>
       <c r="I1727" s="2" t="s">
         <v>28</v>
@@ -84321,7 +84510,7 @@
         <v>19</v>
       </c>
       <c r="K1727" s="2" t="s">
-        <v>2569</v>
+        <v>2592</v>
       </c>
       <c r="L1727" s="2">
         <v>0</v>
@@ -84341,22 +84530,22 @@
         <v>45</v>
       </c>
       <c r="C1728" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="D1728" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="E1728" s="5">
         <v>1</v>
       </c>
       <c r="F1728" s="2" t="s">
-        <v>2571</v>
+        <v>2594</v>
       </c>
       <c r="G1728" s="2" t="s">
-        <v>2572</v>
+        <v>2595</v>
       </c>
       <c r="H1728" s="2" t="s">
-        <v>2573</v>
+        <v>2596</v>
       </c>
       <c r="I1728" s="2" t="s">
         <v>23</v>
@@ -84365,7 +84554,7 @@
         <v>19</v>
       </c>
       <c r="K1728" s="2" t="s">
-        <v>2572</v>
+        <v>2595</v>
       </c>
       <c r="L1728" s="2">
         <v>0</v>
@@ -84397,10 +84586,10 @@
         <v>1806</v>
       </c>
       <c r="G1729" s="2" t="s">
-        <v>2574</v>
+        <v>2553</v>
       </c>
       <c r="H1729" s="2" t="s">
-        <v>2575</v>
+        <v>2554</v>
       </c>
       <c r="I1729" s="2" t="s">
         <v>18</v>
@@ -84409,7 +84598,7 @@
         <v>19</v>
       </c>
       <c r="K1729" s="2" t="s">
-        <v>2574</v>
+        <v>2553</v>
       </c>
       <c r="L1729" s="2">
         <v>0</v>
@@ -84429,22 +84618,22 @@
         <v>57</v>
       </c>
       <c r="C1730" s="2">
-        <v>97</v>
+        <v>168</v>
       </c>
       <c r="D1730" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1730" s="4">
-        <v>0.18556700000000001</v>
+        <v>0.11309520000000001</v>
       </c>
       <c r="F1730" s="2" t="s">
-        <v>2576</v>
+        <v>2597</v>
       </c>
       <c r="G1730" s="2" t="s">
-        <v>2577</v>
+        <v>2598</v>
       </c>
       <c r="H1730" s="2" t="s">
-        <v>2578</v>
+        <v>2599</v>
       </c>
       <c r="I1730" s="2" t="s">
         <v>23</v>
@@ -84453,7 +84642,7 @@
         <v>19</v>
       </c>
       <c r="K1730" s="2" t="s">
-        <v>2577</v>
+        <v>2598</v>
       </c>
       <c r="L1730" s="2">
         <v>0</v>
@@ -84470,34 +84659,34 @@
         <v>46289</v>
       </c>
       <c r="B1731" s="2" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C1731" s="2">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="D1731" s="2">
-        <v>90</v>
-      </c>
-      <c r="E1731" s="4">
-        <v>0.9375</v>
+        <v>121</v>
+      </c>
+      <c r="E1731" s="5">
+        <v>1</v>
       </c>
       <c r="F1731" s="2" t="s">
-        <v>2579</v>
+        <v>2600</v>
       </c>
       <c r="G1731" s="2" t="s">
-        <v>2580</v>
+        <v>2601</v>
       </c>
       <c r="H1731" s="2" t="s">
-        <v>983</v>
+        <v>2602</v>
       </c>
       <c r="I1731" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1731" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1731" s="2" t="s">
-        <v>2580</v>
+        <v>2601</v>
       </c>
       <c r="L1731" s="2">
         <v>0</v>
@@ -84514,34 +84703,34 @@
         <v>46289</v>
       </c>
       <c r="B1732" s="2" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="C1732" s="2">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D1732" s="2">
-        <v>93</v>
-      </c>
-      <c r="E1732" s="5">
-        <v>1</v>
+        <v>95</v>
+      </c>
+      <c r="E1732" s="4">
+        <v>0.94059409999999999</v>
       </c>
       <c r="F1732" s="2" t="s">
-        <v>2581</v>
+        <v>2603</v>
       </c>
       <c r="G1732" s="2" t="s">
-        <v>2582</v>
+        <v>2604</v>
       </c>
       <c r="H1732" s="2" t="s">
-        <v>2583</v>
+        <v>2605</v>
       </c>
       <c r="I1732" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1732" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1732" s="2" t="s">
-        <v>2582</v>
+        <v>2604</v>
       </c>
       <c r="L1732" s="2">
         <v>0</v>
@@ -84561,22 +84750,22 @@
         <v>105</v>
       </c>
       <c r="C1733" s="2">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D1733" s="2">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E1733" s="4">
-        <v>0.97058820000000001</v>
+        <v>0.97959180000000001</v>
       </c>
       <c r="F1733" s="2" t="s">
-        <v>2584</v>
+        <v>2606</v>
       </c>
       <c r="G1733" s="2" t="s">
-        <v>2585</v>
+        <v>2607</v>
       </c>
       <c r="H1733" s="2" t="s">
-        <v>2586</v>
+        <v>944</v>
       </c>
       <c r="I1733" s="2" t="s">
         <v>28</v>
@@ -84585,7 +84774,7 @@
         <v>19</v>
       </c>
       <c r="K1733" s="2" t="s">
-        <v>2585</v>
+        <v>2607</v>
       </c>
       <c r="L1733" s="2">
         <v>0</v>
@@ -84605,22 +84794,22 @@
         <v>124</v>
       </c>
       <c r="C1734" s="2">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D1734" s="2">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E1734" s="4">
-        <v>0.87931029999999999</v>
+        <v>0.8823529</v>
       </c>
       <c r="F1734" s="2" t="s">
-        <v>2587</v>
+        <v>2608</v>
       </c>
       <c r="G1734" s="2" t="s">
-        <v>129</v>
+        <v>963</v>
       </c>
       <c r="H1734" s="2" t="s">
-        <v>155</v>
+        <v>2609</v>
       </c>
       <c r="I1734" s="2" t="s">
         <v>23</v>
@@ -84629,7 +84818,7 @@
         <v>19</v>
       </c>
       <c r="K1734" s="2" t="s">
-        <v>129</v>
+        <v>963</v>
       </c>
       <c r="L1734" s="2">
         <v>0</v>
@@ -84646,34 +84835,34 @@
         <v>46289</v>
       </c>
       <c r="B1735" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="C1735" s="2">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D1735" s="2">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E1735" s="4">
-        <v>0.67500000000000004</v>
+        <v>0.94444439999999996</v>
       </c>
       <c r="F1735" s="2" t="s">
-        <v>2588</v>
+        <v>2610</v>
       </c>
       <c r="G1735" s="2" t="s">
-        <v>2589</v>
+        <v>2611</v>
       </c>
       <c r="H1735" s="2" t="s">
-        <v>2590</v>
+        <v>2612</v>
       </c>
       <c r="I1735" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1735" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1735" s="2" t="s">
-        <v>2589</v>
+        <v>2611</v>
       </c>
       <c r="L1735" s="2">
         <v>0</v>
@@ -84690,34 +84879,34 @@
         <v>46289</v>
       </c>
       <c r="B1736" s="2" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="C1736" s="2">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D1736" s="2">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E1736" s="4">
-        <v>0.29629630000000001</v>
+        <v>0.70833330000000005</v>
       </c>
       <c r="F1736" s="2" t="s">
-        <v>277</v>
+        <v>2613</v>
       </c>
       <c r="G1736" s="2" t="s">
-        <v>1460</v>
+        <v>2614</v>
       </c>
       <c r="H1736" s="2" t="s">
-        <v>1200</v>
+        <v>2615</v>
       </c>
       <c r="I1736" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1736" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1736" s="2" t="s">
-        <v>1460</v>
+        <v>2614</v>
       </c>
       <c r="L1736" s="2">
         <v>0</v>
@@ -84734,34 +84923,34 @@
         <v>46289</v>
       </c>
       <c r="B1737" s="2" t="s">
-        <v>1117</v>
+        <v>144</v>
       </c>
       <c r="C1737" s="2">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D1737" s="2">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="E1737" s="4">
-        <v>0.96296300000000001</v>
+        <v>0.97872340000000002</v>
       </c>
       <c r="F1737" s="2" t="s">
-        <v>495</v>
+        <v>2616</v>
       </c>
       <c r="G1737" s="2" t="s">
-        <v>2339</v>
+        <v>1060</v>
       </c>
       <c r="H1737" s="2" t="s">
-        <v>2591</v>
+        <v>1452</v>
       </c>
       <c r="I1737" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1737" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1737" s="2" t="s">
-        <v>2339</v>
+        <v>1060</v>
       </c>
       <c r="L1737" s="2">
         <v>0</v>
@@ -84781,22 +84970,22 @@
         <v>109</v>
       </c>
       <c r="C1738" s="2">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D1738" s="2">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E1738" s="4">
-        <v>0.83333330000000005</v>
+        <v>0.82222220000000001</v>
       </c>
       <c r="F1738" s="2" t="s">
-        <v>2592</v>
+        <v>2617</v>
       </c>
       <c r="G1738" s="2" t="s">
-        <v>2593</v>
+        <v>2618</v>
       </c>
       <c r="H1738" s="2" t="s">
-        <v>2594</v>
+        <v>2619</v>
       </c>
       <c r="I1738" s="2" t="s">
         <v>18</v>
@@ -84805,7 +84994,7 @@
         <v>19</v>
       </c>
       <c r="K1738" s="2" t="s">
-        <v>2593</v>
+        <v>2618</v>
       </c>
       <c r="L1738" s="2">
         <v>0</v>
@@ -84822,25 +85011,25 @@
         <v>46289</v>
       </c>
       <c r="B1739" s="2" t="s">
-        <v>409</v>
+        <v>140</v>
       </c>
       <c r="C1739" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D1739" s="2">
-        <v>15</v>
-      </c>
-      <c r="E1739" s="5">
-        <v>0.75</v>
+        <v>27</v>
+      </c>
+      <c r="E1739" s="4">
+        <v>0.96428570000000002</v>
       </c>
       <c r="F1739" s="2" t="s">
-        <v>153</v>
+        <v>2620</v>
       </c>
       <c r="G1739" s="2" t="s">
-        <v>1981</v>
+        <v>2621</v>
       </c>
       <c r="H1739" s="2" t="s">
-        <v>358</v>
+        <v>1338</v>
       </c>
       <c r="I1739" s="2" t="s">
         <v>18</v>
@@ -84849,7 +85038,7 @@
         <v>19</v>
       </c>
       <c r="K1739" s="2" t="s">
-        <v>1981</v>
+        <v>2621</v>
       </c>
       <c r="L1739" s="2">
         <v>0</v>
@@ -84866,34 +85055,34 @@
         <v>46289</v>
       </c>
       <c r="B1740" s="2" t="s">
-        <v>81</v>
+        <v>1117</v>
       </c>
       <c r="C1740" s="2">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D1740" s="2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E1740" s="4">
-        <v>0.9375</v>
+        <v>0.96428570000000002</v>
       </c>
       <c r="F1740" s="2" t="s">
-        <v>669</v>
+        <v>287</v>
       </c>
       <c r="G1740" s="2" t="s">
-        <v>1789</v>
+        <v>2622</v>
       </c>
       <c r="H1740" s="2" t="s">
-        <v>2595</v>
+        <v>776</v>
       </c>
       <c r="I1740" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1740" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1740" s="2" t="s">
-        <v>1789</v>
+        <v>2622</v>
       </c>
       <c r="L1740" s="2">
         <v>0</v>
@@ -84910,25 +85099,25 @@
         <v>46289</v>
       </c>
       <c r="B1741" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C1741" s="2">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D1741" s="2">
-        <v>0</v>
-      </c>
-      <c r="E1741" s="5">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="E1741" s="4">
+        <v>0.29629630000000001</v>
       </c>
       <c r="F1741" s="2" t="s">
-        <v>1559</v>
+        <v>277</v>
       </c>
       <c r="G1741" s="2" t="s">
-        <v>2596</v>
+        <v>1460</v>
       </c>
       <c r="H1741" s="2" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="I1741" s="2" t="s">
         <v>18</v>
@@ -84937,7 +85126,7 @@
         <v>19</v>
       </c>
       <c r="K1741" s="2" t="s">
-        <v>2596</v>
+        <v>1460</v>
       </c>
       <c r="L1741" s="2">
         <v>0</v>
@@ -84954,34 +85143,34 @@
         <v>46289</v>
       </c>
       <c r="B1742" s="2" t="s">
-        <v>85</v>
+        <v>409</v>
       </c>
       <c r="C1742" s="2">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D1742" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E1742" s="4">
-        <v>0.69230769999999997</v>
+        <v>0.79166669999999995</v>
       </c>
       <c r="F1742" s="2" t="s">
-        <v>1076</v>
+        <v>448</v>
       </c>
       <c r="G1742" s="2" t="s">
-        <v>2238</v>
+        <v>1068</v>
       </c>
       <c r="H1742" s="2" t="s">
-        <v>2239</v>
+        <v>1058</v>
       </c>
       <c r="I1742" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1742" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1742" s="2" t="s">
-        <v>2238</v>
+        <v>1068</v>
       </c>
       <c r="L1742" s="2">
         <v>0</v>
@@ -84998,25 +85187,25 @@
         <v>46289</v>
       </c>
       <c r="B1743" s="2" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="C1743" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D1743" s="2">
-        <v>10</v>
-      </c>
-      <c r="E1743" s="4">
-        <v>0.76923079999999999</v>
+        <v>0</v>
+      </c>
+      <c r="E1743" s="5">
+        <v>0</v>
       </c>
       <c r="F1743" s="2" t="s">
-        <v>2002</v>
+        <v>2623</v>
       </c>
       <c r="G1743" s="2" t="s">
-        <v>256</v>
+        <v>465</v>
       </c>
       <c r="H1743" s="2" t="s">
-        <v>502</v>
+        <v>441</v>
       </c>
       <c r="I1743" s="2" t="s">
         <v>18</v>
@@ -85025,7 +85214,7 @@
         <v>19</v>
       </c>
       <c r="K1743" s="2" t="s">
-        <v>256</v>
+        <v>465</v>
       </c>
       <c r="L1743" s="2">
         <v>0</v>
@@ -85042,25 +85231,25 @@
         <v>46289</v>
       </c>
       <c r="B1744" s="2" t="s">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="C1744" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D1744" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1744" s="4">
-        <v>0.83333330000000005</v>
+        <v>0.9473684</v>
       </c>
       <c r="F1744" s="2" t="s">
-        <v>1818</v>
+        <v>1580</v>
       </c>
       <c r="G1744" s="2" t="s">
-        <v>2597</v>
+        <v>1141</v>
       </c>
       <c r="H1744" s="2" t="s">
-        <v>2598</v>
+        <v>2624</v>
       </c>
       <c r="I1744" s="2" t="s">
         <v>18</v>
@@ -85069,7 +85258,7 @@
         <v>19</v>
       </c>
       <c r="K1744" s="2" t="s">
-        <v>2597</v>
+        <v>1141</v>
       </c>
       <c r="L1744" s="2">
         <v>0</v>
@@ -85086,34 +85275,34 @@
         <v>46289</v>
       </c>
       <c r="B1745" s="2" t="s">
-        <v>97</v>
+        <v>325</v>
       </c>
       <c r="C1745" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D1745" s="2">
-        <v>2</v>
-      </c>
-      <c r="E1745" s="4">
-        <v>0.1666667</v>
+        <v>15</v>
+      </c>
+      <c r="E1745" s="5">
+        <v>1</v>
       </c>
       <c r="F1745" s="2" t="s">
-        <v>2599</v>
+        <v>911</v>
       </c>
       <c r="G1745" s="2" t="s">
-        <v>2600</v>
+        <v>495</v>
       </c>
       <c r="H1745" s="2" t="s">
-        <v>2002</v>
+        <v>688</v>
       </c>
       <c r="I1745" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1745" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1745" s="2" t="s">
-        <v>2600</v>
+        <v>495</v>
       </c>
       <c r="L1745" s="2">
         <v>0</v>
@@ -85130,25 +85319,25 @@
         <v>46289</v>
       </c>
       <c r="B1746" s="2" t="s">
-        <v>1232</v>
+        <v>136</v>
       </c>
       <c r="C1746" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D1746" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E1746" s="5">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F1746" s="2" t="s">
-        <v>196</v>
+        <v>2625</v>
       </c>
       <c r="G1746" s="2" t="s">
-        <v>663</v>
+        <v>2626</v>
       </c>
       <c r="H1746" s="2" t="s">
-        <v>203</v>
+        <v>2627</v>
       </c>
       <c r="I1746" s="2" t="s">
         <v>18</v>
@@ -85157,7 +85346,7 @@
         <v>19</v>
       </c>
       <c r="K1746" s="2" t="s">
-        <v>663</v>
+        <v>2626</v>
       </c>
       <c r="L1746" s="2">
         <v>0</v>
@@ -85174,25 +85363,25 @@
         <v>46289</v>
       </c>
       <c r="B1747" s="2" t="s">
-        <v>703</v>
+        <v>85</v>
       </c>
       <c r="C1747" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D1747" s="2">
-        <v>0</v>
-      </c>
-      <c r="E1747" s="5">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="E1747" s="4">
+        <v>0.64285709999999996</v>
       </c>
       <c r="F1747" s="2" t="s">
-        <v>2371</v>
+        <v>777</v>
       </c>
       <c r="G1747" s="2" t="s">
-        <v>19</v>
+        <v>1640</v>
       </c>
       <c r="H1747" s="2" t="s">
-        <v>2371</v>
+        <v>1641</v>
       </c>
       <c r="I1747" s="2" t="s">
         <v>28</v>
@@ -85201,7 +85390,7 @@
         <v>19</v>
       </c>
       <c r="K1747" s="2" t="s">
-        <v>19</v>
+        <v>1640</v>
       </c>
       <c r="L1747" s="2">
         <v>0</v>
@@ -85218,34 +85407,34 @@
         <v>46289</v>
       </c>
       <c r="B1748" s="2" t="s">
-        <v>237</v>
+        <v>33</v>
       </c>
       <c r="C1748" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1748" s="2">
         <v>10</v>
       </c>
-      <c r="D1748" s="2">
-        <v>9</v>
-      </c>
-      <c r="E1748" s="5">
-        <v>0.9</v>
+      <c r="E1748" s="4">
+        <v>0.76923079999999999</v>
       </c>
       <c r="F1748" s="2" t="s">
-        <v>2601</v>
+        <v>2002</v>
       </c>
       <c r="G1748" s="2" t="s">
-        <v>2412</v>
+        <v>256</v>
       </c>
       <c r="H1748" s="2" t="s">
-        <v>2602</v>
+        <v>502</v>
       </c>
       <c r="I1748" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1748" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1748" s="2" t="s">
-        <v>2412</v>
+        <v>256</v>
       </c>
       <c r="L1748" s="2">
         <v>0</v>
@@ -85262,34 +85451,34 @@
         <v>46289</v>
       </c>
       <c r="B1749" s="2" t="s">
-        <v>660</v>
+        <v>97</v>
       </c>
       <c r="C1749" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D1749" s="2">
-        <v>6</v>
-      </c>
-      <c r="E1749" s="5">
-        <v>0.6</v>
+        <v>2</v>
+      </c>
+      <c r="E1749" s="4">
+        <v>0.15384619999999999</v>
       </c>
       <c r="F1749" s="2" t="s">
-        <v>2603</v>
+        <v>2628</v>
       </c>
       <c r="G1749" s="2" t="s">
-        <v>1209</v>
+        <v>2629</v>
       </c>
       <c r="H1749" s="2" t="s">
-        <v>227</v>
+        <v>1550</v>
       </c>
       <c r="I1749" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1749" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1749" s="2" t="s">
-        <v>1209</v>
+        <v>2629</v>
       </c>
       <c r="L1749" s="2">
         <v>0</v>
@@ -85306,25 +85495,25 @@
         <v>46289</v>
       </c>
       <c r="B1750" s="2" t="s">
-        <v>1579</v>
+        <v>1232</v>
       </c>
       <c r="C1750" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D1750" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E1750" s="5">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F1750" s="2" t="s">
-        <v>1330</v>
+        <v>196</v>
       </c>
       <c r="G1750" s="2" t="s">
-        <v>2604</v>
+        <v>663</v>
       </c>
       <c r="H1750" s="2" t="s">
-        <v>628</v>
+        <v>203</v>
       </c>
       <c r="I1750" s="2" t="s">
         <v>18</v>
@@ -85333,7 +85522,7 @@
         <v>19</v>
       </c>
       <c r="K1750" s="2" t="s">
-        <v>2604</v>
+        <v>663</v>
       </c>
       <c r="L1750" s="2">
         <v>0</v>
@@ -85350,34 +85539,34 @@
         <v>46289</v>
       </c>
       <c r="B1751" s="2" t="s">
-        <v>329</v>
+        <v>172</v>
       </c>
       <c r="C1751" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D1751" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1751" s="5">
         <v>1</v>
       </c>
       <c r="F1751" s="2" t="s">
-        <v>495</v>
+        <v>921</v>
       </c>
       <c r="G1751" s="2" t="s">
-        <v>270</v>
+        <v>2630</v>
       </c>
       <c r="H1751" s="2" t="s">
-        <v>236</v>
+        <v>1611</v>
       </c>
       <c r="I1751" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1751" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1751" s="2" t="s">
-        <v>270</v>
+        <v>2630</v>
       </c>
       <c r="L1751" s="2">
         <v>0</v>
@@ -85394,10 +85583,10 @@
         <v>46289</v>
       </c>
       <c r="B1752" s="2" t="s">
-        <v>520</v>
+        <v>703</v>
       </c>
       <c r="C1752" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1752" s="2">
         <v>0</v>
@@ -85406,22 +85595,22 @@
         <v>0</v>
       </c>
       <c r="F1752" s="2" t="s">
-        <v>1178</v>
+        <v>2371</v>
       </c>
       <c r="G1752" s="2" t="s">
-        <v>912</v>
+        <v>19</v>
       </c>
       <c r="H1752" s="2" t="s">
-        <v>2002</v>
+        <v>2371</v>
       </c>
       <c r="I1752" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1752" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1752" s="2" t="s">
-        <v>912</v>
+        <v>19</v>
       </c>
       <c r="L1752" s="2">
         <v>0</v>
@@ -85438,34 +85627,34 @@
         <v>46289</v>
       </c>
       <c r="B1753" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C1753" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1753" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1753" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F1753" s="2" t="s">
-        <v>2605</v>
+        <v>2631</v>
       </c>
       <c r="G1753" s="2" t="s">
-        <v>2606</v>
+        <v>1451</v>
       </c>
       <c r="H1753" s="2" t="s">
-        <v>1030</v>
+        <v>2632</v>
       </c>
       <c r="I1753" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1753" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1753" s="2" t="s">
-        <v>2606</v>
+        <v>1451</v>
       </c>
       <c r="L1753" s="2">
         <v>0</v>
@@ -85482,25 +85671,25 @@
         <v>46289</v>
       </c>
       <c r="B1754" s="2" t="s">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="C1754" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D1754" s="2">
-        <v>7</v>
-      </c>
-      <c r="E1754" s="4">
-        <v>0.875</v>
+        <v>9</v>
+      </c>
+      <c r="E1754" s="5">
+        <v>0.9</v>
       </c>
       <c r="F1754" s="2" t="s">
-        <v>1112</v>
+        <v>2555</v>
       </c>
       <c r="G1754" s="2" t="s">
-        <v>231</v>
+        <v>2412</v>
       </c>
       <c r="H1754" s="2" t="s">
-        <v>2607</v>
+        <v>2556</v>
       </c>
       <c r="I1754" s="2" t="s">
         <v>23</v>
@@ -85509,7 +85698,7 @@
         <v>19</v>
       </c>
       <c r="K1754" s="2" t="s">
-        <v>231</v>
+        <v>2412</v>
       </c>
       <c r="L1754" s="2">
         <v>0</v>
@@ -85526,34 +85715,34 @@
         <v>46289</v>
       </c>
       <c r="B1755" s="2" t="s">
-        <v>302</v>
+        <v>660</v>
       </c>
       <c r="C1755" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D1755" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1755" s="5">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F1755" s="2" t="s">
-        <v>453</v>
+        <v>2557</v>
       </c>
       <c r="G1755" s="2" t="s">
-        <v>321</v>
+        <v>1209</v>
       </c>
       <c r="H1755" s="2" t="s">
-        <v>1451</v>
+        <v>227</v>
       </c>
       <c r="I1755" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1755" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1755" s="2" t="s">
-        <v>321</v>
+        <v>1209</v>
       </c>
       <c r="L1755" s="2">
         <v>0</v>
@@ -85570,25 +85759,25 @@
         <v>46289</v>
       </c>
       <c r="B1756" s="2" t="s">
-        <v>144</v>
+        <v>1579</v>
       </c>
       <c r="C1756" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D1756" s="2">
         <v>7</v>
       </c>
       <c r="E1756" s="5">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F1756" s="2" t="s">
-        <v>2608</v>
+        <v>1330</v>
       </c>
       <c r="G1756" s="2" t="s">
-        <v>2609</v>
+        <v>2558</v>
       </c>
       <c r="H1756" s="2" t="s">
-        <v>2610</v>
+        <v>628</v>
       </c>
       <c r="I1756" s="2" t="s">
         <v>18</v>
@@ -85597,7 +85786,7 @@
         <v>19</v>
       </c>
       <c r="K1756" s="2" t="s">
-        <v>2609</v>
+        <v>2558</v>
       </c>
       <c r="L1756" s="2">
         <v>0</v>
@@ -85614,34 +85803,34 @@
         <v>46289</v>
       </c>
       <c r="B1757" s="2" t="s">
-        <v>29</v>
+        <v>329</v>
       </c>
       <c r="C1757" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D1757" s="2">
-        <v>5</v>
-      </c>
-      <c r="E1757" s="4">
-        <v>0.71428570000000002</v>
+        <v>9</v>
+      </c>
+      <c r="E1757" s="5">
+        <v>1</v>
       </c>
       <c r="F1757" s="2" t="s">
-        <v>2611</v>
+        <v>495</v>
       </c>
       <c r="G1757" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="H1757" s="2" t="s">
-        <v>2612</v>
+        <v>236</v>
       </c>
       <c r="I1757" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1757" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1757" s="2" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="L1757" s="2">
         <v>0</v>
@@ -85658,34 +85847,34 @@
         <v>46289</v>
       </c>
       <c r="B1758" s="2" t="s">
-        <v>61</v>
+        <v>520</v>
       </c>
       <c r="C1758" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D1758" s="2">
-        <v>5</v>
-      </c>
-      <c r="E1758" s="4">
-        <v>0.71428570000000002</v>
+        <v>0</v>
+      </c>
+      <c r="E1758" s="5">
+        <v>0</v>
       </c>
       <c r="F1758" s="2" t="s">
-        <v>2613</v>
+        <v>1178</v>
       </c>
       <c r="G1758" s="2" t="s">
-        <v>2614</v>
+        <v>912</v>
       </c>
       <c r="H1758" s="2" t="s">
-        <v>1445</v>
+        <v>2002</v>
       </c>
       <c r="I1758" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1758" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1758" s="2" t="s">
-        <v>2614</v>
+        <v>912</v>
       </c>
       <c r="L1758" s="2">
         <v>0</v>
@@ -85702,34 +85891,34 @@
         <v>46289</v>
       </c>
       <c r="B1759" s="2" t="s">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="C1759" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D1759" s="2">
-        <v>5</v>
-      </c>
-      <c r="E1759" s="4">
-        <v>0.83333330000000005</v>
+        <v>9</v>
+      </c>
+      <c r="E1759" s="5">
+        <v>1</v>
       </c>
       <c r="F1759" s="2" t="s">
-        <v>2615</v>
+        <v>2559</v>
       </c>
       <c r="G1759" s="2" t="s">
-        <v>2616</v>
+        <v>2560</v>
       </c>
       <c r="H1759" s="2" t="s">
-        <v>1827</v>
+        <v>1030</v>
       </c>
       <c r="I1759" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1759" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1759" s="2" t="s">
-        <v>2616</v>
+        <v>2560</v>
       </c>
       <c r="L1759" s="2">
         <v>0</v>
@@ -85746,34 +85935,34 @@
         <v>46289</v>
       </c>
       <c r="B1760" s="2" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="C1760" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1760" s="2">
         <v>6</v>
       </c>
       <c r="E1760" s="5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F1760" s="2" t="s">
-        <v>508</v>
+        <v>2633</v>
       </c>
       <c r="G1760" s="2" t="s">
-        <v>2617</v>
+        <v>2634</v>
       </c>
       <c r="H1760" s="2" t="s">
-        <v>2618</v>
+        <v>2552</v>
       </c>
       <c r="I1760" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1760" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1760" s="2" t="s">
-        <v>2617</v>
+        <v>2634</v>
       </c>
       <c r="L1760" s="2">
         <v>0</v>
@@ -85790,25 +85979,25 @@
         <v>46289</v>
       </c>
       <c r="B1761" s="2" t="s">
-        <v>195</v>
+        <v>271</v>
       </c>
       <c r="C1761" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1761" s="2">
-        <v>0</v>
-      </c>
-      <c r="E1761" s="5">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="E1761" s="4">
+        <v>0.625</v>
       </c>
       <c r="F1761" s="2" t="s">
-        <v>2198</v>
+        <v>1211</v>
       </c>
       <c r="G1761" s="2" t="s">
-        <v>684</v>
+        <v>316</v>
       </c>
       <c r="H1761" s="2" t="s">
-        <v>218</v>
+        <v>826</v>
       </c>
       <c r="I1761" s="2" t="s">
         <v>23</v>
@@ -85817,7 +86006,7 @@
         <v>19</v>
       </c>
       <c r="K1761" s="2" t="s">
-        <v>684</v>
+        <v>316</v>
       </c>
       <c r="L1761" s="2">
         <v>0</v>
@@ -85834,34 +86023,34 @@
         <v>46289</v>
       </c>
       <c r="B1762" s="2" t="s">
-        <v>220</v>
+        <v>302</v>
       </c>
       <c r="C1762" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1762" s="2">
-        <v>2</v>
-      </c>
-      <c r="E1762" s="4">
-        <v>0.3333333</v>
+        <v>8</v>
+      </c>
+      <c r="E1762" s="5">
+        <v>1</v>
       </c>
       <c r="F1762" s="2" t="s">
-        <v>258</v>
+        <v>453</v>
       </c>
       <c r="G1762" s="2" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="H1762" s="2" t="s">
-        <v>471</v>
+        <v>1451</v>
       </c>
       <c r="I1762" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1762" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1762" s="2" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
       <c r="L1762" s="2">
         <v>0</v>
@@ -85878,34 +86067,34 @@
         <v>46289</v>
       </c>
       <c r="B1763" s="2" t="s">
-        <v>211</v>
+        <v>333</v>
       </c>
       <c r="C1763" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1763" s="2">
-        <v>3</v>
-      </c>
-      <c r="E1763" s="5">
-        <v>0.5</v>
+        <v>7</v>
+      </c>
+      <c r="E1763" s="4">
+        <v>0.875</v>
       </c>
       <c r="F1763" s="2" t="s">
-        <v>2619</v>
+        <v>1112</v>
       </c>
       <c r="G1763" s="2" t="s">
-        <v>2620</v>
+        <v>231</v>
       </c>
       <c r="H1763" s="2" t="s">
-        <v>2621</v>
+        <v>2561</v>
       </c>
       <c r="I1763" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1763" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1763" s="2" t="s">
-        <v>2620</v>
+        <v>231</v>
       </c>
       <c r="L1763" s="2">
         <v>0</v>
@@ -85922,34 +86111,34 @@
         <v>46289</v>
       </c>
       <c r="B1764" s="2" t="s">
-        <v>179</v>
+        <v>670</v>
       </c>
       <c r="C1764" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1764" s="2">
-        <v>1</v>
-      </c>
-      <c r="E1764" s="4">
-        <v>0.1666667</v>
+        <v>7</v>
+      </c>
+      <c r="E1764" s="5">
+        <v>1</v>
       </c>
       <c r="F1764" s="2" t="s">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="G1764" s="2" t="s">
-        <v>1340</v>
+        <v>307</v>
       </c>
       <c r="H1764" s="2" t="s">
-        <v>2622</v>
+        <v>671</v>
       </c>
       <c r="I1764" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1764" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1764" s="2" t="s">
-        <v>1340</v>
+        <v>307</v>
       </c>
       <c r="L1764" s="2">
         <v>0</v>
@@ -85966,34 +86155,34 @@
         <v>46289</v>
       </c>
       <c r="B1765" s="2" t="s">
-        <v>250</v>
+        <v>29</v>
       </c>
       <c r="C1765" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1765" s="2">
         <v>5</v>
       </c>
-      <c r="D1765" s="2">
-        <v>0</v>
-      </c>
-      <c r="E1765" s="5">
-        <v>0</v>
+      <c r="E1765" s="4">
+        <v>0.71428570000000002</v>
       </c>
       <c r="F1765" s="2" t="s">
-        <v>2623</v>
+        <v>2562</v>
       </c>
       <c r="G1765" s="2" t="s">
-        <v>2624</v>
+        <v>228</v>
       </c>
       <c r="H1765" s="2" t="s">
-        <v>463</v>
+        <v>2563</v>
       </c>
       <c r="I1765" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1765" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1765" s="2" t="s">
-        <v>2624</v>
+        <v>228</v>
       </c>
       <c r="L1765" s="2">
         <v>0</v>
@@ -86010,25 +86199,25 @@
         <v>46289</v>
       </c>
       <c r="B1766" s="2" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="C1766" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1766" s="2">
-        <v>5</v>
-      </c>
-      <c r="E1766" s="5">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="E1766" s="4">
+        <v>0.14285709999999999</v>
       </c>
       <c r="F1766" s="2" t="s">
-        <v>2120</v>
+        <v>2635</v>
       </c>
       <c r="G1766" s="2" t="s">
-        <v>498</v>
+        <v>2616</v>
       </c>
       <c r="H1766" s="2" t="s">
-        <v>2625</v>
+        <v>2636</v>
       </c>
       <c r="I1766" s="2" t="s">
         <v>23</v>
@@ -86037,7 +86226,7 @@
         <v>19</v>
       </c>
       <c r="K1766" s="2" t="s">
-        <v>498</v>
+        <v>2616</v>
       </c>
       <c r="L1766" s="2">
         <v>0</v>
@@ -86054,34 +86243,34 @@
         <v>46289</v>
       </c>
       <c r="B1767" s="2" t="s">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="C1767" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1767" s="2">
         <v>5</v>
       </c>
-      <c r="D1767" s="2">
-        <v>2</v>
-      </c>
-      <c r="E1767" s="5">
-        <v>0.4</v>
+      <c r="E1767" s="4">
+        <v>0.71428570000000002</v>
       </c>
       <c r="F1767" s="2" t="s">
-        <v>1114</v>
+        <v>2564</v>
       </c>
       <c r="G1767" s="2" t="s">
-        <v>495</v>
+        <v>2565</v>
       </c>
       <c r="H1767" s="2" t="s">
-        <v>991</v>
+        <v>1445</v>
       </c>
       <c r="I1767" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1767" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1767" s="2" t="s">
-        <v>495</v>
+        <v>2565</v>
       </c>
       <c r="L1767" s="2">
         <v>0</v>
@@ -86098,34 +86287,34 @@
         <v>46289</v>
       </c>
       <c r="B1768" s="2" t="s">
-        <v>257</v>
+        <v>195</v>
       </c>
       <c r="C1768" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1768" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E1768" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1768" s="2" t="s">
-        <v>2626</v>
+        <v>2198</v>
       </c>
       <c r="G1768" s="2" t="s">
-        <v>523</v>
+        <v>684</v>
       </c>
       <c r="H1768" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="I1768" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1768" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1768" s="2" t="s">
-        <v>523</v>
+        <v>684</v>
       </c>
       <c r="L1768" s="2">
         <v>0</v>
@@ -86142,25 +86331,25 @@
         <v>46289</v>
       </c>
       <c r="B1769" s="2" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="C1769" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1769" s="2">
-        <v>3</v>
-      </c>
-      <c r="E1769" s="5">
-        <v>0.75</v>
+        <v>2</v>
+      </c>
+      <c r="E1769" s="4">
+        <v>0.3333333</v>
       </c>
       <c r="F1769" s="2" t="s">
-        <v>919</v>
+        <v>258</v>
       </c>
       <c r="G1769" s="2" t="s">
-        <v>2543</v>
+        <v>258</v>
       </c>
       <c r="H1769" s="2" t="s">
-        <v>1214</v>
+        <v>471</v>
       </c>
       <c r="I1769" s="2" t="s">
         <v>23</v>
@@ -86169,7 +86358,7 @@
         <v>19</v>
       </c>
       <c r="K1769" s="2" t="s">
-        <v>2543</v>
+        <v>258</v>
       </c>
       <c r="L1769" s="2">
         <v>0</v>
@@ -86186,34 +86375,34 @@
         <v>46289</v>
       </c>
       <c r="B1770" s="2" t="s">
-        <v>2627</v>
+        <v>211</v>
       </c>
       <c r="C1770" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1770" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1770" s="5">
         <v>0.5</v>
       </c>
       <c r="F1770" s="2" t="s">
-        <v>304</v>
+        <v>2566</v>
       </c>
       <c r="G1770" s="2" t="s">
-        <v>287</v>
+        <v>2567</v>
       </c>
       <c r="H1770" s="2" t="s">
-        <v>1451</v>
+        <v>2568</v>
       </c>
       <c r="I1770" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1770" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1770" s="2" t="s">
-        <v>287</v>
+        <v>2567</v>
       </c>
       <c r="L1770" s="2">
         <v>0</v>
@@ -86230,25 +86419,25 @@
         <v>46289</v>
       </c>
       <c r="B1771" s="2" t="s">
-        <v>183</v>
+        <v>250</v>
       </c>
       <c r="C1771" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1771" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1771" s="5">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F1771" s="2" t="s">
-        <v>2628</v>
+        <v>2569</v>
       </c>
       <c r="G1771" s="2" t="s">
-        <v>2629</v>
+        <v>2570</v>
       </c>
       <c r="H1771" s="2" t="s">
-        <v>535</v>
+        <v>463</v>
       </c>
       <c r="I1771" s="2" t="s">
         <v>23</v>
@@ -86257,7 +86446,7 @@
         <v>19</v>
       </c>
       <c r="K1771" s="2" t="s">
-        <v>2629</v>
+        <v>2570</v>
       </c>
       <c r="L1771" s="2">
         <v>0</v>
@@ -86274,34 +86463,34 @@
         <v>46289</v>
       </c>
       <c r="B1772" s="2" t="s">
-        <v>93</v>
+        <v>315</v>
       </c>
       <c r="C1772" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1772" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E1772" s="5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F1772" s="2" t="s">
-        <v>153</v>
+        <v>303</v>
       </c>
       <c r="G1772" s="2" t="s">
-        <v>153</v>
+        <v>284</v>
       </c>
       <c r="H1772" s="2" t="s">
-        <v>540</v>
+        <v>202</v>
       </c>
       <c r="I1772" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1772" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1772" s="2" t="s">
-        <v>153</v>
+        <v>284</v>
       </c>
       <c r="L1772" s="2">
         <v>0</v>
@@ -86318,34 +86507,34 @@
         <v>46289</v>
       </c>
       <c r="B1773" s="2" t="s">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="C1773" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D1773" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E1773" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1773" s="2" t="s">
-        <v>235</v>
+        <v>2120</v>
       </c>
       <c r="G1773" s="2" t="s">
-        <v>259</v>
+        <v>498</v>
       </c>
       <c r="H1773" s="2" t="s">
-        <v>495</v>
+        <v>2571</v>
       </c>
       <c r="I1773" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1773" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1773" s="2" t="s">
-        <v>259</v>
+        <v>498</v>
       </c>
       <c r="L1773" s="2">
         <v>0</v>
@@ -86362,34 +86551,34 @@
         <v>46289</v>
       </c>
       <c r="B1774" s="2" t="s">
-        <v>1360</v>
+        <v>257</v>
       </c>
       <c r="C1774" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1774" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1774" s="5">
         <v>1</v>
       </c>
       <c r="F1774" s="2" t="s">
-        <v>845</v>
+        <v>2572</v>
       </c>
       <c r="G1774" s="2" t="s">
-        <v>259</v>
+        <v>523</v>
       </c>
       <c r="H1774" s="2" t="s">
-        <v>2027</v>
+        <v>231</v>
       </c>
       <c r="I1774" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1774" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1774" s="2" t="s">
-        <v>259</v>
+        <v>523</v>
       </c>
       <c r="L1774" s="2">
         <v>0</v>
@@ -86406,34 +86595,34 @@
         <v>46289</v>
       </c>
       <c r="B1775" s="2" t="s">
-        <v>1095</v>
+        <v>2573</v>
       </c>
       <c r="C1775" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1775" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1775" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F1775" s="2" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
       <c r="G1775" s="2" t="s">
-        <v>153</v>
+        <v>287</v>
       </c>
       <c r="H1775" s="2" t="s">
-        <v>260</v>
+        <v>1451</v>
       </c>
       <c r="I1775" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1775" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1775" s="2" t="s">
-        <v>153</v>
+        <v>287</v>
       </c>
       <c r="L1775" s="2">
         <v>0</v>
@@ -86450,25 +86639,25 @@
         <v>46289</v>
       </c>
       <c r="B1776" s="2" t="s">
-        <v>550</v>
+        <v>517</v>
       </c>
       <c r="C1776" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1776" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1776" s="5">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F1776" s="2" t="s">
-        <v>2630</v>
+        <v>705</v>
       </c>
       <c r="G1776" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="H1776" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="H1776" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="I1776" s="2" t="s">
         <v>23</v>
@@ -86477,7 +86666,7 @@
         <v>19</v>
       </c>
       <c r="K1776" s="2" t="s">
-        <v>473</v>
+        <v>928</v>
       </c>
       <c r="L1776" s="2">
         <v>0</v>
@@ -86494,34 +86683,34 @@
         <v>46289</v>
       </c>
       <c r="B1777" s="2" t="s">
-        <v>325</v>
+        <v>53</v>
       </c>
       <c r="C1777" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1777" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1777" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1777" s="2" t="s">
-        <v>296</v>
+        <v>1648</v>
       </c>
       <c r="G1777" s="2" t="s">
-        <v>453</v>
+        <v>1342</v>
       </c>
       <c r="H1777" s="2" t="s">
-        <v>841</v>
+        <v>509</v>
       </c>
       <c r="I1777" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1777" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1777" s="2" t="s">
-        <v>453</v>
+        <v>1342</v>
       </c>
       <c r="L1777" s="2">
         <v>0</v>
@@ -86538,34 +86727,34 @@
         <v>46289</v>
       </c>
       <c r="B1778" s="2" t="s">
-        <v>275</v>
+        <v>93</v>
       </c>
       <c r="C1778" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1778" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1778" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F1778" s="2" t="s">
-        <v>276</v>
+        <v>153</v>
       </c>
       <c r="G1778" s="2" t="s">
-        <v>235</v>
+        <v>153</v>
       </c>
       <c r="H1778" s="2" t="s">
-        <v>277</v>
+        <v>540</v>
       </c>
       <c r="I1778" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1778" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1778" s="2" t="s">
-        <v>235</v>
+        <v>153</v>
       </c>
       <c r="L1778" s="2">
         <v>0</v>
@@ -86582,10 +86771,10 @@
         <v>46289</v>
       </c>
       <c r="B1779" s="2" t="s">
-        <v>271</v>
+        <v>529</v>
       </c>
       <c r="C1779" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1779" s="2">
         <v>0</v>
@@ -86594,13 +86783,13 @@
         <v>0</v>
       </c>
       <c r="F1779" s="2" t="s">
-        <v>991</v>
+        <v>1915</v>
       </c>
       <c r="G1779" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H1779" s="2" t="s">
-        <v>991</v>
+        <v>1915</v>
       </c>
       <c r="I1779" s="2" t="s">
         <v>23</v>
@@ -86626,34 +86815,34 @@
         <v>46289</v>
       </c>
       <c r="B1780" s="2" t="s">
-        <v>204</v>
+        <v>512</v>
       </c>
       <c r="C1780" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1780" s="2">
-        <v>1</v>
-      </c>
-      <c r="E1780" s="4">
-        <v>0.3333333</v>
+        <v>4</v>
+      </c>
+      <c r="E1780" s="5">
+        <v>1</v>
       </c>
       <c r="F1780" s="2" t="s">
-        <v>2631</v>
+        <v>700</v>
       </c>
       <c r="G1780" s="2" t="s">
-        <v>2632</v>
+        <v>324</v>
       </c>
       <c r="H1780" s="2" t="s">
-        <v>1813</v>
+        <v>304</v>
       </c>
       <c r="I1780" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1780" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1780" s="2" t="s">
-        <v>2632</v>
+        <v>324</v>
       </c>
       <c r="L1780" s="2">
         <v>0</v>
@@ -86670,25 +86859,25 @@
         <v>46289</v>
       </c>
       <c r="B1781" s="2" t="s">
-        <v>1361</v>
+        <v>152</v>
       </c>
       <c r="C1781" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1781" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1781" s="5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F1781" s="2" t="s">
-        <v>545</v>
+        <v>919</v>
       </c>
       <c r="G1781" s="2" t="s">
-        <v>258</v>
+        <v>2543</v>
       </c>
       <c r="H1781" s="2" t="s">
-        <v>297</v>
+        <v>1214</v>
       </c>
       <c r="I1781" s="2" t="s">
         <v>23</v>
@@ -86697,7 +86886,7 @@
         <v>19</v>
       </c>
       <c r="K1781" s="2" t="s">
-        <v>258</v>
+        <v>2543</v>
       </c>
       <c r="L1781" s="2">
         <v>0</v>
@@ -86714,34 +86903,34 @@
         <v>46289</v>
       </c>
       <c r="B1782" s="2" t="s">
-        <v>89</v>
+        <v>531</v>
       </c>
       <c r="C1782" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1782" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1782" s="5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F1782" s="2" t="s">
-        <v>303</v>
+        <v>2637</v>
       </c>
       <c r="G1782" s="2" t="s">
-        <v>453</v>
+        <v>324</v>
       </c>
       <c r="H1782" s="2" t="s">
-        <v>528</v>
+        <v>830</v>
       </c>
       <c r="I1782" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1782" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1782" s="2" t="s">
-        <v>453</v>
+        <v>324</v>
       </c>
       <c r="L1782" s="2">
         <v>0</v>
@@ -86758,34 +86947,34 @@
         <v>46289</v>
       </c>
       <c r="B1783" s="2" t="s">
-        <v>1479</v>
+        <v>1360</v>
       </c>
       <c r="C1783" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1783" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1783" s="5">
         <v>1</v>
       </c>
       <c r="F1783" s="2" t="s">
-        <v>545</v>
+        <v>845</v>
       </c>
       <c r="G1783" s="2" t="s">
-        <v>298</v>
+        <v>259</v>
       </c>
       <c r="H1783" s="2" t="s">
-        <v>232</v>
+        <v>2027</v>
       </c>
       <c r="I1783" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1783" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1783" s="2" t="s">
-        <v>298</v>
+        <v>259</v>
       </c>
       <c r="L1783" s="2">
         <v>0</v>
@@ -86802,34 +86991,34 @@
         <v>46289</v>
       </c>
       <c r="B1784" s="2" t="s">
-        <v>521</v>
+        <v>215</v>
       </c>
       <c r="C1784" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1784" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1784" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1784" s="2" t="s">
-        <v>304</v>
+        <v>235</v>
       </c>
       <c r="G1784" s="2" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="H1784" s="2" t="s">
-        <v>268</v>
+        <v>495</v>
       </c>
       <c r="I1784" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1784" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1784" s="2" t="s">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="L1784" s="2">
         <v>0</v>
@@ -86846,34 +87035,34 @@
         <v>46289</v>
       </c>
       <c r="B1785" s="2" t="s">
-        <v>77</v>
+        <v>1095</v>
       </c>
       <c r="C1785" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1785" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1785" s="5">
         <v>1</v>
       </c>
       <c r="F1785" s="2" t="s">
-        <v>2202</v>
+        <v>235</v>
       </c>
       <c r="G1785" s="2" t="s">
-        <v>2203</v>
+        <v>153</v>
       </c>
       <c r="H1785" s="2" t="s">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="I1785" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1785" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1785" s="2" t="s">
-        <v>2203</v>
+        <v>153</v>
       </c>
       <c r="L1785" s="2">
         <v>0</v>
@@ -86890,25 +87079,25 @@
         <v>46289</v>
       </c>
       <c r="B1786" s="2" t="s">
-        <v>670</v>
+        <v>275</v>
       </c>
       <c r="C1786" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1786" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1786" s="5">
         <v>1</v>
       </c>
       <c r="F1786" s="2" t="s">
-        <v>545</v>
+        <v>276</v>
       </c>
       <c r="G1786" s="2" t="s">
-        <v>293</v>
+        <v>235</v>
       </c>
       <c r="H1786" s="2" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="I1786" s="2" t="s">
         <v>18</v>
@@ -86917,7 +87106,7 @@
         <v>19</v>
       </c>
       <c r="K1786" s="2" t="s">
-        <v>293</v>
+        <v>235</v>
       </c>
       <c r="L1786" s="2">
         <v>0</v>
@@ -86934,34 +87123,34 @@
         <v>46289</v>
       </c>
       <c r="B1787" s="2" t="s">
-        <v>291</v>
+        <v>550</v>
       </c>
       <c r="C1787" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1787" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1787" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1787" s="2" t="s">
-        <v>284</v>
+        <v>2575</v>
       </c>
       <c r="G1787" s="2" t="s">
-        <v>268</v>
+        <v>473</v>
       </c>
       <c r="H1787" s="2" t="s">
-        <v>933</v>
+        <v>448</v>
       </c>
       <c r="I1787" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1787" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1787" s="2" t="s">
-        <v>268</v>
+        <v>473</v>
       </c>
       <c r="L1787" s="2">
         <v>0</v>
@@ -86978,34 +87167,34 @@
         <v>46289</v>
       </c>
       <c r="B1788" s="2" t="s">
-        <v>53</v>
+        <v>536</v>
       </c>
       <c r="C1788" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1788" s="2">
         <v>2</v>
       </c>
-      <c r="D1788" s="2">
-        <v>0</v>
-      </c>
-      <c r="E1788" s="5">
-        <v>0</v>
+      <c r="E1788" s="4">
+        <v>0.66666669999999995</v>
       </c>
       <c r="F1788" s="2" t="s">
-        <v>1818</v>
+        <v>284</v>
       </c>
       <c r="G1788" s="2" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="H1788" s="2" t="s">
-        <v>248</v>
+        <v>1106</v>
       </c>
       <c r="I1788" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1788" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1788" s="2" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="L1788" s="2">
         <v>0</v>
@@ -87022,25 +87211,25 @@
         <v>46289</v>
       </c>
       <c r="B1789" s="2" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="C1789" s="2">
         <v>2</v>
       </c>
       <c r="D1789" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1789" s="5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F1789" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G1789" s="2" t="s">
-        <v>504</v>
+        <v>153</v>
       </c>
       <c r="H1789" s="2" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="I1789" s="2" t="s">
         <v>28</v>
@@ -87049,7 +87238,7 @@
         <v>19</v>
       </c>
       <c r="K1789" s="2" t="s">
-        <v>504</v>
+        <v>153</v>
       </c>
       <c r="L1789" s="2">
         <v>0</v>
@@ -87066,7 +87255,7 @@
         <v>46289</v>
       </c>
       <c r="B1790" s="2" t="s">
-        <v>696</v>
+        <v>77</v>
       </c>
       <c r="C1790" s="2">
         <v>2</v>
@@ -87078,22 +87267,22 @@
         <v>1</v>
       </c>
       <c r="F1790" s="2" t="s">
-        <v>283</v>
+        <v>2202</v>
       </c>
       <c r="G1790" s="2" t="s">
-        <v>539</v>
+        <v>2203</v>
       </c>
       <c r="H1790" s="2" t="s">
-        <v>537</v>
+        <v>700</v>
       </c>
       <c r="I1790" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1790" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1790" s="2" t="s">
-        <v>539</v>
+        <v>2203</v>
       </c>
       <c r="L1790" s="2">
         <v>0</v>
@@ -87110,25 +87299,25 @@
         <v>46289</v>
       </c>
       <c r="B1791" s="2" t="s">
-        <v>201</v>
+        <v>1361</v>
       </c>
       <c r="C1791" s="2">
         <v>2</v>
       </c>
       <c r="D1791" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1791" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1791" s="2" t="s">
-        <v>838</v>
+        <v>545</v>
       </c>
       <c r="G1791" s="2" t="s">
-        <v>472</v>
+        <v>258</v>
       </c>
       <c r="H1791" s="2" t="s">
-        <v>539</v>
+        <v>297</v>
       </c>
       <c r="I1791" s="2" t="s">
         <v>23</v>
@@ -87137,7 +87326,7 @@
         <v>19</v>
       </c>
       <c r="K1791" s="2" t="s">
-        <v>472</v>
+        <v>258</v>
       </c>
       <c r="L1791" s="2">
         <v>0</v>
@@ -87154,34 +87343,34 @@
         <v>46289</v>
       </c>
       <c r="B1792" s="2" t="s">
-        <v>156</v>
+        <v>89</v>
       </c>
       <c r="C1792" s="2">
         <v>2</v>
       </c>
       <c r="D1792" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1792" s="5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F1792" s="2" t="s">
-        <v>202</v>
+        <v>303</v>
       </c>
       <c r="G1792" s="2" t="s">
-        <v>298</v>
+        <v>453</v>
       </c>
       <c r="H1792" s="2" t="s">
         <v>528</v>
       </c>
       <c r="I1792" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1792" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1792" s="2" t="s">
-        <v>298</v>
+        <v>453</v>
       </c>
       <c r="L1792" s="2">
         <v>0</v>
@@ -87198,34 +87387,34 @@
         <v>46289</v>
       </c>
       <c r="B1793" s="2" t="s">
-        <v>1233</v>
+        <v>291</v>
       </c>
       <c r="C1793" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1793" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1793" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1793" s="2" t="s">
-        <v>840</v>
+        <v>284</v>
       </c>
       <c r="G1793" s="2" t="s">
-        <v>19</v>
+        <v>268</v>
       </c>
       <c r="H1793" s="2" t="s">
-        <v>840</v>
+        <v>933</v>
       </c>
       <c r="I1793" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1793" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1793" s="2" t="s">
-        <v>19</v>
+        <v>268</v>
       </c>
       <c r="L1793" s="2">
         <v>0</v>
@@ -87242,25 +87431,25 @@
         <v>46289</v>
       </c>
       <c r="B1794" s="2" t="s">
-        <v>328</v>
+        <v>1479</v>
       </c>
       <c r="C1794" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1794" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1794" s="5">
         <v>1</v>
       </c>
       <c r="F1794" s="2" t="s">
-        <v>242</v>
+        <v>545</v>
       </c>
       <c r="G1794" s="2" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="H1794" s="2" t="s">
-        <v>321</v>
+        <v>232</v>
       </c>
       <c r="I1794" s="2" t="s">
         <v>23</v>
@@ -87269,7 +87458,7 @@
         <v>19</v>
       </c>
       <c r="K1794" s="2" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="L1794" s="2">
         <v>0</v>
@@ -87286,34 +87475,34 @@
         <v>46289</v>
       </c>
       <c r="B1795" s="2" t="s">
-        <v>198</v>
+        <v>696</v>
       </c>
       <c r="C1795" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1795" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1795" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1795" s="2" t="s">
-        <v>840</v>
+        <v>283</v>
       </c>
       <c r="G1795" s="2" t="s">
-        <v>19</v>
+        <v>539</v>
       </c>
       <c r="H1795" s="2" t="s">
-        <v>840</v>
+        <v>537</v>
       </c>
       <c r="I1795" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1795" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1795" s="2" t="s">
-        <v>19</v>
+        <v>539</v>
       </c>
       <c r="L1795" s="2">
         <v>0</v>
@@ -87330,10 +87519,10 @@
         <v>46289</v>
       </c>
       <c r="B1796" s="2" t="s">
-        <v>1115</v>
+        <v>201</v>
       </c>
       <c r="C1796" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1796" s="2">
         <v>0</v>
@@ -87342,22 +87531,22 @@
         <v>0</v>
       </c>
       <c r="F1796" s="2" t="s">
-        <v>698</v>
+        <v>838</v>
       </c>
       <c r="G1796" s="2" t="s">
-        <v>244</v>
+        <v>472</v>
       </c>
       <c r="H1796" s="2" t="s">
-        <v>471</v>
+        <v>539</v>
       </c>
       <c r="I1796" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1796" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1796" s="2" t="s">
-        <v>244</v>
+        <v>472</v>
       </c>
       <c r="L1796" s="2">
         <v>0</v>
@@ -87374,34 +87563,34 @@
         <v>46289</v>
       </c>
       <c r="B1797" s="2" t="s">
-        <v>41</v>
+        <v>156</v>
       </c>
       <c r="C1797" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1797" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1797" s="5">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F1797" s="2" t="s">
-        <v>276</v>
+        <v>202</v>
       </c>
       <c r="G1797" s="2" t="s">
-        <v>19</v>
+        <v>298</v>
       </c>
       <c r="H1797" s="2" t="s">
-        <v>276</v>
+        <v>528</v>
       </c>
       <c r="I1797" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1797" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1797" s="2" t="s">
-        <v>19</v>
+        <v>298</v>
       </c>
       <c r="L1797" s="2">
         <v>0</v>
@@ -87418,34 +87607,34 @@
         <v>46289</v>
       </c>
       <c r="B1798" s="2" t="s">
-        <v>2194</v>
+        <v>198</v>
       </c>
       <c r="C1798" s="2">
         <v>1</v>
       </c>
       <c r="D1798" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1798" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1798" s="2" t="s">
-        <v>286</v>
+        <v>840</v>
       </c>
       <c r="G1798" s="2" t="s">
-        <v>311</v>
+        <v>19</v>
       </c>
       <c r="H1798" s="2" t="s">
-        <v>208</v>
+        <v>840</v>
       </c>
       <c r="I1798" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1798" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1798" s="2" t="s">
-        <v>311</v>
+        <v>19</v>
       </c>
       <c r="L1798" s="2">
         <v>0</v>
@@ -87462,7 +87651,7 @@
         <v>46289</v>
       </c>
       <c r="B1799" s="2" t="s">
-        <v>230</v>
+        <v>330</v>
       </c>
       <c r="C1799" s="2">
         <v>1</v>
@@ -87474,22 +87663,22 @@
         <v>0</v>
       </c>
       <c r="F1799" s="2" t="s">
-        <v>538</v>
+        <v>286</v>
       </c>
       <c r="G1799" s="2" t="s">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="H1799" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="I1799" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1799" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1799" s="2" t="s">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="L1799" s="2">
         <v>0</v>
@@ -87506,34 +87695,34 @@
         <v>46289</v>
       </c>
       <c r="B1800" s="2" t="s">
-        <v>330</v>
+        <v>2194</v>
       </c>
       <c r="C1800" s="2">
         <v>1</v>
       </c>
       <c r="D1800" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1800" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1800" s="2" t="s">
         <v>286</v>
       </c>
       <c r="G1800" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="H1800" s="2" t="s">
-        <v>542</v>
+        <v>208</v>
       </c>
       <c r="I1800" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1800" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1800" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="L1800" s="2">
         <v>0</v>
@@ -87594,34 +87783,34 @@
         <v>46289</v>
       </c>
       <c r="B1802" s="2" t="s">
-        <v>299</v>
+        <v>328</v>
       </c>
       <c r="C1802" s="2">
         <v>1</v>
       </c>
       <c r="D1802" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1802" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1802" s="2" t="s">
-        <v>294</v>
+        <v>242</v>
       </c>
       <c r="G1802" s="2" t="s">
-        <v>254</v>
+        <v>309</v>
       </c>
       <c r="H1802" s="2" t="s">
-        <v>701</v>
+        <v>321</v>
       </c>
       <c r="I1802" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1802" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1802" s="2" t="s">
-        <v>254</v>
+        <v>309</v>
       </c>
       <c r="L1802" s="2">
         <v>0</v>
@@ -87638,42 +87827,3122 @@
         <v>46289</v>
       </c>
       <c r="B1803" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1803" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1803" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1803" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1803" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G1803" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H1803" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="I1803" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1803" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1803" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="L1803" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1803" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1803" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:14">
+      <c r="A1804" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1804" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1804" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1804" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1804" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1804" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="G1804" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1804" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="I1804" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1804" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1804" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1804" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1804" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1804" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:14">
+      <c r="A1805" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1805" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C1805" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1805" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1805" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1805" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="G1805" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1805" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="I1805" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1805" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1805" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1805" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1805" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1805" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:14">
+      <c r="A1806" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1806" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="C1803" s="2">
-        <v>1</v>
-      </c>
-      <c r="D1803" s="2">
-        <v>1</v>
-      </c>
-      <c r="E1803" s="5">
-        <v>1</v>
-      </c>
-      <c r="F1803" s="2" t="s">
+      <c r="C1806" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1806" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1806" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1806" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G1803" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1803" s="2" t="s">
+      <c r="G1806" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1806" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="I1803" s="2" t="s">
+      <c r="I1806" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J1803" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1803" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1803" s="2">
-        <v>0</v>
-      </c>
-      <c r="M1803" s="5">
-        <v>0</v>
-      </c>
-      <c r="N1803" s="2">
+      <c r="J1806" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1806" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1806" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1806" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1806" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:14">
+      <c r="A1807" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1807" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C1807" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1807" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1807" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1807" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="G1807" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H1807" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="I1807" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1807" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1807" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="L1807" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1807" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1807" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:14">
+      <c r="A1808" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B1808" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1808" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1808" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1808" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1808" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1808" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1808" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1808" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1808" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1808" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1808" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1808" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1808" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:14">
+      <c r="A1809" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1809" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1809" s="2">
+        <v>2866</v>
+      </c>
+      <c r="D1809" s="2">
+        <v>2741</v>
+      </c>
+      <c r="E1809" s="4">
+        <v>0.95638520000000005</v>
+      </c>
+      <c r="F1809" s="2" t="s">
+        <v>2638</v>
+      </c>
+      <c r="G1809" s="2" t="s">
+        <v>2639</v>
+      </c>
+      <c r="H1809" s="2" t="s">
+        <v>2640</v>
+      </c>
+      <c r="I1809" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1809" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1809" s="2" t="s">
+        <v>2639</v>
+      </c>
+      <c r="L1809" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1809" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1809" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:14">
+      <c r="A1810" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1810" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1810" s="2">
+        <v>2790</v>
+      </c>
+      <c r="D1810" s="2">
+        <v>2749</v>
+      </c>
+      <c r="E1810" s="4">
+        <v>0.98530470000000003</v>
+      </c>
+      <c r="F1810" s="2" t="s">
+        <v>2641</v>
+      </c>
+      <c r="G1810" s="2" t="s">
+        <v>2642</v>
+      </c>
+      <c r="H1810" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="I1810" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1810" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1810" s="2" t="s">
+        <v>2642</v>
+      </c>
+      <c r="L1810" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1810" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1810" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:14">
+      <c r="A1811" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1811" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C1811" s="2">
+        <v>1086</v>
+      </c>
+      <c r="D1811" s="2">
+        <v>1034</v>
+      </c>
+      <c r="E1811" s="4">
+        <v>0.95211789999999996</v>
+      </c>
+      <c r="F1811" s="2" t="s">
+        <v>2644</v>
+      </c>
+      <c r="G1811" s="2" t="s">
+        <v>2645</v>
+      </c>
+      <c r="H1811" s="2" t="s">
+        <v>2646</v>
+      </c>
+      <c r="I1811" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1811" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1811" s="2" t="s">
+        <v>2645</v>
+      </c>
+      <c r="L1811" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1811" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1811" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:14">
+      <c r="A1812" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1812" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C1812" s="2">
+        <v>721</v>
+      </c>
+      <c r="D1812" s="2">
+        <v>648</v>
+      </c>
+      <c r="E1812" s="4">
+        <v>0.89875170000000004</v>
+      </c>
+      <c r="F1812" s="2" t="s">
+        <v>2647</v>
+      </c>
+      <c r="G1812" s="2" t="s">
+        <v>2648</v>
+      </c>
+      <c r="H1812" s="2" t="s">
+        <v>2649</v>
+      </c>
+      <c r="I1812" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1812" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1812" s="2" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L1812" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1812" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1812" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:14">
+      <c r="A1813" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1813" s="2" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C1813" s="2">
+        <v>541</v>
+      </c>
+      <c r="D1813" s="2">
+        <v>532</v>
+      </c>
+      <c r="E1813" s="4">
+        <v>0.98336409999999996</v>
+      </c>
+      <c r="F1813" s="2" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G1813" s="2" t="s">
+        <v>2651</v>
+      </c>
+      <c r="H1813" s="2" t="s">
+        <v>2652</v>
+      </c>
+      <c r="I1813" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1813" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1813" s="2" t="s">
+        <v>2651</v>
+      </c>
+      <c r="L1813" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1813" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1813" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:14">
+      <c r="A1814" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1814" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1814" s="2">
+        <v>154</v>
+      </c>
+      <c r="D1814" s="2">
+        <v>22</v>
+      </c>
+      <c r="E1814" s="4">
+        <v>0.14285709999999999</v>
+      </c>
+      <c r="F1814" s="2" t="s">
+        <v>2653</v>
+      </c>
+      <c r="G1814" s="2" t="s">
+        <v>2654</v>
+      </c>
+      <c r="H1814" s="2" t="s">
+        <v>2655</v>
+      </c>
+      <c r="I1814" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1814" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1814" s="2" t="s">
+        <v>2654</v>
+      </c>
+      <c r="L1814" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1814" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1814" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:14">
+      <c r="A1815" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1815" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1815" s="2">
+        <v>120</v>
+      </c>
+      <c r="D1815" s="2">
+        <v>103</v>
+      </c>
+      <c r="E1815" s="4">
+        <v>0.85833329999999997</v>
+      </c>
+      <c r="F1815" s="2" t="s">
+        <v>2656</v>
+      </c>
+      <c r="G1815" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="H1815" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="I1815" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1815" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1815" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="L1815" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1815" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1815" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:14">
+      <c r="A1816" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1816" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1816" s="2">
+        <v>103</v>
+      </c>
+      <c r="D1816" s="2">
+        <v>93</v>
+      </c>
+      <c r="E1816" s="4">
+        <v>0.90291259999999995</v>
+      </c>
+      <c r="F1816" s="2" t="s">
+        <v>2659</v>
+      </c>
+      <c r="G1816" s="2" t="s">
+        <v>2660</v>
+      </c>
+      <c r="H1816" s="2" t="s">
+        <v>2661</v>
+      </c>
+      <c r="I1816" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1816" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1816" s="2" t="s">
+        <v>2660</v>
+      </c>
+      <c r="L1816" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1816" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1816" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:14">
+      <c r="A1817" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1817" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1817" s="2">
+        <v>80</v>
+      </c>
+      <c r="D1817" s="2">
+        <v>79</v>
+      </c>
+      <c r="E1817" s="4">
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="F1817" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="G1817" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="H1817" s="2" t="s">
+        <v>2663</v>
+      </c>
+      <c r="I1817" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1817" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1817" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="L1817" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1817" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1817" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:14">
+      <c r="A1818" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1818" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1818" s="2">
+        <v>56</v>
+      </c>
+      <c r="D1818" s="2">
+        <v>52</v>
+      </c>
+      <c r="E1818" s="4">
+        <v>0.92857140000000005</v>
+      </c>
+      <c r="F1818" s="2" t="s">
+        <v>2664</v>
+      </c>
+      <c r="G1818" s="2" t="s">
+        <v>2665</v>
+      </c>
+      <c r="H1818" s="2" t="s">
+        <v>2285</v>
+      </c>
+      <c r="I1818" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1818" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1818" s="2" t="s">
+        <v>2665</v>
+      </c>
+      <c r="L1818" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1818" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1818" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:14">
+      <c r="A1819" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1819" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C1819" s="2">
+        <v>33</v>
+      </c>
+      <c r="D1819" s="2">
+        <v>22</v>
+      </c>
+      <c r="E1819" s="4">
+        <v>0.66666669999999995</v>
+      </c>
+      <c r="F1819" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G1819" s="2" t="s">
+        <v>2666</v>
+      </c>
+      <c r="H1819" s="2" t="s">
+        <v>2667</v>
+      </c>
+      <c r="I1819" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1819" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1819" s="2" t="s">
+        <v>2666</v>
+      </c>
+      <c r="L1819" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1819" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1819" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:14">
+      <c r="A1820" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1820" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1820" s="2">
+        <v>32</v>
+      </c>
+      <c r="D1820" s="2">
+        <v>23</v>
+      </c>
+      <c r="E1820" s="4">
+        <v>0.71875</v>
+      </c>
+      <c r="F1820" s="2" t="s">
+        <v>2668</v>
+      </c>
+      <c r="G1820" s="2" t="s">
+        <v>2669</v>
+      </c>
+      <c r="H1820" s="2" t="s">
+        <v>2670</v>
+      </c>
+      <c r="I1820" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1820" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1820" s="2" t="s">
+        <v>2669</v>
+      </c>
+      <c r="L1820" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1820" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1820" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:14">
+      <c r="A1821" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1821" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1821" s="2">
+        <v>25</v>
+      </c>
+      <c r="D1821" s="2">
+        <v>23</v>
+      </c>
+      <c r="E1821" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="F1821" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="G1821" s="2" t="s">
+        <v>2671</v>
+      </c>
+      <c r="H1821" s="2" t="s">
+        <v>2055</v>
+      </c>
+      <c r="I1821" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1821" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1821" s="2" t="s">
+        <v>2671</v>
+      </c>
+      <c r="L1821" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1821" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1821" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:14">
+      <c r="A1822" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1822" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1822" s="2">
+        <v>15</v>
+      </c>
+      <c r="D1822" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1822" s="4">
+        <v>0.13333329999999999</v>
+      </c>
+      <c r="F1822" s="2" t="s">
+        <v>2672</v>
+      </c>
+      <c r="G1822" s="2" t="s">
+        <v>2673</v>
+      </c>
+      <c r="H1822" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="I1822" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1822" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1822" s="2" t="s">
+        <v>2673</v>
+      </c>
+      <c r="L1822" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1822" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1822" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:14">
+      <c r="A1823" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1823" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1823" s="2">
+        <v>14</v>
+      </c>
+      <c r="D1823" s="2">
+        <v>11</v>
+      </c>
+      <c r="E1823" s="4">
+        <v>0.78571429999999998</v>
+      </c>
+      <c r="F1823" s="2" t="s">
+        <v>2378</v>
+      </c>
+      <c r="G1823" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="H1823" s="2" t="s">
+        <v>2674</v>
+      </c>
+      <c r="I1823" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1823" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1823" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="L1823" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1823" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1823" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:14">
+      <c r="A1824" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1824" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1824" s="2">
+        <v>12</v>
+      </c>
+      <c r="D1824" s="2">
+        <v>12</v>
+      </c>
+      <c r="E1824" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1824" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="G1824" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1824" s="2" t="s">
+        <v>2675</v>
+      </c>
+      <c r="I1824" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1824" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1824" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="L1824" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1824" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1824" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:14">
+      <c r="A1825" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1825" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1825" s="2">
+        <v>12</v>
+      </c>
+      <c r="D1825" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1825" s="4">
+        <v>0.58333330000000005</v>
+      </c>
+      <c r="F1825" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1825" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H1825" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I1825" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1825" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1825" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="L1825" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1825" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1825" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:14">
+      <c r="A1826" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1826" s="2" t="s">
+        <v>2676</v>
+      </c>
+      <c r="C1826" s="2">
+        <v>11</v>
+      </c>
+      <c r="D1826" s="2">
+        <v>7</v>
+      </c>
+      <c r="E1826" s="4">
+        <v>0.63636360000000003</v>
+      </c>
+      <c r="F1826" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="G1826" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H1826" s="2" t="s">
+        <v>2630</v>
+      </c>
+      <c r="I1826" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1826" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1826" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="L1826" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1826" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1826" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:14">
+      <c r="A1827" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1827" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1827" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1827" s="2">
+        <v>10</v>
+      </c>
+      <c r="E1827" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1827" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G1827" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H1827" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="I1827" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1827" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1827" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="L1827" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1827" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1827" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:14">
+      <c r="A1828" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1828" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1828" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1828" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1828" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="F1828" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G1828" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H1828" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I1828" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1828" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1828" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="L1828" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1828" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1828" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:14">
+      <c r="A1829" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1829" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1829" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1829" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1829" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="F1829" s="2" t="s">
+        <v>2677</v>
+      </c>
+      <c r="G1829" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1829" s="2" t="s">
+        <v>2492</v>
+      </c>
+      <c r="I1829" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1829" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1829" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="L1829" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1829" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1829" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:14">
+      <c r="A1830" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1830" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1830" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1830" s="2">
+        <v>8</v>
+      </c>
+      <c r="E1830" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="F1830" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="G1830" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="H1830" s="2" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I1830" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1830" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1830" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="L1830" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1830" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1830" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:14">
+      <c r="A1831" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1831" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1831" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1831" s="2">
+        <v>9</v>
+      </c>
+      <c r="E1831" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1831" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="G1831" s="2" t="s">
+        <v>2285</v>
+      </c>
+      <c r="H1831" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1831" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1831" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1831" s="2" t="s">
+        <v>2285</v>
+      </c>
+      <c r="L1831" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1831" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1831" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:14">
+      <c r="A1832" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1832" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1832" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1832" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1832" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1832" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="G1832" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="H1832" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1832" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1832" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1832" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="L1832" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1832" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1832" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:14">
+      <c r="A1833" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1833" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1833" s="2">
+        <v>9</v>
+      </c>
+      <c r="D1833" s="2">
+        <v>6</v>
+      </c>
+      <c r="E1833" s="4">
+        <v>0.66666669999999995</v>
+      </c>
+      <c r="F1833" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1833" s="2" t="s">
+        <v>2678</v>
+      </c>
+      <c r="H1833" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="I1833" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1833" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1833" s="2" t="s">
+        <v>2678</v>
+      </c>
+      <c r="L1833" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1833" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1833" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:14">
+      <c r="A1834" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1834" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C1834" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1834" s="2">
+        <v>8</v>
+      </c>
+      <c r="E1834" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1834" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1834" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H1834" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1834" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1834" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1834" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L1834" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1834" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1834" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:14">
+      <c r="A1835" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1835" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1835" s="2">
+        <v>8</v>
+      </c>
+      <c r="D1835" s="2">
+        <v>6</v>
+      </c>
+      <c r="E1835" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F1835" s="2" t="s">
+        <v>2679</v>
+      </c>
+      <c r="G1835" s="2" t="s">
+        <v>2680</v>
+      </c>
+      <c r="H1835" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="I1835" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1835" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1835" s="2" t="s">
+        <v>2680</v>
+      </c>
+      <c r="L1835" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1835" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1835" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:14">
+      <c r="A1836" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1836" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1836" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1836" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1836" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1836" s="2" t="s">
+        <v>2248</v>
+      </c>
+      <c r="G1836" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H1836" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="I1836" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1836" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1836" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="L1836" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1836" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1836" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:14">
+      <c r="A1837" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1837" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1837" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1837" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1837" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1837" s="2" t="s">
+        <v>2681</v>
+      </c>
+      <c r="G1837" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1837" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I1837" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1837" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1837" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="L1837" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1837" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1837" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:14">
+      <c r="A1838" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1838" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1838" s="2">
+        <v>7</v>
+      </c>
+      <c r="D1838" s="2">
+        <v>5</v>
+      </c>
+      <c r="E1838" s="4">
+        <v>0.71428570000000002</v>
+      </c>
+      <c r="F1838" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="G1838" s="2" t="s">
+        <v>2682</v>
+      </c>
+      <c r="H1838" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1838" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1838" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1838" s="2" t="s">
+        <v>2682</v>
+      </c>
+      <c r="L1838" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1838" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1838" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:14">
+      <c r="A1839" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1839" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1839" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1839" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1839" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1839" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1839" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H1839" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="I1839" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1839" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1839" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L1839" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1839" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1839" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:14">
+      <c r="A1840" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1840" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1840" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1840" s="2">
+        <v>5</v>
+      </c>
+      <c r="E1840" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1840" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1840" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="H1840" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="I1840" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1840" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1840" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="L1840" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1840" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1840" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:14">
+      <c r="A1841" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1841" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1841" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1841" s="2">
+        <v>5</v>
+      </c>
+      <c r="E1841" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1841" s="2" t="s">
+        <v>2683</v>
+      </c>
+      <c r="G1841" s="2" t="s">
+        <v>2684</v>
+      </c>
+      <c r="H1841" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="I1841" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1841" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1841" s="2" t="s">
+        <v>2684</v>
+      </c>
+      <c r="L1841" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1841" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1841" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:14">
+      <c r="A1842" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1842" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1842" s="2">
+        <v>5</v>
+      </c>
+      <c r="D1842" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1842" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="F1842" s="2" t="s">
+        <v>2685</v>
+      </c>
+      <c r="G1842" s="2" t="s">
+        <v>2249</v>
+      </c>
+      <c r="H1842" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="I1842" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1842" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1842" s="2" t="s">
+        <v>2249</v>
+      </c>
+      <c r="L1842" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1842" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1842" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:14">
+      <c r="A1843" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1843" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1843" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1843" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1843" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F1843" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="G1843" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="H1843" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="I1843" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1843" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1843" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="L1843" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1843" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1843" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:14">
+      <c r="A1844" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1844" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1844" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1844" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1844" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1844" s="2" t="s">
+        <v>2686</v>
+      </c>
+      <c r="G1844" s="2" t="s">
+        <v>2687</v>
+      </c>
+      <c r="H1844" s="2" t="s">
+        <v>2370</v>
+      </c>
+      <c r="I1844" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1844" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1844" s="2" t="s">
+        <v>2687</v>
+      </c>
+      <c r="L1844" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1844" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1844" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:14">
+      <c r="A1845" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1845" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C1845" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1845" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1845" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1845" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="G1845" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1845" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I1845" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1845" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1845" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="L1845" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1845" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1845" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:14">
+      <c r="A1846" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1846" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1846" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1846" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1846" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1846" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1846" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1846" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="I1846" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1846" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1846" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1846" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1846" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1846" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:14">
+      <c r="A1847" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1847" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1847" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1847" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1847" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1847" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G1847" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H1847" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I1847" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1847" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1847" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="L1847" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1847" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1847" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:14">
+      <c r="A1848" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1848" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1848" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1848" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1848" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1848" s="2" t="s">
+        <v>2688</v>
+      </c>
+      <c r="G1848" s="2" t="s">
+        <v>2489</v>
+      </c>
+      <c r="H1848" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1848" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1848" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1848" s="2" t="s">
+        <v>2489</v>
+      </c>
+      <c r="L1848" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1848" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1848" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:14">
+      <c r="A1849" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1849" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C1849" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1849" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1849" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1849" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="G1849" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1849" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="I1849" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1849" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1849" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1849" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1849" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1849" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:14">
+      <c r="A1850" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1850" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1850" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1850" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1850" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="F1850" s="2" t="s">
+        <v>2689</v>
+      </c>
+      <c r="G1850" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="H1850" s="2" t="s">
+        <v>2690</v>
+      </c>
+      <c r="I1850" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1850" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1850" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="L1850" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1850" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1850" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:14">
+      <c r="A1851" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1851" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C1851" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1851" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1851" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1851" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="G1851" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="H1851" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="I1851" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1851" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1851" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="L1851" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1851" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1851" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:14">
+      <c r="A1852" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1852" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C1852" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1852" s="2">
+        <v>4</v>
+      </c>
+      <c r="E1852" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1852" s="2" t="s">
+        <v>2637</v>
+      </c>
+      <c r="G1852" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H1852" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="I1852" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1852" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1852" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="L1852" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1852" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1852" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:14">
+      <c r="A1853" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1853" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1853" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1853" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1853" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1853" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G1853" s="2" t="s">
+        <v>2691</v>
+      </c>
+      <c r="H1853" s="2" t="s">
+        <v>2692</v>
+      </c>
+      <c r="I1853" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1853" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1853" s="2" t="s">
+        <v>2691</v>
+      </c>
+      <c r="L1853" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1853" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1853" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:14">
+      <c r="A1854" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1854" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1854" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1854" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1854" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1854" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G1854" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1854" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="I1854" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1854" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1854" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="L1854" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1854" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1854" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:14">
+      <c r="A1855" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1855" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1855" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1855" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1855" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1855" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1855" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="H1855" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="I1855" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1855" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1855" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="L1855" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1855" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1855" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:14">
+      <c r="A1856" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1856" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1856" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1856" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1856" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1856" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G1856" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H1856" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1856" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1856" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1856" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="L1856" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1856" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1856" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:14">
+      <c r="A1857" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1857" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1857" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1857" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1857" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1857" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1857" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1857" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1857" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1857" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1857" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="L1857" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1857" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1857" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:14">
+      <c r="A1858" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1858" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C1858" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1858" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1858" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1858" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1858" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="H1858" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="I1858" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1858" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1858" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="L1858" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1858" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1858" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:14">
+      <c r="A1859" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1859" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1859" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1859" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1859" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1859" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1859" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="H1859" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1859" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1859" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1859" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="L1859" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1859" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1859" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:14">
+      <c r="A1860" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1860" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1860" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1860" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1860" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1860" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1860" s="2" t="s">
+        <v>2020</v>
+      </c>
+      <c r="H1860" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="I1860" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1860" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1860" s="2" t="s">
+        <v>2020</v>
+      </c>
+      <c r="L1860" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1860" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1860" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:14">
+      <c r="A1861" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1861" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1861" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1861" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1861" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1861" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G1861" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="H1861" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I1861" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1861" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1861" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="L1861" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1861" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1861" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:14">
+      <c r="A1862" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1862" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C1862" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1862" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1862" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1862" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1862" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="H1862" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1862" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1862" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1862" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="L1862" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1862" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1862" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:14">
+      <c r="A1863" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1863" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1863" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1863" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1863" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1863" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1863" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H1863" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="I1863" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1863" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1863" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="L1863" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1863" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1863" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:14">
+      <c r="A1864" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1864" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1864" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1864" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1864" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1864" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="G1864" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="H1864" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="I1864" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1864" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1864" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="L1864" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1864" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1864" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:14">
+      <c r="A1865" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1865" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1865" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1865" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1865" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1865" s="2" t="s">
+        <v>2693</v>
+      </c>
+      <c r="G1865" s="2" t="s">
+        <v>2694</v>
+      </c>
+      <c r="H1865" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I1865" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1865" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1865" s="2" t="s">
+        <v>2694</v>
+      </c>
+      <c r="L1865" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1865" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1865" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:14">
+      <c r="A1866" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1866" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1866" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1866" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1866" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1866" s="2" t="s">
+        <v>2381</v>
+      </c>
+      <c r="G1866" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1866" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1866" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1866" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1866" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1866" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1866" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1866" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:14">
+      <c r="A1867" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1867" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C1867" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1867" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1867" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1867" s="2" t="s">
+        <v>2575</v>
+      </c>
+      <c r="G1867" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="H1867" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="I1867" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1867" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1867" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="L1867" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1867" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1867" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:14">
+      <c r="A1868" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1868" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1868" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1868" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1868" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1868" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="G1868" s="2" t="s">
+        <v>2695</v>
+      </c>
+      <c r="H1868" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="I1868" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1868" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1868" s="2" t="s">
+        <v>2695</v>
+      </c>
+      <c r="L1868" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1868" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1868" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:14">
+      <c r="A1869" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1869" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C1869" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1869" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1869" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1869" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="G1869" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1869" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="I1869" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1869" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1869" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1869" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1869" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1869" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:14">
+      <c r="A1870" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1870" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C1870" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1870" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1870" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1870" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="G1870" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H1870" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="I1870" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1870" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1870" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="L1870" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1870" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1870" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:14">
+      <c r="A1871" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1871" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1871" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1871" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1871" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1871" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G1871" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1871" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="I1871" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1871" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1871" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1871" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1871" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1871" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:14">
+      <c r="A1872" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1872" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1872" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1872" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1872" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1872" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G1872" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H1872" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="I1872" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1872" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1872" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="L1872" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1872" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1872" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:14">
+      <c r="A1873" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1873" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1873" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1873" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1873" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1873" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G1873" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="H1873" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="I1873" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1873" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1873" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1873" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1873" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1873" s="2">
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\new clone\Salefile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DEB99CB-9AE1-4323-B1CF-24CADC902105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5A82E1-8085-4992-A0A5-A1BAD733C535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13118" uniqueCount="2696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13510" uniqueCount="2770">
   <si>
     <t>Date</t>
   </si>
@@ -7764,9 +7764,6 @@
     <t>Cyvora_HQ(Client)</t>
   </si>
   <si>
-    <t>0.0592 EUR</t>
-  </si>
-  <si>
     <t>0.0624 EUR</t>
   </si>
   <si>
@@ -7956,129 +7953,18 @@
     <t>0.0028 EUR</t>
   </si>
   <si>
-    <t>17.8785 EUR</t>
-  </si>
-  <si>
-    <t>10.7615 EUR</t>
-  </si>
-  <si>
-    <t>28.64 EUR</t>
-  </si>
-  <si>
-    <t>1.6723 EUR</t>
-  </si>
-  <si>
-    <t>20.5957 EUR</t>
-  </si>
-  <si>
-    <t>22.268 EUR</t>
-  </si>
-  <si>
-    <t>9.6189 EUR</t>
-  </si>
-  <si>
-    <t>0.1741 EUR</t>
-  </si>
-  <si>
-    <t>9.793 EUR</t>
-  </si>
-  <si>
-    <t>2.828 EUR</t>
-  </si>
-  <si>
-    <t>7.07 EUR</t>
-  </si>
-  <si>
-    <t>9.898 EUR</t>
-  </si>
-  <si>
-    <t>3.24 EUR</t>
-  </si>
-  <si>
-    <t>24.84 EUR</t>
-  </si>
-  <si>
-    <t>28.08 EUR</t>
-  </si>
-  <si>
-    <t>3.23801 EUR</t>
-  </si>
-  <si>
-    <t>0.71599 EUR</t>
-  </si>
-  <si>
-    <t>3.954 EUR</t>
-  </si>
-  <si>
-    <t>1.156 EUR</t>
-  </si>
-  <si>
-    <t>2.564 EUR</t>
-  </si>
-  <si>
-    <t>3.72 EUR</t>
-  </si>
-  <si>
-    <t>0.56465 EUR</t>
-  </si>
-  <si>
-    <t>0.45715 EUR</t>
-  </si>
-  <si>
-    <t>1.0218 EUR</t>
-  </si>
-  <si>
-    <t>2.048 EUR</t>
-  </si>
-  <si>
-    <t>3.168 EUR</t>
-  </si>
-  <si>
     <t>0.2352 EUR</t>
   </si>
   <si>
     <t>0.2688 EUR</t>
   </si>
   <si>
-    <t>1.65 EUR</t>
-  </si>
-  <si>
-    <t>1.716 EUR</t>
-  </si>
-  <si>
-    <t>0.654 EUR</t>
-  </si>
-  <si>
-    <t>1.5438 EUR</t>
-  </si>
-  <si>
-    <t>2.1978 EUR</t>
-  </si>
-  <si>
-    <t>1.4 EUR</t>
-  </si>
-  <si>
-    <t>0.2484 EUR</t>
-  </si>
-  <si>
-    <t>0.0716 EUR</t>
-  </si>
-  <si>
-    <t>0.2188 EUR</t>
-  </si>
-  <si>
     <t>0.0276 EUR</t>
   </si>
   <si>
     <t>TDNT_DIR(Client)</t>
   </si>
   <si>
-    <t>0.1224 EUR</t>
-  </si>
-  <si>
-    <t>0.03935 EUR</t>
-  </si>
-  <si>
     <t>0.0559 EUR</t>
   </si>
   <si>
@@ -8091,36 +7977,12 @@
     <t>0.0305 EUR</t>
   </si>
   <si>
-    <t>0.16647 EUR</t>
-  </si>
-  <si>
-    <t>0.10653 EUR</t>
-  </si>
-  <si>
     <t>0.0652 EUR</t>
   </si>
   <si>
-    <t>0.0083 EUR</t>
-  </si>
-  <si>
-    <t>0.0462 EUR</t>
-  </si>
-  <si>
     <t>0.3816 EUR</t>
   </si>
   <si>
-    <t>0.04826 EUR</t>
-  </si>
-  <si>
-    <t>0.10226 EUR</t>
-  </si>
-  <si>
-    <t>0.159 EUR</t>
-  </si>
-  <si>
-    <t>0.201 EUR</t>
-  </si>
-  <si>
     <t>0.00145 EUR</t>
   </si>
   <si>
@@ -8128,6 +7990,366 @@
   </si>
   <si>
     <t>0.0013 EUR</t>
+  </si>
+  <si>
+    <t>12.65921 EUR</t>
+  </si>
+  <si>
+    <t>109.38214 EUR</t>
+  </si>
+  <si>
+    <t>122.04135 EUR</t>
+  </si>
+  <si>
+    <t>21.5685 EUR</t>
+  </si>
+  <si>
+    <t>13.0215 EUR</t>
+  </si>
+  <si>
+    <t>34.59 EUR</t>
+  </si>
+  <si>
+    <t>1.6747 EUR</t>
+  </si>
+  <si>
+    <t>20.6253 EUR</t>
+  </si>
+  <si>
+    <t>22.3 EUR</t>
+  </si>
+  <si>
+    <t>11.03955 EUR</t>
+  </si>
+  <si>
+    <t>0.19345 EUR</t>
+  </si>
+  <si>
+    <t>11.233 EUR</t>
+  </si>
+  <si>
+    <t>3.212 EUR</t>
+  </si>
+  <si>
+    <t>8.03 EUR</t>
+  </si>
+  <si>
+    <t>11.242 EUR</t>
+  </si>
+  <si>
+    <t>28.152 EUR</t>
+  </si>
+  <si>
+    <t>31.824 EUR</t>
+  </si>
+  <si>
+    <t>0.7184 EUR</t>
+  </si>
+  <si>
+    <t>3.5966 EUR</t>
+  </si>
+  <si>
+    <t>4.315 EUR</t>
+  </si>
+  <si>
+    <t>11.4 EUR</t>
+  </si>
+  <si>
+    <t>11.856 EUR</t>
+  </si>
+  <si>
+    <t>3.28163 EUR</t>
+  </si>
+  <si>
+    <t>0.72238 EUR</t>
+  </si>
+  <si>
+    <t>4.004 EUR</t>
+  </si>
+  <si>
+    <t>1.373 EUR</t>
+  </si>
+  <si>
+    <t>2.905 EUR</t>
+  </si>
+  <si>
+    <t>4.278 EUR</t>
+  </si>
+  <si>
+    <t>0.56605 EUR</t>
+  </si>
+  <si>
+    <t>0.45755 EUR</t>
+  </si>
+  <si>
+    <t>1.0236 EUR</t>
+  </si>
+  <si>
+    <t>2.5088 EUR</t>
+  </si>
+  <si>
+    <t>1.372 EUR</t>
+  </si>
+  <si>
+    <t>3.8808 EUR</t>
+  </si>
+  <si>
+    <t>2.52 EUR</t>
+  </si>
+  <si>
+    <t>3.15 EUR</t>
+  </si>
+  <si>
+    <t>0.82232 EUR</t>
+  </si>
+  <si>
+    <t>1.9422 EUR</t>
+  </si>
+  <si>
+    <t>2.76452 EUR</t>
+  </si>
+  <si>
+    <t>Sprint_Direct(Client)</t>
+  </si>
+  <si>
+    <t>4.116 EUR</t>
+  </si>
+  <si>
+    <t>4.2 EUR</t>
+  </si>
+  <si>
+    <t>0.0745 EUR</t>
+  </si>
+  <si>
+    <t>0.1641 EUR</t>
+  </si>
+  <si>
+    <t>0.2386 EUR</t>
+  </si>
+  <si>
+    <t>0.5355 EUR</t>
+  </si>
+  <si>
+    <t>0.567 EUR</t>
+  </si>
+  <si>
+    <t>0.0703 EUR</t>
+  </si>
+  <si>
+    <t>0.1073 EUR</t>
+  </si>
+  <si>
+    <t>0.03605 EUR</t>
+  </si>
+  <si>
+    <t>0.05135 EUR</t>
+  </si>
+  <si>
+    <t>0.0874 EUR</t>
+  </si>
+  <si>
+    <t>0.816 EUR</t>
+  </si>
+  <si>
+    <t>0.0299 EUR</t>
+  </si>
+  <si>
+    <t>0.1824 EUR</t>
+  </si>
+  <si>
+    <t>0.1872 EUR</t>
+  </si>
+  <si>
+    <t>0.23688 EUR</t>
+  </si>
+  <si>
+    <t>0.18612 EUR</t>
+  </si>
+  <si>
+    <t>0.469 EUR</t>
+  </si>
+  <si>
+    <t>0.05198 EUR</t>
+  </si>
+  <si>
+    <t>0.15998 EUR</t>
+  </si>
+  <si>
+    <t>0.0474 EUR</t>
+  </si>
+  <si>
+    <t>19.8195 EUR</t>
+  </si>
+  <si>
+    <t>11.8305 EUR</t>
+  </si>
+  <si>
+    <t>31.65 EUR</t>
+  </si>
+  <si>
+    <t>28.2366 EUR</t>
+  </si>
+  <si>
+    <t>67.3054 EUR</t>
+  </si>
+  <si>
+    <t>95.542 EUR</t>
+  </si>
+  <si>
+    <t>10.166 EUR</t>
+  </si>
+  <si>
+    <t>20.332 EUR</t>
+  </si>
+  <si>
+    <t>10.06988 EUR</t>
+  </si>
+  <si>
+    <t>0.14513 EUR</t>
+  </si>
+  <si>
+    <t>10.215 EUR</t>
+  </si>
+  <si>
+    <t>1.2495 EUR</t>
+  </si>
+  <si>
+    <t>22.97 EUR</t>
+  </si>
+  <si>
+    <t>24.2195 EUR</t>
+  </si>
+  <si>
+    <t>1.456 EUR</t>
+  </si>
+  <si>
+    <t>3.64 EUR</t>
+  </si>
+  <si>
+    <t>5.096 EUR</t>
+  </si>
+  <si>
+    <t>0.996 EUR</t>
+  </si>
+  <si>
+    <t>48.804 EUR</t>
+  </si>
+  <si>
+    <t>49.8 EUR</t>
+  </si>
+  <si>
+    <t>0.1087 EUR</t>
+  </si>
+  <si>
+    <t>1.3113 EUR</t>
+  </si>
+  <si>
+    <t>1.42 EUR</t>
+  </si>
+  <si>
+    <t>0.666 EUR</t>
+  </si>
+  <si>
+    <t>5.106 EUR</t>
+  </si>
+  <si>
+    <t>5.772 EUR</t>
+  </si>
+  <si>
+    <t>4.8 EUR</t>
+  </si>
+  <si>
+    <t>5.3 EUR</t>
+  </si>
+  <si>
+    <t>0.5405 EUR</t>
+  </si>
+  <si>
+    <t>0.4395 EUR</t>
+  </si>
+  <si>
+    <t>2.0224 EUR</t>
+  </si>
+  <si>
+    <t>1.106 EUR</t>
+  </si>
+  <si>
+    <t>3.1284 EUR</t>
+  </si>
+  <si>
+    <t>1.14761 EUR</t>
+  </si>
+  <si>
+    <t>0.42239 EUR</t>
+  </si>
+  <si>
+    <t>1.57 EUR</t>
+  </si>
+  <si>
+    <t>1.122 EUR</t>
+  </si>
+  <si>
+    <t>3.008 EUR</t>
+  </si>
+  <si>
+    <t>4.13 EUR</t>
+  </si>
+  <si>
+    <t>0.85752 EUR</t>
+  </si>
+  <si>
+    <t>2.79972 EUR</t>
+  </si>
+  <si>
+    <t>1.82 EUR</t>
+  </si>
+  <si>
+    <t>1.5128 EUR</t>
+  </si>
+  <si>
+    <t>0.6572 EUR</t>
+  </si>
+  <si>
+    <t>2.17 EUR</t>
+  </si>
+  <si>
+    <t>0.55 EUR</t>
+  </si>
+  <si>
+    <t>0.07705 EUR</t>
+  </si>
+  <si>
+    <t>0.07515 EUR</t>
+  </si>
+  <si>
+    <t>0.1522 EUR</t>
+  </si>
+  <si>
+    <t>0.689 EUR</t>
+  </si>
+  <si>
+    <t>0.871 EUR</t>
+  </si>
+  <si>
+    <t>0.0676 EUR</t>
+  </si>
+  <si>
+    <t>0.0482 EUR</t>
+  </si>
+  <si>
+    <t>0.0626 EUR</t>
+  </si>
+  <si>
+    <t>0.0194 EUR</t>
+  </si>
+  <si>
+    <t>0.00435 EUR</t>
+  </si>
+  <si>
+    <t>0.0235 EUR</t>
+  </si>
+  <si>
+    <t>-0.002 EUR</t>
   </si>
 </sst>
 </file>
@@ -8516,7 +8738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1873"/>
+  <dimension ref="A1:N1929"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
@@ -84275,13 +84497,13 @@
         <v>0.63585309999999995</v>
       </c>
       <c r="F1722" s="2" t="s">
+        <v>2575</v>
+      </c>
+      <c r="G1722" s="2" t="s">
         <v>2576</v>
       </c>
-      <c r="G1722" s="2" t="s">
+      <c r="H1722" s="2" t="s">
         <v>2577</v>
-      </c>
-      <c r="H1722" s="2" t="s">
-        <v>2578</v>
       </c>
       <c r="I1722" s="2" t="s">
         <v>23</v>
@@ -84290,7 +84512,7 @@
         <v>19</v>
       </c>
       <c r="K1722" s="2" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="L1722" s="2">
         <v>0</v>
@@ -84319,13 +84541,13 @@
         <v>0.94479069999999998</v>
       </c>
       <c r="F1723" s="2" t="s">
+        <v>2578</v>
+      </c>
+      <c r="G1723" s="2" t="s">
         <v>2579</v>
       </c>
-      <c r="G1723" s="2" t="s">
+      <c r="H1723" s="2" t="s">
         <v>2580</v>
-      </c>
-      <c r="H1723" s="2" t="s">
-        <v>2581</v>
       </c>
       <c r="I1723" s="2" t="s">
         <v>28</v>
@@ -84334,7 +84556,7 @@
         <v>19</v>
       </c>
       <c r="K1723" s="2" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="L1723" s="2">
         <v>0</v>
@@ -84363,13 +84585,13 @@
         <v>0.88284289999999999</v>
       </c>
       <c r="F1724" s="2" t="s">
+        <v>2581</v>
+      </c>
+      <c r="G1724" s="2" t="s">
         <v>2582</v>
       </c>
-      <c r="G1724" s="2" t="s">
+      <c r="H1724" s="2" t="s">
         <v>2583</v>
-      </c>
-      <c r="H1724" s="2" t="s">
-        <v>2584</v>
       </c>
       <c r="I1724" s="2" t="s">
         <v>18</v>
@@ -84378,7 +84600,7 @@
         <v>19</v>
       </c>
       <c r="K1724" s="2" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="L1724" s="2">
         <v>0</v>
@@ -84407,13 +84629,13 @@
         <v>0.86680610000000002</v>
       </c>
       <c r="F1725" s="2" t="s">
+        <v>2584</v>
+      </c>
+      <c r="G1725" s="2" t="s">
         <v>2585</v>
       </c>
-      <c r="G1725" s="2" t="s">
+      <c r="H1725" s="2" t="s">
         <v>2586</v>
-      </c>
-      <c r="H1725" s="2" t="s">
-        <v>2587</v>
       </c>
       <c r="I1725" s="2" t="s">
         <v>28</v>
@@ -84422,7 +84644,7 @@
         <v>19</v>
       </c>
       <c r="K1725" s="2" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="L1725" s="2">
         <v>0</v>
@@ -84451,13 +84673,13 @@
         <v>0.98076920000000001</v>
       </c>
       <c r="F1726" s="2" t="s">
+        <v>2587</v>
+      </c>
+      <c r="G1726" s="2" t="s">
         <v>2588</v>
       </c>
-      <c r="G1726" s="2" t="s">
+      <c r="H1726" s="2" t="s">
         <v>2589</v>
-      </c>
-      <c r="H1726" s="2" t="s">
-        <v>2590</v>
       </c>
       <c r="I1726" s="2" t="s">
         <v>28</v>
@@ -84466,7 +84688,7 @@
         <v>19</v>
       </c>
       <c r="K1726" s="2" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="L1726" s="2">
         <v>0</v>
@@ -84495,13 +84717,13 @@
         <v>0.9701149</v>
       </c>
       <c r="F1727" s="2" t="s">
+        <v>2590</v>
+      </c>
+      <c r="G1727" s="2" t="s">
         <v>2591</v>
       </c>
-      <c r="G1727" s="2" t="s">
+      <c r="H1727" s="2" t="s">
         <v>2592</v>
-      </c>
-      <c r="H1727" s="2" t="s">
-        <v>2593</v>
       </c>
       <c r="I1727" s="2" t="s">
         <v>28</v>
@@ -84510,7 +84732,7 @@
         <v>19</v>
       </c>
       <c r="K1727" s="2" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="L1727" s="2">
         <v>0</v>
@@ -84539,13 +84761,13 @@
         <v>1</v>
       </c>
       <c r="F1728" s="2" t="s">
+        <v>2593</v>
+      </c>
+      <c r="G1728" s="2" t="s">
         <v>2594</v>
       </c>
-      <c r="G1728" s="2" t="s">
+      <c r="H1728" s="2" t="s">
         <v>2595</v>
-      </c>
-      <c r="H1728" s="2" t="s">
-        <v>2596</v>
       </c>
       <c r="I1728" s="2" t="s">
         <v>23</v>
@@ -84554,7 +84776,7 @@
         <v>19</v>
       </c>
       <c r="K1728" s="2" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="L1728" s="2">
         <v>0</v>
@@ -84627,13 +84849,13 @@
         <v>0.11309520000000001</v>
       </c>
       <c r="F1730" s="2" t="s">
+        <v>2596</v>
+      </c>
+      <c r="G1730" s="2" t="s">
         <v>2597</v>
       </c>
-      <c r="G1730" s="2" t="s">
+      <c r="H1730" s="2" t="s">
         <v>2598</v>
-      </c>
-      <c r="H1730" s="2" t="s">
-        <v>2599</v>
       </c>
       <c r="I1730" s="2" t="s">
         <v>23</v>
@@ -84642,7 +84864,7 @@
         <v>19</v>
       </c>
       <c r="K1730" s="2" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="L1730" s="2">
         <v>0</v>
@@ -84671,13 +84893,13 @@
         <v>1</v>
       </c>
       <c r="F1731" s="2" t="s">
+        <v>2599</v>
+      </c>
+      <c r="G1731" s="2" t="s">
         <v>2600</v>
       </c>
-      <c r="G1731" s="2" t="s">
+      <c r="H1731" s="2" t="s">
         <v>2601</v>
-      </c>
-      <c r="H1731" s="2" t="s">
-        <v>2602</v>
       </c>
       <c r="I1731" s="2" t="s">
         <v>18</v>
@@ -84686,7 +84908,7 @@
         <v>19</v>
       </c>
       <c r="K1731" s="2" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="L1731" s="2">
         <v>0</v>
@@ -84715,13 +84937,13 @@
         <v>0.94059409999999999</v>
       </c>
       <c r="F1732" s="2" t="s">
+        <v>2602</v>
+      </c>
+      <c r="G1732" s="2" t="s">
         <v>2603</v>
       </c>
-      <c r="G1732" s="2" t="s">
+      <c r="H1732" s="2" t="s">
         <v>2604</v>
-      </c>
-      <c r="H1732" s="2" t="s">
-        <v>2605</v>
       </c>
       <c r="I1732" s="2" t="s">
         <v>23</v>
@@ -84730,7 +84952,7 @@
         <v>19</v>
       </c>
       <c r="K1732" s="2" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="L1732" s="2">
         <v>0</v>
@@ -84759,10 +84981,10 @@
         <v>0.97959180000000001</v>
       </c>
       <c r="F1733" s="2" t="s">
+        <v>2605</v>
+      </c>
+      <c r="G1733" s="2" t="s">
         <v>2606</v>
-      </c>
-      <c r="G1733" s="2" t="s">
-        <v>2607</v>
       </c>
       <c r="H1733" s="2" t="s">
         <v>944</v>
@@ -84774,7 +84996,7 @@
         <v>19</v>
       </c>
       <c r="K1733" s="2" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="L1733" s="2">
         <v>0</v>
@@ -84803,13 +85025,13 @@
         <v>0.8823529</v>
       </c>
       <c r="F1734" s="2" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="G1734" s="2" t="s">
         <v>963</v>
       </c>
       <c r="H1734" s="2" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="I1734" s="2" t="s">
         <v>23</v>
@@ -84847,13 +85069,13 @@
         <v>0.94444439999999996</v>
       </c>
       <c r="F1735" s="2" t="s">
+        <v>2609</v>
+      </c>
+      <c r="G1735" s="2" t="s">
         <v>2610</v>
       </c>
-      <c r="G1735" s="2" t="s">
+      <c r="H1735" s="2" t="s">
         <v>2611</v>
-      </c>
-      <c r="H1735" s="2" t="s">
-        <v>2612</v>
       </c>
       <c r="I1735" s="2" t="s">
         <v>18</v>
@@ -84862,7 +85084,7 @@
         <v>19</v>
       </c>
       <c r="K1735" s="2" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="L1735" s="2">
         <v>0</v>
@@ -84891,13 +85113,13 @@
         <v>0.70833330000000005</v>
       </c>
       <c r="F1736" s="2" t="s">
+        <v>2612</v>
+      </c>
+      <c r="G1736" s="2" t="s">
         <v>2613</v>
       </c>
-      <c r="G1736" s="2" t="s">
+      <c r="H1736" s="2" t="s">
         <v>2614</v>
-      </c>
-      <c r="H1736" s="2" t="s">
-        <v>2615</v>
       </c>
       <c r="I1736" s="2" t="s">
         <v>28</v>
@@ -84906,7 +85128,7 @@
         <v>19</v>
       </c>
       <c r="K1736" s="2" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="L1736" s="2">
         <v>0</v>
@@ -84935,7 +85157,7 @@
         <v>0.97872340000000002</v>
       </c>
       <c r="F1737" s="2" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="G1737" s="2" t="s">
         <v>1060</v>
@@ -84979,13 +85201,13 @@
         <v>0.82222220000000001</v>
       </c>
       <c r="F1738" s="2" t="s">
+        <v>2616</v>
+      </c>
+      <c r="G1738" s="2" t="s">
         <v>2617</v>
       </c>
-      <c r="G1738" s="2" t="s">
+      <c r="H1738" s="2" t="s">
         <v>2618</v>
-      </c>
-      <c r="H1738" s="2" t="s">
-        <v>2619</v>
       </c>
       <c r="I1738" s="2" t="s">
         <v>18</v>
@@ -84994,7 +85216,7 @@
         <v>19</v>
       </c>
       <c r="K1738" s="2" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="L1738" s="2">
         <v>0</v>
@@ -85023,10 +85245,10 @@
         <v>0.96428570000000002</v>
       </c>
       <c r="F1739" s="2" t="s">
+        <v>2619</v>
+      </c>
+      <c r="G1739" s="2" t="s">
         <v>2620</v>
-      </c>
-      <c r="G1739" s="2" t="s">
-        <v>2621</v>
       </c>
       <c r="H1739" s="2" t="s">
         <v>1338</v>
@@ -85038,7 +85260,7 @@
         <v>19</v>
       </c>
       <c r="K1739" s="2" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="L1739" s="2">
         <v>0</v>
@@ -85070,7 +85292,7 @@
         <v>287</v>
       </c>
       <c r="G1740" s="2" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="H1740" s="2" t="s">
         <v>776</v>
@@ -85082,7 +85304,7 @@
         <v>19</v>
       </c>
       <c r="K1740" s="2" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="L1740" s="2">
         <v>0</v>
@@ -85199,7 +85421,7 @@
         <v>0</v>
       </c>
       <c r="F1743" s="2" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="G1743" s="2" t="s">
         <v>465</v>
@@ -85249,7 +85471,7 @@
         <v>1141</v>
       </c>
       <c r="H1744" s="2" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="I1744" s="2" t="s">
         <v>18</v>
@@ -85331,13 +85553,13 @@
         <v>0.6</v>
       </c>
       <c r="F1746" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="G1746" s="2" t="s">
         <v>2625</v>
       </c>
-      <c r="G1746" s="2" t="s">
+      <c r="H1746" s="2" t="s">
         <v>2626</v>
-      </c>
-      <c r="H1746" s="2" t="s">
-        <v>2627</v>
       </c>
       <c r="I1746" s="2" t="s">
         <v>18</v>
@@ -85346,7 +85568,7 @@
         <v>19</v>
       </c>
       <c r="K1746" s="2" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="L1746" s="2">
         <v>0</v>
@@ -85463,10 +85685,10 @@
         <v>0.15384619999999999</v>
       </c>
       <c r="F1749" s="2" t="s">
+        <v>2627</v>
+      </c>
+      <c r="G1749" s="2" t="s">
         <v>2628</v>
-      </c>
-      <c r="G1749" s="2" t="s">
-        <v>2629</v>
       </c>
       <c r="H1749" s="2" t="s">
         <v>1550</v>
@@ -85478,7 +85700,7 @@
         <v>19</v>
       </c>
       <c r="K1749" s="2" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="L1749" s="2">
         <v>0</v>
@@ -85554,7 +85776,7 @@
         <v>921</v>
       </c>
       <c r="G1751" s="2" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="H1751" s="2" t="s">
         <v>1611</v>
@@ -85566,7 +85788,7 @@
         <v>19</v>
       </c>
       <c r="K1751" s="2" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="L1751" s="2">
         <v>0</v>
@@ -85639,13 +85861,13 @@
         <v>0.5</v>
       </c>
       <c r="F1753" s="2" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="G1753" s="2" t="s">
         <v>1451</v>
       </c>
       <c r="H1753" s="2" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="I1753" s="2" t="s">
         <v>23</v>
@@ -85947,10 +86169,10 @@
         <v>0.75</v>
       </c>
       <c r="F1760" s="2" t="s">
+        <v>2632</v>
+      </c>
+      <c r="G1760" s="2" t="s">
         <v>2633</v>
-      </c>
-      <c r="G1760" s="2" t="s">
-        <v>2634</v>
       </c>
       <c r="H1760" s="2" t="s">
         <v>2552</v>
@@ -85962,7 +86184,7 @@
         <v>19</v>
       </c>
       <c r="K1760" s="2" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="L1760" s="2">
         <v>0</v>
@@ -86211,13 +86433,13 @@
         <v>0.14285709999999999</v>
       </c>
       <c r="F1766" s="2" t="s">
+        <v>2634</v>
+      </c>
+      <c r="G1766" s="2" t="s">
+        <v>2615</v>
+      </c>
+      <c r="H1766" s="2" t="s">
         <v>2635</v>
-      </c>
-      <c r="G1766" s="2" t="s">
-        <v>2616</v>
-      </c>
-      <c r="H1766" s="2" t="s">
-        <v>2636</v>
       </c>
       <c r="I1766" s="2" t="s">
         <v>23</v>
@@ -86226,7 +86448,7 @@
         <v>19</v>
       </c>
       <c r="K1766" s="2" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="L1766" s="2">
         <v>0</v>
@@ -86915,7 +87137,7 @@
         <v>0.75</v>
       </c>
       <c r="F1782" s="2" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="G1782" s="2" t="s">
         <v>324</v>
@@ -87135,7 +87357,7 @@
         <v>0</v>
       </c>
       <c r="F1787" s="2" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="G1787" s="2" t="s">
         <v>473</v>
@@ -88091,34 +88313,34 @@
         <v>46290</v>
       </c>
       <c r="B1809" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C1809" s="2">
-        <v>2866</v>
+        <v>46041</v>
       </c>
       <c r="D1809" s="2">
-        <v>2741</v>
+        <v>43358</v>
       </c>
       <c r="E1809" s="4">
-        <v>0.95638520000000005</v>
+        <v>0.9417259</v>
       </c>
       <c r="F1809" s="2" t="s">
-        <v>2638</v>
+        <v>2650</v>
       </c>
       <c r="G1809" s="2" t="s">
-        <v>2639</v>
+        <v>2651</v>
       </c>
       <c r="H1809" s="2" t="s">
-        <v>2640</v>
+        <v>2652</v>
       </c>
       <c r="I1809" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1809" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1809" s="2" t="s">
-        <v>2639</v>
+        <v>2651</v>
       </c>
       <c r="L1809" s="2">
         <v>0</v>
@@ -88135,34 +88357,34 @@
         <v>46290</v>
       </c>
       <c r="B1810" s="2" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C1810" s="2">
-        <v>2790</v>
+        <v>3460</v>
       </c>
       <c r="D1810" s="2">
-        <v>2749</v>
+        <v>3305</v>
       </c>
       <c r="E1810" s="4">
-        <v>0.98530470000000003</v>
+        <v>0.95520229999999995</v>
       </c>
       <c r="F1810" s="2" t="s">
-        <v>2641</v>
+        <v>2653</v>
       </c>
       <c r="G1810" s="2" t="s">
-        <v>2642</v>
+        <v>2654</v>
       </c>
       <c r="H1810" s="2" t="s">
-        <v>2643</v>
+        <v>2655</v>
       </c>
       <c r="I1810" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1810" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1810" s="2" t="s">
-        <v>2642</v>
+        <v>2654</v>
       </c>
       <c r="L1810" s="2">
         <v>0</v>
@@ -88179,34 +88401,34 @@
         <v>46290</v>
       </c>
       <c r="B1811" s="2" t="s">
-        <v>525</v>
+        <v>45</v>
       </c>
       <c r="C1811" s="2">
-        <v>1086</v>
+        <v>2794</v>
       </c>
       <c r="D1811" s="2">
-        <v>1034</v>
+        <v>2753</v>
       </c>
       <c r="E1811" s="4">
-        <v>0.95211789999999996</v>
+        <v>0.98532569999999997</v>
       </c>
       <c r="F1811" s="2" t="s">
-        <v>2644</v>
+        <v>2656</v>
       </c>
       <c r="G1811" s="2" t="s">
-        <v>2645</v>
+        <v>2657</v>
       </c>
       <c r="H1811" s="2" t="s">
-        <v>2646</v>
+        <v>2658</v>
       </c>
       <c r="I1811" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1811" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1811" s="2" t="s">
-        <v>2645</v>
+        <v>2657</v>
       </c>
       <c r="L1811" s="2">
         <v>0</v>
@@ -88223,34 +88445,34 @@
         <v>46290</v>
       </c>
       <c r="B1812" s="2" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="C1812" s="2">
-        <v>721</v>
+        <v>1246</v>
       </c>
       <c r="D1812" s="2">
-        <v>648</v>
+        <v>1188</v>
       </c>
       <c r="E1812" s="4">
-        <v>0.89875170000000004</v>
+        <v>0.95345100000000005</v>
       </c>
       <c r="F1812" s="2" t="s">
-        <v>2647</v>
+        <v>2659</v>
       </c>
       <c r="G1812" s="2" t="s">
-        <v>2648</v>
+        <v>2660</v>
       </c>
       <c r="H1812" s="2" t="s">
-        <v>2649</v>
+        <v>2661</v>
       </c>
       <c r="I1812" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1812" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1812" s="2" t="s">
-        <v>2648</v>
+        <v>2660</v>
       </c>
       <c r="L1812" s="2">
         <v>0</v>
@@ -88267,34 +88489,34 @@
         <v>46290</v>
       </c>
       <c r="B1813" s="2" t="s">
-        <v>2391</v>
+        <v>534</v>
       </c>
       <c r="C1813" s="2">
-        <v>541</v>
+        <v>817</v>
       </c>
       <c r="D1813" s="2">
-        <v>532</v>
+        <v>736</v>
       </c>
       <c r="E1813" s="4">
-        <v>0.98336409999999996</v>
+        <v>0.90085680000000001</v>
       </c>
       <c r="F1813" s="2" t="s">
-        <v>2650</v>
+        <v>2662</v>
       </c>
       <c r="G1813" s="2" t="s">
-        <v>2651</v>
+        <v>2663</v>
       </c>
       <c r="H1813" s="2" t="s">
-        <v>2652</v>
+        <v>2664</v>
       </c>
       <c r="I1813" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1813" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1813" s="2" t="s">
-        <v>2651</v>
+        <v>2663</v>
       </c>
       <c r="L1813" s="2">
         <v>0</v>
@@ -88311,34 +88533,34 @@
         <v>46290</v>
       </c>
       <c r="B1814" s="2" t="s">
-        <v>57</v>
+        <v>2391</v>
       </c>
       <c r="C1814" s="2">
-        <v>154</v>
+        <v>612</v>
       </c>
       <c r="D1814" s="2">
-        <v>22</v>
+        <v>602</v>
       </c>
       <c r="E1814" s="4">
-        <v>0.14285709999999999</v>
+        <v>0.98366010000000004</v>
       </c>
       <c r="F1814" s="2" t="s">
-        <v>2653</v>
+        <v>2154</v>
       </c>
       <c r="G1814" s="2" t="s">
-        <v>2654</v>
+        <v>2665</v>
       </c>
       <c r="H1814" s="2" t="s">
-        <v>2655</v>
+        <v>2666</v>
       </c>
       <c r="I1814" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1814" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1814" s="2" t="s">
-        <v>2654</v>
+        <v>2665</v>
       </c>
       <c r="L1814" s="2">
         <v>0</v>
@@ -88355,34 +88577,34 @@
         <v>46290</v>
       </c>
       <c r="B1815" s="2" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C1815" s="2">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="D1815" s="2">
-        <v>103</v>
+        <v>237</v>
       </c>
       <c r="E1815" s="4">
-        <v>0.85833329999999997</v>
+        <v>0.94799999999999995</v>
       </c>
       <c r="F1815" s="2" t="s">
-        <v>2656</v>
+        <v>2667</v>
       </c>
       <c r="G1815" s="2" t="s">
-        <v>2657</v>
+        <v>2668</v>
       </c>
       <c r="H1815" s="2" t="s">
-        <v>2658</v>
+        <v>2669</v>
       </c>
       <c r="I1815" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1815" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1815" s="2" t="s">
-        <v>2657</v>
+        <v>2668</v>
       </c>
       <c r="L1815" s="2">
         <v>0</v>
@@ -88399,34 +88621,34 @@
         <v>46290</v>
       </c>
       <c r="B1816" s="2" t="s">
-        <v>101</v>
+        <v>536</v>
       </c>
       <c r="C1816" s="2">
-        <v>103</v>
+        <v>228</v>
       </c>
       <c r="D1816" s="2">
-        <v>93</v>
+        <v>210</v>
       </c>
       <c r="E1816" s="4">
-        <v>0.90291259999999995</v>
+        <v>0.9210526</v>
       </c>
       <c r="F1816" s="2" t="s">
-        <v>2659</v>
+        <v>2015</v>
       </c>
       <c r="G1816" s="2" t="s">
-        <v>2660</v>
+        <v>2670</v>
       </c>
       <c r="H1816" s="2" t="s">
-        <v>2661</v>
+        <v>2671</v>
       </c>
       <c r="I1816" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1816" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1816" s="2" t="s">
-        <v>2660</v>
+        <v>2670</v>
       </c>
       <c r="L1816" s="2">
         <v>0</v>
@@ -88443,34 +88665,34 @@
         <v>46290</v>
       </c>
       <c r="B1817" s="2" t="s">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="C1817" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="D1817" s="2">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="E1817" s="4">
-        <v>0.98750000000000004</v>
+        <v>0.1410256</v>
       </c>
       <c r="F1817" s="2" t="s">
-        <v>2662</v>
+        <v>2672</v>
       </c>
       <c r="G1817" s="2" t="s">
-        <v>1640</v>
+        <v>2673</v>
       </c>
       <c r="H1817" s="2" t="s">
-        <v>2663</v>
+        <v>2674</v>
       </c>
       <c r="I1817" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1817" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1817" s="2" t="s">
-        <v>1640</v>
+        <v>2673</v>
       </c>
       <c r="L1817" s="2">
         <v>0</v>
@@ -88487,34 +88709,34 @@
         <v>46290</v>
       </c>
       <c r="B1818" s="2" t="s">
-        <v>124</v>
+        <v>49</v>
       </c>
       <c r="C1818" s="2">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D1818" s="2">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="E1818" s="4">
-        <v>0.92857140000000005</v>
+        <v>0.87681160000000002</v>
       </c>
       <c r="F1818" s="2" t="s">
-        <v>2664</v>
+        <v>2675</v>
       </c>
       <c r="G1818" s="2" t="s">
-        <v>2665</v>
+        <v>2676</v>
       </c>
       <c r="H1818" s="2" t="s">
-        <v>2285</v>
+        <v>2677</v>
       </c>
       <c r="I1818" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1818" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1818" s="2" t="s">
-        <v>2665</v>
+        <v>2676</v>
       </c>
       <c r="L1818" s="2">
         <v>0</v>
@@ -88531,34 +88753,34 @@
         <v>46290</v>
       </c>
       <c r="B1819" s="2" t="s">
-        <v>536</v>
+        <v>101</v>
       </c>
       <c r="C1819" s="2">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="D1819" s="2">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="E1819" s="4">
-        <v>0.66666669999999995</v>
+        <v>0.90384620000000004</v>
       </c>
       <c r="F1819" s="2" t="s">
-        <v>281</v>
+        <v>2678</v>
       </c>
       <c r="G1819" s="2" t="s">
-        <v>2666</v>
+        <v>2679</v>
       </c>
       <c r="H1819" s="2" t="s">
-        <v>2667</v>
+        <v>2680</v>
       </c>
       <c r="I1819" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1819" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1819" s="2" t="s">
-        <v>2666</v>
+        <v>2679</v>
       </c>
       <c r="L1819" s="2">
         <v>0</v>
@@ -88575,34 +88797,34 @@
         <v>46290</v>
       </c>
       <c r="B1820" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C1820" s="2">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D1820" s="2">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="E1820" s="4">
-        <v>0.71875</v>
+        <v>0.97959180000000001</v>
       </c>
       <c r="F1820" s="2" t="s">
-        <v>2668</v>
+        <v>2681</v>
       </c>
       <c r="G1820" s="2" t="s">
-        <v>2669</v>
+        <v>2682</v>
       </c>
       <c r="H1820" s="2" t="s">
-        <v>2670</v>
+        <v>2683</v>
       </c>
       <c r="I1820" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1820" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1820" s="2" t="s">
-        <v>2669</v>
+        <v>2682</v>
       </c>
       <c r="L1820" s="2">
         <v>0</v>
@@ -88619,34 +88841,34 @@
         <v>46290</v>
       </c>
       <c r="B1821" s="2" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C1821" s="2">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="D1821" s="2">
+        <v>52</v>
+      </c>
+      <c r="E1821" s="4">
+        <v>0.92857140000000005</v>
+      </c>
+      <c r="F1821" s="2" t="s">
+        <v>2637</v>
+      </c>
+      <c r="G1821" s="2" t="s">
+        <v>2638</v>
+      </c>
+      <c r="H1821" s="2" t="s">
+        <v>2285</v>
+      </c>
+      <c r="I1821" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E1821" s="5">
-        <v>0.92</v>
-      </c>
-      <c r="F1821" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="G1821" s="2" t="s">
-        <v>2671</v>
-      </c>
-      <c r="H1821" s="2" t="s">
-        <v>2055</v>
-      </c>
-      <c r="I1821" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="J1821" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1821" s="2" t="s">
-        <v>2671</v>
+        <v>2638</v>
       </c>
       <c r="L1821" s="2">
         <v>0</v>
@@ -88663,34 +88885,34 @@
         <v>46290</v>
       </c>
       <c r="B1822" s="2" t="s">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="C1822" s="2">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D1822" s="2">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E1822" s="4">
-        <v>0.13333329999999999</v>
+        <v>0.91111109999999995</v>
       </c>
       <c r="F1822" s="2" t="s">
-        <v>2672</v>
+        <v>762</v>
       </c>
       <c r="G1822" s="2" t="s">
-        <v>2673</v>
+        <v>2684</v>
       </c>
       <c r="H1822" s="2" t="s">
-        <v>1795</v>
+        <v>2685</v>
       </c>
       <c r="I1822" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1822" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1822" s="2" t="s">
-        <v>2673</v>
+        <v>2684</v>
       </c>
       <c r="L1822" s="2">
         <v>0</v>
@@ -88707,34 +88929,34 @@
         <v>46290</v>
       </c>
       <c r="B1823" s="2" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="C1823" s="2">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D1823" s="2">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E1823" s="4">
-        <v>0.78571429999999998</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="F1823" s="2" t="s">
-        <v>2378</v>
+        <v>2686</v>
       </c>
       <c r="G1823" s="2" t="s">
-        <v>947</v>
+        <v>2687</v>
       </c>
       <c r="H1823" s="2" t="s">
-        <v>2674</v>
+        <v>2688</v>
       </c>
       <c r="I1823" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1823" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1823" s="2" t="s">
-        <v>947</v>
+        <v>2687</v>
       </c>
       <c r="L1823" s="2">
         <v>0</v>
@@ -88751,34 +88973,34 @@
         <v>46290</v>
       </c>
       <c r="B1824" s="2" t="s">
-        <v>81</v>
+        <v>2689</v>
       </c>
       <c r="C1824" s="2">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D1824" s="2">
-        <v>12</v>
-      </c>
-      <c r="E1824" s="5">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="E1824" s="4">
+        <v>0.85714290000000004</v>
       </c>
       <c r="F1824" s="2" t="s">
-        <v>473</v>
+        <v>508</v>
       </c>
       <c r="G1824" s="2" t="s">
-        <v>276</v>
+        <v>2690</v>
       </c>
       <c r="H1824" s="2" t="s">
-        <v>2675</v>
+        <v>2691</v>
       </c>
       <c r="I1824" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J1824" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1824" s="2" t="s">
-        <v>276</v>
+        <v>2690</v>
       </c>
       <c r="L1824" s="2">
         <v>0</v>
@@ -88795,25 +89017,25 @@
         <v>46290</v>
       </c>
       <c r="B1825" s="2" t="s">
-        <v>308</v>
+        <v>168</v>
       </c>
       <c r="C1825" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D1825" s="2">
-        <v>7</v>
-      </c>
-      <c r="E1825" s="4">
-        <v>0.58333330000000005</v>
+        <v>22</v>
+      </c>
+      <c r="E1825" s="5">
+        <v>0.88</v>
       </c>
       <c r="F1825" s="2" t="s">
-        <v>276</v>
+        <v>2692</v>
       </c>
       <c r="G1825" s="2" t="s">
-        <v>1174</v>
+        <v>2693</v>
       </c>
       <c r="H1825" s="2" t="s">
-        <v>418</v>
+        <v>2694</v>
       </c>
       <c r="I1825" s="2" t="s">
         <v>18</v>
@@ -88822,7 +89044,7 @@
         <v>19</v>
       </c>
       <c r="K1825" s="2" t="s">
-        <v>1174</v>
+        <v>2693</v>
       </c>
       <c r="L1825" s="2">
         <v>0</v>
@@ -88839,34 +89061,34 @@
         <v>46290</v>
       </c>
       <c r="B1826" s="2" t="s">
-        <v>2676</v>
+        <v>308</v>
       </c>
       <c r="C1826" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D1826" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E1826" s="4">
-        <v>0.63636360000000003</v>
+        <v>0.57142859999999995</v>
       </c>
       <c r="F1826" s="2" t="s">
-        <v>803</v>
+        <v>923</v>
       </c>
       <c r="G1826" s="2" t="s">
-        <v>1068</v>
+        <v>2695</v>
       </c>
       <c r="H1826" s="2" t="s">
-        <v>2630</v>
+        <v>2696</v>
       </c>
       <c r="I1826" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J1826" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1826" s="2" t="s">
-        <v>1068</v>
+        <v>2695</v>
       </c>
       <c r="L1826" s="2">
         <v>0</v>
@@ -88883,25 +89105,25 @@
         <v>46290</v>
       </c>
       <c r="B1827" s="2" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="C1827" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D1827" s="2">
-        <v>10</v>
-      </c>
-      <c r="E1827" s="5">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="E1827" s="4">
+        <v>0.85714290000000004</v>
       </c>
       <c r="F1827" s="2" t="s">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="G1827" s="2" t="s">
-        <v>244</v>
+        <v>2697</v>
       </c>
       <c r="H1827" s="2" t="s">
-        <v>528</v>
+        <v>2698</v>
       </c>
       <c r="I1827" s="2" t="s">
         <v>18</v>
@@ -88910,7 +89132,7 @@
         <v>19</v>
       </c>
       <c r="K1827" s="2" t="s">
-        <v>244</v>
+        <v>2697</v>
       </c>
       <c r="L1827" s="2">
         <v>0</v>
@@ -88927,25 +89149,25 @@
         <v>46290</v>
       </c>
       <c r="B1828" s="2" t="s">
-        <v>409</v>
+        <v>144</v>
       </c>
       <c r="C1828" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D1828" s="2">
-        <v>4</v>
-      </c>
-      <c r="E1828" s="5">
-        <v>0.4</v>
+        <v>15</v>
+      </c>
+      <c r="E1828" s="4">
+        <v>0.78947369999999994</v>
       </c>
       <c r="F1828" s="2" t="s">
-        <v>298</v>
+        <v>2699</v>
       </c>
       <c r="G1828" s="2" t="s">
-        <v>203</v>
+        <v>2700</v>
       </c>
       <c r="H1828" s="2" t="s">
-        <v>1938</v>
+        <v>2701</v>
       </c>
       <c r="I1828" s="2" t="s">
         <v>18</v>
@@ -88954,7 +89176,7 @@
         <v>19</v>
       </c>
       <c r="K1828" s="2" t="s">
-        <v>203</v>
+        <v>2700</v>
       </c>
       <c r="L1828" s="2">
         <v>0</v>
@@ -88971,34 +89193,34 @@
         <v>46290</v>
       </c>
       <c r="B1829" s="2" t="s">
-        <v>183</v>
+        <v>2640</v>
       </c>
       <c r="C1829" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D1829" s="2">
-        <v>4</v>
-      </c>
-      <c r="E1829" s="5">
-        <v>0.4</v>
+        <v>8</v>
+      </c>
+      <c r="E1829" s="4">
+        <v>0.47058820000000001</v>
       </c>
       <c r="F1829" s="2" t="s">
-        <v>2677</v>
+        <v>991</v>
       </c>
       <c r="G1829" s="2" t="s">
-        <v>324</v>
+        <v>2702</v>
       </c>
       <c r="H1829" s="2" t="s">
-        <v>2492</v>
+        <v>1790</v>
       </c>
       <c r="I1829" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1829" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1829" s="2" t="s">
-        <v>324</v>
+        <v>2702</v>
       </c>
       <c r="L1829" s="2">
         <v>0</v>
@@ -89015,25 +89237,25 @@
         <v>46290</v>
       </c>
       <c r="B1830" s="2" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="C1830" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D1830" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1830" s="5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F1830" s="2" t="s">
-        <v>526</v>
+        <v>1915</v>
       </c>
       <c r="G1830" s="2" t="s">
-        <v>2574</v>
+        <v>648</v>
       </c>
       <c r="H1830" s="2" t="s">
-        <v>2199</v>
+        <v>2703</v>
       </c>
       <c r="I1830" s="2" t="s">
         <v>18</v>
@@ -89042,7 +89264,7 @@
         <v>19</v>
       </c>
       <c r="K1830" s="2" t="s">
-        <v>2574</v>
+        <v>648</v>
       </c>
       <c r="L1830" s="2">
         <v>0</v>
@@ -89059,25 +89281,25 @@
         <v>46290</v>
       </c>
       <c r="B1831" s="2" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="C1831" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D1831" s="2">
-        <v>9</v>
-      </c>
-      <c r="E1831" s="5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="E1831" s="4">
+        <v>0.30769229999999997</v>
       </c>
       <c r="F1831" s="2" t="s">
-        <v>453</v>
+        <v>2704</v>
       </c>
       <c r="G1831" s="2" t="s">
-        <v>2285</v>
+        <v>324</v>
       </c>
       <c r="H1831" s="2" t="s">
-        <v>116</v>
+        <v>2705</v>
       </c>
       <c r="I1831" s="2" t="s">
         <v>23</v>
@@ -89086,7 +89308,7 @@
         <v>19</v>
       </c>
       <c r="K1831" s="2" t="s">
-        <v>2285</v>
+        <v>324</v>
       </c>
       <c r="L1831" s="2">
         <v>0</v>
@@ -89103,34 +89325,34 @@
         <v>46290</v>
       </c>
       <c r="B1832" s="2" t="s">
-        <v>250</v>
+        <v>409</v>
       </c>
       <c r="C1832" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D1832" s="2">
-        <v>0</v>
-      </c>
-      <c r="E1832" s="5">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="E1832" s="4">
+        <v>0.53846150000000004</v>
       </c>
       <c r="F1832" s="2" t="s">
-        <v>811</v>
+        <v>290</v>
       </c>
       <c r="G1832" s="2" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="H1832" s="2" t="s">
-        <v>159</v>
+        <v>1076</v>
       </c>
       <c r="I1832" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1832" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1832" s="2" t="s">
-        <v>812</v>
+        <v>798</v>
       </c>
       <c r="L1832" s="2">
         <v>0</v>
@@ -89147,25 +89369,25 @@
         <v>46290</v>
       </c>
       <c r="B1833" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C1833" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D1833" s="2">
-        <v>6</v>
-      </c>
-      <c r="E1833" s="4">
-        <v>0.66666669999999995</v>
+        <v>12</v>
+      </c>
+      <c r="E1833" s="5">
+        <v>1</v>
       </c>
       <c r="F1833" s="2" t="s">
-        <v>142</v>
+        <v>519</v>
       </c>
       <c r="G1833" s="2" t="s">
-        <v>2678</v>
+        <v>930</v>
       </c>
       <c r="H1833" s="2" t="s">
-        <v>1574</v>
+        <v>193</v>
       </c>
       <c r="I1833" s="2" t="s">
         <v>18</v>
@@ -89174,7 +89396,7 @@
         <v>19</v>
       </c>
       <c r="K1833" s="2" t="s">
-        <v>2678</v>
+        <v>930</v>
       </c>
       <c r="L1833" s="2">
         <v>0</v>
@@ -89191,25 +89413,25 @@
         <v>46290</v>
       </c>
       <c r="B1834" s="2" t="s">
-        <v>1587</v>
+        <v>14</v>
       </c>
       <c r="C1834" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D1834" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1834" s="5">
         <v>1</v>
       </c>
       <c r="F1834" s="2" t="s">
-        <v>304</v>
+        <v>254</v>
       </c>
       <c r="G1834" s="2" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="H1834" s="2" t="s">
-        <v>232</v>
+        <v>528</v>
       </c>
       <c r="I1834" s="2" t="s">
         <v>18</v>
@@ -89218,7 +89440,7 @@
         <v>19</v>
       </c>
       <c r="K1834" s="2" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="L1834" s="2">
         <v>0</v>
@@ -89235,25 +89457,25 @@
         <v>46290</v>
       </c>
       <c r="B1835" s="2" t="s">
-        <v>211</v>
+        <v>65</v>
       </c>
       <c r="C1835" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D1835" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E1835" s="5">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F1835" s="2" t="s">
-        <v>2679</v>
+        <v>202</v>
       </c>
       <c r="G1835" s="2" t="s">
-        <v>2680</v>
+        <v>499</v>
       </c>
       <c r="H1835" s="2" t="s">
-        <v>249</v>
+        <v>210</v>
       </c>
       <c r="I1835" s="2" t="s">
         <v>18</v>
@@ -89262,7 +89484,7 @@
         <v>19</v>
       </c>
       <c r="K1835" s="2" t="s">
-        <v>2680</v>
+        <v>499</v>
       </c>
       <c r="L1835" s="2">
         <v>0</v>
@@ -89279,34 +89501,34 @@
         <v>46290</v>
       </c>
       <c r="B1836" s="2" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="C1836" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D1836" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E1836" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1836" s="2" t="s">
-        <v>2248</v>
+        <v>453</v>
       </c>
       <c r="G1836" s="2" t="s">
-        <v>1209</v>
+        <v>2285</v>
       </c>
       <c r="H1836" s="2" t="s">
-        <v>1337</v>
+        <v>116</v>
       </c>
       <c r="I1836" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1836" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1836" s="2" t="s">
-        <v>1209</v>
+        <v>2285</v>
       </c>
       <c r="L1836" s="2">
         <v>0</v>
@@ -89323,10 +89545,10 @@
         <v>46290</v>
       </c>
       <c r="B1837" s="2" t="s">
-        <v>152</v>
+        <v>250</v>
       </c>
       <c r="C1837" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D1837" s="2">
         <v>0</v>
@@ -89335,13 +89557,13 @@
         <v>0</v>
       </c>
       <c r="F1837" s="2" t="s">
-        <v>2681</v>
+        <v>811</v>
       </c>
       <c r="G1837" s="2" t="s">
-        <v>473</v>
+        <v>812</v>
       </c>
       <c r="H1837" s="2" t="s">
-        <v>199</v>
+        <v>159</v>
       </c>
       <c r="I1837" s="2" t="s">
         <v>23</v>
@@ -89350,7 +89572,7 @@
         <v>19</v>
       </c>
       <c r="K1837" s="2" t="s">
-        <v>473</v>
+        <v>812</v>
       </c>
       <c r="L1837" s="2">
         <v>0</v>
@@ -89367,25 +89589,25 @@
         <v>46290</v>
       </c>
       <c r="B1838" s="2" t="s">
-        <v>302</v>
+        <v>1587</v>
       </c>
       <c r="C1838" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1838" s="2">
-        <v>5</v>
-      </c>
-      <c r="E1838" s="4">
-        <v>0.71428570000000002</v>
+        <v>8</v>
+      </c>
+      <c r="E1838" s="5">
+        <v>1</v>
       </c>
       <c r="F1838" s="2" t="s">
-        <v>702</v>
+        <v>304</v>
       </c>
       <c r="G1838" s="2" t="s">
-        <v>2682</v>
+        <v>258</v>
       </c>
       <c r="H1838" s="2" t="s">
-        <v>153</v>
+        <v>232</v>
       </c>
       <c r="I1838" s="2" t="s">
         <v>18</v>
@@ -89394,7 +89616,7 @@
         <v>19</v>
       </c>
       <c r="K1838" s="2" t="s">
-        <v>2682</v>
+        <v>258</v>
       </c>
       <c r="L1838" s="2">
         <v>0</v>
@@ -89411,34 +89633,34 @@
         <v>46290</v>
       </c>
       <c r="B1839" s="2" t="s">
-        <v>220</v>
+        <v>61</v>
       </c>
       <c r="C1839" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D1839" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E1839" s="5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F1839" s="2" t="s">
-        <v>258</v>
+        <v>2706</v>
       </c>
       <c r="G1839" s="2" t="s">
-        <v>258</v>
+        <v>2707</v>
       </c>
       <c r="H1839" s="2" t="s">
-        <v>471</v>
+        <v>2527</v>
       </c>
       <c r="I1839" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1839" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1839" s="2" t="s">
-        <v>258</v>
+        <v>2707</v>
       </c>
       <c r="L1839" s="2">
         <v>0</v>
@@ -89455,25 +89677,25 @@
         <v>46290</v>
       </c>
       <c r="B1840" s="2" t="s">
-        <v>65</v>
+        <v>211</v>
       </c>
       <c r="C1840" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D1840" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1840" s="5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F1840" s="2" t="s">
-        <v>296</v>
+        <v>2641</v>
       </c>
       <c r="G1840" s="2" t="s">
-        <v>503</v>
+        <v>2642</v>
       </c>
       <c r="H1840" s="2" t="s">
-        <v>449</v>
+        <v>249</v>
       </c>
       <c r="I1840" s="2" t="s">
         <v>18</v>
@@ -89482,7 +89704,7 @@
         <v>19</v>
       </c>
       <c r="K1840" s="2" t="s">
-        <v>503</v>
+        <v>2642</v>
       </c>
       <c r="L1840" s="2">
         <v>0</v>
@@ -89499,25 +89721,25 @@
         <v>46290</v>
       </c>
       <c r="B1841" s="2" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="C1841" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1841" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1841" s="5">
         <v>1</v>
       </c>
       <c r="F1841" s="2" t="s">
-        <v>2683</v>
+        <v>1224</v>
       </c>
       <c r="G1841" s="2" t="s">
-        <v>2684</v>
+        <v>435</v>
       </c>
       <c r="H1841" s="2" t="s">
-        <v>649</v>
+        <v>2708</v>
       </c>
       <c r="I1841" s="2" t="s">
         <v>28</v>
@@ -89526,7 +89748,7 @@
         <v>19</v>
       </c>
       <c r="K1841" s="2" t="s">
-        <v>2684</v>
+        <v>435</v>
       </c>
       <c r="L1841" s="2">
         <v>0</v>
@@ -89543,25 +89765,25 @@
         <v>46290</v>
       </c>
       <c r="B1842" s="2" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="C1842" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D1842" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1842" s="5">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F1842" s="2" t="s">
-        <v>2685</v>
+        <v>2248</v>
       </c>
       <c r="G1842" s="2" t="s">
-        <v>2249</v>
+        <v>1209</v>
       </c>
       <c r="H1842" s="2" t="s">
-        <v>429</v>
+        <v>1337</v>
       </c>
       <c r="I1842" s="2" t="s">
         <v>18</v>
@@ -89570,7 +89792,7 @@
         <v>19</v>
       </c>
       <c r="K1842" s="2" t="s">
-        <v>2249</v>
+        <v>1209</v>
       </c>
       <c r="L1842" s="2">
         <v>0</v>
@@ -89587,25 +89809,25 @@
         <v>46290</v>
       </c>
       <c r="B1843" s="2" t="s">
-        <v>237</v>
+        <v>152</v>
       </c>
       <c r="C1843" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1843" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E1843" s="5">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F1843" s="2" t="s">
-        <v>474</v>
+        <v>2643</v>
       </c>
       <c r="G1843" s="2" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="H1843" s="2" t="s">
-        <v>929</v>
+        <v>199</v>
       </c>
       <c r="I1843" s="2" t="s">
         <v>23</v>
@@ -89614,7 +89836,7 @@
         <v>19</v>
       </c>
       <c r="K1843" s="2" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="L1843" s="2">
         <v>0</v>
@@ -89631,34 +89853,34 @@
         <v>46290</v>
       </c>
       <c r="B1844" s="2" t="s">
-        <v>204</v>
+        <v>302</v>
       </c>
       <c r="C1844" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1844" s="2">
-        <v>4</v>
-      </c>
-      <c r="E1844" s="5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="E1844" s="4">
+        <v>0.71428570000000002</v>
       </c>
       <c r="F1844" s="2" t="s">
-        <v>2686</v>
+        <v>702</v>
       </c>
       <c r="G1844" s="2" t="s">
-        <v>2687</v>
+        <v>2644</v>
       </c>
       <c r="H1844" s="2" t="s">
-        <v>2370</v>
+        <v>153</v>
       </c>
       <c r="I1844" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1844" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1844" s="2" t="s">
-        <v>2687</v>
+        <v>2644</v>
       </c>
       <c r="L1844" s="2">
         <v>0</v>
@@ -89675,34 +89897,34 @@
         <v>46290</v>
       </c>
       <c r="B1845" s="2" t="s">
-        <v>512</v>
+        <v>220</v>
       </c>
       <c r="C1845" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1845" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1845" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F1845" s="2" t="s">
-        <v>700</v>
+        <v>258</v>
       </c>
       <c r="G1845" s="2" t="s">
-        <v>324</v>
+        <v>258</v>
       </c>
       <c r="H1845" s="2" t="s">
-        <v>304</v>
+        <v>471</v>
       </c>
       <c r="I1845" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1845" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1845" s="2" t="s">
-        <v>324</v>
+        <v>258</v>
       </c>
       <c r="L1845" s="2">
         <v>0</v>
@@ -89719,28 +89941,28 @@
         <v>46290</v>
       </c>
       <c r="B1846" s="2" t="s">
-        <v>234</v>
+        <v>136</v>
       </c>
       <c r="C1846" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1846" s="2">
-        <v>2</v>
-      </c>
-      <c r="E1846" s="5">
-        <v>0.5</v>
+        <v>5</v>
+      </c>
+      <c r="E1846" s="4">
+        <v>0.83333330000000005</v>
       </c>
       <c r="F1846" s="2" t="s">
-        <v>498</v>
+        <v>258</v>
       </c>
       <c r="G1846" s="2" t="s">
         <v>153</v>
       </c>
       <c r="H1846" s="2" t="s">
-        <v>448</v>
+        <v>508</v>
       </c>
       <c r="I1846" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1846" s="2" t="s">
         <v>19</v>
@@ -89763,25 +89985,25 @@
         <v>46290</v>
       </c>
       <c r="B1847" s="2" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="C1847" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D1847" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1847" s="5">
         <v>0.5</v>
       </c>
       <c r="F1847" s="2" t="s">
-        <v>504</v>
+        <v>2709</v>
       </c>
       <c r="G1847" s="2" t="s">
-        <v>1795</v>
+        <v>505</v>
       </c>
       <c r="H1847" s="2" t="s">
-        <v>1203</v>
+        <v>2710</v>
       </c>
       <c r="I1847" s="2" t="s">
         <v>28</v>
@@ -89790,7 +90012,7 @@
         <v>19</v>
       </c>
       <c r="K1847" s="2" t="s">
-        <v>1795</v>
+        <v>505</v>
       </c>
       <c r="L1847" s="2">
         <v>0</v>
@@ -89807,34 +90029,34 @@
         <v>46290</v>
       </c>
       <c r="B1848" s="2" t="s">
-        <v>521</v>
+        <v>204</v>
       </c>
       <c r="C1848" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1848" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E1848" s="5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F1848" s="2" t="s">
-        <v>2688</v>
+        <v>2551</v>
       </c>
       <c r="G1848" s="2" t="s">
-        <v>2489</v>
+        <v>2711</v>
       </c>
       <c r="H1848" s="2" t="s">
-        <v>116</v>
+        <v>267</v>
       </c>
       <c r="I1848" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1848" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1848" s="2" t="s">
-        <v>2489</v>
+        <v>2711</v>
       </c>
       <c r="L1848" s="2">
         <v>0</v>
@@ -89851,34 +90073,34 @@
         <v>46290</v>
       </c>
       <c r="B1849" s="2" t="s">
-        <v>529</v>
+        <v>97</v>
       </c>
       <c r="C1849" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D1849" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1849" s="5">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F1849" s="2" t="s">
-        <v>1915</v>
+        <v>2645</v>
       </c>
       <c r="G1849" s="2" t="s">
-        <v>19</v>
+        <v>2249</v>
       </c>
       <c r="H1849" s="2" t="s">
-        <v>1915</v>
+        <v>429</v>
       </c>
       <c r="I1849" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1849" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1849" s="2" t="s">
-        <v>19</v>
+        <v>2249</v>
       </c>
       <c r="L1849" s="2">
         <v>0</v>
@@ -89895,34 +90117,34 @@
         <v>46290</v>
       </c>
       <c r="B1850" s="2" t="s">
-        <v>29</v>
+        <v>237</v>
       </c>
       <c r="C1850" s="2">
         <v>4</v>
       </c>
       <c r="D1850" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1850" s="5">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="F1850" s="2" t="s">
-        <v>2689</v>
+        <v>474</v>
       </c>
       <c r="G1850" s="2" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="H1850" s="2" t="s">
-        <v>2690</v>
+        <v>929</v>
       </c>
       <c r="I1850" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1850" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1850" s="2" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="L1850" s="2">
         <v>0</v>
@@ -89939,25 +90161,25 @@
         <v>46290</v>
       </c>
       <c r="B1851" s="2" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C1851" s="2">
         <v>4</v>
       </c>
       <c r="D1851" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1851" s="5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F1851" s="2" t="s">
-        <v>705</v>
+        <v>1915</v>
       </c>
       <c r="G1851" s="2" t="s">
-        <v>928</v>
+        <v>19</v>
       </c>
       <c r="H1851" s="2" t="s">
-        <v>473</v>
+        <v>1915</v>
       </c>
       <c r="I1851" s="2" t="s">
         <v>23</v>
@@ -89966,7 +90188,7 @@
         <v>19</v>
       </c>
       <c r="K1851" s="2" t="s">
-        <v>928</v>
+        <v>19</v>
       </c>
       <c r="L1851" s="2">
         <v>0</v>
@@ -89983,7 +90205,7 @@
         <v>46290</v>
       </c>
       <c r="B1852" s="2" t="s">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="C1852" s="2">
         <v>4</v>
@@ -89995,13 +90217,13 @@
         <v>1</v>
       </c>
       <c r="F1852" s="2" t="s">
-        <v>2637</v>
+        <v>700</v>
       </c>
       <c r="G1852" s="2" t="s">
         <v>324</v>
       </c>
       <c r="H1852" s="2" t="s">
-        <v>830</v>
+        <v>304</v>
       </c>
       <c r="I1852" s="2" t="s">
         <v>18</v>
@@ -90027,25 +90249,25 @@
         <v>46290</v>
       </c>
       <c r="B1853" s="2" t="s">
-        <v>172</v>
+        <v>521</v>
       </c>
       <c r="C1853" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1853" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1853" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F1853" s="2" t="s">
-        <v>408</v>
+        <v>2646</v>
       </c>
       <c r="G1853" s="2" t="s">
-        <v>2691</v>
+        <v>2489</v>
       </c>
       <c r="H1853" s="2" t="s">
-        <v>2692</v>
+        <v>116</v>
       </c>
       <c r="I1853" s="2" t="s">
         <v>28</v>
@@ -90054,7 +90276,7 @@
         <v>19</v>
       </c>
       <c r="K1853" s="2" t="s">
-        <v>2691</v>
+        <v>2489</v>
       </c>
       <c r="L1853" s="2">
         <v>0</v>
@@ -90071,34 +90293,34 @@
         <v>46290</v>
       </c>
       <c r="B1854" s="2" t="s">
-        <v>201</v>
+        <v>531</v>
       </c>
       <c r="C1854" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1854" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E1854" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1854" s="2" t="s">
-        <v>1922</v>
+        <v>2636</v>
       </c>
       <c r="G1854" s="2" t="s">
-        <v>473</v>
+        <v>324</v>
       </c>
       <c r="H1854" s="2" t="s">
-        <v>281</v>
+        <v>830</v>
       </c>
       <c r="I1854" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1854" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1854" s="2" t="s">
-        <v>473</v>
+        <v>324</v>
       </c>
       <c r="L1854" s="2">
         <v>0</v>
@@ -90115,25 +90337,25 @@
         <v>46290</v>
       </c>
       <c r="B1855" s="2" t="s">
-        <v>20</v>
+        <v>517</v>
       </c>
       <c r="C1855" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1855" s="2">
         <v>2</v>
       </c>
-      <c r="D1855" s="2">
-        <v>0</v>
-      </c>
       <c r="E1855" s="5">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F1855" s="2" t="s">
-        <v>303</v>
+        <v>705</v>
       </c>
       <c r="G1855" s="2" t="s">
-        <v>840</v>
+        <v>928</v>
       </c>
       <c r="H1855" s="2" t="s">
-        <v>637</v>
+        <v>473</v>
       </c>
       <c r="I1855" s="2" t="s">
         <v>23</v>
@@ -90142,7 +90364,7 @@
         <v>19</v>
       </c>
       <c r="K1855" s="2" t="s">
-        <v>840</v>
+        <v>928</v>
       </c>
       <c r="L1855" s="2">
         <v>0</v>
@@ -90159,34 +90381,34 @@
         <v>46290</v>
       </c>
       <c r="B1856" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C1856" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1856" s="2">
         <v>2</v>
       </c>
       <c r="E1856" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F1856" s="2" t="s">
-        <v>304</v>
+        <v>504</v>
       </c>
       <c r="G1856" s="2" t="s">
-        <v>471</v>
+        <v>1795</v>
       </c>
       <c r="H1856" s="2" t="s">
-        <v>287</v>
+        <v>1203</v>
       </c>
       <c r="I1856" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1856" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1856" s="2" t="s">
-        <v>471</v>
+        <v>1795</v>
       </c>
       <c r="L1856" s="2">
         <v>0</v>
@@ -90203,25 +90425,25 @@
         <v>46290</v>
       </c>
       <c r="B1857" s="2" t="s">
-        <v>329</v>
+        <v>234</v>
       </c>
       <c r="C1857" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1857" s="2">
         <v>2</v>
       </c>
       <c r="E1857" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F1857" s="2" t="s">
         <v>498</v>
       </c>
       <c r="G1857" s="2" t="s">
-        <v>276</v>
+        <v>153</v>
       </c>
       <c r="H1857" s="2" t="s">
-        <v>298</v>
+        <v>448</v>
       </c>
       <c r="I1857" s="2" t="s">
         <v>23</v>
@@ -90230,7 +90452,7 @@
         <v>19</v>
       </c>
       <c r="K1857" s="2" t="s">
-        <v>276</v>
+        <v>153</v>
       </c>
       <c r="L1857" s="2">
         <v>0</v>
@@ -90247,34 +90469,34 @@
         <v>46290</v>
       </c>
       <c r="B1858" s="2" t="s">
-        <v>1232</v>
+        <v>201</v>
       </c>
       <c r="C1858" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1858" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1858" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1858" s="2" t="s">
-        <v>303</v>
+        <v>1922</v>
       </c>
       <c r="G1858" s="2" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="H1858" s="2" t="s">
-        <v>528</v>
+        <v>281</v>
       </c>
       <c r="I1858" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1858" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1858" s="2" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="L1858" s="2">
         <v>0</v>
@@ -90291,7 +90513,7 @@
         <v>46290</v>
       </c>
       <c r="B1859" s="2" t="s">
-        <v>33</v>
+        <v>1232</v>
       </c>
       <c r="C1859" s="2">
         <v>2</v>
@@ -90306,10 +90528,10 @@
         <v>303</v>
       </c>
       <c r="G1859" s="2" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="H1859" s="2" t="s">
-        <v>208</v>
+        <v>528</v>
       </c>
       <c r="I1859" s="2" t="s">
         <v>18</v>
@@ -90318,7 +90540,7 @@
         <v>19</v>
       </c>
       <c r="K1859" s="2" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="L1859" s="2">
         <v>0</v>
@@ -90335,25 +90557,25 @@
         <v>46290</v>
       </c>
       <c r="B1860" s="2" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="C1860" s="2">
         <v>2</v>
       </c>
       <c r="D1860" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1860" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1860" s="2" t="s">
         <v>303</v>
       </c>
       <c r="G1860" s="2" t="s">
-        <v>2020</v>
+        <v>474</v>
       </c>
       <c r="H1860" s="2" t="s">
-        <v>897</v>
+        <v>208</v>
       </c>
       <c r="I1860" s="2" t="s">
         <v>18</v>
@@ -90362,7 +90584,7 @@
         <v>19</v>
       </c>
       <c r="K1860" s="2" t="s">
-        <v>2020</v>
+        <v>474</v>
       </c>
       <c r="L1860" s="2">
         <v>0</v>
@@ -90379,7 +90601,7 @@
         <v>46290</v>
       </c>
       <c r="B1861" s="2" t="s">
-        <v>93</v>
+        <v>329</v>
       </c>
       <c r="C1861" s="2">
         <v>2</v>
@@ -90391,22 +90613,22 @@
         <v>1</v>
       </c>
       <c r="F1861" s="2" t="s">
-        <v>312</v>
+        <v>498</v>
       </c>
       <c r="G1861" s="2" t="s">
-        <v>312</v>
+        <v>276</v>
       </c>
       <c r="H1861" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I1861" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1861" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1861" s="2" t="s">
-        <v>312</v>
+        <v>276</v>
       </c>
       <c r="L1861" s="2">
         <v>0</v>
@@ -90423,7 +90645,7 @@
         <v>46290</v>
       </c>
       <c r="B1862" s="2" t="s">
-        <v>1117</v>
+        <v>89</v>
       </c>
       <c r="C1862" s="2">
         <v>2</v>
@@ -90435,13 +90657,13 @@
         <v>1</v>
       </c>
       <c r="F1862" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G1862" s="2" t="s">
-        <v>537</v>
+        <v>471</v>
       </c>
       <c r="H1862" s="2" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="I1862" s="2" t="s">
         <v>23</v>
@@ -90450,7 +90672,7 @@
         <v>19</v>
       </c>
       <c r="K1862" s="2" t="s">
-        <v>537</v>
+        <v>471</v>
       </c>
       <c r="L1862" s="2">
         <v>0</v>
@@ -90467,34 +90689,34 @@
         <v>46290</v>
       </c>
       <c r="B1863" s="2" t="s">
-        <v>333</v>
+        <v>118</v>
       </c>
       <c r="C1863" s="2">
         <v>2</v>
       </c>
       <c r="D1863" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1863" s="5">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F1863" s="2" t="s">
-        <v>498</v>
+        <v>303</v>
       </c>
       <c r="G1863" s="2" t="s">
-        <v>321</v>
+        <v>2020</v>
       </c>
       <c r="H1863" s="2" t="s">
-        <v>528</v>
+        <v>897</v>
       </c>
       <c r="I1863" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J1863" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1863" s="2" t="s">
-        <v>321</v>
+        <v>2020</v>
       </c>
       <c r="L1863" s="2">
         <v>0</v>
@@ -90514,22 +90736,22 @@
         <v>315</v>
       </c>
       <c r="C1864" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1864" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1864" s="5">
         <v>1</v>
       </c>
       <c r="F1864" s="2" t="s">
-        <v>705</v>
+        <v>326</v>
       </c>
       <c r="G1864" s="2" t="s">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="H1864" s="2" t="s">
-        <v>545</v>
+        <v>303</v>
       </c>
       <c r="I1864" s="2" t="s">
         <v>23</v>
@@ -90538,7 +90760,7 @@
         <v>19</v>
       </c>
       <c r="K1864" s="2" t="s">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="L1864" s="2">
         <v>0</v>
@@ -90555,25 +90777,25 @@
         <v>46290</v>
       </c>
       <c r="B1865" s="2" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C1865" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1865" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1865" s="5">
         <v>1</v>
       </c>
       <c r="F1865" s="2" t="s">
-        <v>2693</v>
+        <v>312</v>
       </c>
       <c r="G1865" s="2" t="s">
-        <v>2694</v>
+        <v>312</v>
       </c>
       <c r="H1865" s="2" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="I1865" s="2" t="s">
         <v>28</v>
@@ -90582,7 +90804,7 @@
         <v>19</v>
       </c>
       <c r="K1865" s="2" t="s">
-        <v>2694</v>
+        <v>312</v>
       </c>
       <c r="L1865" s="2">
         <v>0</v>
@@ -90599,34 +90821,34 @@
         <v>46290</v>
       </c>
       <c r="B1866" s="2" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C1866" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1866" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1866" s="5">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F1866" s="2" t="s">
-        <v>2381</v>
+        <v>498</v>
       </c>
       <c r="G1866" s="2" t="s">
-        <v>700</v>
+        <v>321</v>
       </c>
       <c r="H1866" s="2" t="s">
-        <v>244</v>
+        <v>528</v>
       </c>
       <c r="I1866" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1866" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1866" s="2" t="s">
-        <v>700</v>
+        <v>321</v>
       </c>
       <c r="L1866" s="2">
         <v>0</v>
@@ -90643,34 +90865,34 @@
         <v>46290</v>
       </c>
       <c r="B1867" s="2" t="s">
-        <v>1579</v>
+        <v>1117</v>
       </c>
       <c r="C1867" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1867" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1867" s="5">
         <v>1</v>
       </c>
       <c r="F1867" s="2" t="s">
-        <v>2575</v>
+        <v>303</v>
       </c>
       <c r="G1867" s="2" t="s">
-        <v>830</v>
+        <v>537</v>
       </c>
       <c r="H1867" s="2" t="s">
-        <v>541</v>
+        <v>245</v>
       </c>
       <c r="I1867" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1867" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1867" s="2" t="s">
-        <v>830</v>
+        <v>537</v>
       </c>
       <c r="L1867" s="2">
         <v>0</v>
@@ -90687,34 +90909,34 @@
         <v>46290</v>
       </c>
       <c r="B1868" s="2" t="s">
-        <v>140</v>
+        <v>271</v>
       </c>
       <c r="C1868" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1868" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E1868" s="5">
         <v>1</v>
       </c>
       <c r="F1868" s="2" t="s">
-        <v>507</v>
+        <v>286</v>
       </c>
       <c r="G1868" s="2" t="s">
-        <v>2695</v>
+        <v>293</v>
       </c>
       <c r="H1868" s="2" t="s">
-        <v>697</v>
+        <v>303</v>
       </c>
       <c r="I1868" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J1868" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1868" s="2" t="s">
-        <v>2695</v>
+        <v>293</v>
       </c>
       <c r="L1868" s="2">
         <v>0</v>
@@ -90819,34 +91041,34 @@
         <v>46290</v>
       </c>
       <c r="B1871" s="2" t="s">
-        <v>265</v>
+        <v>179</v>
       </c>
       <c r="C1871" s="2">
         <v>1</v>
       </c>
       <c r="D1871" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1871" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1871" s="2" t="s">
-        <v>208</v>
+        <v>1093</v>
       </c>
       <c r="G1871" s="2" t="s">
-        <v>153</v>
+        <v>700</v>
       </c>
       <c r="H1871" s="2" t="s">
-        <v>449</v>
+        <v>314</v>
       </c>
       <c r="I1871" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J1871" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K1871" s="2" t="s">
-        <v>153</v>
+        <v>700</v>
       </c>
       <c r="L1871" s="2">
         <v>0</v>
@@ -90863,7 +91085,7 @@
         <v>46290</v>
       </c>
       <c r="B1872" s="2" t="s">
-        <v>271</v>
+        <v>368</v>
       </c>
       <c r="C1872" s="2">
         <v>1</v>
@@ -90875,16 +91097,16 @@
         <v>1</v>
       </c>
       <c r="F1872" s="2" t="s">
-        <v>292</v>
+        <v>1003</v>
       </c>
       <c r="G1872" s="2" t="s">
         <v>306</v>
       </c>
       <c r="H1872" s="2" t="s">
-        <v>545</v>
+        <v>830</v>
       </c>
       <c r="I1872" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1872" s="2" t="s">
         <v>19</v>
@@ -90907,42 +91129,2506 @@
         <v>46290</v>
       </c>
       <c r="B1873" s="2" t="s">
-        <v>179</v>
+        <v>265</v>
       </c>
       <c r="C1873" s="2">
         <v>1</v>
       </c>
       <c r="D1873" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1873" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1873" s="2" t="s">
-        <v>1093</v>
+        <v>208</v>
       </c>
       <c r="G1873" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1873" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="I1873" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1873" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1873" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1873" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1873" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1873" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:14">
+      <c r="A1874" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1874" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C1874" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1874" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1874" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1874" s="2" t="s">
+        <v>2574</v>
+      </c>
+      <c r="G1874" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="H1874" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="I1874" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1874" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1874" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="L1874" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1874" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1874" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:14">
+      <c r="A1875" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1875" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1875" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1875" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1875" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1875" s="2" t="s">
+        <v>2647</v>
+      </c>
+      <c r="G1875" s="2" t="s">
+        <v>2648</v>
+      </c>
+      <c r="H1875" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="I1875" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1875" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1875" s="2" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L1875" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1875" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1875" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:14">
+      <c r="A1876" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1876" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1876" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1876" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1876" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1876" s="2" t="s">
+        <v>2381</v>
+      </c>
+      <c r="G1876" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="H1873" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="I1873" s="2" t="s">
+      <c r="H1876" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1876" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1876" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1876" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1876" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1876" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1876" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:14">
+      <c r="A1877" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B1877" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="C1877" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1877" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1877" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1877" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1877" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H1877" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1877" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1877" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1877" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="L1877" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1877" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1877" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:14">
+      <c r="A1878" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1878" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1878" s="2">
+        <v>3165</v>
+      </c>
+      <c r="D1878" s="2">
+        <v>3012</v>
+      </c>
+      <c r="E1878" s="4">
+        <v>0.95165880000000003</v>
+      </c>
+      <c r="F1878" s="2" t="s">
+        <v>2712</v>
+      </c>
+      <c r="G1878" s="2" t="s">
+        <v>2713</v>
+      </c>
+      <c r="H1878" s="2" t="s">
+        <v>2714</v>
+      </c>
+      <c r="I1878" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1878" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1878" s="2" t="s">
+        <v>2713</v>
+      </c>
+      <c r="L1878" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1878" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1878" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:14">
+      <c r="A1879" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1879" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1879" s="2">
+        <v>3082</v>
+      </c>
+      <c r="D1879" s="2">
+        <v>2670</v>
+      </c>
+      <c r="E1879" s="4">
+        <v>0.8663206</v>
+      </c>
+      <c r="F1879" s="2" t="s">
+        <v>2715</v>
+      </c>
+      <c r="G1879" s="2" t="s">
+        <v>2716</v>
+      </c>
+      <c r="H1879" s="2" t="s">
+        <v>2717</v>
+      </c>
+      <c r="I1879" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1879" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1879" s="2" t="s">
+        <v>2716</v>
+      </c>
+      <c r="L1879" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1879" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1879" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:14">
+      <c r="A1880" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1880" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1880" s="2">
+        <v>1564</v>
+      </c>
+      <c r="D1880" s="2">
+        <v>1422</v>
+      </c>
+      <c r="E1880" s="4">
+        <v>0.90920719999999999</v>
+      </c>
+      <c r="F1880" s="2" t="s">
+        <v>2718</v>
+      </c>
+      <c r="G1880" s="2" t="s">
+        <v>2718</v>
+      </c>
+      <c r="H1880" s="2" t="s">
+        <v>2719</v>
+      </c>
+      <c r="I1880" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1880" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1880" s="2" t="s">
+        <v>2718</v>
+      </c>
+      <c r="L1880" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1880" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1880" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:14">
+      <c r="A1881" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1881" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="C1881" s="2">
+        <v>1135</v>
+      </c>
+      <c r="D1881" s="2">
+        <v>1090</v>
+      </c>
+      <c r="E1881" s="4">
+        <v>0.96035239999999999</v>
+      </c>
+      <c r="F1881" s="2" t="s">
+        <v>2720</v>
+      </c>
+      <c r="G1881" s="2" t="s">
+        <v>2721</v>
+      </c>
+      <c r="H1881" s="2" t="s">
+        <v>2722</v>
+      </c>
+      <c r="I1881" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1881" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1881" s="2" t="s">
+        <v>2721</v>
+      </c>
+      <c r="L1881" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1881" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1881" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:14">
+      <c r="A1882" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1882" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1882" s="2">
+        <v>821</v>
+      </c>
+      <c r="D1882" s="2">
+        <v>783</v>
+      </c>
+      <c r="E1882" s="4">
+        <v>0.95371499999999998</v>
+      </c>
+      <c r="F1882" s="2" t="s">
+        <v>2723</v>
+      </c>
+      <c r="G1882" s="2" t="s">
+        <v>2724</v>
+      </c>
+      <c r="H1882" s="2" t="s">
+        <v>2725</v>
+      </c>
+      <c r="I1882" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J1873" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1873" s="2" t="s">
+      <c r="J1882" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1882" s="2" t="s">
+        <v>2724</v>
+      </c>
+      <c r="L1882" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1882" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1882" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:14">
+      <c r="A1883" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1883" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C1883" s="2">
+        <v>379</v>
+      </c>
+      <c r="D1883" s="2">
+        <v>329</v>
+      </c>
+      <c r="E1883" s="4">
+        <v>0.86807389999999995</v>
+      </c>
+      <c r="F1883" s="2" t="s">
+        <v>2726</v>
+      </c>
+      <c r="G1883" s="2" t="s">
+        <v>2727</v>
+      </c>
+      <c r="H1883" s="2" t="s">
+        <v>2728</v>
+      </c>
+      <c r="I1883" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1883" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1883" s="2" t="s">
+        <v>2727</v>
+      </c>
+      <c r="L1883" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1883" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1883" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:14">
+      <c r="A1884" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1884" s="2" t="s">
+        <v>2689</v>
+      </c>
+      <c r="C1884" s="2">
+        <v>332</v>
+      </c>
+      <c r="D1884" s="2">
+        <v>317</v>
+      </c>
+      <c r="E1884" s="4">
+        <v>0.95481930000000004</v>
+      </c>
+      <c r="F1884" s="2" t="s">
+        <v>2729</v>
+      </c>
+      <c r="G1884" s="2" t="s">
+        <v>2730</v>
+      </c>
+      <c r="H1884" s="2" t="s">
+        <v>2731</v>
+      </c>
+      <c r="I1884" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1884" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1884" s="2" t="s">
+        <v>2730</v>
+      </c>
+      <c r="L1884" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1884" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1884" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:14">
+      <c r="A1885" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1885" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1885" s="2">
+        <v>185</v>
+      </c>
+      <c r="D1885" s="2">
+        <v>178</v>
+      </c>
+      <c r="E1885" s="4">
+        <v>0.96216219999999997</v>
+      </c>
+      <c r="F1885" s="2" t="s">
+        <v>2732</v>
+      </c>
+      <c r="G1885" s="2" t="s">
+        <v>2733</v>
+      </c>
+      <c r="H1885" s="2" t="s">
+        <v>2734</v>
+      </c>
+      <c r="I1885" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1885" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1885" s="2" t="s">
+        <v>2733</v>
+      </c>
+      <c r="L1885" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1885" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1885" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:14">
+      <c r="A1886" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1886" s="2" t="s">
+        <v>2391</v>
+      </c>
+      <c r="C1886" s="2">
+        <v>111</v>
+      </c>
+      <c r="D1886" s="2">
+        <v>108</v>
+      </c>
+      <c r="E1886" s="4">
+        <v>0.97297299999999998</v>
+      </c>
+      <c r="F1886" s="2" t="s">
+        <v>2735</v>
+      </c>
+      <c r="G1886" s="2" t="s">
+        <v>2736</v>
+      </c>
+      <c r="H1886" s="2" t="s">
+        <v>2737</v>
+      </c>
+      <c r="I1886" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1886" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1886" s="2" t="s">
+        <v>2736</v>
+      </c>
+      <c r="L1886" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1886" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1886" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:14">
+      <c r="A1887" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1887" s="2" t="s">
+        <v>2640</v>
+      </c>
+      <c r="C1887" s="2">
+        <v>100</v>
+      </c>
+      <c r="D1887" s="2">
+        <v>98</v>
+      </c>
+      <c r="E1887" s="5">
+        <v>0.98</v>
+      </c>
+      <c r="F1887" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G1887" s="2" t="s">
+        <v>2738</v>
+      </c>
+      <c r="H1887" s="2" t="s">
+        <v>2739</v>
+      </c>
+      <c r="I1887" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1887" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1887" s="2" t="s">
+        <v>2738</v>
+      </c>
+      <c r="L1887" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1887" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1887" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:14">
+      <c r="A1888" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1888" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1888" s="2">
+        <v>98</v>
+      </c>
+      <c r="D1888" s="2">
+        <v>94</v>
+      </c>
+      <c r="E1888" s="4">
+        <v>0.95918369999999997</v>
+      </c>
+      <c r="F1888" s="2" t="s">
+        <v>2740</v>
+      </c>
+      <c r="G1888" s="2" t="s">
+        <v>2741</v>
+      </c>
+      <c r="H1888" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="I1888" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1888" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1888" s="2" t="s">
+        <v>2741</v>
+      </c>
+      <c r="L1888" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1888" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1888" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:14">
+      <c r="A1889" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1889" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1889" s="2">
+        <v>79</v>
+      </c>
+      <c r="D1889" s="2">
+        <v>78</v>
+      </c>
+      <c r="E1889" s="4">
+        <v>0.98734180000000005</v>
+      </c>
+      <c r="F1889" s="2" t="s">
+        <v>2742</v>
+      </c>
+      <c r="G1889" s="2" t="s">
+        <v>2743</v>
+      </c>
+      <c r="H1889" s="2" t="s">
+        <v>2744</v>
+      </c>
+      <c r="I1889" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1889" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1889" s="2" t="s">
+        <v>2743</v>
+      </c>
+      <c r="L1889" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1889" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1889" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:14">
+      <c r="A1890" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1890" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1890" s="2">
+        <v>62</v>
+      </c>
+      <c r="D1890" s="2">
+        <v>20</v>
+      </c>
+      <c r="E1890" s="4">
+        <v>0.3225806</v>
+      </c>
+      <c r="F1890" s="2" t="s">
+        <v>2745</v>
+      </c>
+      <c r="G1890" s="2" t="s">
+        <v>2746</v>
+      </c>
+      <c r="H1890" s="2" t="s">
+        <v>2747</v>
+      </c>
+      <c r="I1890" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1890" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1890" s="2" t="s">
+        <v>2746</v>
+      </c>
+      <c r="L1890" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1890" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1890" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:14">
+      <c r="A1891" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1891" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1891" s="2">
+        <v>49</v>
+      </c>
+      <c r="D1891" s="2">
+        <v>45</v>
+      </c>
+      <c r="E1891" s="4">
+        <v>0.9183673</v>
+      </c>
+      <c r="F1891" s="2" t="s">
+        <v>2748</v>
+      </c>
+      <c r="G1891" s="2" t="s">
+        <v>2749</v>
+      </c>
+      <c r="H1891" s="2" t="s">
+        <v>2750</v>
+      </c>
+      <c r="I1891" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1891" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1891" s="2" t="s">
+        <v>2749</v>
+      </c>
+      <c r="L1891" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1891" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1891" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:14">
+      <c r="A1892" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1892" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1892" s="2">
+        <v>40</v>
+      </c>
+      <c r="D1892" s="2">
+        <v>28</v>
+      </c>
+      <c r="E1892" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="F1892" s="2" t="s">
+        <v>2751</v>
+      </c>
+      <c r="G1892" s="2" t="s">
+        <v>2687</v>
+      </c>
+      <c r="H1892" s="2" t="s">
+        <v>2752</v>
+      </c>
+      <c r="I1892" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1892" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1892" s="2" t="s">
+        <v>2687</v>
+      </c>
+      <c r="L1892" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1892" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1892" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:14">
+      <c r="A1893" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1893" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="C1893" s="2">
+        <v>35</v>
+      </c>
+      <c r="D1893" s="2">
+        <v>33</v>
+      </c>
+      <c r="E1893" s="4">
+        <v>0.9428571</v>
+      </c>
+      <c r="F1893" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="G1893" s="2" t="s">
+        <v>2055</v>
+      </c>
+      <c r="H1893" s="2" t="s">
+        <v>2753</v>
+      </c>
+      <c r="I1893" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1893" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1893" s="2" t="s">
+        <v>2055</v>
+      </c>
+      <c r="L1893" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1893" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1893" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:14">
+      <c r="A1894" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1894" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C1894" s="2">
+        <v>31</v>
+      </c>
+      <c r="D1894" s="2">
+        <v>28</v>
+      </c>
+      <c r="E1894" s="4">
+        <v>0.90322579999999997</v>
+      </c>
+      <c r="F1894" s="2" t="s">
+        <v>2754</v>
+      </c>
+      <c r="G1894" s="2" t="s">
+        <v>2755</v>
+      </c>
+      <c r="H1894" s="2" t="s">
+        <v>2756</v>
+      </c>
+      <c r="I1894" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1894" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1894" s="2" t="s">
+        <v>2755</v>
+      </c>
+      <c r="L1894" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1894" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1894" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:14">
+      <c r="A1895" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1895" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1895" s="2">
+        <v>22</v>
+      </c>
+      <c r="D1895" s="2">
+        <v>10</v>
+      </c>
+      <c r="E1895" s="4">
+        <v>0.45454549999999999</v>
+      </c>
+      <c r="F1895" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G1895" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="H1895" s="2" t="s">
+        <v>2757</v>
+      </c>
+      <c r="I1895" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1895" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1895" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="L1895" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1895" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1895" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:14">
+      <c r="A1896" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1896" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1896" s="2">
+        <v>21</v>
+      </c>
+      <c r="D1896" s="2">
+        <v>18</v>
+      </c>
+      <c r="E1896" s="4">
+        <v>0.85714290000000004</v>
+      </c>
+      <c r="F1896" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="G1896" s="2" t="s">
+        <v>2695</v>
+      </c>
+      <c r="H1896" s="2" t="s">
+        <v>2696</v>
+      </c>
+      <c r="I1896" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1896" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1896" s="2" t="s">
+        <v>2695</v>
+      </c>
+      <c r="L1896" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1896" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1896" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:14">
+      <c r="A1897" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1897" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1897" s="2">
+        <v>20</v>
+      </c>
+      <c r="D1897" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1897" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="F1897" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="G1897" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H1897" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="I1897" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1897" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1897" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="L1897" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1897" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1897" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:14">
+      <c r="A1898" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1898" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1898" s="2">
+        <v>17</v>
+      </c>
+      <c r="D1898" s="2">
+        <v>17</v>
+      </c>
+      <c r="E1898" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1898" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1898" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H1898" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="I1898" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1898" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1898" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="L1898" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1898" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1898" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:14">
+      <c r="A1899" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1899" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1899" s="2">
+        <v>16</v>
+      </c>
+      <c r="D1899" s="2">
+        <v>16</v>
+      </c>
+      <c r="E1899" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1899" s="2" t="s">
+        <v>2758</v>
+      </c>
+      <c r="G1899" s="2" t="s">
+        <v>2759</v>
+      </c>
+      <c r="H1899" s="2" t="s">
+        <v>2760</v>
+      </c>
+      <c r="I1899" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1899" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1899" s="2" t="s">
+        <v>2759</v>
+      </c>
+      <c r="L1899" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1899" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1899" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:14">
+      <c r="A1900" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1900" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1900" s="2">
+        <v>13</v>
+      </c>
+      <c r="D1900" s="2">
+        <v>13</v>
+      </c>
+      <c r="E1900" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1900" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="G1900" s="2" t="s">
+        <v>2761</v>
+      </c>
+      <c r="H1900" s="2" t="s">
+        <v>2762</v>
+      </c>
+      <c r="I1900" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1900" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1900" s="2" t="s">
+        <v>2761</v>
+      </c>
+      <c r="L1900" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1900" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1900" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:14">
+      <c r="A1901" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1901" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1901" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1901" s="2">
+        <v>10</v>
+      </c>
+      <c r="E1901" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1901" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1901" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="H1901" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="I1901" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1901" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1901" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="L1901" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1901" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1901" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:14">
+      <c r="A1902" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1902" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1902" s="2">
+        <v>10</v>
+      </c>
+      <c r="D1902" s="2">
+        <v>6</v>
+      </c>
+      <c r="E1902" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="F1902" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="G1902" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="H1902" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="I1902" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1902" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1902" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="L1902" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1902" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1902" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:14">
+      <c r="A1903" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1903" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1903" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1903" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1903" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1903" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="G1903" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="H1903" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="I1903" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1903" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1903" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="L1903" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1903" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1903" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:14">
+      <c r="A1904" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1904" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1904" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1904" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1904" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1904" s="2" t="s">
+        <v>2763</v>
+      </c>
+      <c r="G1904" s="2" t="s">
+        <v>2764</v>
+      </c>
+      <c r="H1904" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I1904" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1904" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1904" s="2" t="s">
+        <v>2764</v>
+      </c>
+      <c r="L1904" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1904" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1904" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:14">
+      <c r="A1905" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1905" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1905" s="2">
+        <v>6</v>
+      </c>
+      <c r="D1905" s="2">
+        <v>6</v>
+      </c>
+      <c r="E1905" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1905" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G1905" s="2" t="s">
+        <v>2402</v>
+      </c>
+      <c r="H1905" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1905" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1905" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1905" s="2" t="s">
+        <v>2402</v>
+      </c>
+      <c r="L1905" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1905" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1905" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:14">
+      <c r="A1906" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1906" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1906" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1906" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1906" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1906" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1906" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H1906" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I1906" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1906" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1906" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="L1906" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1906" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1906" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:14">
+      <c r="A1907" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1907" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1907" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1907" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1907" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="F1907" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G1907" s="2" t="s">
+        <v>2251</v>
+      </c>
+      <c r="H1907" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="I1907" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1907" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1907" s="2" t="s">
+        <v>2251</v>
+      </c>
+      <c r="L1907" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1907" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1907" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:14">
+      <c r="A1908" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1908" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1908" s="2">
+        <v>4</v>
+      </c>
+      <c r="D1908" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1908" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1908" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G1908" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H1908" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I1908" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1908" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1908" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="L1908" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1908" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1908" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:14">
+      <c r="A1909" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1909" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1909" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1909" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1909" s="4">
+        <v>0.3333333</v>
+      </c>
+      <c r="F1909" s="2" t="s">
+        <v>2765</v>
+      </c>
+      <c r="G1909" s="2" t="s">
+        <v>2766</v>
+      </c>
+      <c r="H1909" s="2" t="s">
+        <v>2251</v>
+      </c>
+      <c r="I1909" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1909" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1909" s="2" t="s">
+        <v>2766</v>
+      </c>
+      <c r="L1909" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1909" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1909" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:14">
+      <c r="A1910" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1910" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1910" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1910" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1910" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1910" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G1910" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H1910" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="I1910" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1910" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1910" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="L1910" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1910" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1910" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:14">
+      <c r="A1911" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1911" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1911" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1911" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1911" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1911" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="G1911" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="H1911" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="I1911" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1911" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1911" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="L1911" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1911" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1911" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:14">
+      <c r="A1912" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1912" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1912" s="2">
+        <v>3</v>
+      </c>
+      <c r="D1912" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1912" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1912" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="G1912" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="H1912" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="I1912" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1912" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1912" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="L1912" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1912" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1912" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:14">
+      <c r="A1913" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1913" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C1913" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1913" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1913" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1913" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1913" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H1913" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1913" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1913" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1913" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="L1913" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1913" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1913" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:14">
+      <c r="A1914" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1914" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1914" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1914" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1914" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1914" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="G1914" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H1914" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="I1914" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1914" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1914" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="L1914" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1914" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1914" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:14">
+      <c r="A1915" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1915" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1915" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1915" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1915" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1915" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G1915" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H1915" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="I1915" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1915" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1915" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="L1915" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1915" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1915" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:14">
+      <c r="A1916" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1916" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1916" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1916" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1916" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1916" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="G1916" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="H1916" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1916" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1916" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1916" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1916" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1916" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1916" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:14">
+      <c r="A1917" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1917" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C1917" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1917" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1917" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="F1917" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1917" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H1917" s="2" t="s">
+        <v>2639</v>
+      </c>
+      <c r="I1917" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1917" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1917" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="L1917" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1917" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1917" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:14">
+      <c r="A1918" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1918" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1918" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1918" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1918" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1918" s="2" t="s">
+        <v>2767</v>
+      </c>
+      <c r="G1918" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="H1918" s="2" t="s">
+        <v>2768</v>
+      </c>
+      <c r="I1918" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1918" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1918" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="L1918" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1918" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1918" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:14">
+      <c r="A1919" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1919" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1919" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1919" s="2">
+        <v>2</v>
+      </c>
+      <c r="E1919" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1919" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G1919" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H1919" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="I1919" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1919" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1919" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="L1919" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1919" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1919" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:14">
+      <c r="A1920" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1920" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1920" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1920" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1920" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1920" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1920" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H1920" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1920" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1920" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1920" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="L1920" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1920" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1920" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:14">
+      <c r="A1921" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1921" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1921" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1921" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1921" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1921" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1921" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1921" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1921" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1921" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1921" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="L1921" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1921" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1921" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:14">
+      <c r="A1922" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1922" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1922" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1922" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1922" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1922" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G1922" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="L1873" s="2">
-        <v>0</v>
-      </c>
-      <c r="M1873" s="5">
-        <v>0</v>
-      </c>
-      <c r="N1873" s="2">
+      <c r="H1922" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1922" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1922" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1922" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="L1922" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1922" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1922" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:14">
+      <c r="A1923" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1923" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C1923" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1923" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1923" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1923" s="2" t="s">
+        <v>2769</v>
+      </c>
+      <c r="G1923" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H1923" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="I1923" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1923" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1923" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="L1923" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1923" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1923" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:14">
+      <c r="A1924" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1924" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C1924" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1924" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1924" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1924" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="G1924" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="H1924" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="I1924" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1924" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1924" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="L1924" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1924" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1924" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:14">
+      <c r="A1925" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1925" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1925" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1925" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1925" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1925" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G1925" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H1925" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I1925" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1925" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1925" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="L1925" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1925" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1925" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:14">
+      <c r="A1926" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1926" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C1926" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1926" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1926" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1926" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G1926" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H1926" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1926" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1926" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1926" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="L1926" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1926" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1926" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:14">
+      <c r="A1927" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1927" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1927" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1927" s="2">
+        <v>0</v>
+      </c>
+      <c r="E1927" s="5">
+        <v>0</v>
+      </c>
+      <c r="F1927" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G1927" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1927" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I1927" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1927" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1927" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1927" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1927" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1927" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:14">
+      <c r="A1928" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1928" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1928" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1928" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1928" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1928" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1928" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H1928" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="I1928" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1928" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1928" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="L1928" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1928" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1928" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:14">
+      <c r="A1929" s="3">
+        <v>46291</v>
+      </c>
+      <c r="B1929" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1929" s="2">
+        <v>1</v>
+      </c>
+      <c r="D1929" s="2">
+        <v>1</v>
+      </c>
+      <c r="E1929" s="5">
+        <v>1</v>
+      </c>
+      <c r="F1929" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="G1929" s="2" t="s">
+        <v>2649</v>
+      </c>
+      <c r="H1929" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="I1929" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1929" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1929" s="2" t="s">
+        <v>2649</v>
+      </c>
+      <c r="L1929" s="2">
+        <v>0</v>
+      </c>
+      <c r="M1929" s="5">
+        <v>0</v>
+      </c>
+      <c r="N1929" s="2">
         <v>0</v>
       </c>
     </row>
